--- a/data/remanejamento.xlsx
+++ b/data/remanejamento.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\guilhermemelof\code\splor-mg\siafi-automacao\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\guilhermemelof\code\splor-mg\siafi-automacao-cota\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{715E5411-3101-4150-A7CE-36E590E37121}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34E0ED5D-E8DD-4DD3-B23B-73A4BB4F7D9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -126,55 +126,13 @@
   <numFmts count="3">
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* \-??_);_(@_)"/>
-    <numFmt numFmtId="169" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@"/>
+    <numFmt numFmtId="165" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@"/>
   </numFmts>
-  <fonts count="26" x14ac:knownFonts="1">
+  <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -240,6 +198,13 @@
       <charset val="1"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
       <b/>
       <i/>
       <sz val="10"/>
@@ -251,23 +216,6 @@
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -299,14 +247,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.39997558519241921"/>
-        <bgColor rgb="FF953734"/>
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0"/>
-        <bgColor indexed="64"/>
+        <fgColor theme="4" tint="0.39997558519241921"/>
+        <bgColor rgb="FF953734"/>
       </patternFill>
     </fill>
     <fill>
@@ -388,286 +336,182 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="110">
+  <cellStyleXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1"/>
-    <xf numFmtId="9" fontId="14" fillId="0" borderId="1" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="1" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="1" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1"/>
-    <xf numFmtId="43" fontId="9" fillId="0" borderId="1" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1"/>
-    <xf numFmtId="9" fontId="13" fillId="0" borderId="1" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="9" fillId="0" borderId="1" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="1" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="1" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="1"/>
-    <xf numFmtId="43" fontId="12" fillId="0" borderId="1" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1"/>
-    <xf numFmtId="43" fontId="8" fillId="0" borderId="1" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1"/>
-    <xf numFmtId="43" fontId="8" fillId="0" borderId="1" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1"/>
-    <xf numFmtId="43" fontId="18" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1"/>
+    <xf numFmtId="9" fontId="8" fillId="0" borderId="1" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1"/>
+    <xf numFmtId="43" fontId="3" fillId="0" borderId="1" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1"/>
-    <xf numFmtId="43" fontId="7" fillId="0" borderId="1" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="12" fillId="0" borderId="1" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="7" fillId="0" borderId="1" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1"/>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="1" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="3" fillId="0" borderId="1" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1"/>
+    <xf numFmtId="43" fontId="6" fillId="0" borderId="1" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1"/>
-    <xf numFmtId="43" fontId="7" fillId="0" borderId="1" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="12" fillId="0" borderId="1" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="7" fillId="0" borderId="1" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="1"/>
-    <xf numFmtId="43" fontId="12" fillId="0" borderId="1" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1"/>
-    <xf numFmtId="43" fontId="6" fillId="0" borderId="1" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1"/>
-    <xf numFmtId="43" fontId="6" fillId="0" borderId="1" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1"/>
-    <xf numFmtId="43" fontId="5" fillId="0" borderId="1" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="12" fillId="0" borderId="1" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="5" fillId="0" borderId="1" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1"/>
-    <xf numFmtId="43" fontId="5" fillId="0" borderId="1" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="12" fillId="0" borderId="1" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="5" fillId="0" borderId="1" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="1"/>
-    <xf numFmtId="43" fontId="12" fillId="0" borderId="1" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1"/>
-    <xf numFmtId="43" fontId="4" fillId="0" borderId="1" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1"/>
-    <xf numFmtId="43" fontId="4" fillId="0" borderId="1" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="1"/>
-    <xf numFmtId="43" fontId="12" fillId="0" borderId="1" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1"/>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="1" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1"/>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="1" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1"/>
     <xf numFmtId="43" fontId="2" fillId="0" borderId="1" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="12" fillId="0" borderId="1" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="1" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1"/>
     <xf numFmtId="43" fontId="2" fillId="0" borderId="1" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="12" fillId="0" borderId="1" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="1" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="1" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="12" fillId="0" borderId="1" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="6" fillId="0" borderId="1" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="1" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="1" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="12" fillId="0" borderId="1" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="6" fillId="0" borderId="1" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="1" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="1"/>
   </cellStyleXfs>
   <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="22" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="23" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="1" fontId="5" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="10" fillId="0" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="43" fontId="11" fillId="0" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="10" fontId="17" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="12" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="34" applyFont="1"/>
-    <xf numFmtId="1" fontId="19" fillId="3" borderId="2" xfId="96" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="14" fillId="4" borderId="4" xfId="34" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" xfId="33" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="34" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="43" fontId="21" fillId="0" borderId="3" xfId="101" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="16" fillId="0" borderId="5" xfId="34" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="43" fontId="20" fillId="0" borderId="3" xfId="101" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="17" fillId="0" borderId="5" xfId="34" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="1" fontId="20" fillId="3" borderId="2" xfId="96" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="33" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="1" fontId="22" fillId="4" borderId="4" xfId="109" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="43" fontId="11" fillId="0" borderId="3" xfId="26" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="4" xfId="109" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="24" fillId="0" borderId="5" xfId="109" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="23" fillId="0" borderId="5" xfId="109" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="25" fillId="0" borderId="5" xfId="109" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="43" fontId="10" fillId="0" borderId="3" xfId="26" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="110">
+  <cellStyles count="50">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 10" xfId="25" xr:uid="{8A749151-D6DB-422A-BCB5-39C8CC4F690D}"/>
-    <cellStyle name="Normal 11" xfId="35" xr:uid="{E1BCAD5A-F4D2-45ED-B8C3-58C0600BA593}"/>
-    <cellStyle name="Normal 12" xfId="49" xr:uid="{AB4807A5-D9E5-400C-BAA8-37561EB763DE}"/>
-    <cellStyle name="Normal 13" xfId="56" xr:uid="{7DB3A5E1-0C51-470D-AE27-669235D86534}"/>
-    <cellStyle name="Normal 14" xfId="69" xr:uid="{B0D7FA54-07DA-45D2-A1B4-59B54179AA20}"/>
-    <cellStyle name="Normal 15" xfId="76" xr:uid="{575D8C85-FEF6-4A1E-9BDF-BAB7CFA7940E}"/>
-    <cellStyle name="Normal 16" xfId="83" xr:uid="{BFD53EA8-35F4-46DF-AE4D-51D40F1BD21D}"/>
-    <cellStyle name="Normal 17" xfId="96" xr:uid="{D3D7A541-BCF4-41F7-890E-CFA46D9B9056}"/>
-    <cellStyle name="Normal 18" xfId="109" xr:uid="{F9C8017B-60E7-4DEE-BC8B-348347DFD6B6}"/>
-    <cellStyle name="Normal 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
-    <cellStyle name="Normal 2 10" xfId="78" xr:uid="{4949DE3E-B171-4957-B01C-9A8E005571C1}"/>
-    <cellStyle name="Normal 2 11" xfId="84" xr:uid="{BDCBBD6F-7317-4EB3-9664-7114E2C5FD5D}"/>
-    <cellStyle name="Normal 2 12" xfId="97" xr:uid="{476ED26E-F056-4878-879A-AAD08DCEE3C9}"/>
-    <cellStyle name="Normal 2 2" xfId="4" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
-    <cellStyle name="Normal 2 2 2" xfId="14" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
-    <cellStyle name="Normal 2 3" xfId="3" xr:uid="{00000000-0005-0000-0000-000004000000}"/>
-    <cellStyle name="Normal 2 3 2" xfId="28" xr:uid="{2AEC6B1E-ADCD-48A3-9B6B-5A0B146704C0}"/>
-    <cellStyle name="Normal 2 4" xfId="13" xr:uid="{00000000-0005-0000-0000-000005000000}"/>
-    <cellStyle name="Normal 2 5" xfId="27" xr:uid="{01B61594-B548-45D4-AD8A-557A695D8AD1}"/>
-    <cellStyle name="Normal 2 5 2" xfId="43" xr:uid="{BDD26B90-39E2-4271-B160-4F67B7B567C6}"/>
-    <cellStyle name="Normal 2 5 3" xfId="63" xr:uid="{0781D72F-BC23-414A-98DD-DECC4C9D0005}"/>
-    <cellStyle name="Normal 2 5 4" xfId="90" xr:uid="{5A972341-D152-4622-B622-03E65F52C9F4}"/>
-    <cellStyle name="Normal 2 5 5" xfId="103" xr:uid="{D54406CB-3857-4076-818B-BE56C12CA6BF}"/>
-    <cellStyle name="Normal 2 6" xfId="36" xr:uid="{F9915709-FD33-44DB-A309-8AFB633B4983}"/>
-    <cellStyle name="Normal 2 7" xfId="51" xr:uid="{91EE0F67-49B9-438E-8389-41F2A8742F89}"/>
-    <cellStyle name="Normal 2 8" xfId="57" xr:uid="{7F115B20-B49C-4F12-93F0-D8267520B5C4}"/>
-    <cellStyle name="Normal 2 9" xfId="71" xr:uid="{03F0B9D0-A0F3-43E5-830F-40EA83D0EB0F}"/>
-    <cellStyle name="Normal 3" xfId="5" xr:uid="{00000000-0005-0000-0000-000006000000}"/>
-    <cellStyle name="Normal 3 2" xfId="6" xr:uid="{00000000-0005-0000-0000-000007000000}"/>
-    <cellStyle name="Normal 3 2 2" xfId="16" xr:uid="{00000000-0005-0000-0000-000008000000}"/>
-    <cellStyle name="Normal 3 3" xfId="15" xr:uid="{00000000-0005-0000-0000-000009000000}"/>
-    <cellStyle name="Normal 4" xfId="2" xr:uid="{00000000-0005-0000-0000-00000A000000}"/>
-    <cellStyle name="Normal 4 2" xfId="17" xr:uid="{00000000-0005-0000-0000-00000B000000}"/>
-    <cellStyle name="Normal 4 2 2" xfId="31" xr:uid="{D5D9455B-99E8-4278-97E2-156C160376FF}"/>
-    <cellStyle name="Normal 4 2 2 2" xfId="44" xr:uid="{23BEF082-30AE-4286-9ACA-8A2D938D83CE}"/>
-    <cellStyle name="Normal 4 2 2 3" xfId="64" xr:uid="{2F5C0107-A837-4154-B610-9E3272C95B7F}"/>
-    <cellStyle name="Normal 4 2 2 4" xfId="91" xr:uid="{BF2086C9-56C0-4416-91A3-EF08816E7AD9}"/>
-    <cellStyle name="Normal 4 2 2 5" xfId="104" xr:uid="{A81FA1B0-C90F-40BA-8438-0DE0A86389DF}"/>
-    <cellStyle name="Normal 4 2 3" xfId="37" xr:uid="{007ECDE3-A411-4B0B-AE38-851A45C56806}"/>
-    <cellStyle name="Normal 4 2 4" xfId="54" xr:uid="{17ABE792-5AD0-48D6-A72A-BCFA87B38229}"/>
-    <cellStyle name="Normal 4 2 5" xfId="58" xr:uid="{85505879-3E34-44E4-93D5-D2A6ECD719C7}"/>
-    <cellStyle name="Normal 4 2 6" xfId="74" xr:uid="{1D5960B4-2719-4651-902E-6D06EC01CE03}"/>
-    <cellStyle name="Normal 4 2 7" xfId="81" xr:uid="{BA6D2879-9947-473D-A0D5-BFE5BDF2EBC8}"/>
-    <cellStyle name="Normal 4 2 8" xfId="85" xr:uid="{4EA3E176-C484-4592-A516-0EEBECEFF7F1}"/>
-    <cellStyle name="Normal 4 2 9" xfId="98" xr:uid="{CC521C9E-8C30-4EFB-9B17-7EE980D64AD2}"/>
-    <cellStyle name="Normal 5" xfId="12" xr:uid="{00000000-0005-0000-0000-00000C000000}"/>
-    <cellStyle name="Normal 6" xfId="10" xr:uid="{00000000-0005-0000-0000-00000D000000}"/>
-    <cellStyle name="Normal 6 2" xfId="29" xr:uid="{32DD8B5F-BA0D-44AC-8B8F-7D56F88426E9}"/>
-    <cellStyle name="Normal 6 2 2" xfId="45" xr:uid="{03DD0F07-55D0-4FEC-8671-A5AA1833FB40}"/>
-    <cellStyle name="Normal 6 2 3" xfId="65" xr:uid="{0F680E5B-45B6-4C6B-8199-06A176F9933B}"/>
-    <cellStyle name="Normal 6 2 4" xfId="92" xr:uid="{A015448C-4D46-4F2F-92C7-DF90EC5E8039}"/>
-    <cellStyle name="Normal 6 2 5" xfId="105" xr:uid="{B1AF09E5-9E90-4848-8843-C27E951BDDCF}"/>
-    <cellStyle name="Normal 6 3" xfId="38" xr:uid="{5BD4E0B3-43C4-4F8F-B4B1-8927B3A8ED98}"/>
-    <cellStyle name="Normal 6 4" xfId="52" xr:uid="{6F37102F-F1A1-4F28-BC94-517FD5098B23}"/>
-    <cellStyle name="Normal 6 5" xfId="59" xr:uid="{0413B762-622B-46F7-82D3-84ACAFD00AB3}"/>
-    <cellStyle name="Normal 6 6" xfId="72" xr:uid="{DB542C97-D5BC-4CC4-8759-36072BA3DD4B}"/>
-    <cellStyle name="Normal 6 7" xfId="79" xr:uid="{49D41AA3-657A-4013-ACA3-2B4D5F6A5DE6}"/>
-    <cellStyle name="Normal 6 8" xfId="86" xr:uid="{47651835-330A-46BE-A17D-1651A2FC1EBA}"/>
-    <cellStyle name="Normal 6 9" xfId="99" xr:uid="{4BCC6743-8663-4BBD-AA3A-BFA5F07716A8}"/>
-    <cellStyle name="Normal 7" xfId="22" xr:uid="{00000000-0005-0000-0000-00000E000000}"/>
-    <cellStyle name="Normal 7 2" xfId="33" xr:uid="{F7DF0F21-FBBD-40E7-A454-3B714DC94107}"/>
-    <cellStyle name="Normal 8" xfId="23" xr:uid="{2F5BB569-187B-4AF5-A097-7727071E48AB}"/>
-    <cellStyle name="Normal 8 2" xfId="42" xr:uid="{B9C9F938-8475-45E3-811B-48723220DB32}"/>
-    <cellStyle name="Normal 9" xfId="24" xr:uid="{8ACFD8F1-F4D8-46C1-8439-FD86D22D338C}"/>
-    <cellStyle name="Porcentagem 5" xfId="7" xr:uid="{00000000-0005-0000-0000-00000F000000}"/>
-    <cellStyle name="Porcentagem 5 2" xfId="18" xr:uid="{00000000-0005-0000-0000-000010000000}"/>
-    <cellStyle name="Separador de milhares" xfId="19" xr:uid="{00000000-0005-0000-0000-000011000000}"/>
-    <cellStyle name="Separador de milhares 10" xfId="100" xr:uid="{34852885-F47D-470A-98F3-EE181A2F2089}"/>
-    <cellStyle name="Separador de milhares 2" xfId="8" xr:uid="{00000000-0005-0000-0000-000012000000}"/>
-    <cellStyle name="Separador de milhares 2 2" xfId="20" xr:uid="{00000000-0005-0000-0000-000013000000}"/>
-    <cellStyle name="Separador de milhares 3" xfId="32" xr:uid="{AF3B97AD-D4F0-4F04-B9DB-5796C3A0BBFC}"/>
-    <cellStyle name="Separador de milhares 3 2" xfId="46" xr:uid="{7F7EC8DC-A347-4968-A843-F7DE2161E949}"/>
-    <cellStyle name="Separador de milhares 3 3" xfId="66" xr:uid="{E497639D-2AD6-4589-AD51-770AF24E1839}"/>
-    <cellStyle name="Separador de milhares 3 4" xfId="93" xr:uid="{4909975B-E2DC-4480-808F-58E13CBB5747}"/>
-    <cellStyle name="Separador de milhares 3 5" xfId="106" xr:uid="{66551610-B5A3-4062-B3E4-31F51C3C3CF8}"/>
-    <cellStyle name="Separador de milhares 4" xfId="39" xr:uid="{FA6A9C53-19EE-48D8-8F5C-3BF0A1C93901}"/>
-    <cellStyle name="Separador de milhares 5" xfId="55" xr:uid="{05348126-2563-4D34-9FF2-78088370F02E}"/>
-    <cellStyle name="Separador de milhares 6" xfId="60" xr:uid="{A4505790-E9E0-4DB6-A3B3-3311595D03F4}"/>
-    <cellStyle name="Separador de milhares 7" xfId="75" xr:uid="{B5AA919B-6C91-41E7-94D9-DC52BCBB5895}"/>
-    <cellStyle name="Separador de milhares 8" xfId="82" xr:uid="{E760FF5D-79F1-4492-A41C-DBFD68BC0C71}"/>
-    <cellStyle name="Separador de milhares 9" xfId="87" xr:uid="{CE0DB2D6-99AE-4655-9EF4-02A28954C4BA}"/>
-    <cellStyle name="Vírgula" xfId="34" builtinId="3"/>
-    <cellStyle name="Vírgula 10" xfId="88" xr:uid="{6FFA5635-6689-4064-A74D-6BAFB47FCBC6}"/>
-    <cellStyle name="Vírgula 11" xfId="101" xr:uid="{9337C74F-5630-47C6-BBA1-D76FD8E9D4C7}"/>
-    <cellStyle name="Vírgula 2" xfId="9" xr:uid="{00000000-0005-0000-0000-000015000000}"/>
-    <cellStyle name="Vírgula 2 2" xfId="21" xr:uid="{00000000-0005-0000-0000-000016000000}"/>
-    <cellStyle name="Vírgula 3" xfId="11" xr:uid="{00000000-0005-0000-0000-000017000000}"/>
-    <cellStyle name="Vírgula 3 2" xfId="30" xr:uid="{D5371392-092C-4283-B100-B0C53D49133B}"/>
-    <cellStyle name="Vírgula 3 2 2" xfId="48" xr:uid="{7B851662-0D8B-4258-AEF0-5F71EA29E1BE}"/>
-    <cellStyle name="Vírgula 3 2 3" xfId="68" xr:uid="{B1493109-DDE4-4866-A5C4-D546D36473CB}"/>
-    <cellStyle name="Vírgula 3 2 4" xfId="95" xr:uid="{C791828C-A54C-431A-A223-C8FCEA999130}"/>
-    <cellStyle name="Vírgula 3 2 5" xfId="108" xr:uid="{324BE24A-FC24-43F9-ACBB-572085C0BABB}"/>
-    <cellStyle name="Vírgula 3 3" xfId="41" xr:uid="{38A82038-5AED-4F37-89CA-EFC241D9E53D}"/>
-    <cellStyle name="Vírgula 3 4" xfId="53" xr:uid="{94B36A63-4C20-40DD-932D-D117EB32C4F9}"/>
-    <cellStyle name="Vírgula 3 5" xfId="62" xr:uid="{6AFCFF0A-B5C1-4527-8304-65E08C11EE27}"/>
-    <cellStyle name="Vírgula 3 6" xfId="73" xr:uid="{E815F8C0-9BEB-4D39-95AE-F093775085C7}"/>
-    <cellStyle name="Vírgula 3 7" xfId="80" xr:uid="{06E7442C-87C9-45FB-B986-4E0729C8ABD2}"/>
-    <cellStyle name="Vírgula 3 8" xfId="89" xr:uid="{0A72909F-3C92-48BB-A569-37E79A164FBF}"/>
-    <cellStyle name="Vírgula 3 9" xfId="102" xr:uid="{4B6A14DC-E126-4942-B12C-657E999D10C7}"/>
-    <cellStyle name="Vírgula 4" xfId="26" xr:uid="{4CB0C6CE-2F1D-40C8-BF26-C764DA52573A}"/>
-    <cellStyle name="Vírgula 4 2" xfId="47" xr:uid="{E3D684FE-F501-445F-9CCA-FD8FEEDC6182}"/>
-    <cellStyle name="Vírgula 4 3" xfId="67" xr:uid="{1D3955E7-20D8-4E02-89DF-E12B1693DE0D}"/>
-    <cellStyle name="Vírgula 4 4" xfId="94" xr:uid="{AE4A10C5-FF76-47B0-9037-199636648658}"/>
-    <cellStyle name="Vírgula 4 5" xfId="107" xr:uid="{A27D0A19-8E37-4DAF-AF58-9AF439E70253}"/>
-    <cellStyle name="Vírgula 5" xfId="40" xr:uid="{4759D89C-D763-4A3E-8C3B-4F2D686F6C9B}"/>
-    <cellStyle name="Vírgula 6" xfId="50" xr:uid="{EFFD4332-6CB0-4DE0-9C63-ADDA6ABF27BD}"/>
-    <cellStyle name="Vírgula 7" xfId="61" xr:uid="{61BFEE28-72B7-40CA-9FBE-F05C25E604DF}"/>
-    <cellStyle name="Vírgula 8" xfId="70" xr:uid="{C56AF86E-5B4F-4DC8-B877-1AB5C5AC89A5}"/>
-    <cellStyle name="Vírgula 9" xfId="77" xr:uid="{2D358B4B-0060-4ECD-8593-554A9C18E871}"/>
+    <cellStyle name="Normal 10" xfId="34" xr:uid="{33A903FE-6042-4AF0-923C-36D36E20A1B8}"/>
+    <cellStyle name="Normal 11" xfId="35" xr:uid="{86B0CEAD-A340-4809-849E-EFB7DA62FD00}"/>
+    <cellStyle name="Normal 12" xfId="41" xr:uid="{71D13D50-E988-402F-AD91-F81F508B4B69}"/>
+    <cellStyle name="Normal 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
+    <cellStyle name="Normal 2 2" xfId="5" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
+    <cellStyle name="Normal 2 2 2" xfId="15" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
+    <cellStyle name="Normal 2 3" xfId="4" xr:uid="{00000000-0005-0000-0000-000004000000}"/>
+    <cellStyle name="Normal 2 3 2" xfId="28" xr:uid="{322B7639-0873-4A97-923F-4F3D3DC96829}"/>
+    <cellStyle name="Normal 2 4" xfId="14" xr:uid="{00000000-0005-0000-0000-000005000000}"/>
+    <cellStyle name="Normal 2 5" xfId="27" xr:uid="{572F838E-2CAF-48FF-93A3-5D845650E7EA}"/>
+    <cellStyle name="Normal 2 5 2" xfId="44" xr:uid="{5DF84890-CBC1-41C5-B69C-3FC59B22E566}"/>
+    <cellStyle name="Normal 2 6" xfId="36" xr:uid="{49A26D5B-93A6-414A-BFDE-655EEFD4F9FA}"/>
+    <cellStyle name="Normal 3" xfId="6" xr:uid="{00000000-0005-0000-0000-000006000000}"/>
+    <cellStyle name="Normal 3 2" xfId="7" xr:uid="{00000000-0005-0000-0000-000007000000}"/>
+    <cellStyle name="Normal 3 2 2" xfId="17" xr:uid="{00000000-0005-0000-0000-000008000000}"/>
+    <cellStyle name="Normal 3 3" xfId="16" xr:uid="{00000000-0005-0000-0000-000009000000}"/>
+    <cellStyle name="Normal 4" xfId="3" xr:uid="{00000000-0005-0000-0000-00000A000000}"/>
+    <cellStyle name="Normal 4 2" xfId="18" xr:uid="{00000000-0005-0000-0000-00000B000000}"/>
+    <cellStyle name="Normal 4 2 2" xfId="31" xr:uid="{925F456F-7B11-4B79-8686-01EA91051904}"/>
+    <cellStyle name="Normal 4 2 2 2" xfId="45" xr:uid="{32A3061A-2A68-444E-97A7-FB34ED5E847C}"/>
+    <cellStyle name="Normal 4 2 3" xfId="37" xr:uid="{FEFA67F0-CA56-4AA1-AF81-D7F17D85D0BB}"/>
+    <cellStyle name="Normal 5" xfId="13" xr:uid="{00000000-0005-0000-0000-00000C000000}"/>
+    <cellStyle name="Normal 6" xfId="11" xr:uid="{00000000-0005-0000-0000-00000D000000}"/>
+    <cellStyle name="Normal 6 2" xfId="29" xr:uid="{AA4B0175-93EB-42D6-AA73-9C2F4A4B21DF}"/>
+    <cellStyle name="Normal 6 2 2" xfId="46" xr:uid="{6D916395-DE45-4025-89C8-691A74645FF6}"/>
+    <cellStyle name="Normal 6 3" xfId="38" xr:uid="{63DCAB06-4680-4EC4-9CE0-CD9B82E3A1B8}"/>
+    <cellStyle name="Normal 7" xfId="23" xr:uid="{00000000-0005-0000-0000-00000E000000}"/>
+    <cellStyle name="Normal 7 2" xfId="33" xr:uid="{C680B102-ABC3-4E8C-AED0-3EA7C38A369F}"/>
+    <cellStyle name="Normal 8" xfId="24" xr:uid="{610176CD-C114-45F9-AFAC-A038177884A2}"/>
+    <cellStyle name="Normal 8 2" xfId="43" xr:uid="{55C94F8D-5F42-4AB7-8B41-8D5091AE74A2}"/>
+    <cellStyle name="Normal 9" xfId="25" xr:uid="{26FCF183-7CBE-4301-A32A-9696BB46E0BF}"/>
+    <cellStyle name="Porcentagem 5" xfId="8" xr:uid="{00000000-0005-0000-0000-00000F000000}"/>
+    <cellStyle name="Porcentagem 5 2" xfId="19" xr:uid="{00000000-0005-0000-0000-000010000000}"/>
+    <cellStyle name="Separador de milhares" xfId="20" xr:uid="{00000000-0005-0000-0000-000011000000}"/>
+    <cellStyle name="Separador de milhares 2" xfId="9" xr:uid="{00000000-0005-0000-0000-000012000000}"/>
+    <cellStyle name="Separador de milhares 2 2" xfId="21" xr:uid="{00000000-0005-0000-0000-000013000000}"/>
+    <cellStyle name="Separador de milhares 3" xfId="32" xr:uid="{A90BA5B8-F1E6-4D45-9B21-8364CF9BDA54}"/>
+    <cellStyle name="Separador de milhares 3 2" xfId="47" xr:uid="{CD4B3295-3326-4B36-9EDC-E8D8F9758E18}"/>
+    <cellStyle name="Separador de milhares 4" xfId="39" xr:uid="{5EA28D93-BCB7-45D7-A04C-E2FACDA0B44E}"/>
+    <cellStyle name="Vírgula" xfId="1" builtinId="3"/>
+    <cellStyle name="Vírgula 2" xfId="10" xr:uid="{00000000-0005-0000-0000-000015000000}"/>
+    <cellStyle name="Vírgula 2 2" xfId="22" xr:uid="{00000000-0005-0000-0000-000016000000}"/>
+    <cellStyle name="Vírgula 3" xfId="12" xr:uid="{00000000-0005-0000-0000-000017000000}"/>
+    <cellStyle name="Vírgula 3 2" xfId="30" xr:uid="{8664CD27-A34F-4626-AB85-393B9B18DCA5}"/>
+    <cellStyle name="Vírgula 3 2 2" xfId="49" xr:uid="{E359B432-0500-4C0D-AC9E-633EB7D6B955}"/>
+    <cellStyle name="Vírgula 3 3" xfId="42" xr:uid="{46A1A2E9-572B-4E85-8CAF-7B623134E843}"/>
+    <cellStyle name="Vírgula 4" xfId="26" xr:uid="{7D196F15-1797-48DA-B9E8-B25C9B58B5EA}"/>
+    <cellStyle name="Vírgula 4 2" xfId="48" xr:uid="{18530662-802C-4388-BEC4-2B49646BFBD4}"/>
+    <cellStyle name="Vírgula 5" xfId="40" xr:uid="{B67B9729-63AB-4D31-8497-4C7E3D71E88D}"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="3">
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
       <fill>
         <patternFill patternType="solid">
           <bgColor rgb="FFAE5252"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
         </patternFill>
       </fill>
     </dxf>
@@ -887,7 +731,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L12"/>
+  <dimension ref="A1:Q520"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.5703125" style="1"/>
@@ -904,277 +748,7486 @@
     <col min="18" max="16384" width="12.5703125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="6" t="s">
+    <row r="1" spans="1:17" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="D1" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="E1" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="F1" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="G1" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="6" t="s">
+      <c r="H1" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="6" t="s">
+      <c r="I1" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="6" t="s">
+      <c r="J1" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="6" t="s">
+      <c r="K1" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="6" t="s">
+      <c r="L1" s="10" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="13">
-        <v>2161</v>
-      </c>
-      <c r="B2" s="13">
-        <v>3</v>
-      </c>
-      <c r="C2" s="13">
+    <row r="2" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="3">
+        <v>1231</v>
+      </c>
+      <c r="B2" s="3">
+        <v>4</v>
+      </c>
+      <c r="C2" s="3">
         <v>0</v>
       </c>
-      <c r="D2" s="13">
-        <v>10</v>
-      </c>
-      <c r="E2" s="13">
+      <c r="D2" s="3">
+        <v>15</v>
+      </c>
+      <c r="E2" s="3">
         <v>1</v>
       </c>
-      <c r="F2" s="14">
-        <v>4515</v>
-      </c>
-      <c r="G2" s="14" t="s">
+      <c r="F2" s="15">
+        <v>4419</v>
+      </c>
+      <c r="G2" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="H2" s="14"/>
-      <c r="I2" s="15">
-        <v>6926.26</v>
-      </c>
-      <c r="J2" s="16"/>
+      <c r="H2" s="15"/>
+      <c r="I2" s="16"/>
+      <c r="J2" s="17">
+        <v>18380103.300000001</v>
+      </c>
       <c r="K2" s="2"/>
       <c r="L2" s="2"/>
     </row>
-    <row r="3" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="13">
-        <v>2161</v>
-      </c>
-      <c r="B3" s="13">
-        <v>3</v>
-      </c>
-      <c r="C3" s="13">
+    <row r="3" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="11">
+        <v>1231</v>
+      </c>
+      <c r="B3" s="11">
+        <v>4</v>
+      </c>
+      <c r="C3" s="11">
         <v>0</v>
       </c>
-      <c r="D3" s="13">
-        <v>10</v>
-      </c>
-      <c r="E3" s="13">
+      <c r="D3" s="11">
+        <v>15</v>
+      </c>
+      <c r="E3" s="11">
         <v>1</v>
       </c>
-      <c r="F3" s="14">
-        <v>4515</v>
-      </c>
-      <c r="G3" s="14"/>
-      <c r="H3" s="14">
-        <v>4003</v>
-      </c>
-      <c r="I3" s="15"/>
-      <c r="J3" s="17">
-        <v>6926.26</v>
+      <c r="F3" s="12">
+        <v>4420</v>
+      </c>
+      <c r="G3" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="H3" s="12"/>
+      <c r="I3" s="13"/>
+      <c r="J3" s="14">
+        <v>888800.80999999994</v>
       </c>
       <c r="K3" s="2"/>
       <c r="L3" s="2"/>
     </row>
-    <row r="4" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="13">
-        <v>2161</v>
-      </c>
-      <c r="B4" s="13">
-        <v>3</v>
-      </c>
-      <c r="C4" s="13">
-        <v>0</v>
-      </c>
-      <c r="D4" s="13">
-        <v>10</v>
-      </c>
-      <c r="E4" s="13">
-        <v>1</v>
-      </c>
-      <c r="F4" s="14">
-        <v>4515</v>
-      </c>
-      <c r="G4" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="H4" s="14"/>
-      <c r="I4" s="15">
-        <v>2486.67</v>
-      </c>
-      <c r="J4" s="16"/>
+    <row r="4" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="3"/>
+      <c r="B4" s="3"/>
+      <c r="C4" s="3"/>
+      <c r="D4" s="3"/>
+      <c r="E4" s="3"/>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
+      <c r="H4" s="2"/>
+      <c r="I4" s="7"/>
+      <c r="J4" s="4"/>
       <c r="K4" s="2"/>
       <c r="L4" s="2"/>
-    </row>
-    <row r="5" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="13">
-        <v>2161</v>
-      </c>
-      <c r="B5" s="13">
-        <v>3</v>
-      </c>
-      <c r="C5" s="13">
-        <v>0</v>
-      </c>
-      <c r="D5" s="13">
-        <v>10</v>
-      </c>
-      <c r="E5" s="13">
-        <v>1</v>
-      </c>
-      <c r="F5" s="14">
-        <v>4515</v>
-      </c>
-      <c r="G5" s="14"/>
-      <c r="H5" s="14">
-        <v>4005</v>
-      </c>
-      <c r="I5" s="15"/>
-      <c r="J5" s="17">
-        <v>2486.67</v>
-      </c>
+      <c r="M4" s="8"/>
+      <c r="N4" s="8"/>
+      <c r="O4" s="8"/>
+      <c r="P4" s="8"/>
+      <c r="Q4" s="8"/>
+    </row>
+    <row r="5" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="3"/>
+      <c r="B5" s="3"/>
+      <c r="C5" s="3"/>
+      <c r="D5" s="3"/>
+      <c r="E5" s="3"/>
+      <c r="F5" s="2"/>
+      <c r="G5" s="2"/>
+      <c r="H5" s="2"/>
+      <c r="I5" s="7"/>
+      <c r="J5" s="4"/>
       <c r="K5" s="2"/>
       <c r="L5" s="2"/>
-    </row>
-    <row r="6" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="12"/>
-      <c r="B6" s="12"/>
-      <c r="C6" s="12"/>
-      <c r="D6" s="12"/>
-      <c r="E6" s="12"/>
-      <c r="F6" s="8"/>
-      <c r="G6" s="8"/>
-      <c r="H6" s="9"/>
-      <c r="I6" s="10"/>
-      <c r="J6" s="11"/>
+      <c r="M5" s="8"/>
+      <c r="N5" s="8"/>
+      <c r="O5" s="8"/>
+      <c r="P5" s="8"/>
+      <c r="Q5" s="8"/>
+    </row>
+    <row r="6" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="3"/>
+      <c r="B6" s="3"/>
+      <c r="C6" s="3"/>
+      <c r="D6" s="3"/>
+      <c r="E6" s="3"/>
+      <c r="F6" s="2"/>
+      <c r="G6" s="2"/>
+      <c r="H6" s="2"/>
+      <c r="I6" s="7"/>
+      <c r="J6" s="4"/>
       <c r="K6" s="2"/>
       <c r="L6" s="2"/>
-    </row>
-    <row r="7" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="12"/>
-      <c r="B7" s="12"/>
-      <c r="C7" s="12"/>
-      <c r="D7" s="12"/>
-      <c r="E7" s="12"/>
-      <c r="F7" s="8"/>
-      <c r="G7" s="8"/>
-      <c r="H7" s="9"/>
-      <c r="I7" s="10"/>
-      <c r="J7" s="11"/>
+      <c r="M6" s="8"/>
+      <c r="N6" s="8"/>
+      <c r="O6" s="8"/>
+      <c r="P6" s="8"/>
+      <c r="Q6" s="8"/>
+    </row>
+    <row r="7" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="3"/>
+      <c r="B7" s="3"/>
+      <c r="C7" s="3"/>
+      <c r="D7" s="3"/>
+      <c r="E7" s="3"/>
+      <c r="F7" s="2"/>
+      <c r="G7" s="2"/>
+      <c r="H7" s="2"/>
+      <c r="I7" s="7"/>
+      <c r="J7" s="4"/>
       <c r="K7" s="2"/>
       <c r="L7" s="2"/>
-    </row>
-    <row r="8" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8"/>
-      <c r="B8"/>
-      <c r="C8"/>
-      <c r="D8"/>
-      <c r="E8"/>
-      <c r="F8"/>
-      <c r="G8"/>
-      <c r="H8"/>
+      <c r="M7" s="8"/>
+      <c r="N7" s="8"/>
+      <c r="O7" s="8"/>
+      <c r="P7" s="8"/>
+      <c r="Q7" s="8"/>
+    </row>
+    <row r="8" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="3"/>
+      <c r="B8" s="3"/>
+      <c r="C8" s="3"/>
+      <c r="D8" s="3"/>
+      <c r="E8" s="3"/>
+      <c r="F8" s="2"/>
+      <c r="G8" s="2"/>
+      <c r="H8" s="2"/>
       <c r="I8" s="7"/>
-      <c r="J8" s="7"/>
+      <c r="J8" s="4"/>
       <c r="K8" s="2"/>
       <c r="L8" s="2"/>
-    </row>
-    <row r="9" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9"/>
-      <c r="B9"/>
-      <c r="C9"/>
-      <c r="D9"/>
-      <c r="E9"/>
-      <c r="F9"/>
-      <c r="G9"/>
-      <c r="H9"/>
+      <c r="M8" s="8"/>
+      <c r="N8" s="8"/>
+      <c r="O8" s="8"/>
+      <c r="P8" s="8"/>
+      <c r="Q8" s="8"/>
+    </row>
+    <row r="9" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="3"/>
+      <c r="B9" s="3"/>
+      <c r="C9" s="3"/>
+      <c r="D9" s="3"/>
+      <c r="E9" s="3"/>
+      <c r="F9" s="2"/>
+      <c r="G9" s="2"/>
+      <c r="H9" s="2"/>
       <c r="I9" s="7"/>
-      <c r="J9" s="7"/>
+      <c r="J9" s="4"/>
       <c r="K9" s="2"/>
       <c r="L9" s="2"/>
-    </row>
-    <row r="10" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10"/>
-      <c r="B10"/>
-      <c r="C10"/>
-      <c r="D10"/>
-      <c r="E10"/>
-      <c r="F10"/>
-      <c r="G10"/>
-      <c r="H10"/>
+      <c r="M9" s="8"/>
+      <c r="N9" s="8"/>
+      <c r="O9" s="8"/>
+      <c r="P9" s="8"/>
+      <c r="Q9" s="8"/>
+    </row>
+    <row r="10" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="3"/>
+      <c r="B10" s="3"/>
+      <c r="C10" s="3"/>
+      <c r="D10" s="3"/>
+      <c r="E10" s="3"/>
+      <c r="F10" s="2"/>
+      <c r="G10" s="2"/>
+      <c r="H10" s="2"/>
       <c r="I10" s="7"/>
-      <c r="J10" s="7"/>
+      <c r="J10" s="4"/>
       <c r="K10" s="2"/>
       <c r="L10" s="2"/>
-    </row>
-    <row r="11" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11"/>
-      <c r="B11"/>
-      <c r="C11"/>
-      <c r="D11"/>
-      <c r="E11"/>
-      <c r="F11"/>
-      <c r="G11"/>
-      <c r="H11"/>
+      <c r="M10" s="8"/>
+      <c r="N10" s="8"/>
+      <c r="O10" s="8"/>
+      <c r="P10" s="8"/>
+      <c r="Q10" s="8"/>
+    </row>
+    <row r="11" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="3"/>
+      <c r="B11" s="3"/>
+      <c r="C11" s="3"/>
+      <c r="D11" s="3"/>
+      <c r="E11" s="3"/>
+      <c r="F11" s="2"/>
+      <c r="G11" s="2"/>
+      <c r="H11" s="2"/>
       <c r="I11" s="7"/>
-      <c r="J11" s="7"/>
+      <c r="J11" s="4"/>
       <c r="K11" s="2"/>
       <c r="L11" s="2"/>
-    </row>
-    <row r="12" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12"/>
-      <c r="B12"/>
-      <c r="C12"/>
-      <c r="D12"/>
-      <c r="E12"/>
-      <c r="F12"/>
-      <c r="G12"/>
-      <c r="H12"/>
+      <c r="M11" s="8"/>
+      <c r="N11" s="8"/>
+      <c r="O11" s="8"/>
+      <c r="P11" s="8"/>
+      <c r="Q11" s="8"/>
+    </row>
+    <row r="12" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="3"/>
+      <c r="B12" s="3"/>
+      <c r="C12" s="3"/>
+      <c r="D12" s="3"/>
+      <c r="E12" s="3"/>
+      <c r="F12" s="2"/>
+      <c r="G12" s="2"/>
+      <c r="H12" s="2"/>
       <c r="I12" s="7"/>
-      <c r="J12" s="7"/>
+      <c r="J12" s="4"/>
       <c r="K12" s="2"/>
       <c r="L12" s="2"/>
+      <c r="M12" s="8"/>
+      <c r="N12" s="8"/>
+      <c r="O12" s="8"/>
+      <c r="P12" s="8"/>
+      <c r="Q12" s="8"/>
+    </row>
+    <row r="13" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="3"/>
+      <c r="B13" s="3"/>
+      <c r="C13" s="3"/>
+      <c r="D13" s="3"/>
+      <c r="E13" s="3"/>
+      <c r="F13" s="2"/>
+      <c r="G13" s="2"/>
+      <c r="H13" s="2"/>
+      <c r="I13" s="7"/>
+      <c r="J13" s="4"/>
+      <c r="K13" s="2"/>
+      <c r="L13" s="2"/>
+      <c r="M13" s="8"/>
+      <c r="N13" s="8"/>
+      <c r="O13" s="8"/>
+      <c r="P13" s="8"/>
+      <c r="Q13" s="8"/>
+    </row>
+    <row r="14" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="3"/>
+      <c r="B14" s="3"/>
+      <c r="C14" s="3"/>
+      <c r="D14" s="3"/>
+      <c r="E14" s="3"/>
+      <c r="F14" s="2"/>
+      <c r="G14" s="2"/>
+      <c r="H14" s="2"/>
+      <c r="I14" s="7"/>
+      <c r="J14" s="4"/>
+      <c r="K14" s="2"/>
+      <c r="L14" s="2"/>
+      <c r="M14" s="8"/>
+      <c r="N14" s="8"/>
+      <c r="O14" s="8"/>
+      <c r="P14" s="8"/>
+      <c r="Q14" s="8"/>
+    </row>
+    <row r="15" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="3"/>
+      <c r="B15" s="3"/>
+      <c r="C15" s="3"/>
+      <c r="D15" s="3"/>
+      <c r="E15" s="3"/>
+      <c r="F15" s="2"/>
+      <c r="G15" s="2"/>
+      <c r="H15" s="2"/>
+      <c r="I15" s="7"/>
+      <c r="J15" s="4"/>
+      <c r="K15" s="2"/>
+      <c r="L15" s="2"/>
+      <c r="M15" s="8"/>
+      <c r="N15" s="8"/>
+      <c r="O15" s="8"/>
+      <c r="P15" s="8"/>
+      <c r="Q15" s="8"/>
+    </row>
+    <row r="16" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="3"/>
+      <c r="B16" s="3"/>
+      <c r="C16" s="3"/>
+      <c r="D16" s="3"/>
+      <c r="E16" s="3"/>
+      <c r="F16" s="2"/>
+      <c r="G16" s="2"/>
+      <c r="H16" s="2"/>
+      <c r="I16" s="7"/>
+      <c r="J16" s="4"/>
+      <c r="K16" s="2"/>
+      <c r="L16" s="2"/>
+      <c r="M16" s="8"/>
+      <c r="N16" s="8"/>
+      <c r="O16" s="8"/>
+      <c r="P16" s="8"/>
+      <c r="Q16" s="8"/>
+    </row>
+    <row r="17" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="3"/>
+      <c r="B17" s="3"/>
+      <c r="C17" s="3"/>
+      <c r="D17" s="3"/>
+      <c r="E17" s="3"/>
+      <c r="F17" s="2"/>
+      <c r="G17" s="2"/>
+      <c r="H17" s="2"/>
+      <c r="I17" s="7"/>
+      <c r="J17" s="4"/>
+      <c r="K17" s="2"/>
+      <c r="L17" s="2"/>
+    </row>
+    <row r="18" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="3"/>
+      <c r="B18" s="3"/>
+      <c r="C18" s="3"/>
+      <c r="D18" s="3"/>
+      <c r="E18" s="3"/>
+      <c r="F18" s="2"/>
+      <c r="G18" s="2"/>
+      <c r="H18" s="2"/>
+      <c r="I18" s="7"/>
+      <c r="J18" s="4"/>
+      <c r="K18" s="2"/>
+      <c r="L18" s="2"/>
+    </row>
+    <row r="19" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="3"/>
+      <c r="B19" s="3"/>
+      <c r="C19" s="3"/>
+      <c r="D19" s="3"/>
+      <c r="E19" s="3"/>
+      <c r="F19" s="2"/>
+      <c r="G19" s="2"/>
+      <c r="H19" s="2"/>
+      <c r="I19" s="7"/>
+      <c r="J19" s="4"/>
+      <c r="K19" s="2"/>
+      <c r="L19" s="2"/>
+    </row>
+    <row r="20" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="3"/>
+      <c r="B20" s="3"/>
+      <c r="C20" s="3"/>
+      <c r="D20" s="3"/>
+      <c r="E20" s="3"/>
+      <c r="F20" s="2"/>
+      <c r="G20" s="2"/>
+      <c r="H20" s="2"/>
+      <c r="I20" s="7"/>
+      <c r="J20" s="4"/>
+      <c r="K20" s="2"/>
+      <c r="L20" s="2"/>
+    </row>
+    <row r="21" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="3"/>
+      <c r="B21" s="3"/>
+      <c r="C21" s="3"/>
+      <c r="D21" s="3"/>
+      <c r="E21" s="3"/>
+      <c r="F21" s="2"/>
+      <c r="G21" s="2"/>
+      <c r="H21" s="2"/>
+      <c r="I21" s="7"/>
+      <c r="J21" s="4"/>
+      <c r="K21" s="2"/>
+      <c r="L21" s="2"/>
+    </row>
+    <row r="22" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="3"/>
+      <c r="B22" s="3"/>
+      <c r="C22" s="3"/>
+      <c r="D22" s="3"/>
+      <c r="E22" s="3"/>
+      <c r="F22" s="2"/>
+      <c r="G22" s="2"/>
+      <c r="H22" s="2"/>
+      <c r="I22" s="7"/>
+      <c r="J22" s="4"/>
+      <c r="K22" s="2"/>
+      <c r="L22" s="2"/>
+    </row>
+    <row r="23" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="3"/>
+      <c r="B23" s="3"/>
+      <c r="C23" s="3"/>
+      <c r="D23" s="3"/>
+      <c r="E23" s="3"/>
+      <c r="F23" s="2"/>
+      <c r="G23" s="2"/>
+      <c r="H23" s="2"/>
+      <c r="I23" s="7"/>
+      <c r="J23" s="4"/>
+      <c r="K23" s="2"/>
+      <c r="L23" s="2"/>
+    </row>
+    <row r="24" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="3"/>
+      <c r="B24" s="3"/>
+      <c r="C24" s="3"/>
+      <c r="D24" s="3"/>
+      <c r="E24" s="3"/>
+      <c r="F24" s="2"/>
+      <c r="G24" s="2"/>
+      <c r="H24" s="2"/>
+      <c r="I24" s="7"/>
+      <c r="J24" s="4"/>
+      <c r="K24" s="2"/>
+      <c r="L24" s="2"/>
+    </row>
+    <row r="25" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="3"/>
+      <c r="B25" s="3"/>
+      <c r="C25" s="3"/>
+      <c r="D25" s="3"/>
+      <c r="E25" s="3"/>
+      <c r="F25" s="2"/>
+      <c r="G25" s="2"/>
+      <c r="H25" s="2"/>
+      <c r="I25" s="7"/>
+      <c r="J25" s="4"/>
+      <c r="K25" s="2"/>
+      <c r="L25" s="2"/>
+    </row>
+    <row r="26" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="3"/>
+      <c r="B26" s="3"/>
+      <c r="C26" s="3"/>
+      <c r="D26" s="3"/>
+      <c r="E26" s="3"/>
+      <c r="F26" s="2"/>
+      <c r="G26" s="2"/>
+      <c r="H26" s="2"/>
+      <c r="I26" s="7"/>
+      <c r="J26" s="4"/>
+      <c r="K26" s="2"/>
+      <c r="L26" s="2"/>
+    </row>
+    <row r="27" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="3"/>
+      <c r="B27" s="3"/>
+      <c r="C27" s="3"/>
+      <c r="D27" s="3"/>
+      <c r="E27" s="3"/>
+      <c r="F27" s="2"/>
+      <c r="G27" s="2"/>
+      <c r="H27" s="2"/>
+      <c r="I27" s="7"/>
+      <c r="J27" s="4"/>
+      <c r="K27" s="2"/>
+      <c r="L27" s="2"/>
+    </row>
+    <row r="28" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="3"/>
+      <c r="B28" s="3"/>
+      <c r="C28" s="3"/>
+      <c r="D28" s="3"/>
+      <c r="E28" s="3"/>
+      <c r="F28" s="2"/>
+      <c r="G28" s="2"/>
+      <c r="H28" s="2"/>
+      <c r="I28" s="7"/>
+      <c r="J28" s="4"/>
+      <c r="K28" s="2"/>
+      <c r="L28" s="2"/>
+    </row>
+    <row r="29" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="3"/>
+      <c r="B29" s="3"/>
+      <c r="C29" s="3"/>
+      <c r="D29" s="3"/>
+      <c r="E29" s="3"/>
+      <c r="F29" s="2"/>
+      <c r="G29" s="2"/>
+      <c r="H29" s="2"/>
+      <c r="I29" s="7"/>
+      <c r="J29" s="4"/>
+      <c r="K29" s="2"/>
+      <c r="L29" s="2"/>
+    </row>
+    <row r="30" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="3"/>
+      <c r="B30" s="3"/>
+      <c r="C30" s="3"/>
+      <c r="D30" s="3"/>
+      <c r="E30" s="3"/>
+      <c r="F30" s="2"/>
+      <c r="G30" s="2"/>
+      <c r="H30" s="2"/>
+      <c r="I30" s="7"/>
+      <c r="J30" s="4"/>
+      <c r="K30" s="2"/>
+      <c r="L30" s="2"/>
+    </row>
+    <row r="31" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="3"/>
+      <c r="B31" s="3"/>
+      <c r="C31" s="3"/>
+      <c r="D31" s="3"/>
+      <c r="E31" s="3"/>
+      <c r="F31" s="2"/>
+      <c r="G31" s="2"/>
+      <c r="H31" s="2"/>
+      <c r="I31" s="7"/>
+      <c r="J31" s="4"/>
+      <c r="K31" s="2"/>
+      <c r="L31" s="2"/>
+    </row>
+    <row r="32" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="3"/>
+      <c r="B32" s="3"/>
+      <c r="C32" s="3"/>
+      <c r="D32" s="3"/>
+      <c r="E32" s="3"/>
+      <c r="F32" s="2"/>
+      <c r="G32" s="2"/>
+      <c r="H32" s="2"/>
+      <c r="I32" s="7"/>
+      <c r="J32" s="4"/>
+      <c r="K32" s="2"/>
+      <c r="L32" s="2"/>
+    </row>
+    <row r="33" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="3"/>
+      <c r="B33" s="3"/>
+      <c r="C33" s="3"/>
+      <c r="D33" s="3"/>
+      <c r="E33" s="3"/>
+      <c r="F33" s="2"/>
+      <c r="G33" s="2"/>
+      <c r="H33" s="2"/>
+      <c r="I33" s="7"/>
+      <c r="J33" s="4"/>
+      <c r="K33" s="2"/>
+      <c r="L33" s="2"/>
+    </row>
+    <row r="34" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="3"/>
+      <c r="B34" s="3"/>
+      <c r="C34" s="3"/>
+      <c r="D34" s="3"/>
+      <c r="E34" s="3"/>
+      <c r="F34" s="2"/>
+      <c r="G34" s="2"/>
+      <c r="H34" s="2"/>
+      <c r="I34" s="7"/>
+      <c r="J34" s="4"/>
+      <c r="K34" s="2"/>
+      <c r="L34" s="2"/>
+    </row>
+    <row r="35" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="3"/>
+      <c r="B35" s="3"/>
+      <c r="C35" s="3"/>
+      <c r="D35" s="3"/>
+      <c r="E35" s="3"/>
+      <c r="F35" s="2"/>
+      <c r="G35" s="2"/>
+      <c r="H35" s="2"/>
+      <c r="I35" s="7"/>
+      <c r="J35" s="4"/>
+      <c r="K35" s="2"/>
+      <c r="L35" s="2"/>
+    </row>
+    <row r="36" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="3"/>
+      <c r="B36" s="3"/>
+      <c r="C36" s="3"/>
+      <c r="D36" s="3"/>
+      <c r="E36" s="3"/>
+      <c r="F36" s="2"/>
+      <c r="G36" s="2"/>
+      <c r="H36" s="2"/>
+      <c r="I36" s="7"/>
+      <c r="J36" s="4"/>
+      <c r="K36" s="2"/>
+      <c r="L36" s="2"/>
+    </row>
+    <row r="37" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="3"/>
+      <c r="B37" s="3"/>
+      <c r="C37" s="3"/>
+      <c r="D37" s="3"/>
+      <c r="E37" s="3"/>
+      <c r="F37" s="2"/>
+      <c r="G37" s="2"/>
+      <c r="H37" s="2"/>
+      <c r="I37" s="7"/>
+      <c r="J37" s="4"/>
+      <c r="K37" s="2"/>
+      <c r="L37" s="2"/>
+    </row>
+    <row r="38" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="3"/>
+      <c r="B38" s="3"/>
+      <c r="C38" s="3"/>
+      <c r="D38" s="3"/>
+      <c r="E38" s="3"/>
+      <c r="F38" s="2"/>
+      <c r="G38" s="2"/>
+      <c r="H38" s="2"/>
+      <c r="I38" s="7"/>
+      <c r="J38" s="4"/>
+      <c r="K38" s="2"/>
+      <c r="L38" s="2"/>
+    </row>
+    <row r="39" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="3"/>
+      <c r="B39" s="3"/>
+      <c r="C39" s="3"/>
+      <c r="D39" s="3"/>
+      <c r="E39" s="3"/>
+      <c r="F39" s="2"/>
+      <c r="G39" s="2"/>
+      <c r="H39" s="2"/>
+      <c r="I39" s="7"/>
+      <c r="J39" s="4"/>
+      <c r="K39" s="2"/>
+      <c r="L39" s="2"/>
+    </row>
+    <row r="40" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="3"/>
+      <c r="B40" s="3"/>
+      <c r="C40" s="3"/>
+      <c r="D40" s="3"/>
+      <c r="E40" s="3"/>
+      <c r="F40" s="2"/>
+      <c r="G40" s="2"/>
+      <c r="H40" s="2"/>
+      <c r="I40" s="7"/>
+      <c r="J40" s="4"/>
+      <c r="K40" s="2"/>
+      <c r="L40" s="2"/>
+    </row>
+    <row r="41" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="3"/>
+      <c r="B41" s="3"/>
+      <c r="C41" s="3"/>
+      <c r="D41" s="3"/>
+      <c r="E41" s="3"/>
+      <c r="F41" s="2"/>
+      <c r="G41" s="2"/>
+      <c r="H41" s="2"/>
+      <c r="I41" s="7"/>
+      <c r="J41" s="4"/>
+      <c r="K41" s="2"/>
+      <c r="L41" s="2"/>
+    </row>
+    <row r="42" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="3"/>
+      <c r="B42" s="3"/>
+      <c r="C42" s="3"/>
+      <c r="D42" s="3"/>
+      <c r="E42" s="3"/>
+      <c r="F42" s="2"/>
+      <c r="G42" s="2"/>
+      <c r="H42" s="2"/>
+      <c r="I42" s="7"/>
+      <c r="J42" s="4"/>
+      <c r="K42" s="2"/>
+      <c r="L42" s="2"/>
+    </row>
+    <row r="43" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="3"/>
+      <c r="B43" s="3"/>
+      <c r="C43" s="3"/>
+      <c r="D43" s="3"/>
+      <c r="E43" s="3"/>
+      <c r="F43" s="2"/>
+      <c r="G43" s="2"/>
+      <c r="H43" s="2"/>
+      <c r="I43" s="7"/>
+      <c r="J43" s="4"/>
+      <c r="K43" s="2"/>
+      <c r="L43" s="2"/>
+    </row>
+    <row r="44" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="3"/>
+      <c r="B44" s="3"/>
+      <c r="C44" s="3"/>
+      <c r="D44" s="3"/>
+      <c r="E44" s="3"/>
+      <c r="F44" s="2"/>
+      <c r="G44" s="2"/>
+      <c r="H44" s="2"/>
+      <c r="I44" s="7"/>
+      <c r="J44" s="4"/>
+      <c r="K44" s="2"/>
+      <c r="L44" s="2"/>
+    </row>
+    <row r="45" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="3"/>
+      <c r="B45" s="3"/>
+      <c r="C45" s="3"/>
+      <c r="D45" s="3"/>
+      <c r="E45" s="3"/>
+      <c r="F45" s="2"/>
+      <c r="G45" s="2"/>
+      <c r="H45" s="2"/>
+      <c r="I45" s="7"/>
+      <c r="J45" s="4"/>
+      <c r="K45" s="2"/>
+      <c r="L45" s="2"/>
+    </row>
+    <row r="46" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="3"/>
+      <c r="B46" s="3"/>
+      <c r="C46" s="3"/>
+      <c r="D46" s="3"/>
+      <c r="E46" s="3"/>
+      <c r="F46" s="2"/>
+      <c r="G46" s="2"/>
+      <c r="H46" s="2"/>
+      <c r="I46" s="7"/>
+      <c r="J46" s="4"/>
+      <c r="K46" s="2"/>
+      <c r="L46" s="2"/>
+    </row>
+    <row r="47" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="3"/>
+      <c r="B47" s="3"/>
+      <c r="C47" s="3"/>
+      <c r="D47" s="3"/>
+      <c r="E47" s="3"/>
+      <c r="F47" s="2"/>
+      <c r="G47" s="2"/>
+      <c r="H47" s="2"/>
+      <c r="I47" s="7"/>
+      <c r="J47" s="4"/>
+      <c r="K47" s="2"/>
+      <c r="L47" s="2"/>
+    </row>
+    <row r="48" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="3"/>
+      <c r="B48" s="3"/>
+      <c r="C48" s="3"/>
+      <c r="D48" s="3"/>
+      <c r="E48" s="3"/>
+      <c r="F48" s="2"/>
+      <c r="G48" s="2"/>
+      <c r="H48" s="2"/>
+      <c r="I48" s="7"/>
+      <c r="J48" s="4"/>
+      <c r="K48" s="2"/>
+      <c r="L48" s="2"/>
+    </row>
+    <row r="49" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="3"/>
+      <c r="B49" s="3"/>
+      <c r="C49" s="3"/>
+      <c r="D49" s="3"/>
+      <c r="E49" s="3"/>
+      <c r="F49" s="2"/>
+      <c r="G49" s="2"/>
+      <c r="H49" s="2"/>
+      <c r="I49" s="7"/>
+      <c r="J49" s="4"/>
+      <c r="K49" s="2"/>
+      <c r="L49" s="2"/>
+    </row>
+    <row r="50" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="3"/>
+      <c r="B50" s="3"/>
+      <c r="C50" s="3"/>
+      <c r="D50" s="3"/>
+      <c r="E50" s="3"/>
+      <c r="F50" s="2"/>
+      <c r="G50" s="2"/>
+      <c r="H50" s="2"/>
+      <c r="I50" s="7"/>
+      <c r="J50" s="4"/>
+      <c r="K50" s="2"/>
+      <c r="L50" s="2"/>
+    </row>
+    <row r="51" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="3"/>
+      <c r="B51" s="3"/>
+      <c r="C51" s="3"/>
+      <c r="D51" s="3"/>
+      <c r="E51" s="3"/>
+      <c r="F51" s="2"/>
+      <c r="G51" s="2"/>
+      <c r="H51" s="2"/>
+      <c r="I51" s="7"/>
+      <c r="J51" s="4"/>
+      <c r="K51" s="2"/>
+      <c r="L51" s="2"/>
+    </row>
+    <row r="52" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="3"/>
+      <c r="B52" s="3"/>
+      <c r="C52" s="3"/>
+      <c r="D52" s="3"/>
+      <c r="E52" s="3"/>
+      <c r="F52" s="2"/>
+      <c r="G52" s="2"/>
+      <c r="H52" s="2"/>
+      <c r="I52" s="7"/>
+      <c r="J52" s="4"/>
+      <c r="K52" s="2"/>
+      <c r="L52" s="2"/>
+    </row>
+    <row r="53" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="3"/>
+      <c r="B53" s="3"/>
+      <c r="C53" s="3"/>
+      <c r="D53" s="3"/>
+      <c r="E53" s="3"/>
+      <c r="F53" s="2"/>
+      <c r="G53" s="2"/>
+      <c r="H53" s="2"/>
+      <c r="I53" s="7"/>
+      <c r="J53" s="4"/>
+      <c r="K53" s="2"/>
+      <c r="L53" s="2"/>
+    </row>
+    <row r="54" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="3"/>
+      <c r="B54" s="3"/>
+      <c r="C54" s="3"/>
+      <c r="D54" s="3"/>
+      <c r="E54" s="3"/>
+      <c r="F54" s="2"/>
+      <c r="G54" s="2"/>
+      <c r="H54" s="2"/>
+      <c r="I54" s="7"/>
+      <c r="J54" s="4"/>
+      <c r="K54" s="2"/>
+      <c r="L54" s="2"/>
+    </row>
+    <row r="55" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="3"/>
+      <c r="B55" s="3"/>
+      <c r="C55" s="3"/>
+      <c r="D55" s="3"/>
+      <c r="E55" s="3"/>
+      <c r="F55" s="2"/>
+      <c r="G55" s="2"/>
+      <c r="H55" s="2"/>
+      <c r="I55" s="7"/>
+      <c r="J55" s="4"/>
+      <c r="K55" s="2"/>
+      <c r="L55" s="2"/>
+    </row>
+    <row r="56" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="3"/>
+      <c r="B56" s="3"/>
+      <c r="C56" s="3"/>
+      <c r="D56" s="3"/>
+      <c r="E56" s="3"/>
+      <c r="F56" s="2"/>
+      <c r="G56" s="2"/>
+      <c r="H56" s="2"/>
+      <c r="I56" s="7"/>
+      <c r="J56" s="4"/>
+      <c r="K56" s="2"/>
+      <c r="L56" s="2"/>
+    </row>
+    <row r="57" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="3"/>
+      <c r="B57" s="3"/>
+      <c r="C57" s="3"/>
+      <c r="D57" s="3"/>
+      <c r="E57" s="3"/>
+      <c r="F57" s="2"/>
+      <c r="G57" s="2"/>
+      <c r="H57" s="2"/>
+      <c r="I57" s="7"/>
+      <c r="J57" s="4"/>
+      <c r="K57" s="2"/>
+      <c r="L57" s="2"/>
+    </row>
+    <row r="58" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="3"/>
+      <c r="B58" s="3"/>
+      <c r="C58" s="3"/>
+      <c r="D58" s="3"/>
+      <c r="E58" s="3"/>
+      <c r="F58" s="2"/>
+      <c r="G58" s="2"/>
+      <c r="H58" s="2"/>
+      <c r="I58" s="7"/>
+      <c r="J58" s="4"/>
+      <c r="K58" s="2"/>
+      <c r="L58" s="2"/>
+    </row>
+    <row r="59" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A59" s="3"/>
+      <c r="B59" s="3"/>
+      <c r="C59" s="3"/>
+      <c r="D59" s="3"/>
+      <c r="E59" s="3"/>
+      <c r="F59" s="2"/>
+      <c r="G59" s="2"/>
+      <c r="H59" s="2"/>
+      <c r="I59" s="7"/>
+      <c r="J59" s="4"/>
+      <c r="K59" s="2"/>
+      <c r="L59" s="2"/>
+    </row>
+    <row r="60" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A60" s="3"/>
+      <c r="B60" s="3"/>
+      <c r="C60" s="3"/>
+      <c r="D60" s="3"/>
+      <c r="E60" s="3"/>
+      <c r="F60" s="2"/>
+      <c r="G60" s="2"/>
+      <c r="H60" s="2"/>
+      <c r="I60" s="7"/>
+      <c r="J60" s="4"/>
+      <c r="K60" s="2"/>
+      <c r="L60" s="2"/>
+    </row>
+    <row r="61" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A61" s="3"/>
+      <c r="B61" s="3"/>
+      <c r="C61" s="3"/>
+      <c r="D61" s="3"/>
+      <c r="E61" s="3"/>
+      <c r="F61" s="2"/>
+      <c r="G61" s="2"/>
+      <c r="H61" s="2"/>
+      <c r="I61" s="7"/>
+      <c r="J61" s="4"/>
+      <c r="K61" s="2"/>
+      <c r="L61" s="2"/>
+    </row>
+    <row r="62" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A62" s="3"/>
+      <c r="B62" s="3"/>
+      <c r="C62" s="3"/>
+      <c r="D62" s="3"/>
+      <c r="E62" s="3"/>
+      <c r="F62" s="2"/>
+      <c r="G62" s="2"/>
+      <c r="H62" s="2"/>
+      <c r="I62" s="7"/>
+      <c r="J62" s="4"/>
+      <c r="K62" s="2"/>
+      <c r="L62" s="2"/>
+    </row>
+    <row r="63" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A63" s="3"/>
+      <c r="B63" s="3"/>
+      <c r="C63" s="3"/>
+      <c r="D63" s="3"/>
+      <c r="E63" s="3"/>
+      <c r="F63" s="2"/>
+      <c r="G63" s="2"/>
+      <c r="H63" s="2"/>
+      <c r="I63" s="7"/>
+      <c r="J63" s="4"/>
+      <c r="K63" s="2"/>
+      <c r="L63" s="2"/>
+    </row>
+    <row r="64" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A64" s="3"/>
+      <c r="B64" s="3"/>
+      <c r="C64" s="3"/>
+      <c r="D64" s="3"/>
+      <c r="E64" s="3"/>
+      <c r="F64" s="2"/>
+      <c r="G64" s="2"/>
+      <c r="H64" s="2"/>
+      <c r="I64" s="7"/>
+      <c r="J64" s="4"/>
+      <c r="K64" s="2"/>
+      <c r="L64" s="2"/>
+    </row>
+    <row r="65" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A65" s="3"/>
+      <c r="B65" s="3"/>
+      <c r="C65" s="3"/>
+      <c r="D65" s="3"/>
+      <c r="E65" s="3"/>
+      <c r="F65" s="2"/>
+      <c r="G65" s="2"/>
+      <c r="H65" s="2"/>
+      <c r="I65" s="7"/>
+      <c r="J65" s="4"/>
+      <c r="K65" s="2"/>
+      <c r="L65" s="2"/>
+    </row>
+    <row r="66" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A66" s="3"/>
+      <c r="B66" s="3"/>
+      <c r="C66" s="3"/>
+      <c r="D66" s="3"/>
+      <c r="E66" s="3"/>
+      <c r="F66" s="2"/>
+      <c r="G66" s="2"/>
+      <c r="H66" s="2"/>
+      <c r="I66" s="7"/>
+      <c r="J66" s="4"/>
+      <c r="K66" s="2"/>
+      <c r="L66" s="2"/>
+    </row>
+    <row r="67" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A67" s="3"/>
+      <c r="B67" s="3"/>
+      <c r="C67" s="3"/>
+      <c r="D67" s="3"/>
+      <c r="E67" s="3"/>
+      <c r="F67" s="2"/>
+      <c r="G67" s="2"/>
+      <c r="H67" s="2"/>
+      <c r="I67" s="7"/>
+      <c r="J67" s="4"/>
+      <c r="K67" s="2"/>
+      <c r="L67" s="2"/>
+    </row>
+    <row r="68" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A68" s="3"/>
+      <c r="B68" s="3"/>
+      <c r="C68" s="3"/>
+      <c r="D68" s="3"/>
+      <c r="E68" s="3"/>
+      <c r="F68" s="2"/>
+      <c r="G68" s="2"/>
+      <c r="H68" s="2"/>
+      <c r="I68" s="7"/>
+      <c r="J68" s="4"/>
+      <c r="K68" s="2"/>
+      <c r="L68" s="2"/>
+    </row>
+    <row r="69" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A69" s="3"/>
+      <c r="B69" s="3"/>
+      <c r="C69" s="3"/>
+      <c r="D69" s="3"/>
+      <c r="E69" s="3"/>
+      <c r="F69" s="2"/>
+      <c r="G69" s="2"/>
+      <c r="H69" s="2"/>
+      <c r="I69" s="7"/>
+      <c r="J69" s="4"/>
+      <c r="K69" s="2"/>
+      <c r="L69" s="2"/>
+    </row>
+    <row r="70" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A70" s="3"/>
+      <c r="B70" s="3"/>
+      <c r="C70" s="3"/>
+      <c r="D70" s="3"/>
+      <c r="E70" s="3"/>
+      <c r="F70" s="2"/>
+      <c r="G70" s="2"/>
+      <c r="H70" s="2"/>
+      <c r="I70" s="7"/>
+      <c r="J70" s="4"/>
+      <c r="K70" s="2"/>
+      <c r="L70" s="2"/>
+    </row>
+    <row r="71" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A71" s="3"/>
+      <c r="B71" s="3"/>
+      <c r="C71" s="3"/>
+      <c r="D71" s="3"/>
+      <c r="E71" s="3"/>
+      <c r="F71" s="2"/>
+      <c r="G71" s="2"/>
+      <c r="H71" s="2"/>
+      <c r="I71" s="7"/>
+      <c r="J71" s="4"/>
+      <c r="K71" s="2"/>
+      <c r="L71" s="2"/>
+    </row>
+    <row r="72" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A72" s="3"/>
+      <c r="B72" s="3"/>
+      <c r="C72" s="3"/>
+      <c r="D72" s="3"/>
+      <c r="E72" s="3"/>
+      <c r="F72" s="2"/>
+      <c r="G72" s="2"/>
+      <c r="H72" s="2"/>
+      <c r="I72" s="7"/>
+      <c r="J72" s="4"/>
+      <c r="K72" s="2"/>
+      <c r="L72" s="2"/>
+    </row>
+    <row r="73" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A73" s="3"/>
+      <c r="B73" s="3"/>
+      <c r="C73" s="3"/>
+      <c r="D73" s="3"/>
+      <c r="E73" s="3"/>
+      <c r="F73" s="2"/>
+      <c r="G73" s="2"/>
+      <c r="H73" s="2"/>
+      <c r="I73" s="7"/>
+      <c r="J73" s="4"/>
+      <c r="K73" s="2"/>
+      <c r="L73" s="2"/>
+    </row>
+    <row r="74" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A74" s="3"/>
+      <c r="B74" s="3"/>
+      <c r="C74" s="3"/>
+      <c r="D74" s="3"/>
+      <c r="E74" s="3"/>
+      <c r="F74" s="2"/>
+      <c r="G74" s="2"/>
+      <c r="H74" s="2"/>
+      <c r="I74" s="7"/>
+      <c r="J74" s="4"/>
+      <c r="K74" s="2"/>
+      <c r="L74" s="2"/>
+    </row>
+    <row r="75" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A75" s="3"/>
+      <c r="B75" s="3"/>
+      <c r="C75" s="3"/>
+      <c r="D75" s="3"/>
+      <c r="E75" s="3"/>
+      <c r="F75" s="2"/>
+      <c r="G75" s="2"/>
+      <c r="H75" s="2"/>
+      <c r="I75" s="7"/>
+      <c r="J75" s="4"/>
+      <c r="K75" s="2"/>
+      <c r="L75" s="2"/>
+    </row>
+    <row r="76" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A76" s="3"/>
+      <c r="B76" s="3"/>
+      <c r="C76" s="3"/>
+      <c r="D76" s="3"/>
+      <c r="E76" s="3"/>
+      <c r="F76" s="2"/>
+      <c r="G76" s="2"/>
+      <c r="H76" s="2"/>
+      <c r="I76" s="7"/>
+      <c r="J76" s="4"/>
+      <c r="K76" s="2"/>
+      <c r="L76" s="2"/>
+    </row>
+    <row r="77" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A77" s="3"/>
+      <c r="B77" s="3"/>
+      <c r="C77" s="3"/>
+      <c r="D77" s="3"/>
+      <c r="E77" s="3"/>
+      <c r="F77" s="2"/>
+      <c r="G77" s="2"/>
+      <c r="H77" s="2"/>
+      <c r="I77" s="7"/>
+      <c r="J77" s="4"/>
+      <c r="K77" s="2"/>
+      <c r="L77" s="2"/>
+    </row>
+    <row r="78" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A78" s="3"/>
+      <c r="B78" s="3"/>
+      <c r="C78" s="3"/>
+      <c r="D78" s="3"/>
+      <c r="E78" s="3"/>
+      <c r="F78" s="2"/>
+      <c r="G78" s="2"/>
+      <c r="H78" s="2"/>
+      <c r="I78" s="7"/>
+      <c r="J78" s="4"/>
+      <c r="K78" s="2"/>
+      <c r="L78" s="2"/>
+    </row>
+    <row r="79" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A79" s="3"/>
+      <c r="B79" s="3"/>
+      <c r="C79" s="3"/>
+      <c r="D79" s="3"/>
+      <c r="E79" s="3"/>
+      <c r="F79" s="2"/>
+      <c r="G79" s="2"/>
+      <c r="H79" s="2"/>
+      <c r="I79" s="7"/>
+      <c r="J79" s="4"/>
+      <c r="K79" s="2"/>
+      <c r="L79" s="2"/>
+    </row>
+    <row r="80" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A80" s="3"/>
+      <c r="B80" s="3"/>
+      <c r="C80" s="3"/>
+      <c r="D80" s="3"/>
+      <c r="E80" s="3"/>
+      <c r="F80" s="2"/>
+      <c r="G80" s="2"/>
+      <c r="H80" s="2"/>
+      <c r="I80" s="7"/>
+      <c r="J80" s="4"/>
+      <c r="K80" s="2"/>
+      <c r="L80" s="2"/>
+    </row>
+    <row r="81" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A81" s="3"/>
+      <c r="B81" s="3"/>
+      <c r="C81" s="3"/>
+      <c r="D81" s="3"/>
+      <c r="E81" s="3"/>
+      <c r="F81" s="2"/>
+      <c r="G81" s="2"/>
+      <c r="H81" s="2"/>
+      <c r="I81" s="7"/>
+      <c r="J81" s="4"/>
+      <c r="K81" s="2"/>
+      <c r="L81" s="2"/>
+    </row>
+    <row r="82" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A82" s="3"/>
+      <c r="B82" s="3"/>
+      <c r="C82" s="3"/>
+      <c r="D82" s="3"/>
+      <c r="E82" s="3"/>
+      <c r="F82" s="2"/>
+      <c r="G82" s="2"/>
+      <c r="H82" s="2"/>
+      <c r="I82" s="7"/>
+      <c r="J82" s="4"/>
+      <c r="K82" s="2"/>
+      <c r="L82" s="2"/>
+    </row>
+    <row r="83" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A83" s="3"/>
+      <c r="B83" s="3"/>
+      <c r="C83" s="3"/>
+      <c r="D83" s="3"/>
+      <c r="E83" s="3"/>
+      <c r="F83" s="2"/>
+      <c r="G83" s="2"/>
+      <c r="H83" s="2"/>
+      <c r="I83" s="7"/>
+      <c r="J83" s="4"/>
+      <c r="K83" s="2"/>
+      <c r="L83" s="2"/>
+    </row>
+    <row r="84" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A84" s="3"/>
+      <c r="B84" s="3"/>
+      <c r="C84" s="3"/>
+      <c r="D84" s="3"/>
+      <c r="E84" s="3"/>
+      <c r="F84" s="2"/>
+      <c r="G84" s="2"/>
+      <c r="H84" s="2"/>
+      <c r="I84" s="7"/>
+      <c r="J84" s="4"/>
+      <c r="K84" s="2"/>
+      <c r="L84" s="2"/>
+    </row>
+    <row r="85" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A85" s="3"/>
+      <c r="B85" s="3"/>
+      <c r="C85" s="3"/>
+      <c r="D85" s="3"/>
+      <c r="E85" s="3"/>
+      <c r="F85" s="2"/>
+      <c r="G85" s="2"/>
+      <c r="H85" s="2"/>
+      <c r="I85" s="7"/>
+      <c r="J85" s="4"/>
+      <c r="K85" s="2"/>
+      <c r="L85" s="2"/>
+    </row>
+    <row r="86" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A86" s="3"/>
+      <c r="B86" s="3"/>
+      <c r="C86" s="3"/>
+      <c r="D86" s="3"/>
+      <c r="E86" s="3"/>
+      <c r="F86" s="2"/>
+      <c r="G86" s="2"/>
+      <c r="H86" s="2"/>
+      <c r="I86" s="7"/>
+      <c r="J86" s="4"/>
+      <c r="K86" s="2"/>
+      <c r="L86" s="2"/>
+    </row>
+    <row r="87" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A87" s="3"/>
+      <c r="B87" s="3"/>
+      <c r="C87" s="3"/>
+      <c r="D87" s="3"/>
+      <c r="E87" s="3"/>
+      <c r="F87" s="2"/>
+      <c r="G87" s="2"/>
+      <c r="H87" s="2"/>
+      <c r="I87" s="7"/>
+      <c r="J87" s="4"/>
+      <c r="K87" s="2"/>
+      <c r="L87" s="2"/>
+    </row>
+    <row r="88" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A88" s="3"/>
+      <c r="B88" s="3"/>
+      <c r="C88" s="3"/>
+      <c r="D88" s="3"/>
+      <c r="E88" s="3"/>
+      <c r="F88" s="2"/>
+      <c r="G88" s="2"/>
+      <c r="H88" s="2"/>
+      <c r="I88" s="7"/>
+      <c r="J88" s="4"/>
+      <c r="K88" s="2"/>
+      <c r="L88" s="2"/>
+    </row>
+    <row r="89" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A89" s="3"/>
+      <c r="B89" s="3"/>
+      <c r="C89" s="3"/>
+      <c r="D89" s="3"/>
+      <c r="E89" s="3"/>
+      <c r="F89" s="2"/>
+      <c r="G89" s="2"/>
+      <c r="H89" s="2"/>
+      <c r="I89" s="7"/>
+      <c r="J89" s="4"/>
+      <c r="K89" s="2"/>
+      <c r="L89" s="2"/>
+    </row>
+    <row r="90" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A90" s="3"/>
+      <c r="B90" s="3"/>
+      <c r="C90" s="3"/>
+      <c r="D90" s="3"/>
+      <c r="E90" s="3"/>
+      <c r="F90" s="2"/>
+      <c r="G90" s="2"/>
+      <c r="H90" s="2"/>
+      <c r="I90" s="7"/>
+      <c r="J90" s="4"/>
+      <c r="K90" s="2"/>
+      <c r="L90" s="2"/>
+    </row>
+    <row r="91" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A91" s="3"/>
+      <c r="B91" s="3"/>
+      <c r="C91" s="3"/>
+      <c r="D91" s="3"/>
+      <c r="E91" s="3"/>
+      <c r="F91" s="2"/>
+      <c r="G91" s="2"/>
+      <c r="H91" s="2"/>
+      <c r="I91" s="7"/>
+      <c r="J91" s="4"/>
+      <c r="K91" s="2"/>
+      <c r="L91" s="2"/>
+    </row>
+    <row r="92" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A92" s="3"/>
+      <c r="B92" s="3"/>
+      <c r="C92" s="3"/>
+      <c r="D92" s="3"/>
+      <c r="E92" s="3"/>
+      <c r="F92" s="2"/>
+      <c r="G92" s="2"/>
+      <c r="H92" s="2"/>
+      <c r="I92" s="7"/>
+      <c r="J92" s="4"/>
+      <c r="K92" s="2"/>
+      <c r="L92" s="2"/>
+    </row>
+    <row r="93" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A93" s="3"/>
+      <c r="B93" s="3"/>
+      <c r="C93" s="3"/>
+      <c r="D93" s="3"/>
+      <c r="E93" s="3"/>
+      <c r="F93" s="2"/>
+      <c r="G93" s="2"/>
+      <c r="H93" s="2"/>
+      <c r="I93" s="7"/>
+      <c r="J93" s="4"/>
+      <c r="K93" s="2"/>
+      <c r="L93" s="2"/>
+    </row>
+    <row r="94" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A94" s="3"/>
+      <c r="B94" s="3"/>
+      <c r="C94" s="3"/>
+      <c r="D94" s="3"/>
+      <c r="E94" s="3"/>
+      <c r="F94" s="2"/>
+      <c r="G94" s="2"/>
+      <c r="H94" s="2"/>
+      <c r="I94" s="7"/>
+      <c r="J94" s="4"/>
+      <c r="K94" s="2"/>
+      <c r="L94" s="2"/>
+    </row>
+    <row r="95" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A95" s="3"/>
+      <c r="B95" s="3"/>
+      <c r="C95" s="3"/>
+      <c r="D95" s="3"/>
+      <c r="E95" s="3"/>
+      <c r="F95" s="2"/>
+      <c r="G95" s="2"/>
+      <c r="H95" s="2"/>
+      <c r="I95" s="7"/>
+      <c r="J95" s="4"/>
+      <c r="K95" s="2"/>
+      <c r="L95" s="2"/>
+    </row>
+    <row r="96" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A96" s="3"/>
+      <c r="B96" s="3"/>
+      <c r="C96" s="3"/>
+      <c r="D96" s="3"/>
+      <c r="E96" s="3"/>
+      <c r="F96" s="2"/>
+      <c r="G96" s="2"/>
+      <c r="H96" s="2"/>
+      <c r="I96" s="7"/>
+      <c r="J96" s="4"/>
+      <c r="K96" s="2"/>
+      <c r="L96" s="2"/>
+    </row>
+    <row r="97" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A97" s="3"/>
+      <c r="B97" s="3"/>
+      <c r="C97" s="3"/>
+      <c r="D97" s="3"/>
+      <c r="E97" s="3"/>
+      <c r="F97" s="2"/>
+      <c r="G97" s="2"/>
+      <c r="H97" s="2"/>
+      <c r="I97" s="7"/>
+      <c r="J97" s="4"/>
+      <c r="K97" s="2"/>
+      <c r="L97" s="2"/>
+    </row>
+    <row r="98" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A98" s="3"/>
+      <c r="B98" s="3"/>
+      <c r="C98" s="3"/>
+      <c r="D98" s="3"/>
+      <c r="E98" s="3"/>
+      <c r="F98" s="2"/>
+      <c r="G98" s="2"/>
+      <c r="H98" s="2"/>
+      <c r="I98" s="7"/>
+      <c r="J98" s="4"/>
+      <c r="K98" s="2"/>
+      <c r="L98" s="2"/>
+    </row>
+    <row r="99" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A99" s="3"/>
+      <c r="B99" s="3"/>
+      <c r="C99" s="3"/>
+      <c r="D99" s="3"/>
+      <c r="E99" s="3"/>
+      <c r="F99" s="2"/>
+      <c r="G99" s="2"/>
+      <c r="H99" s="2"/>
+      <c r="I99" s="7"/>
+      <c r="J99" s="4"/>
+      <c r="K99" s="2"/>
+      <c r="L99" s="2"/>
+    </row>
+    <row r="100" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A100" s="3"/>
+      <c r="B100" s="3"/>
+      <c r="C100" s="3"/>
+      <c r="D100" s="3"/>
+      <c r="E100" s="3"/>
+      <c r="F100" s="2"/>
+      <c r="G100" s="2"/>
+      <c r="H100" s="2"/>
+      <c r="I100" s="7"/>
+      <c r="J100" s="4"/>
+      <c r="K100" s="2"/>
+      <c r="L100" s="2"/>
+    </row>
+    <row r="101" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A101" s="3"/>
+      <c r="B101" s="3"/>
+      <c r="C101" s="3"/>
+      <c r="D101" s="3"/>
+      <c r="E101" s="3"/>
+      <c r="F101" s="2"/>
+      <c r="G101" s="2"/>
+      <c r="H101" s="2"/>
+      <c r="I101" s="7"/>
+      <c r="J101" s="4"/>
+      <c r="K101" s="2"/>
+      <c r="L101" s="2"/>
+    </row>
+    <row r="102" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A102" s="3"/>
+      <c r="B102" s="3"/>
+      <c r="C102" s="3"/>
+      <c r="D102" s="3"/>
+      <c r="E102" s="3"/>
+      <c r="F102" s="2"/>
+      <c r="G102" s="2"/>
+      <c r="H102" s="2"/>
+      <c r="I102" s="7"/>
+      <c r="J102" s="4"/>
+      <c r="K102" s="2"/>
+      <c r="L102" s="2"/>
+    </row>
+    <row r="103" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A103" s="3"/>
+      <c r="B103" s="3"/>
+      <c r="C103" s="3"/>
+      <c r="D103" s="3"/>
+      <c r="E103" s="3"/>
+      <c r="F103" s="2"/>
+      <c r="G103" s="2"/>
+      <c r="H103" s="2"/>
+      <c r="I103" s="7"/>
+      <c r="J103" s="4"/>
+      <c r="K103" s="2"/>
+      <c r="L103" s="2"/>
+    </row>
+    <row r="104" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A104" s="3"/>
+      <c r="B104" s="3"/>
+      <c r="C104" s="3"/>
+      <c r="D104" s="3"/>
+      <c r="E104" s="3"/>
+      <c r="F104" s="2"/>
+      <c r="G104" s="2"/>
+      <c r="H104" s="2"/>
+      <c r="I104" s="7"/>
+      <c r="J104" s="4"/>
+      <c r="K104" s="2"/>
+      <c r="L104" s="2"/>
+    </row>
+    <row r="105" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A105" s="3"/>
+      <c r="B105" s="3"/>
+      <c r="C105" s="3"/>
+      <c r="D105" s="3"/>
+      <c r="E105" s="3"/>
+      <c r="F105" s="2"/>
+      <c r="G105" s="2"/>
+      <c r="H105" s="2"/>
+      <c r="I105" s="7"/>
+      <c r="J105" s="4"/>
+      <c r="K105" s="2"/>
+      <c r="L105" s="2"/>
+    </row>
+    <row r="106" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A106" s="3"/>
+      <c r="B106" s="3"/>
+      <c r="C106" s="3"/>
+      <c r="D106" s="3"/>
+      <c r="E106" s="3"/>
+      <c r="F106" s="2"/>
+      <c r="G106" s="2"/>
+      <c r="H106" s="2"/>
+      <c r="I106" s="7"/>
+      <c r="J106" s="4"/>
+      <c r="K106" s="2"/>
+      <c r="L106" s="2"/>
+    </row>
+    <row r="107" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A107" s="3"/>
+      <c r="B107" s="3"/>
+      <c r="C107" s="3"/>
+      <c r="D107" s="3"/>
+      <c r="E107" s="3"/>
+      <c r="F107" s="2"/>
+      <c r="G107" s="2"/>
+      <c r="H107" s="2"/>
+      <c r="I107" s="7"/>
+      <c r="J107" s="4"/>
+      <c r="K107" s="2"/>
+      <c r="L107" s="2"/>
+    </row>
+    <row r="108" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A108" s="3"/>
+      <c r="B108" s="3"/>
+      <c r="C108" s="3"/>
+      <c r="D108" s="3"/>
+      <c r="E108" s="3"/>
+      <c r="F108" s="2"/>
+      <c r="G108" s="2"/>
+      <c r="H108" s="2"/>
+      <c r="I108" s="7"/>
+      <c r="J108" s="4"/>
+      <c r="K108" s="2"/>
+      <c r="L108" s="2"/>
+    </row>
+    <row r="109" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A109" s="3"/>
+      <c r="B109" s="3"/>
+      <c r="C109" s="3"/>
+      <c r="D109" s="3"/>
+      <c r="E109" s="3"/>
+      <c r="F109" s="2"/>
+      <c r="G109" s="2"/>
+      <c r="H109" s="2"/>
+      <c r="I109" s="7"/>
+      <c r="J109" s="4"/>
+      <c r="K109" s="2"/>
+      <c r="L109" s="2"/>
+    </row>
+    <row r="110" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A110" s="3"/>
+      <c r="B110" s="3"/>
+      <c r="C110" s="3"/>
+      <c r="D110" s="3"/>
+      <c r="E110" s="3"/>
+      <c r="F110" s="2"/>
+      <c r="G110" s="2"/>
+      <c r="H110" s="2"/>
+      <c r="I110" s="7"/>
+      <c r="J110" s="4"/>
+      <c r="K110" s="2"/>
+      <c r="L110" s="2"/>
+    </row>
+    <row r="111" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A111" s="3"/>
+      <c r="B111" s="3"/>
+      <c r="C111" s="3"/>
+      <c r="D111" s="3"/>
+      <c r="E111" s="3"/>
+      <c r="F111" s="2"/>
+      <c r="G111" s="2"/>
+      <c r="H111" s="2"/>
+      <c r="I111" s="7"/>
+      <c r="J111" s="4"/>
+      <c r="K111" s="2"/>
+      <c r="L111" s="2"/>
+    </row>
+    <row r="112" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A112" s="3"/>
+      <c r="B112" s="3"/>
+      <c r="C112" s="3"/>
+      <c r="D112" s="3"/>
+      <c r="E112" s="3"/>
+      <c r="F112" s="2"/>
+      <c r="G112" s="2"/>
+      <c r="H112" s="2"/>
+      <c r="I112" s="7"/>
+      <c r="J112" s="4"/>
+      <c r="K112" s="2"/>
+      <c r="L112" s="2"/>
+    </row>
+    <row r="113" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A113" s="3"/>
+      <c r="B113" s="3"/>
+      <c r="C113" s="3"/>
+      <c r="D113" s="3"/>
+      <c r="E113" s="3"/>
+      <c r="F113" s="2"/>
+      <c r="G113" s="2"/>
+      <c r="H113" s="2"/>
+      <c r="I113" s="7"/>
+      <c r="J113" s="4"/>
+      <c r="K113" s="2"/>
+      <c r="L113" s="2"/>
+    </row>
+    <row r="114" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A114" s="3"/>
+      <c r="B114" s="3"/>
+      <c r="C114" s="3"/>
+      <c r="D114" s="3"/>
+      <c r="E114" s="3"/>
+      <c r="F114" s="2"/>
+      <c r="G114" s="2"/>
+      <c r="H114" s="2"/>
+      <c r="I114" s="7"/>
+      <c r="J114" s="4"/>
+      <c r="K114" s="2"/>
+      <c r="L114" s="2"/>
+    </row>
+    <row r="115" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A115" s="3"/>
+      <c r="B115" s="3"/>
+      <c r="C115" s="3"/>
+      <c r="D115" s="3"/>
+      <c r="E115" s="3"/>
+      <c r="F115" s="2"/>
+      <c r="G115" s="2"/>
+      <c r="H115" s="2"/>
+      <c r="I115" s="7"/>
+      <c r="J115" s="4"/>
+      <c r="K115" s="2"/>
+      <c r="L115" s="2"/>
+    </row>
+    <row r="116" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A116" s="3"/>
+      <c r="B116" s="3"/>
+      <c r="C116" s="3"/>
+      <c r="D116" s="3"/>
+      <c r="E116" s="3"/>
+      <c r="F116" s="2"/>
+      <c r="G116" s="2"/>
+      <c r="H116" s="2"/>
+      <c r="I116" s="7"/>
+      <c r="J116" s="4"/>
+      <c r="K116" s="2"/>
+      <c r="L116" s="2"/>
+    </row>
+    <row r="117" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A117" s="3"/>
+      <c r="B117" s="3"/>
+      <c r="C117" s="3"/>
+      <c r="D117" s="3"/>
+      <c r="E117" s="3"/>
+      <c r="F117" s="2"/>
+      <c r="G117" s="2"/>
+      <c r="H117" s="2"/>
+      <c r="I117" s="7"/>
+      <c r="J117" s="4"/>
+      <c r="K117" s="2"/>
+      <c r="L117" s="2"/>
+    </row>
+    <row r="118" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A118" s="3"/>
+      <c r="B118" s="3"/>
+      <c r="C118" s="3"/>
+      <c r="D118" s="3"/>
+      <c r="E118" s="3"/>
+      <c r="F118" s="2"/>
+      <c r="G118" s="2"/>
+      <c r="H118" s="2"/>
+      <c r="I118" s="7"/>
+      <c r="J118" s="4"/>
+      <c r="K118" s="2"/>
+      <c r="L118" s="2"/>
+    </row>
+    <row r="119" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A119" s="3"/>
+      <c r="B119" s="3"/>
+      <c r="C119" s="3"/>
+      <c r="D119" s="3"/>
+      <c r="E119" s="3"/>
+      <c r="F119" s="2"/>
+      <c r="G119" s="2"/>
+      <c r="H119" s="2"/>
+      <c r="I119" s="7"/>
+      <c r="J119" s="4"/>
+      <c r="K119" s="2"/>
+      <c r="L119" s="2"/>
+    </row>
+    <row r="120" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A120" s="3"/>
+      <c r="B120" s="3"/>
+      <c r="C120" s="3"/>
+      <c r="D120" s="3"/>
+      <c r="E120" s="3"/>
+      <c r="F120" s="2"/>
+      <c r="G120" s="2"/>
+      <c r="H120" s="2"/>
+      <c r="I120" s="7"/>
+      <c r="J120" s="4"/>
+      <c r="K120" s="2"/>
+      <c r="L120" s="2"/>
+    </row>
+    <row r="121" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A121" s="3"/>
+      <c r="B121" s="3"/>
+      <c r="C121" s="3"/>
+      <c r="D121" s="3"/>
+      <c r="E121" s="3"/>
+      <c r="F121" s="2"/>
+      <c r="G121" s="2"/>
+      <c r="H121" s="2"/>
+      <c r="I121" s="7"/>
+      <c r="J121" s="4"/>
+      <c r="K121" s="2"/>
+      <c r="L121" s="2"/>
+    </row>
+    <row r="122" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A122" s="3"/>
+      <c r="B122" s="3"/>
+      <c r="C122" s="3"/>
+      <c r="D122" s="3"/>
+      <c r="E122" s="3"/>
+      <c r="F122" s="2"/>
+      <c r="G122" s="2"/>
+      <c r="H122" s="2"/>
+      <c r="I122" s="7"/>
+      <c r="J122" s="4"/>
+      <c r="K122" s="2"/>
+      <c r="L122" s="2"/>
+    </row>
+    <row r="123" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A123" s="3"/>
+      <c r="B123" s="3"/>
+      <c r="C123" s="3"/>
+      <c r="D123" s="3"/>
+      <c r="E123" s="3"/>
+      <c r="F123" s="2"/>
+      <c r="G123" s="2"/>
+      <c r="H123" s="2"/>
+      <c r="I123" s="7"/>
+      <c r="J123" s="4"/>
+      <c r="K123" s="2"/>
+      <c r="L123" s="2"/>
+    </row>
+    <row r="124" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A124" s="3"/>
+      <c r="B124" s="3"/>
+      <c r="C124" s="3"/>
+      <c r="D124" s="3"/>
+      <c r="E124" s="3"/>
+      <c r="F124" s="2"/>
+      <c r="G124" s="2"/>
+      <c r="H124" s="2"/>
+      <c r="I124" s="7"/>
+      <c r="J124" s="4"/>
+      <c r="K124" s="2"/>
+      <c r="L124" s="2"/>
+    </row>
+    <row r="125" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A125" s="3"/>
+      <c r="B125" s="3"/>
+      <c r="C125" s="3"/>
+      <c r="D125" s="3"/>
+      <c r="E125" s="3"/>
+      <c r="F125" s="2"/>
+      <c r="G125" s="2"/>
+      <c r="H125" s="2"/>
+      <c r="I125" s="7"/>
+      <c r="J125" s="4"/>
+      <c r="K125" s="2"/>
+      <c r="L125" s="2"/>
+    </row>
+    <row r="126" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A126" s="3"/>
+      <c r="B126" s="3"/>
+      <c r="C126" s="3"/>
+      <c r="D126" s="3"/>
+      <c r="E126" s="3"/>
+      <c r="F126" s="2"/>
+      <c r="G126" s="2"/>
+      <c r="H126" s="2"/>
+      <c r="I126" s="7"/>
+      <c r="J126" s="4"/>
+      <c r="K126" s="2"/>
+      <c r="L126" s="2"/>
+    </row>
+    <row r="127" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A127" s="3"/>
+      <c r="B127" s="3"/>
+      <c r="C127" s="3"/>
+      <c r="D127" s="3"/>
+      <c r="E127" s="3"/>
+      <c r="F127" s="2"/>
+      <c r="G127" s="2"/>
+      <c r="H127" s="2"/>
+      <c r="I127" s="7"/>
+      <c r="J127" s="4"/>
+      <c r="K127" s="2"/>
+      <c r="L127" s="2"/>
+    </row>
+    <row r="128" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A128" s="3"/>
+      <c r="B128" s="3"/>
+      <c r="C128" s="3"/>
+      <c r="D128" s="3"/>
+      <c r="E128" s="3"/>
+      <c r="F128" s="2"/>
+      <c r="G128" s="2"/>
+      <c r="H128" s="2"/>
+      <c r="I128" s="7"/>
+      <c r="J128" s="4"/>
+      <c r="K128" s="2"/>
+      <c r="L128" s="2"/>
+    </row>
+    <row r="129" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A129" s="3"/>
+      <c r="B129" s="3"/>
+      <c r="C129" s="3"/>
+      <c r="D129" s="3"/>
+      <c r="E129" s="3"/>
+      <c r="F129" s="2"/>
+      <c r="G129" s="2"/>
+      <c r="H129" s="2"/>
+      <c r="I129" s="7"/>
+      <c r="J129" s="4"/>
+      <c r="K129" s="2"/>
+      <c r="L129" s="2"/>
+    </row>
+    <row r="130" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A130" s="3"/>
+      <c r="B130" s="3"/>
+      <c r="C130" s="3"/>
+      <c r="D130" s="3"/>
+      <c r="E130" s="3"/>
+      <c r="F130" s="2"/>
+      <c r="G130" s="2"/>
+      <c r="H130" s="2"/>
+      <c r="I130" s="7"/>
+      <c r="J130" s="4"/>
+      <c r="K130" s="2"/>
+      <c r="L130" s="2"/>
+    </row>
+    <row r="131" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A131" s="3"/>
+      <c r="B131" s="3"/>
+      <c r="C131" s="3"/>
+      <c r="D131" s="3"/>
+      <c r="E131" s="3"/>
+      <c r="F131" s="2"/>
+      <c r="G131" s="2"/>
+      <c r="H131" s="2"/>
+      <c r="I131" s="7"/>
+      <c r="J131" s="4"/>
+      <c r="K131" s="2"/>
+      <c r="L131" s="2"/>
+    </row>
+    <row r="132" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A132" s="3"/>
+      <c r="B132" s="3"/>
+      <c r="C132" s="3"/>
+      <c r="D132" s="3"/>
+      <c r="E132" s="3"/>
+      <c r="F132" s="2"/>
+      <c r="G132" s="2"/>
+      <c r="H132" s="2"/>
+      <c r="I132" s="7"/>
+      <c r="J132" s="4"/>
+      <c r="K132" s="2"/>
+      <c r="L132" s="2"/>
+    </row>
+    <row r="133" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A133" s="3"/>
+      <c r="B133" s="3"/>
+      <c r="C133" s="3"/>
+      <c r="D133" s="3"/>
+      <c r="E133" s="3"/>
+      <c r="F133" s="2"/>
+      <c r="G133" s="2"/>
+      <c r="H133" s="2"/>
+      <c r="I133" s="7"/>
+      <c r="J133" s="4"/>
+      <c r="K133" s="2"/>
+      <c r="L133" s="2"/>
+    </row>
+    <row r="134" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A134" s="3"/>
+      <c r="B134" s="3"/>
+      <c r="C134" s="3"/>
+      <c r="D134" s="3"/>
+      <c r="E134" s="3"/>
+      <c r="F134" s="2"/>
+      <c r="G134" s="2"/>
+      <c r="H134" s="2"/>
+      <c r="I134" s="7"/>
+      <c r="J134" s="4"/>
+      <c r="K134" s="2"/>
+      <c r="L134" s="2"/>
+    </row>
+    <row r="135" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A135" s="3"/>
+      <c r="B135" s="3"/>
+      <c r="C135" s="3"/>
+      <c r="D135" s="3"/>
+      <c r="E135" s="3"/>
+      <c r="F135" s="2"/>
+      <c r="G135" s="2"/>
+      <c r="H135" s="2"/>
+      <c r="I135" s="7"/>
+      <c r="J135" s="4"/>
+      <c r="K135" s="2"/>
+      <c r="L135" s="2"/>
+    </row>
+    <row r="136" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A136" s="3"/>
+      <c r="B136" s="3"/>
+      <c r="C136" s="3"/>
+      <c r="D136" s="3"/>
+      <c r="E136" s="3"/>
+      <c r="F136" s="2"/>
+      <c r="G136" s="2"/>
+      <c r="H136" s="2"/>
+      <c r="I136" s="7"/>
+      <c r="J136" s="4"/>
+      <c r="K136" s="2"/>
+      <c r="L136" s="2"/>
+    </row>
+    <row r="137" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A137" s="3"/>
+      <c r="B137" s="3"/>
+      <c r="C137" s="3"/>
+      <c r="D137" s="3"/>
+      <c r="E137" s="3"/>
+      <c r="F137" s="2"/>
+      <c r="G137" s="2"/>
+      <c r="H137" s="2"/>
+      <c r="I137" s="7"/>
+      <c r="J137" s="4"/>
+      <c r="K137" s="2"/>
+      <c r="L137" s="2"/>
+    </row>
+    <row r="138" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A138" s="3"/>
+      <c r="B138" s="3"/>
+      <c r="C138" s="3"/>
+      <c r="D138" s="3"/>
+      <c r="E138" s="3"/>
+      <c r="F138" s="2"/>
+      <c r="G138" s="2"/>
+      <c r="H138" s="2"/>
+      <c r="I138" s="7"/>
+      <c r="J138" s="4"/>
+      <c r="K138" s="2"/>
+      <c r="L138" s="2"/>
+    </row>
+    <row r="139" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A139" s="3"/>
+      <c r="B139" s="3"/>
+      <c r="C139" s="3"/>
+      <c r="D139" s="3"/>
+      <c r="E139" s="3"/>
+      <c r="F139" s="2"/>
+      <c r="G139" s="2"/>
+      <c r="H139" s="2"/>
+      <c r="I139" s="7"/>
+      <c r="J139" s="4"/>
+      <c r="K139" s="2"/>
+      <c r="L139" s="2"/>
+    </row>
+    <row r="140" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A140" s="3"/>
+      <c r="B140" s="3"/>
+      <c r="C140" s="3"/>
+      <c r="D140" s="3"/>
+      <c r="E140" s="3"/>
+      <c r="F140" s="2"/>
+      <c r="G140" s="2"/>
+      <c r="H140" s="2"/>
+      <c r="I140" s="7"/>
+      <c r="J140" s="4"/>
+      <c r="K140" s="2"/>
+      <c r="L140" s="2"/>
+    </row>
+    <row r="141" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A141" s="3"/>
+      <c r="B141" s="3"/>
+      <c r="C141" s="3"/>
+      <c r="D141" s="3"/>
+      <c r="E141" s="3"/>
+      <c r="F141" s="2"/>
+      <c r="G141" s="2"/>
+      <c r="H141" s="2"/>
+      <c r="I141" s="7"/>
+      <c r="J141" s="4"/>
+      <c r="K141" s="2"/>
+      <c r="L141" s="2"/>
+    </row>
+    <row r="142" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A142" s="3"/>
+      <c r="B142" s="3"/>
+      <c r="C142" s="3"/>
+      <c r="D142" s="3"/>
+      <c r="E142" s="3"/>
+      <c r="F142" s="2"/>
+      <c r="G142" s="2"/>
+      <c r="H142" s="2"/>
+      <c r="I142" s="7"/>
+      <c r="J142" s="4"/>
+      <c r="K142" s="2"/>
+      <c r="L142" s="2"/>
+    </row>
+    <row r="143" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A143" s="3"/>
+      <c r="B143" s="3"/>
+      <c r="C143" s="3"/>
+      <c r="D143" s="3"/>
+      <c r="E143" s="3"/>
+      <c r="F143" s="2"/>
+      <c r="G143" s="2"/>
+      <c r="H143" s="2"/>
+      <c r="I143" s="7"/>
+      <c r="J143" s="4"/>
+      <c r="K143" s="2"/>
+      <c r="L143" s="2"/>
+    </row>
+    <row r="144" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A144" s="3"/>
+      <c r="B144" s="3"/>
+      <c r="C144" s="3"/>
+      <c r="D144" s="3"/>
+      <c r="E144" s="3"/>
+      <c r="F144" s="2"/>
+      <c r="G144" s="2"/>
+      <c r="H144" s="2"/>
+      <c r="I144" s="7"/>
+      <c r="J144" s="4"/>
+      <c r="K144" s="2"/>
+      <c r="L144" s="2"/>
+    </row>
+    <row r="145" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A145" s="3"/>
+      <c r="B145" s="3"/>
+      <c r="C145" s="3"/>
+      <c r="D145" s="3"/>
+      <c r="E145" s="3"/>
+      <c r="F145" s="2"/>
+      <c r="G145" s="2"/>
+      <c r="H145" s="2"/>
+      <c r="I145" s="7"/>
+      <c r="J145" s="4"/>
+      <c r="K145" s="2"/>
+      <c r="L145" s="2"/>
+    </row>
+    <row r="146" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A146" s="3"/>
+      <c r="B146" s="3"/>
+      <c r="C146" s="3"/>
+      <c r="D146" s="3"/>
+      <c r="E146" s="3"/>
+      <c r="F146" s="2"/>
+      <c r="G146" s="2"/>
+      <c r="H146" s="2"/>
+      <c r="I146" s="7"/>
+      <c r="J146" s="4"/>
+      <c r="K146" s="2"/>
+      <c r="L146" s="2"/>
+    </row>
+    <row r="147" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A147" s="3"/>
+      <c r="B147" s="3"/>
+      <c r="C147" s="3"/>
+      <c r="D147" s="3"/>
+      <c r="E147" s="3"/>
+      <c r="F147" s="2"/>
+      <c r="G147" s="2"/>
+      <c r="H147" s="2"/>
+      <c r="I147" s="7"/>
+      <c r="J147" s="4"/>
+      <c r="K147" s="2"/>
+      <c r="L147" s="2"/>
+    </row>
+    <row r="148" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A148" s="3"/>
+      <c r="B148" s="3"/>
+      <c r="C148" s="3"/>
+      <c r="D148" s="3"/>
+      <c r="E148" s="3"/>
+      <c r="F148" s="2"/>
+      <c r="G148" s="2"/>
+      <c r="H148" s="2"/>
+      <c r="I148" s="7"/>
+      <c r="J148" s="4"/>
+      <c r="K148" s="2"/>
+      <c r="L148" s="2"/>
+    </row>
+    <row r="149" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A149" s="3"/>
+      <c r="B149" s="3"/>
+      <c r="C149" s="3"/>
+      <c r="D149" s="3"/>
+      <c r="E149" s="3"/>
+      <c r="F149" s="2"/>
+      <c r="G149" s="2"/>
+      <c r="H149" s="2"/>
+      <c r="I149" s="7"/>
+      <c r="J149" s="4"/>
+      <c r="K149" s="2"/>
+      <c r="L149" s="2"/>
+    </row>
+    <row r="150" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A150" s="3"/>
+      <c r="B150" s="3"/>
+      <c r="C150" s="3"/>
+      <c r="D150" s="3"/>
+      <c r="E150" s="3"/>
+      <c r="F150" s="2"/>
+      <c r="G150" s="2"/>
+      <c r="H150" s="2"/>
+      <c r="I150" s="7"/>
+      <c r="J150" s="4"/>
+      <c r="K150" s="2"/>
+      <c r="L150" s="2"/>
+    </row>
+    <row r="151" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A151" s="3"/>
+      <c r="B151" s="3"/>
+      <c r="C151" s="3"/>
+      <c r="D151" s="3"/>
+      <c r="E151" s="3"/>
+      <c r="F151" s="2"/>
+      <c r="G151" s="2"/>
+      <c r="H151" s="2"/>
+      <c r="I151" s="7"/>
+      <c r="J151" s="4"/>
+      <c r="K151" s="2"/>
+      <c r="L151" s="2"/>
+    </row>
+    <row r="152" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A152" s="3"/>
+      <c r="B152" s="3"/>
+      <c r="C152" s="3"/>
+      <c r="D152" s="3"/>
+      <c r="E152" s="3"/>
+      <c r="F152" s="2"/>
+      <c r="G152" s="2"/>
+      <c r="H152" s="2"/>
+      <c r="I152" s="7"/>
+      <c r="J152" s="4"/>
+      <c r="K152" s="2"/>
+      <c r="L152" s="2"/>
+    </row>
+    <row r="153" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A153" s="3"/>
+      <c r="B153" s="3"/>
+      <c r="C153" s="3"/>
+      <c r="D153" s="3"/>
+      <c r="E153" s="3"/>
+      <c r="F153" s="2"/>
+      <c r="G153" s="2"/>
+      <c r="H153" s="2"/>
+      <c r="I153" s="7"/>
+      <c r="J153" s="4"/>
+      <c r="K153" s="2"/>
+      <c r="L153" s="2"/>
+    </row>
+    <row r="154" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A154" s="3"/>
+      <c r="B154" s="3"/>
+      <c r="C154" s="3"/>
+      <c r="D154" s="3"/>
+      <c r="E154" s="3"/>
+      <c r="F154" s="2"/>
+      <c r="G154" s="2"/>
+      <c r="H154" s="2"/>
+      <c r="I154" s="7"/>
+      <c r="J154" s="4"/>
+      <c r="K154" s="2"/>
+      <c r="L154" s="2"/>
+    </row>
+    <row r="155" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A155" s="3"/>
+      <c r="B155" s="3"/>
+      <c r="C155" s="3"/>
+      <c r="D155" s="3"/>
+      <c r="E155" s="3"/>
+      <c r="F155" s="2"/>
+      <c r="G155" s="2"/>
+      <c r="H155" s="2"/>
+      <c r="I155" s="7"/>
+      <c r="J155" s="4"/>
+      <c r="K155" s="2"/>
+      <c r="L155" s="2"/>
+    </row>
+    <row r="156" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A156" s="3"/>
+      <c r="B156" s="3"/>
+      <c r="C156" s="3"/>
+      <c r="D156" s="3"/>
+      <c r="E156" s="3"/>
+      <c r="F156" s="2"/>
+      <c r="G156" s="2"/>
+      <c r="H156" s="2"/>
+      <c r="I156" s="7"/>
+      <c r="J156" s="4"/>
+      <c r="K156" s="2"/>
+      <c r="L156" s="2"/>
+    </row>
+    <row r="157" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A157" s="3"/>
+      <c r="B157" s="3"/>
+      <c r="C157" s="3"/>
+      <c r="D157" s="3"/>
+      <c r="E157" s="3"/>
+      <c r="F157" s="2"/>
+      <c r="G157" s="2"/>
+      <c r="H157" s="2"/>
+      <c r="I157" s="7"/>
+      <c r="J157" s="4"/>
+      <c r="K157" s="2"/>
+      <c r="L157" s="2"/>
+    </row>
+    <row r="158" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A158" s="3"/>
+      <c r="B158" s="3"/>
+      <c r="C158" s="3"/>
+      <c r="D158" s="3"/>
+      <c r="E158" s="3"/>
+      <c r="F158" s="2"/>
+      <c r="G158" s="2"/>
+      <c r="H158" s="2"/>
+      <c r="I158" s="7"/>
+      <c r="J158" s="4"/>
+      <c r="K158" s="2"/>
+      <c r="L158" s="2"/>
+    </row>
+    <row r="159" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A159" s="3"/>
+      <c r="B159" s="3"/>
+      <c r="C159" s="3"/>
+      <c r="D159" s="3"/>
+      <c r="E159" s="3"/>
+      <c r="F159" s="2"/>
+      <c r="G159" s="2"/>
+      <c r="H159" s="2"/>
+      <c r="I159" s="7"/>
+      <c r="J159" s="4"/>
+      <c r="K159" s="2"/>
+      <c r="L159" s="2"/>
+    </row>
+    <row r="160" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A160" s="3"/>
+      <c r="B160" s="3"/>
+      <c r="C160" s="3"/>
+      <c r="D160" s="3"/>
+      <c r="E160" s="3"/>
+      <c r="F160" s="2"/>
+      <c r="G160" s="2"/>
+      <c r="H160" s="2"/>
+      <c r="I160" s="7"/>
+      <c r="J160" s="4"/>
+      <c r="K160" s="2"/>
+      <c r="L160" s="2"/>
+    </row>
+    <row r="161" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A161" s="3"/>
+      <c r="B161" s="3"/>
+      <c r="C161" s="3"/>
+      <c r="D161" s="3"/>
+      <c r="E161" s="3"/>
+      <c r="F161" s="2"/>
+      <c r="G161" s="2"/>
+      <c r="H161" s="2"/>
+      <c r="I161" s="7"/>
+      <c r="J161" s="4"/>
+      <c r="K161" s="2"/>
+      <c r="L161" s="2"/>
+    </row>
+    <row r="162" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A162" s="3"/>
+      <c r="B162" s="3"/>
+      <c r="C162" s="3"/>
+      <c r="D162" s="3"/>
+      <c r="E162" s="3"/>
+      <c r="F162" s="2"/>
+      <c r="G162" s="2"/>
+      <c r="H162" s="2"/>
+      <c r="I162" s="7"/>
+      <c r="J162" s="4"/>
+      <c r="K162" s="2"/>
+      <c r="L162" s="2"/>
+    </row>
+    <row r="163" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A163" s="3"/>
+      <c r="B163" s="3"/>
+      <c r="C163" s="3"/>
+      <c r="D163" s="3"/>
+      <c r="E163" s="3"/>
+      <c r="F163" s="2"/>
+      <c r="G163" s="2"/>
+      <c r="H163" s="2"/>
+      <c r="I163" s="7"/>
+      <c r="J163" s="4"/>
+      <c r="K163" s="2"/>
+      <c r="L163" s="2"/>
+    </row>
+    <row r="164" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A164" s="3"/>
+      <c r="B164" s="3"/>
+      <c r="C164" s="3"/>
+      <c r="D164" s="3"/>
+      <c r="E164" s="3"/>
+      <c r="F164" s="2"/>
+      <c r="G164" s="2"/>
+      <c r="H164" s="2"/>
+      <c r="I164" s="7"/>
+      <c r="J164" s="4"/>
+      <c r="K164" s="2"/>
+      <c r="L164" s="2"/>
+    </row>
+    <row r="165" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A165" s="3"/>
+      <c r="B165" s="3"/>
+      <c r="C165" s="3"/>
+      <c r="D165" s="3"/>
+      <c r="E165" s="3"/>
+      <c r="F165" s="2"/>
+      <c r="G165" s="2"/>
+      <c r="H165" s="2"/>
+      <c r="I165" s="7"/>
+      <c r="J165" s="4"/>
+      <c r="K165" s="2"/>
+      <c r="L165" s="2"/>
+    </row>
+    <row r="166" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A166" s="3"/>
+      <c r="B166" s="3"/>
+      <c r="C166" s="3"/>
+      <c r="D166" s="3"/>
+      <c r="E166" s="3"/>
+      <c r="F166" s="2"/>
+      <c r="G166" s="2"/>
+      <c r="H166" s="2"/>
+      <c r="I166" s="7"/>
+      <c r="J166" s="4"/>
+      <c r="K166" s="2"/>
+      <c r="L166" s="2"/>
+    </row>
+    <row r="167" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A167" s="3"/>
+      <c r="B167" s="3"/>
+      <c r="C167" s="3"/>
+      <c r="D167" s="3"/>
+      <c r="E167" s="3"/>
+      <c r="F167" s="2"/>
+      <c r="G167" s="2"/>
+      <c r="H167" s="2"/>
+      <c r="I167" s="7"/>
+      <c r="J167" s="4"/>
+      <c r="K167" s="2"/>
+      <c r="L167" s="2"/>
+    </row>
+    <row r="168" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A168" s="3"/>
+      <c r="B168" s="3"/>
+      <c r="C168" s="3"/>
+      <c r="D168" s="3"/>
+      <c r="E168" s="3"/>
+      <c r="F168" s="2"/>
+      <c r="G168" s="2"/>
+      <c r="H168" s="2"/>
+      <c r="I168" s="7"/>
+      <c r="J168" s="4"/>
+      <c r="K168" s="2"/>
+      <c r="L168" s="2"/>
+    </row>
+    <row r="169" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A169" s="3"/>
+      <c r="B169" s="3"/>
+      <c r="C169" s="3"/>
+      <c r="D169" s="3"/>
+      <c r="E169" s="3"/>
+      <c r="F169" s="2"/>
+      <c r="G169" s="2"/>
+      <c r="H169" s="2"/>
+      <c r="I169" s="7"/>
+      <c r="J169" s="4"/>
+      <c r="K169" s="2"/>
+      <c r="L169" s="2"/>
+    </row>
+    <row r="170" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A170" s="3"/>
+      <c r="B170" s="3"/>
+      <c r="C170" s="3"/>
+      <c r="D170" s="3"/>
+      <c r="E170" s="3"/>
+      <c r="F170" s="2"/>
+      <c r="G170" s="2"/>
+      <c r="H170" s="2"/>
+      <c r="I170" s="7"/>
+      <c r="J170" s="4"/>
+      <c r="K170" s="2"/>
+      <c r="L170" s="2"/>
+    </row>
+    <row r="171" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A171" s="3"/>
+      <c r="B171" s="3"/>
+      <c r="C171" s="3"/>
+      <c r="D171" s="3"/>
+      <c r="E171" s="3"/>
+      <c r="F171" s="2"/>
+      <c r="G171" s="2"/>
+      <c r="H171" s="2"/>
+      <c r="I171" s="7"/>
+      <c r="J171" s="4"/>
+      <c r="K171" s="2"/>
+      <c r="L171" s="2"/>
+    </row>
+    <row r="172" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A172" s="3"/>
+      <c r="B172" s="3"/>
+      <c r="C172" s="3"/>
+      <c r="D172" s="3"/>
+      <c r="E172" s="3"/>
+      <c r="F172" s="2"/>
+      <c r="G172" s="2"/>
+      <c r="H172" s="2"/>
+      <c r="I172" s="7"/>
+      <c r="J172" s="4"/>
+      <c r="K172" s="2"/>
+      <c r="L172" s="2"/>
+    </row>
+    <row r="173" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A173" s="3"/>
+      <c r="B173" s="3"/>
+      <c r="C173" s="3"/>
+      <c r="D173" s="3"/>
+      <c r="E173" s="3"/>
+      <c r="F173" s="2"/>
+      <c r="G173" s="2"/>
+      <c r="H173" s="2"/>
+      <c r="I173" s="7"/>
+      <c r="J173" s="4"/>
+      <c r="K173" s="2"/>
+      <c r="L173" s="2"/>
+    </row>
+    <row r="174" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A174" s="3"/>
+      <c r="B174" s="3"/>
+      <c r="C174" s="3"/>
+      <c r="D174" s="3"/>
+      <c r="E174" s="3"/>
+      <c r="F174" s="2"/>
+      <c r="G174" s="2"/>
+      <c r="H174" s="2"/>
+      <c r="I174" s="7"/>
+      <c r="J174" s="4"/>
+      <c r="K174" s="2"/>
+      <c r="L174" s="2"/>
+    </row>
+    <row r="175" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A175" s="3"/>
+      <c r="B175" s="3"/>
+      <c r="C175" s="3"/>
+      <c r="D175" s="3"/>
+      <c r="E175" s="3"/>
+      <c r="F175" s="2"/>
+      <c r="G175" s="2"/>
+      <c r="H175" s="2"/>
+      <c r="I175" s="7"/>
+      <c r="J175" s="4"/>
+      <c r="K175" s="2"/>
+      <c r="L175" s="2"/>
+    </row>
+    <row r="176" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A176" s="3"/>
+      <c r="B176" s="3"/>
+      <c r="C176" s="3"/>
+      <c r="D176" s="3"/>
+      <c r="E176" s="3"/>
+      <c r="F176" s="2"/>
+      <c r="G176" s="2"/>
+      <c r="H176" s="2"/>
+      <c r="I176" s="7"/>
+      <c r="J176" s="4"/>
+      <c r="K176" s="2"/>
+      <c r="L176" s="2"/>
+    </row>
+    <row r="177" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A177" s="3"/>
+      <c r="B177" s="3"/>
+      <c r="C177" s="3"/>
+      <c r="D177" s="3"/>
+      <c r="E177" s="3"/>
+      <c r="F177" s="2"/>
+      <c r="G177" s="2"/>
+      <c r="H177" s="2"/>
+      <c r="I177" s="7"/>
+      <c r="J177" s="4"/>
+      <c r="K177" s="2"/>
+      <c r="L177" s="2"/>
+    </row>
+    <row r="178" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A178" s="3"/>
+      <c r="B178" s="3"/>
+      <c r="C178" s="3"/>
+      <c r="D178" s="3"/>
+      <c r="E178" s="3"/>
+      <c r="F178" s="2"/>
+      <c r="G178" s="2"/>
+      <c r="H178" s="2"/>
+      <c r="I178" s="7"/>
+      <c r="J178" s="4"/>
+      <c r="K178" s="2"/>
+      <c r="L178" s="2"/>
+    </row>
+    <row r="179" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A179" s="3"/>
+      <c r="B179" s="3"/>
+      <c r="C179" s="3"/>
+      <c r="D179" s="3"/>
+      <c r="E179" s="3"/>
+      <c r="F179" s="2"/>
+      <c r="G179" s="2"/>
+      <c r="H179" s="2"/>
+      <c r="I179" s="7"/>
+      <c r="J179" s="4"/>
+      <c r="K179" s="2"/>
+      <c r="L179" s="2"/>
+    </row>
+    <row r="180" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A180" s="3"/>
+      <c r="B180" s="3"/>
+      <c r="C180" s="3"/>
+      <c r="D180" s="3"/>
+      <c r="E180" s="3"/>
+      <c r="F180" s="2"/>
+      <c r="G180" s="2"/>
+      <c r="H180" s="2"/>
+      <c r="I180" s="7"/>
+      <c r="J180" s="4"/>
+      <c r="K180" s="2"/>
+      <c r="L180" s="2"/>
+    </row>
+    <row r="181" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A181" s="3"/>
+      <c r="B181" s="3"/>
+      <c r="C181" s="3"/>
+      <c r="D181" s="3"/>
+      <c r="E181" s="3"/>
+      <c r="F181" s="2"/>
+      <c r="G181" s="2"/>
+      <c r="H181" s="2"/>
+      <c r="I181" s="7"/>
+      <c r="J181" s="4"/>
+      <c r="K181" s="2"/>
+      <c r="L181" s="2"/>
+    </row>
+    <row r="182" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A182" s="3"/>
+      <c r="B182" s="3"/>
+      <c r="C182" s="3"/>
+      <c r="D182" s="3"/>
+      <c r="E182" s="3"/>
+      <c r="F182" s="2"/>
+      <c r="G182" s="2"/>
+      <c r="H182" s="2"/>
+      <c r="I182" s="7"/>
+      <c r="J182" s="4"/>
+      <c r="K182" s="2"/>
+      <c r="L182" s="2"/>
+    </row>
+    <row r="183" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A183" s="3"/>
+      <c r="B183" s="3"/>
+      <c r="C183" s="3"/>
+      <c r="D183" s="3"/>
+      <c r="E183" s="3"/>
+      <c r="F183" s="2"/>
+      <c r="G183" s="2"/>
+      <c r="H183" s="2"/>
+      <c r="I183" s="7"/>
+      <c r="J183" s="4"/>
+      <c r="K183" s="2"/>
+      <c r="L183" s="2"/>
+    </row>
+    <row r="184" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A184" s="3"/>
+      <c r="B184" s="3"/>
+      <c r="C184" s="3"/>
+      <c r="D184" s="3"/>
+      <c r="E184" s="3"/>
+      <c r="F184" s="2"/>
+      <c r="G184" s="2"/>
+      <c r="H184" s="2"/>
+      <c r="I184" s="7"/>
+      <c r="J184" s="4"/>
+      <c r="K184" s="2"/>
+      <c r="L184" s="2"/>
+    </row>
+    <row r="185" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A185" s="3"/>
+      <c r="B185" s="3"/>
+      <c r="C185" s="3"/>
+      <c r="D185" s="3"/>
+      <c r="E185" s="3"/>
+      <c r="F185" s="2"/>
+      <c r="G185" s="2"/>
+      <c r="H185" s="2"/>
+      <c r="I185" s="7"/>
+      <c r="J185" s="4"/>
+      <c r="K185" s="2"/>
+      <c r="L185" s="2"/>
+    </row>
+    <row r="186" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A186" s="3"/>
+      <c r="B186" s="3"/>
+      <c r="C186" s="3"/>
+      <c r="D186" s="3"/>
+      <c r="E186" s="3"/>
+      <c r="F186" s="2"/>
+      <c r="G186" s="2"/>
+      <c r="H186" s="2"/>
+      <c r="I186" s="7"/>
+      <c r="J186" s="4"/>
+      <c r="K186" s="2"/>
+      <c r="L186" s="2"/>
+    </row>
+    <row r="187" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A187" s="3"/>
+      <c r="B187" s="3"/>
+      <c r="C187" s="3"/>
+      <c r="D187" s="3"/>
+      <c r="E187" s="3"/>
+      <c r="F187" s="2"/>
+      <c r="G187" s="2"/>
+      <c r="H187" s="2"/>
+      <c r="I187" s="7"/>
+      <c r="J187" s="4"/>
+      <c r="K187" s="2"/>
+      <c r="L187" s="2"/>
+    </row>
+    <row r="188" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A188" s="3"/>
+      <c r="B188" s="3"/>
+      <c r="C188" s="3"/>
+      <c r="D188" s="3"/>
+      <c r="E188" s="3"/>
+      <c r="F188" s="2"/>
+      <c r="G188" s="2"/>
+      <c r="H188" s="2"/>
+      <c r="I188" s="7"/>
+      <c r="J188" s="4"/>
+      <c r="K188" s="2"/>
+      <c r="L188" s="2"/>
+    </row>
+    <row r="189" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A189" s="3"/>
+      <c r="B189" s="3"/>
+      <c r="C189" s="3"/>
+      <c r="D189" s="3"/>
+      <c r="E189" s="3"/>
+      <c r="F189" s="2"/>
+      <c r="G189" s="2"/>
+      <c r="H189" s="2"/>
+      <c r="I189" s="7"/>
+      <c r="J189" s="4"/>
+      <c r="K189" s="2"/>
+      <c r="L189" s="2"/>
+    </row>
+    <row r="190" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A190" s="3"/>
+      <c r="B190" s="3"/>
+      <c r="C190" s="3"/>
+      <c r="D190" s="3"/>
+      <c r="E190" s="3"/>
+      <c r="F190" s="2"/>
+      <c r="G190" s="2"/>
+      <c r="H190" s="2"/>
+      <c r="I190" s="7"/>
+      <c r="J190" s="4"/>
+      <c r="K190" s="2"/>
+      <c r="L190" s="2"/>
+    </row>
+    <row r="191" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A191" s="3"/>
+      <c r="B191" s="3"/>
+      <c r="C191" s="3"/>
+      <c r="D191" s="3"/>
+      <c r="E191" s="3"/>
+      <c r="F191" s="2"/>
+      <c r="G191" s="2"/>
+      <c r="H191" s="2"/>
+      <c r="I191" s="7"/>
+      <c r="J191" s="4"/>
+      <c r="K191" s="2"/>
+      <c r="L191" s="2"/>
+    </row>
+    <row r="192" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A192" s="3"/>
+      <c r="B192" s="3"/>
+      <c r="C192" s="3"/>
+      <c r="D192" s="3"/>
+      <c r="E192" s="3"/>
+      <c r="F192" s="2"/>
+      <c r="G192" s="2"/>
+      <c r="H192" s="2"/>
+      <c r="I192" s="7"/>
+      <c r="J192" s="4"/>
+      <c r="K192" s="2"/>
+      <c r="L192" s="2"/>
+    </row>
+    <row r="193" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A193" s="3"/>
+      <c r="B193" s="3"/>
+      <c r="C193" s="3"/>
+      <c r="D193" s="3"/>
+      <c r="E193" s="3"/>
+      <c r="F193" s="2"/>
+      <c r="G193" s="2"/>
+      <c r="H193" s="2"/>
+      <c r="I193" s="7"/>
+      <c r="J193" s="4"/>
+      <c r="K193" s="2"/>
+      <c r="L193" s="2"/>
+    </row>
+    <row r="194" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A194" s="3"/>
+      <c r="B194" s="3"/>
+      <c r="C194" s="3"/>
+      <c r="D194" s="3"/>
+      <c r="E194" s="3"/>
+      <c r="F194" s="2"/>
+      <c r="G194" s="2"/>
+      <c r="H194" s="2"/>
+      <c r="I194" s="7"/>
+      <c r="J194" s="4"/>
+      <c r="K194" s="2"/>
+      <c r="L194" s="2"/>
+    </row>
+    <row r="195" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A195" s="3"/>
+      <c r="B195" s="3"/>
+      <c r="C195" s="3"/>
+      <c r="D195" s="3"/>
+      <c r="E195" s="3"/>
+      <c r="F195" s="2"/>
+      <c r="G195" s="2"/>
+      <c r="H195" s="2"/>
+      <c r="I195" s="7"/>
+      <c r="J195" s="4"/>
+      <c r="K195" s="2"/>
+      <c r="L195" s="2"/>
+    </row>
+    <row r="196" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A196" s="3"/>
+      <c r="B196" s="3"/>
+      <c r="C196" s="3"/>
+      <c r="D196" s="3"/>
+      <c r="E196" s="3"/>
+      <c r="F196" s="2"/>
+      <c r="G196" s="2"/>
+      <c r="H196" s="2"/>
+      <c r="I196" s="7"/>
+      <c r="J196" s="4"/>
+      <c r="K196" s="2"/>
+      <c r="L196" s="2"/>
+    </row>
+    <row r="197" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A197" s="3"/>
+      <c r="B197" s="3"/>
+      <c r="C197" s="3"/>
+      <c r="D197" s="3"/>
+      <c r="E197" s="3"/>
+      <c r="F197" s="2"/>
+      <c r="G197" s="2"/>
+      <c r="H197" s="2"/>
+      <c r="I197" s="7"/>
+      <c r="J197" s="4"/>
+      <c r="K197" s="2"/>
+      <c r="L197" s="2"/>
+    </row>
+    <row r="198" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A198" s="3"/>
+      <c r="B198" s="3"/>
+      <c r="C198" s="3"/>
+      <c r="D198" s="3"/>
+      <c r="E198" s="3"/>
+      <c r="F198" s="2"/>
+      <c r="G198" s="2"/>
+      <c r="H198" s="2"/>
+      <c r="I198" s="7"/>
+      <c r="J198" s="4"/>
+      <c r="K198" s="2"/>
+      <c r="L198" s="2"/>
+    </row>
+    <row r="199" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A199" s="3"/>
+      <c r="B199" s="3"/>
+      <c r="C199" s="3"/>
+      <c r="D199" s="3"/>
+      <c r="E199" s="3"/>
+      <c r="F199" s="2"/>
+      <c r="G199" s="2"/>
+      <c r="H199" s="2"/>
+      <c r="I199" s="7"/>
+      <c r="J199" s="4"/>
+      <c r="K199" s="2"/>
+      <c r="L199" s="2"/>
+    </row>
+    <row r="200" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A200" s="3"/>
+      <c r="B200" s="3"/>
+      <c r="C200" s="3"/>
+      <c r="D200" s="3"/>
+      <c r="E200" s="3"/>
+      <c r="F200" s="2"/>
+      <c r="G200" s="2"/>
+      <c r="H200" s="2"/>
+      <c r="I200" s="7"/>
+      <c r="J200" s="4"/>
+      <c r="K200" s="2"/>
+      <c r="L200" s="2"/>
+    </row>
+    <row r="201" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A201" s="3"/>
+      <c r="B201" s="3"/>
+      <c r="C201" s="3"/>
+      <c r="D201" s="3"/>
+      <c r="E201" s="3"/>
+      <c r="F201" s="2"/>
+      <c r="G201" s="2"/>
+      <c r="H201" s="2"/>
+      <c r="I201" s="7"/>
+      <c r="J201" s="4"/>
+      <c r="K201" s="2"/>
+      <c r="L201" s="2"/>
+    </row>
+    <row r="202" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A202" s="3"/>
+      <c r="B202" s="3"/>
+      <c r="C202" s="3"/>
+      <c r="D202" s="3"/>
+      <c r="E202" s="3"/>
+      <c r="F202" s="2"/>
+      <c r="G202" s="2"/>
+      <c r="H202" s="2"/>
+      <c r="I202" s="7"/>
+      <c r="J202" s="4"/>
+      <c r="K202" s="2"/>
+      <c r="L202" s="2"/>
+    </row>
+    <row r="203" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A203" s="3"/>
+      <c r="B203" s="3"/>
+      <c r="C203" s="3"/>
+      <c r="D203" s="3"/>
+      <c r="E203" s="3"/>
+      <c r="F203" s="2"/>
+      <c r="G203" s="2"/>
+      <c r="H203" s="2"/>
+      <c r="I203" s="7"/>
+      <c r="J203" s="4"/>
+      <c r="K203" s="2"/>
+      <c r="L203" s="2"/>
+    </row>
+    <row r="204" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A204" s="3"/>
+      <c r="B204" s="3"/>
+      <c r="C204" s="3"/>
+      <c r="D204" s="3"/>
+      <c r="E204" s="3"/>
+      <c r="F204" s="2"/>
+      <c r="G204" s="2"/>
+      <c r="H204" s="2"/>
+      <c r="I204" s="7"/>
+      <c r="J204" s="4"/>
+      <c r="K204" s="2"/>
+      <c r="L204" s="2"/>
+    </row>
+    <row r="205" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A205" s="3"/>
+      <c r="B205" s="3"/>
+      <c r="C205" s="3"/>
+      <c r="D205" s="3"/>
+      <c r="E205" s="3"/>
+      <c r="F205" s="2"/>
+      <c r="G205" s="2"/>
+      <c r="H205" s="2"/>
+      <c r="I205" s="7"/>
+      <c r="J205" s="4"/>
+      <c r="K205" s="2"/>
+      <c r="L205" s="2"/>
+    </row>
+    <row r="206" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A206" s="3"/>
+      <c r="B206" s="3"/>
+      <c r="C206" s="3"/>
+      <c r="D206" s="3"/>
+      <c r="E206" s="3"/>
+      <c r="F206" s="2"/>
+      <c r="G206" s="2"/>
+      <c r="H206" s="2"/>
+      <c r="I206" s="7"/>
+      <c r="J206" s="4"/>
+      <c r="K206" s="2"/>
+      <c r="L206" s="2"/>
+    </row>
+    <row r="207" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A207" s="3"/>
+      <c r="B207" s="3"/>
+      <c r="C207" s="3"/>
+      <c r="D207" s="3"/>
+      <c r="E207" s="3"/>
+      <c r="F207" s="2"/>
+      <c r="G207" s="2"/>
+      <c r="H207" s="2"/>
+      <c r="I207" s="7"/>
+      <c r="J207" s="4"/>
+      <c r="K207" s="2"/>
+      <c r="L207" s="2"/>
+    </row>
+    <row r="208" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A208" s="3"/>
+      <c r="B208" s="3"/>
+      <c r="C208" s="3"/>
+      <c r="D208" s="3"/>
+      <c r="E208" s="3"/>
+      <c r="F208" s="2"/>
+      <c r="G208" s="2"/>
+      <c r="H208" s="2"/>
+      <c r="I208" s="7"/>
+      <c r="J208" s="4"/>
+      <c r="K208" s="2"/>
+      <c r="L208" s="2"/>
+    </row>
+    <row r="209" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A209" s="3"/>
+      <c r="B209" s="3"/>
+      <c r="C209" s="3"/>
+      <c r="D209" s="3"/>
+      <c r="E209" s="3"/>
+      <c r="F209" s="2"/>
+      <c r="G209" s="2"/>
+      <c r="H209" s="2"/>
+      <c r="I209" s="7"/>
+      <c r="J209" s="4"/>
+      <c r="K209" s="2"/>
+      <c r="L209" s="2"/>
+    </row>
+    <row r="210" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A210" s="3"/>
+      <c r="B210" s="3"/>
+      <c r="C210" s="3"/>
+      <c r="D210" s="3"/>
+      <c r="E210" s="3"/>
+      <c r="F210" s="2"/>
+      <c r="G210" s="2"/>
+      <c r="H210" s="2"/>
+      <c r="I210" s="7"/>
+      <c r="J210" s="4"/>
+      <c r="K210" s="2"/>
+      <c r="L210" s="2"/>
+    </row>
+    <row r="211" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A211" s="3"/>
+      <c r="B211" s="3"/>
+      <c r="C211" s="3"/>
+      <c r="D211" s="3"/>
+      <c r="E211" s="3"/>
+      <c r="F211" s="2"/>
+      <c r="G211" s="2"/>
+      <c r="H211" s="2"/>
+      <c r="I211" s="7"/>
+      <c r="J211" s="4"/>
+      <c r="K211" s="2"/>
+      <c r="L211" s="2"/>
+    </row>
+    <row r="212" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A212" s="3"/>
+      <c r="B212" s="3"/>
+      <c r="C212" s="3"/>
+      <c r="D212" s="3"/>
+      <c r="E212" s="3"/>
+      <c r="F212" s="2"/>
+      <c r="G212" s="2"/>
+      <c r="H212" s="2"/>
+      <c r="I212" s="7"/>
+      <c r="J212" s="4"/>
+      <c r="K212" s="2"/>
+      <c r="L212" s="2"/>
+    </row>
+    <row r="213" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A213" s="3"/>
+      <c r="B213" s="3"/>
+      <c r="C213" s="3"/>
+      <c r="D213" s="3"/>
+      <c r="E213" s="3"/>
+      <c r="F213" s="2"/>
+      <c r="G213" s="2"/>
+      <c r="H213" s="2"/>
+      <c r="I213" s="7"/>
+      <c r="J213" s="4"/>
+      <c r="K213" s="2"/>
+      <c r="L213" s="2"/>
+    </row>
+    <row r="214" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A214" s="3"/>
+      <c r="B214" s="3"/>
+      <c r="C214" s="3"/>
+      <c r="D214" s="3"/>
+      <c r="E214" s="3"/>
+      <c r="F214" s="2"/>
+      <c r="G214" s="2"/>
+      <c r="H214" s="2"/>
+      <c r="I214" s="7"/>
+      <c r="J214" s="4"/>
+      <c r="K214" s="2"/>
+      <c r="L214" s="2"/>
+    </row>
+    <row r="215" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A215" s="3"/>
+      <c r="B215" s="3"/>
+      <c r="C215" s="3"/>
+      <c r="D215" s="3"/>
+      <c r="E215" s="3"/>
+      <c r="F215" s="2"/>
+      <c r="G215" s="2"/>
+      <c r="H215" s="2"/>
+      <c r="I215" s="7"/>
+      <c r="J215" s="4"/>
+      <c r="K215" s="2"/>
+      <c r="L215" s="2"/>
+    </row>
+    <row r="216" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A216" s="3"/>
+      <c r="B216" s="3"/>
+      <c r="C216" s="3"/>
+      <c r="D216" s="3"/>
+      <c r="E216" s="3"/>
+      <c r="F216" s="2"/>
+      <c r="G216" s="2"/>
+      <c r="H216" s="2"/>
+      <c r="I216" s="7"/>
+      <c r="J216" s="4"/>
+      <c r="K216" s="2"/>
+      <c r="L216" s="2"/>
+    </row>
+    <row r="217" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A217" s="3"/>
+      <c r="B217" s="3"/>
+      <c r="C217" s="3"/>
+      <c r="D217" s="3"/>
+      <c r="E217" s="3"/>
+      <c r="F217" s="2"/>
+      <c r="G217" s="2"/>
+      <c r="H217" s="2"/>
+      <c r="I217" s="7"/>
+      <c r="J217" s="4"/>
+      <c r="K217" s="2"/>
+      <c r="L217" s="2"/>
+    </row>
+    <row r="218" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A218" s="3"/>
+      <c r="B218" s="3"/>
+      <c r="C218" s="3"/>
+      <c r="D218" s="3"/>
+      <c r="E218" s="3"/>
+      <c r="F218" s="2"/>
+      <c r="G218" s="2"/>
+      <c r="H218" s="2"/>
+      <c r="I218" s="7"/>
+      <c r="J218" s="4"/>
+      <c r="K218" s="2"/>
+      <c r="L218" s="2"/>
+    </row>
+    <row r="219" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A219" s="3"/>
+      <c r="B219" s="3"/>
+      <c r="C219" s="3"/>
+      <c r="D219" s="3"/>
+      <c r="E219" s="3"/>
+      <c r="F219" s="2"/>
+      <c r="G219" s="2"/>
+      <c r="H219" s="2"/>
+      <c r="I219" s="7"/>
+      <c r="J219" s="4"/>
+      <c r="K219" s="2"/>
+      <c r="L219" s="2"/>
+    </row>
+    <row r="220" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A220" s="3"/>
+      <c r="B220" s="3"/>
+      <c r="C220" s="3"/>
+      <c r="D220" s="3"/>
+      <c r="E220" s="3"/>
+      <c r="F220" s="2"/>
+      <c r="G220" s="2"/>
+      <c r="H220" s="2"/>
+      <c r="I220" s="7"/>
+      <c r="J220" s="4"/>
+      <c r="K220" s="2"/>
+      <c r="L220" s="2"/>
+    </row>
+    <row r="221" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A221" s="3"/>
+      <c r="B221" s="3"/>
+      <c r="C221" s="3"/>
+      <c r="D221" s="3"/>
+      <c r="E221" s="3"/>
+      <c r="F221" s="2"/>
+      <c r="G221" s="2"/>
+      <c r="H221" s="2"/>
+      <c r="I221" s="7"/>
+      <c r="J221" s="4"/>
+      <c r="K221" s="2"/>
+      <c r="L221" s="2"/>
+    </row>
+    <row r="222" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A222" s="3"/>
+      <c r="B222" s="3"/>
+      <c r="C222" s="3"/>
+      <c r="D222" s="3"/>
+      <c r="E222" s="3"/>
+      <c r="F222" s="2"/>
+      <c r="G222" s="2"/>
+      <c r="H222" s="2"/>
+      <c r="I222" s="7"/>
+      <c r="J222" s="4"/>
+      <c r="K222" s="2"/>
+      <c r="L222" s="2"/>
+    </row>
+    <row r="223" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A223" s="3"/>
+      <c r="B223" s="3"/>
+      <c r="C223" s="3"/>
+      <c r="D223" s="3"/>
+      <c r="E223" s="3"/>
+      <c r="F223" s="2"/>
+      <c r="G223" s="2"/>
+      <c r="H223" s="2"/>
+      <c r="I223" s="7"/>
+      <c r="J223" s="4"/>
+      <c r="K223" s="2"/>
+      <c r="L223" s="2"/>
+    </row>
+    <row r="224" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A224" s="3"/>
+      <c r="B224" s="3"/>
+      <c r="C224" s="3"/>
+      <c r="D224" s="3"/>
+      <c r="E224" s="3"/>
+      <c r="F224" s="2"/>
+      <c r="G224" s="2"/>
+      <c r="H224" s="2"/>
+      <c r="I224" s="7"/>
+      <c r="J224" s="4"/>
+      <c r="K224" s="2"/>
+      <c r="L224" s="2"/>
+    </row>
+    <row r="225" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A225" s="3"/>
+      <c r="B225" s="3"/>
+      <c r="C225" s="3"/>
+      <c r="D225" s="3"/>
+      <c r="E225" s="3"/>
+      <c r="F225" s="2"/>
+      <c r="G225" s="2"/>
+      <c r="H225" s="2"/>
+      <c r="I225" s="7"/>
+      <c r="J225" s="4"/>
+      <c r="K225" s="2"/>
+      <c r="L225" s="2"/>
+    </row>
+    <row r="226" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A226" s="3"/>
+      <c r="B226" s="3"/>
+      <c r="C226" s="3"/>
+      <c r="D226" s="3"/>
+      <c r="E226" s="3"/>
+      <c r="F226" s="2"/>
+      <c r="G226" s="2"/>
+      <c r="H226" s="2"/>
+      <c r="I226" s="7"/>
+      <c r="J226" s="4"/>
+      <c r="K226" s="2"/>
+      <c r="L226" s="2"/>
+    </row>
+    <row r="227" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A227" s="3"/>
+      <c r="B227" s="3"/>
+      <c r="C227" s="3"/>
+      <c r="D227" s="3"/>
+      <c r="E227" s="3"/>
+      <c r="F227" s="2"/>
+      <c r="G227" s="2"/>
+      <c r="H227" s="2"/>
+      <c r="I227" s="7"/>
+      <c r="J227" s="4"/>
+      <c r="K227" s="2"/>
+      <c r="L227" s="2"/>
+    </row>
+    <row r="228" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A228" s="3"/>
+      <c r="B228" s="3"/>
+      <c r="C228" s="3"/>
+      <c r="D228" s="3"/>
+      <c r="E228" s="3"/>
+      <c r="F228" s="2"/>
+      <c r="G228" s="2"/>
+      <c r="H228" s="2"/>
+      <c r="I228" s="7"/>
+      <c r="J228" s="4"/>
+      <c r="K228" s="2"/>
+      <c r="L228" s="2"/>
+    </row>
+    <row r="229" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A229" s="3"/>
+      <c r="B229" s="3"/>
+      <c r="C229" s="3"/>
+      <c r="D229" s="3"/>
+      <c r="E229" s="3"/>
+      <c r="F229" s="2"/>
+      <c r="G229" s="2"/>
+      <c r="H229" s="2"/>
+      <c r="I229" s="7"/>
+      <c r="J229" s="4"/>
+      <c r="K229" s="2"/>
+      <c r="L229" s="2"/>
+    </row>
+    <row r="230" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A230" s="3"/>
+      <c r="B230" s="3"/>
+      <c r="C230" s="3"/>
+      <c r="D230" s="3"/>
+      <c r="E230" s="3"/>
+      <c r="F230" s="2"/>
+      <c r="G230" s="2"/>
+      <c r="H230" s="2"/>
+      <c r="I230" s="7"/>
+      <c r="J230" s="4"/>
+      <c r="K230" s="2"/>
+      <c r="L230" s="2"/>
+    </row>
+    <row r="231" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A231" s="3"/>
+      <c r="B231" s="3"/>
+      <c r="C231" s="3"/>
+      <c r="D231" s="3"/>
+      <c r="E231" s="3"/>
+      <c r="F231" s="2"/>
+      <c r="G231" s="2"/>
+      <c r="H231" s="2"/>
+      <c r="I231" s="7"/>
+      <c r="J231" s="4"/>
+      <c r="K231" s="2"/>
+      <c r="L231" s="2"/>
+    </row>
+    <row r="232" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A232" s="3"/>
+      <c r="B232" s="3"/>
+      <c r="C232" s="3"/>
+      <c r="D232" s="3"/>
+      <c r="E232" s="3"/>
+      <c r="F232" s="2"/>
+      <c r="G232" s="2"/>
+      <c r="H232" s="2"/>
+      <c r="I232" s="7"/>
+      <c r="J232" s="4"/>
+      <c r="K232" s="2"/>
+      <c r="L232" s="2"/>
+    </row>
+    <row r="233" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A233" s="3"/>
+      <c r="B233" s="3"/>
+      <c r="C233" s="3"/>
+      <c r="D233" s="3"/>
+      <c r="E233" s="3"/>
+      <c r="F233" s="2"/>
+      <c r="G233" s="2"/>
+      <c r="H233" s="2"/>
+      <c r="I233" s="7"/>
+      <c r="J233" s="4"/>
+      <c r="K233" s="2"/>
+      <c r="L233" s="2"/>
+    </row>
+    <row r="234" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A234" s="3"/>
+      <c r="B234" s="3"/>
+      <c r="C234" s="3"/>
+      <c r="D234" s="3"/>
+      <c r="E234" s="3"/>
+      <c r="F234" s="2"/>
+      <c r="G234" s="2"/>
+      <c r="H234" s="2"/>
+      <c r="I234" s="7"/>
+      <c r="J234" s="4"/>
+      <c r="K234" s="2"/>
+      <c r="L234" s="2"/>
+    </row>
+    <row r="235" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A235" s="3"/>
+      <c r="B235" s="3"/>
+      <c r="C235" s="3"/>
+      <c r="D235" s="3"/>
+      <c r="E235" s="3"/>
+      <c r="F235" s="2"/>
+      <c r="G235" s="2"/>
+      <c r="H235" s="2"/>
+      <c r="I235" s="7"/>
+      <c r="J235" s="4"/>
+      <c r="K235" s="2"/>
+      <c r="L235" s="2"/>
+    </row>
+    <row r="236" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A236" s="3"/>
+      <c r="B236" s="3"/>
+      <c r="C236" s="3"/>
+      <c r="D236" s="3"/>
+      <c r="E236" s="3"/>
+      <c r="F236" s="2"/>
+      <c r="G236" s="2"/>
+      <c r="H236" s="2"/>
+      <c r="I236" s="7"/>
+      <c r="J236" s="4"/>
+      <c r="K236" s="2"/>
+      <c r="L236" s="2"/>
+    </row>
+    <row r="237" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A237" s="3"/>
+      <c r="B237" s="3"/>
+      <c r="C237" s="3"/>
+      <c r="D237" s="3"/>
+      <c r="E237" s="3"/>
+      <c r="F237" s="2"/>
+      <c r="G237" s="2"/>
+      <c r="H237" s="2"/>
+      <c r="I237" s="7"/>
+      <c r="J237" s="4"/>
+      <c r="K237" s="2"/>
+      <c r="L237" s="2"/>
+    </row>
+    <row r="238" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A238" s="3"/>
+      <c r="B238" s="3"/>
+      <c r="C238" s="3"/>
+      <c r="D238" s="3"/>
+      <c r="E238" s="3"/>
+      <c r="F238" s="2"/>
+      <c r="G238" s="2"/>
+      <c r="H238" s="2"/>
+      <c r="I238" s="7"/>
+      <c r="J238" s="4"/>
+      <c r="K238" s="2"/>
+      <c r="L238" s="2"/>
+    </row>
+    <row r="239" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A239" s="3"/>
+      <c r="B239" s="3"/>
+      <c r="C239" s="3"/>
+      <c r="D239" s="3"/>
+      <c r="E239" s="3"/>
+      <c r="F239" s="2"/>
+      <c r="G239" s="2"/>
+      <c r="H239" s="2"/>
+      <c r="I239" s="7"/>
+      <c r="J239" s="4"/>
+      <c r="K239" s="2"/>
+      <c r="L239" s="2"/>
+    </row>
+    <row r="240" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A240" s="3"/>
+      <c r="B240" s="3"/>
+      <c r="C240" s="3"/>
+      <c r="D240" s="3"/>
+      <c r="E240" s="3"/>
+      <c r="F240" s="2"/>
+      <c r="G240" s="2"/>
+      <c r="H240" s="2"/>
+      <c r="I240" s="7"/>
+      <c r="J240" s="4"/>
+      <c r="K240" s="2"/>
+      <c r="L240" s="2"/>
+    </row>
+    <row r="241" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A241" s="3"/>
+      <c r="B241" s="3"/>
+      <c r="C241" s="3"/>
+      <c r="D241" s="3"/>
+      <c r="E241" s="3"/>
+      <c r="F241" s="2"/>
+      <c r="G241" s="2"/>
+      <c r="H241" s="2"/>
+      <c r="I241" s="7"/>
+      <c r="J241" s="4"/>
+      <c r="K241" s="2"/>
+      <c r="L241" s="2"/>
+    </row>
+    <row r="242" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A242" s="3"/>
+      <c r="B242" s="3"/>
+      <c r="C242" s="3"/>
+      <c r="D242" s="3"/>
+      <c r="E242" s="3"/>
+      <c r="F242" s="2"/>
+      <c r="G242" s="2"/>
+      <c r="H242" s="2"/>
+      <c r="I242" s="7"/>
+      <c r="J242" s="4"/>
+      <c r="K242" s="2"/>
+      <c r="L242" s="2"/>
+    </row>
+    <row r="243" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A243" s="3"/>
+      <c r="B243" s="3"/>
+      <c r="C243" s="3"/>
+      <c r="D243" s="3"/>
+      <c r="E243" s="3"/>
+      <c r="F243" s="2"/>
+      <c r="G243" s="2"/>
+      <c r="H243" s="2"/>
+      <c r="I243" s="7"/>
+      <c r="J243" s="4"/>
+      <c r="K243" s="2"/>
+      <c r="L243" s="2"/>
+    </row>
+    <row r="244" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A244" s="3"/>
+      <c r="B244" s="3"/>
+      <c r="C244" s="3"/>
+      <c r="D244" s="3"/>
+      <c r="E244" s="3"/>
+      <c r="F244" s="2"/>
+      <c r="G244" s="2"/>
+      <c r="H244" s="2"/>
+      <c r="I244" s="7"/>
+      <c r="J244" s="4"/>
+      <c r="K244" s="2"/>
+      <c r="L244" s="2"/>
+    </row>
+    <row r="245" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A245" s="3"/>
+      <c r="B245" s="3"/>
+      <c r="C245" s="3"/>
+      <c r="D245" s="3"/>
+      <c r="E245" s="3"/>
+      <c r="F245" s="2"/>
+      <c r="G245" s="2"/>
+      <c r="H245" s="2"/>
+      <c r="I245" s="7"/>
+      <c r="J245" s="4"/>
+      <c r="K245" s="2"/>
+      <c r="L245" s="2"/>
+    </row>
+    <row r="246" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A246" s="3"/>
+      <c r="B246" s="3"/>
+      <c r="C246" s="3"/>
+      <c r="D246" s="3"/>
+      <c r="E246" s="3"/>
+      <c r="F246" s="2"/>
+      <c r="G246" s="2"/>
+      <c r="H246" s="2"/>
+      <c r="I246" s="7"/>
+      <c r="J246" s="4"/>
+      <c r="K246" s="2"/>
+      <c r="L246" s="2"/>
+    </row>
+    <row r="247" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A247" s="3"/>
+      <c r="B247" s="3"/>
+      <c r="C247" s="3"/>
+      <c r="D247" s="3"/>
+      <c r="E247" s="3"/>
+      <c r="F247" s="2"/>
+      <c r="G247" s="2"/>
+      <c r="H247" s="2"/>
+      <c r="I247" s="7"/>
+      <c r="J247" s="4"/>
+      <c r="K247" s="2"/>
+      <c r="L247" s="2"/>
+    </row>
+    <row r="248" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A248" s="3"/>
+      <c r="B248" s="3"/>
+      <c r="C248" s="3"/>
+      <c r="D248" s="3"/>
+      <c r="E248" s="3"/>
+      <c r="F248" s="2"/>
+      <c r="G248" s="2"/>
+      <c r="H248" s="2"/>
+      <c r="I248" s="7"/>
+      <c r="J248" s="4"/>
+      <c r="K248" s="2"/>
+      <c r="L248" s="2"/>
+    </row>
+    <row r="249" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A249" s="3"/>
+      <c r="B249" s="3"/>
+      <c r="C249" s="3"/>
+      <c r="D249" s="3"/>
+      <c r="E249" s="3"/>
+      <c r="F249" s="2"/>
+      <c r="G249" s="2"/>
+      <c r="H249" s="2"/>
+      <c r="I249" s="7"/>
+      <c r="J249" s="4"/>
+      <c r="K249" s="2"/>
+      <c r="L249" s="2"/>
+    </row>
+    <row r="250" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A250" s="3"/>
+      <c r="B250" s="3"/>
+      <c r="C250" s="3"/>
+      <c r="D250" s="3"/>
+      <c r="E250" s="3"/>
+      <c r="F250" s="2"/>
+      <c r="G250" s="2"/>
+      <c r="H250" s="2"/>
+      <c r="I250" s="7"/>
+      <c r="J250" s="4"/>
+      <c r="K250" s="2"/>
+      <c r="L250" s="2"/>
+    </row>
+    <row r="251" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A251" s="3"/>
+      <c r="B251" s="3"/>
+      <c r="C251" s="3"/>
+      <c r="D251" s="3"/>
+      <c r="E251" s="3"/>
+      <c r="F251" s="2"/>
+      <c r="G251" s="2"/>
+      <c r="H251" s="2"/>
+      <c r="I251" s="7"/>
+      <c r="J251" s="4"/>
+      <c r="K251" s="2"/>
+      <c r="L251" s="2"/>
+    </row>
+    <row r="252" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A252" s="3"/>
+      <c r="B252" s="3"/>
+      <c r="C252" s="3"/>
+      <c r="D252" s="3"/>
+      <c r="E252" s="3"/>
+      <c r="F252" s="2"/>
+      <c r="G252" s="2"/>
+      <c r="H252" s="2"/>
+      <c r="I252" s="7"/>
+      <c r="J252" s="4"/>
+      <c r="K252" s="2"/>
+      <c r="L252" s="2"/>
+    </row>
+    <row r="253" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A253" s="3"/>
+      <c r="B253" s="3"/>
+      <c r="C253" s="3"/>
+      <c r="D253" s="3"/>
+      <c r="E253" s="3"/>
+      <c r="F253" s="2"/>
+      <c r="G253" s="2"/>
+      <c r="H253" s="2"/>
+      <c r="I253" s="7"/>
+      <c r="J253" s="4"/>
+      <c r="K253" s="2"/>
+      <c r="L253" s="2"/>
+    </row>
+    <row r="254" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A254" s="3"/>
+      <c r="B254" s="3"/>
+      <c r="C254" s="3"/>
+      <c r="D254" s="3"/>
+      <c r="E254" s="3"/>
+      <c r="F254" s="2"/>
+      <c r="G254" s="2"/>
+      <c r="H254" s="2"/>
+      <c r="I254" s="7"/>
+      <c r="J254" s="4"/>
+      <c r="K254" s="2"/>
+      <c r="L254" s="2"/>
+    </row>
+    <row r="255" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A255" s="3"/>
+      <c r="B255" s="3"/>
+      <c r="C255" s="3"/>
+      <c r="D255" s="3"/>
+      <c r="E255" s="3"/>
+      <c r="F255" s="2"/>
+      <c r="G255" s="2"/>
+      <c r="H255" s="2"/>
+      <c r="I255" s="7"/>
+      <c r="J255" s="4"/>
+      <c r="K255" s="2"/>
+      <c r="L255" s="2"/>
+    </row>
+    <row r="256" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A256" s="3"/>
+      <c r="B256" s="3"/>
+      <c r="C256" s="3"/>
+      <c r="D256" s="3"/>
+      <c r="E256" s="3"/>
+      <c r="F256" s="2"/>
+      <c r="G256" s="2"/>
+      <c r="H256" s="2"/>
+      <c r="I256" s="7"/>
+      <c r="J256" s="4"/>
+      <c r="K256" s="2"/>
+      <c r="L256" s="2"/>
+    </row>
+    <row r="257" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A257" s="3"/>
+      <c r="B257" s="3"/>
+      <c r="C257" s="3"/>
+      <c r="D257" s="3"/>
+      <c r="E257" s="3"/>
+      <c r="F257" s="2"/>
+      <c r="G257" s="2"/>
+      <c r="H257" s="2"/>
+      <c r="I257" s="7"/>
+      <c r="J257" s="4"/>
+      <c r="K257" s="2"/>
+      <c r="L257" s="2"/>
+    </row>
+    <row r="258" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A258" s="3"/>
+      <c r="B258" s="3"/>
+      <c r="C258" s="3"/>
+      <c r="D258" s="3"/>
+      <c r="E258" s="3"/>
+      <c r="F258" s="2"/>
+      <c r="G258" s="2"/>
+      <c r="H258" s="2"/>
+      <c r="I258" s="7"/>
+      <c r="J258" s="4"/>
+      <c r="K258" s="2"/>
+      <c r="L258" s="2"/>
+    </row>
+    <row r="259" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A259" s="3"/>
+      <c r="B259" s="3"/>
+      <c r="C259" s="3"/>
+      <c r="D259" s="3"/>
+      <c r="E259" s="3"/>
+      <c r="F259" s="2"/>
+      <c r="G259" s="2"/>
+      <c r="H259" s="2"/>
+      <c r="I259" s="7"/>
+      <c r="J259" s="4"/>
+      <c r="K259" s="2"/>
+      <c r="L259" s="2"/>
+    </row>
+    <row r="260" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A260" s="3"/>
+      <c r="B260" s="3"/>
+      <c r="C260" s="3"/>
+      <c r="D260" s="3"/>
+      <c r="E260" s="3"/>
+      <c r="F260" s="2"/>
+      <c r="G260" s="2"/>
+      <c r="H260" s="2"/>
+      <c r="I260" s="7"/>
+      <c r="J260" s="4"/>
+      <c r="K260" s="2"/>
+      <c r="L260" s="2"/>
+    </row>
+    <row r="261" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A261" s="3"/>
+      <c r="B261" s="3"/>
+      <c r="C261" s="3"/>
+      <c r="D261" s="3"/>
+      <c r="E261" s="3"/>
+      <c r="F261" s="2"/>
+      <c r="G261" s="2"/>
+      <c r="H261" s="2"/>
+      <c r="I261" s="7"/>
+      <c r="J261" s="4"/>
+      <c r="K261" s="2"/>
+      <c r="L261" s="2"/>
+    </row>
+    <row r="262" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A262" s="3"/>
+      <c r="B262" s="3"/>
+      <c r="C262" s="3"/>
+      <c r="D262" s="3"/>
+      <c r="E262" s="3"/>
+      <c r="F262" s="2"/>
+      <c r="G262" s="2"/>
+      <c r="H262" s="2"/>
+      <c r="I262" s="7"/>
+      <c r="J262" s="4"/>
+      <c r="K262" s="2"/>
+      <c r="L262" s="2"/>
+    </row>
+    <row r="263" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A263" s="3"/>
+      <c r="B263" s="3"/>
+      <c r="C263" s="3"/>
+      <c r="D263" s="3"/>
+      <c r="E263" s="3"/>
+      <c r="F263" s="2"/>
+      <c r="G263" s="2"/>
+      <c r="H263" s="2"/>
+      <c r="I263" s="7"/>
+      <c r="J263" s="4"/>
+      <c r="K263" s="2"/>
+      <c r="L263" s="2"/>
+    </row>
+    <row r="264" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A264" s="3"/>
+      <c r="B264" s="3"/>
+      <c r="C264" s="3"/>
+      <c r="D264" s="3"/>
+      <c r="E264" s="3"/>
+      <c r="F264" s="2"/>
+      <c r="G264" s="2"/>
+      <c r="H264" s="2"/>
+      <c r="I264" s="7"/>
+      <c r="J264" s="4"/>
+      <c r="K264" s="2"/>
+      <c r="L264" s="2"/>
+    </row>
+    <row r="265" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A265" s="3"/>
+      <c r="B265" s="3"/>
+      <c r="C265" s="3"/>
+      <c r="D265" s="3"/>
+      <c r="E265" s="3"/>
+      <c r="F265" s="2"/>
+      <c r="G265" s="2"/>
+      <c r="H265" s="2"/>
+      <c r="I265" s="7"/>
+      <c r="J265" s="4"/>
+      <c r="K265" s="2"/>
+      <c r="L265" s="2"/>
+    </row>
+    <row r="266" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A266" s="3"/>
+      <c r="B266" s="3"/>
+      <c r="C266" s="3"/>
+      <c r="D266" s="3"/>
+      <c r="E266" s="3"/>
+      <c r="F266" s="2"/>
+      <c r="G266" s="2"/>
+      <c r="H266" s="2"/>
+      <c r="I266" s="7"/>
+      <c r="J266" s="4"/>
+      <c r="K266" s="2"/>
+      <c r="L266" s="2"/>
+    </row>
+    <row r="267" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A267" s="3"/>
+      <c r="B267" s="3"/>
+      <c r="C267" s="3"/>
+      <c r="D267" s="3"/>
+      <c r="E267" s="3"/>
+      <c r="F267" s="2"/>
+      <c r="G267" s="2"/>
+      <c r="H267" s="2"/>
+      <c r="I267" s="7"/>
+      <c r="J267" s="4"/>
+      <c r="K267" s="2"/>
+      <c r="L267" s="2"/>
+    </row>
+    <row r="268" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A268" s="3"/>
+      <c r="B268" s="3"/>
+      <c r="C268" s="3"/>
+      <c r="D268" s="3"/>
+      <c r="E268" s="3"/>
+      <c r="F268" s="2"/>
+      <c r="G268" s="2"/>
+      <c r="H268" s="2"/>
+      <c r="I268" s="7"/>
+      <c r="J268" s="4"/>
+      <c r="K268" s="2"/>
+      <c r="L268" s="2"/>
+    </row>
+    <row r="269" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A269" s="3"/>
+      <c r="B269" s="3"/>
+      <c r="C269" s="3"/>
+      <c r="D269" s="3"/>
+      <c r="E269" s="3"/>
+      <c r="F269" s="2"/>
+      <c r="G269" s="2"/>
+      <c r="H269" s="2"/>
+      <c r="I269" s="7"/>
+      <c r="J269" s="4"/>
+      <c r="K269" s="2"/>
+      <c r="L269" s="2"/>
+    </row>
+    <row r="270" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A270" s="3"/>
+      <c r="B270" s="3"/>
+      <c r="C270" s="3"/>
+      <c r="D270" s="3"/>
+      <c r="E270" s="3"/>
+      <c r="F270" s="2"/>
+      <c r="G270" s="2"/>
+      <c r="H270" s="2"/>
+      <c r="I270" s="7"/>
+      <c r="J270" s="4"/>
+      <c r="K270" s="2"/>
+      <c r="L270" s="2"/>
+    </row>
+    <row r="271" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A271" s="3"/>
+      <c r="B271" s="3"/>
+      <c r="C271" s="3"/>
+      <c r="D271" s="3"/>
+      <c r="E271" s="3"/>
+      <c r="F271" s="2"/>
+      <c r="G271" s="2"/>
+      <c r="H271" s="2"/>
+      <c r="I271" s="7"/>
+      <c r="J271" s="4"/>
+      <c r="K271" s="2"/>
+      <c r="L271" s="2"/>
+    </row>
+    <row r="272" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A272" s="3"/>
+      <c r="B272" s="3"/>
+      <c r="C272" s="3"/>
+      <c r="D272" s="3"/>
+      <c r="E272" s="3"/>
+      <c r="F272" s="2"/>
+      <c r="G272" s="2"/>
+      <c r="H272" s="2"/>
+      <c r="I272" s="7"/>
+      <c r="J272" s="4"/>
+      <c r="K272" s="2"/>
+      <c r="L272" s="2"/>
+    </row>
+    <row r="273" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A273" s="3"/>
+      <c r="B273" s="3"/>
+      <c r="C273" s="3"/>
+      <c r="D273" s="3"/>
+      <c r="E273" s="3"/>
+      <c r="F273" s="2"/>
+      <c r="G273" s="2"/>
+      <c r="H273" s="2"/>
+      <c r="I273" s="7"/>
+      <c r="J273" s="4"/>
+      <c r="K273" s="2"/>
+      <c r="L273" s="2"/>
+    </row>
+    <row r="274" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A274" s="3"/>
+      <c r="B274" s="3"/>
+      <c r="C274" s="3"/>
+      <c r="D274" s="3"/>
+      <c r="E274" s="3"/>
+      <c r="F274" s="2"/>
+      <c r="G274" s="2"/>
+      <c r="H274" s="2"/>
+      <c r="I274" s="7"/>
+      <c r="J274" s="4"/>
+      <c r="K274" s="2"/>
+      <c r="L274" s="2"/>
+    </row>
+    <row r="275" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A275" s="3"/>
+      <c r="B275" s="3"/>
+      <c r="C275" s="3"/>
+      <c r="D275" s="3"/>
+      <c r="E275" s="3"/>
+      <c r="F275" s="2"/>
+      <c r="G275" s="2"/>
+      <c r="H275" s="2"/>
+      <c r="I275" s="7"/>
+      <c r="J275" s="4"/>
+      <c r="K275" s="2"/>
+      <c r="L275" s="2"/>
+    </row>
+    <row r="276" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A276" s="3"/>
+      <c r="B276" s="3"/>
+      <c r="C276" s="3"/>
+      <c r="D276" s="3"/>
+      <c r="E276" s="3"/>
+      <c r="F276" s="2"/>
+      <c r="G276" s="2"/>
+      <c r="H276" s="2"/>
+      <c r="I276" s="7"/>
+      <c r="J276" s="4"/>
+      <c r="K276" s="2"/>
+      <c r="L276" s="2"/>
+    </row>
+    <row r="277" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A277" s="3"/>
+      <c r="B277" s="3"/>
+      <c r="C277" s="3"/>
+      <c r="D277" s="3"/>
+      <c r="E277" s="3"/>
+      <c r="F277" s="2"/>
+      <c r="G277" s="2"/>
+      <c r="H277" s="2"/>
+      <c r="I277" s="7"/>
+      <c r="J277" s="4"/>
+      <c r="K277" s="2"/>
+      <c r="L277" s="2"/>
+    </row>
+    <row r="278" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A278" s="3"/>
+      <c r="B278" s="3"/>
+      <c r="C278" s="3"/>
+      <c r="D278" s="3"/>
+      <c r="E278" s="3"/>
+      <c r="F278" s="2"/>
+      <c r="G278" s="2"/>
+      <c r="H278" s="2"/>
+      <c r="I278" s="7"/>
+      <c r="J278" s="4"/>
+      <c r="K278" s="2"/>
+      <c r="L278" s="2"/>
+    </row>
+    <row r="279" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A279" s="3"/>
+      <c r="B279" s="3"/>
+      <c r="C279" s="3"/>
+      <c r="D279" s="3"/>
+      <c r="E279" s="3"/>
+      <c r="F279" s="2"/>
+      <c r="G279" s="2"/>
+      <c r="H279" s="2"/>
+      <c r="I279" s="7"/>
+      <c r="J279" s="4"/>
+      <c r="K279" s="2"/>
+      <c r="L279" s="2"/>
+    </row>
+    <row r="280" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A280" s="3"/>
+      <c r="B280" s="3"/>
+      <c r="C280" s="3"/>
+      <c r="D280" s="3"/>
+      <c r="E280" s="3"/>
+      <c r="F280" s="2"/>
+      <c r="G280" s="2"/>
+      <c r="H280" s="2"/>
+      <c r="I280" s="7"/>
+      <c r="J280" s="4"/>
+      <c r="K280" s="2"/>
+      <c r="L280" s="2"/>
+    </row>
+    <row r="281" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A281" s="3"/>
+      <c r="B281" s="3"/>
+      <c r="C281" s="3"/>
+      <c r="D281" s="3"/>
+      <c r="E281" s="3"/>
+      <c r="F281" s="2"/>
+      <c r="G281" s="2"/>
+      <c r="H281" s="2"/>
+      <c r="I281" s="7"/>
+      <c r="J281" s="4"/>
+      <c r="K281" s="2"/>
+      <c r="L281" s="2"/>
+    </row>
+    <row r="282" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A282" s="3"/>
+      <c r="B282" s="3"/>
+      <c r="C282" s="3"/>
+      <c r="D282" s="3"/>
+      <c r="E282" s="3"/>
+      <c r="F282" s="2"/>
+      <c r="G282" s="2"/>
+      <c r="H282" s="2"/>
+      <c r="I282" s="7"/>
+      <c r="J282" s="4"/>
+      <c r="K282" s="2"/>
+      <c r="L282" s="2"/>
+    </row>
+    <row r="283" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A283" s="3"/>
+      <c r="B283" s="3"/>
+      <c r="C283" s="3"/>
+      <c r="D283" s="3"/>
+      <c r="E283" s="3"/>
+      <c r="F283" s="2"/>
+      <c r="G283" s="2"/>
+      <c r="H283" s="2"/>
+      <c r="I283" s="7"/>
+      <c r="J283" s="4"/>
+      <c r="K283" s="2"/>
+      <c r="L283" s="2"/>
+    </row>
+    <row r="284" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A284" s="3"/>
+      <c r="B284" s="3"/>
+      <c r="C284" s="3"/>
+      <c r="D284" s="3"/>
+      <c r="E284" s="3"/>
+      <c r="F284" s="2"/>
+      <c r="G284" s="2"/>
+      <c r="H284" s="2"/>
+      <c r="I284" s="7"/>
+      <c r="J284" s="4"/>
+      <c r="K284" s="2"/>
+      <c r="L284" s="2"/>
+    </row>
+    <row r="285" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A285" s="3"/>
+      <c r="B285" s="3"/>
+      <c r="C285" s="3"/>
+      <c r="D285" s="3"/>
+      <c r="E285" s="3"/>
+      <c r="F285" s="2"/>
+      <c r="G285" s="2"/>
+      <c r="H285" s="2"/>
+      <c r="I285" s="7"/>
+      <c r="J285" s="4"/>
+      <c r="K285" s="2"/>
+      <c r="L285" s="2"/>
+    </row>
+    <row r="286" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A286" s="3"/>
+      <c r="B286" s="3"/>
+      <c r="C286" s="3"/>
+      <c r="D286" s="3"/>
+      <c r="E286" s="3"/>
+      <c r="F286" s="2"/>
+      <c r="G286" s="2"/>
+      <c r="H286" s="2"/>
+      <c r="I286" s="7"/>
+      <c r="J286" s="4"/>
+      <c r="K286" s="2"/>
+      <c r="L286" s="2"/>
+    </row>
+    <row r="287" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A287" s="3"/>
+      <c r="B287" s="3"/>
+      <c r="C287" s="3"/>
+      <c r="D287" s="3"/>
+      <c r="E287" s="3"/>
+      <c r="F287" s="2"/>
+      <c r="G287" s="2"/>
+      <c r="H287" s="2"/>
+      <c r="I287" s="7"/>
+      <c r="J287" s="4"/>
+      <c r="K287" s="2"/>
+      <c r="L287" s="2"/>
+    </row>
+    <row r="288" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A288" s="3"/>
+      <c r="B288" s="3"/>
+      <c r="C288" s="3"/>
+      <c r="D288" s="3"/>
+      <c r="E288" s="3"/>
+      <c r="F288" s="2"/>
+      <c r="G288" s="2"/>
+      <c r="H288" s="2"/>
+      <c r="I288" s="7"/>
+      <c r="J288" s="4"/>
+      <c r="K288" s="2"/>
+      <c r="L288" s="2"/>
+    </row>
+    <row r="289" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A289" s="3"/>
+      <c r="B289" s="3"/>
+      <c r="C289" s="3"/>
+      <c r="D289" s="3"/>
+      <c r="E289" s="3"/>
+      <c r="F289" s="2"/>
+      <c r="G289" s="2"/>
+      <c r="H289" s="2"/>
+      <c r="I289" s="7"/>
+      <c r="J289" s="4"/>
+      <c r="K289" s="2"/>
+      <c r="L289" s="2"/>
+    </row>
+    <row r="290" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A290" s="3"/>
+      <c r="B290" s="3"/>
+      <c r="C290" s="3"/>
+      <c r="D290" s="3"/>
+      <c r="E290" s="3"/>
+      <c r="F290" s="2"/>
+      <c r="G290" s="2"/>
+      <c r="H290" s="2"/>
+      <c r="I290" s="7"/>
+      <c r="J290" s="4"/>
+      <c r="K290" s="2"/>
+      <c r="L290" s="2"/>
+    </row>
+    <row r="291" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A291" s="3"/>
+      <c r="B291" s="3"/>
+      <c r="C291" s="3"/>
+      <c r="D291" s="3"/>
+      <c r="E291" s="3"/>
+      <c r="F291" s="2"/>
+      <c r="G291" s="2"/>
+      <c r="H291" s="2"/>
+      <c r="I291" s="7"/>
+      <c r="J291" s="4"/>
+      <c r="K291" s="2"/>
+      <c r="L291" s="2"/>
+    </row>
+    <row r="292" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A292" s="3"/>
+      <c r="B292" s="3"/>
+      <c r="C292" s="3"/>
+      <c r="D292" s="3"/>
+      <c r="E292" s="3"/>
+      <c r="F292" s="2"/>
+      <c r="G292" s="2"/>
+      <c r="H292" s="2"/>
+      <c r="I292" s="7"/>
+      <c r="J292" s="4"/>
+      <c r="K292" s="2"/>
+      <c r="L292" s="2"/>
+    </row>
+    <row r="293" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A293" s="3"/>
+      <c r="B293" s="3"/>
+      <c r="C293" s="3"/>
+      <c r="D293" s="3"/>
+      <c r="E293" s="3"/>
+      <c r="F293" s="2"/>
+      <c r="G293" s="2"/>
+      <c r="H293" s="2"/>
+      <c r="I293" s="7"/>
+      <c r="J293" s="4"/>
+      <c r="K293" s="2"/>
+      <c r="L293" s="2"/>
+    </row>
+    <row r="294" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A294" s="3"/>
+      <c r="B294" s="3"/>
+      <c r="C294" s="3"/>
+      <c r="D294" s="3"/>
+      <c r="E294" s="3"/>
+      <c r="F294" s="2"/>
+      <c r="G294" s="2"/>
+      <c r="H294" s="2"/>
+      <c r="I294" s="7"/>
+      <c r="J294" s="4"/>
+      <c r="K294" s="2"/>
+      <c r="L294" s="2"/>
+    </row>
+    <row r="295" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A295" s="3"/>
+      <c r="B295" s="3"/>
+      <c r="C295" s="3"/>
+      <c r="D295" s="3"/>
+      <c r="E295" s="3"/>
+      <c r="F295" s="2"/>
+      <c r="G295" s="2"/>
+      <c r="H295" s="2"/>
+      <c r="I295" s="7"/>
+      <c r="J295" s="4"/>
+      <c r="K295" s="2"/>
+      <c r="L295" s="2"/>
+    </row>
+    <row r="296" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A296" s="3"/>
+      <c r="B296" s="3"/>
+      <c r="C296" s="3"/>
+      <c r="D296" s="3"/>
+      <c r="E296" s="3"/>
+      <c r="F296" s="2"/>
+      <c r="G296" s="2"/>
+      <c r="H296" s="2"/>
+      <c r="I296" s="7"/>
+      <c r="J296" s="4"/>
+      <c r="K296" s="2"/>
+      <c r="L296" s="2"/>
+    </row>
+    <row r="297" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A297" s="3"/>
+      <c r="B297" s="3"/>
+      <c r="C297" s="3"/>
+      <c r="D297" s="3"/>
+      <c r="E297" s="3"/>
+      <c r="F297" s="2"/>
+      <c r="G297" s="2"/>
+      <c r="H297" s="2"/>
+      <c r="I297" s="7"/>
+      <c r="J297" s="4"/>
+      <c r="K297" s="2"/>
+      <c r="L297" s="2"/>
+    </row>
+    <row r="298" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A298" s="3"/>
+      <c r="B298" s="3"/>
+      <c r="C298" s="3"/>
+      <c r="D298" s="3"/>
+      <c r="E298" s="3"/>
+      <c r="F298" s="2"/>
+      <c r="G298" s="2"/>
+      <c r="H298" s="2"/>
+      <c r="I298" s="7"/>
+      <c r="J298" s="4"/>
+      <c r="K298" s="2"/>
+      <c r="L298" s="2"/>
+    </row>
+    <row r="299" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A299" s="3"/>
+      <c r="B299" s="3"/>
+      <c r="C299" s="3"/>
+      <c r="D299" s="3"/>
+      <c r="E299" s="3"/>
+      <c r="F299" s="2"/>
+      <c r="G299" s="2"/>
+      <c r="H299" s="2"/>
+      <c r="I299" s="7"/>
+      <c r="J299" s="4"/>
+      <c r="K299" s="2"/>
+      <c r="L299" s="2"/>
+    </row>
+    <row r="300" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A300" s="3"/>
+      <c r="B300" s="3"/>
+      <c r="C300" s="3"/>
+      <c r="D300" s="3"/>
+      <c r="E300" s="3"/>
+      <c r="F300" s="2"/>
+      <c r="G300" s="2"/>
+      <c r="H300" s="2"/>
+      <c r="I300" s="7"/>
+      <c r="J300" s="4"/>
+      <c r="K300" s="2"/>
+      <c r="L300" s="2"/>
+    </row>
+    <row r="301" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A301" s="3"/>
+      <c r="B301" s="3"/>
+      <c r="C301" s="3"/>
+      <c r="D301" s="3"/>
+      <c r="E301" s="3"/>
+      <c r="F301" s="2"/>
+      <c r="G301" s="2"/>
+      <c r="H301" s="2"/>
+      <c r="I301" s="7"/>
+      <c r="J301" s="4"/>
+      <c r="K301" s="2"/>
+      <c r="L301" s="2"/>
+    </row>
+    <row r="302" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A302" s="3"/>
+      <c r="B302" s="3"/>
+      <c r="C302" s="3"/>
+      <c r="D302" s="3"/>
+      <c r="E302" s="3"/>
+      <c r="F302" s="2"/>
+      <c r="G302" s="2"/>
+      <c r="H302" s="2"/>
+      <c r="I302" s="7"/>
+      <c r="J302" s="4"/>
+      <c r="K302" s="2"/>
+      <c r="L302" s="2"/>
+    </row>
+    <row r="303" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A303" s="3"/>
+      <c r="B303" s="3"/>
+      <c r="C303" s="3"/>
+      <c r="D303" s="3"/>
+      <c r="E303" s="3"/>
+      <c r="F303" s="2"/>
+      <c r="G303" s="2"/>
+      <c r="H303" s="2"/>
+      <c r="I303" s="7"/>
+      <c r="J303" s="4"/>
+      <c r="K303" s="2"/>
+      <c r="L303" s="2"/>
+    </row>
+    <row r="304" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A304" s="3"/>
+      <c r="B304" s="3"/>
+      <c r="C304" s="3"/>
+      <c r="D304" s="3"/>
+      <c r="E304" s="3"/>
+      <c r="F304" s="2"/>
+      <c r="G304" s="2"/>
+      <c r="H304" s="2"/>
+      <c r="I304" s="7"/>
+      <c r="J304" s="4"/>
+      <c r="K304" s="2"/>
+      <c r="L304" s="2"/>
+    </row>
+    <row r="305" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A305" s="3"/>
+      <c r="B305" s="3"/>
+      <c r="C305" s="3"/>
+      <c r="D305" s="3"/>
+      <c r="E305" s="3"/>
+      <c r="F305" s="2"/>
+      <c r="G305" s="2"/>
+      <c r="H305" s="2"/>
+      <c r="I305" s="7"/>
+      <c r="J305" s="4"/>
+      <c r="K305" s="2"/>
+      <c r="L305" s="2"/>
+    </row>
+    <row r="306" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A306" s="3"/>
+      <c r="B306" s="3"/>
+      <c r="C306" s="3"/>
+      <c r="D306" s="3"/>
+      <c r="E306" s="3"/>
+      <c r="F306" s="2"/>
+      <c r="G306" s="2"/>
+      <c r="H306" s="2"/>
+      <c r="I306" s="7"/>
+      <c r="J306" s="4"/>
+      <c r="K306" s="2"/>
+      <c r="L306" s="2"/>
+    </row>
+    <row r="307" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A307" s="3"/>
+      <c r="B307" s="3"/>
+      <c r="C307" s="3"/>
+      <c r="D307" s="3"/>
+      <c r="E307" s="3"/>
+      <c r="F307" s="2"/>
+      <c r="G307" s="2"/>
+      <c r="H307" s="2"/>
+      <c r="I307" s="7"/>
+      <c r="J307" s="4"/>
+      <c r="K307" s="2"/>
+      <c r="L307" s="2"/>
+    </row>
+    <row r="308" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A308" s="3"/>
+      <c r="B308" s="3"/>
+      <c r="C308" s="3"/>
+      <c r="D308" s="3"/>
+      <c r="E308" s="3"/>
+      <c r="F308" s="2"/>
+      <c r="G308" s="2"/>
+      <c r="H308" s="2"/>
+      <c r="I308" s="7"/>
+      <c r="J308" s="4"/>
+      <c r="K308" s="2"/>
+      <c r="L308" s="2"/>
+    </row>
+    <row r="309" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A309" s="3"/>
+      <c r="B309" s="3"/>
+      <c r="C309" s="3"/>
+      <c r="D309" s="3"/>
+      <c r="E309" s="3"/>
+      <c r="F309" s="2"/>
+      <c r="G309" s="2"/>
+      <c r="H309" s="2"/>
+      <c r="I309" s="7"/>
+      <c r="J309" s="4"/>
+      <c r="K309" s="2"/>
+      <c r="L309" s="2"/>
+    </row>
+    <row r="310" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A310" s="3"/>
+      <c r="B310" s="3"/>
+      <c r="C310" s="3"/>
+      <c r="D310" s="3"/>
+      <c r="E310" s="3"/>
+      <c r="F310" s="2"/>
+      <c r="G310" s="2"/>
+      <c r="H310" s="2"/>
+      <c r="I310" s="7"/>
+      <c r="J310" s="4"/>
+      <c r="K310" s="2"/>
+      <c r="L310" s="2"/>
+    </row>
+    <row r="311" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A311" s="3"/>
+      <c r="B311" s="3"/>
+      <c r="C311" s="3"/>
+      <c r="D311" s="3"/>
+      <c r="E311" s="3"/>
+      <c r="F311" s="2"/>
+      <c r="G311" s="2"/>
+      <c r="H311" s="2"/>
+      <c r="I311" s="7"/>
+      <c r="J311" s="4"/>
+      <c r="K311" s="2"/>
+      <c r="L311" s="2"/>
+    </row>
+    <row r="312" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A312" s="3"/>
+      <c r="B312" s="3"/>
+      <c r="C312" s="3"/>
+      <c r="D312" s="3"/>
+      <c r="E312" s="3"/>
+      <c r="F312" s="2"/>
+      <c r="G312" s="2"/>
+      <c r="H312" s="2"/>
+      <c r="I312" s="7"/>
+      <c r="J312" s="4"/>
+      <c r="K312" s="2"/>
+      <c r="L312" s="2"/>
+    </row>
+    <row r="313" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A313" s="3"/>
+      <c r="B313" s="3"/>
+      <c r="C313" s="3"/>
+      <c r="D313" s="3"/>
+      <c r="E313" s="3"/>
+      <c r="F313" s="2"/>
+      <c r="G313" s="2"/>
+      <c r="H313" s="2"/>
+      <c r="I313" s="7"/>
+      <c r="J313" s="4"/>
+      <c r="K313" s="2"/>
+      <c r="L313" s="2"/>
+    </row>
+    <row r="314" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A314" s="3"/>
+      <c r="B314" s="3"/>
+      <c r="C314" s="3"/>
+      <c r="D314" s="3"/>
+      <c r="E314" s="3"/>
+      <c r="F314" s="2"/>
+      <c r="G314" s="2"/>
+      <c r="H314" s="2"/>
+      <c r="I314" s="7"/>
+      <c r="J314" s="4"/>
+      <c r="K314" s="2"/>
+      <c r="L314" s="2"/>
+    </row>
+    <row r="315" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A315" s="3"/>
+      <c r="B315" s="3"/>
+      <c r="C315" s="3"/>
+      <c r="D315" s="3"/>
+      <c r="E315" s="3"/>
+      <c r="F315" s="2"/>
+      <c r="G315" s="2"/>
+      <c r="H315" s="2"/>
+      <c r="I315" s="7"/>
+      <c r="J315" s="4"/>
+      <c r="K315" s="2"/>
+      <c r="L315" s="2"/>
+    </row>
+    <row r="316" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A316" s="3"/>
+      <c r="B316" s="3"/>
+      <c r="C316" s="3"/>
+      <c r="D316" s="3"/>
+      <c r="E316" s="3"/>
+      <c r="F316" s="2"/>
+      <c r="G316" s="2"/>
+      <c r="H316" s="2"/>
+      <c r="I316" s="7"/>
+      <c r="J316" s="4"/>
+      <c r="K316" s="2"/>
+      <c r="L316" s="2"/>
+    </row>
+    <row r="317" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A317" s="3"/>
+      <c r="B317" s="3"/>
+      <c r="C317" s="3"/>
+      <c r="D317" s="3"/>
+      <c r="E317" s="3"/>
+      <c r="F317" s="2"/>
+      <c r="G317" s="2"/>
+      <c r="H317" s="2"/>
+      <c r="I317" s="7"/>
+      <c r="J317" s="4"/>
+      <c r="K317" s="2"/>
+      <c r="L317" s="2"/>
+    </row>
+    <row r="318" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A318" s="3"/>
+      <c r="B318" s="3"/>
+      <c r="C318" s="3"/>
+      <c r="D318" s="3"/>
+      <c r="E318" s="3"/>
+      <c r="F318" s="2"/>
+      <c r="G318" s="2"/>
+      <c r="H318" s="2"/>
+      <c r="I318" s="7"/>
+      <c r="J318" s="4"/>
+      <c r="K318" s="2"/>
+      <c r="L318" s="2"/>
+    </row>
+    <row r="319" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A319" s="3"/>
+      <c r="B319" s="3"/>
+      <c r="C319" s="3"/>
+      <c r="D319" s="3"/>
+      <c r="E319" s="3"/>
+      <c r="F319" s="2"/>
+      <c r="G319" s="2"/>
+      <c r="H319" s="2"/>
+      <c r="I319" s="7"/>
+      <c r="J319" s="4"/>
+      <c r="K319" s="2"/>
+      <c r="L319" s="2"/>
+    </row>
+    <row r="320" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A320" s="3"/>
+      <c r="B320" s="3"/>
+      <c r="C320" s="3"/>
+      <c r="D320" s="3"/>
+      <c r="E320" s="3"/>
+      <c r="F320" s="2"/>
+      <c r="G320" s="2"/>
+      <c r="H320" s="2"/>
+      <c r="I320" s="7"/>
+      <c r="J320" s="4"/>
+      <c r="K320" s="2"/>
+      <c r="L320" s="2"/>
+    </row>
+    <row r="321" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A321" s="3"/>
+      <c r="B321" s="3"/>
+      <c r="C321" s="3"/>
+      <c r="D321" s="3"/>
+      <c r="E321" s="3"/>
+      <c r="F321" s="2"/>
+      <c r="G321" s="2"/>
+      <c r="H321" s="2"/>
+      <c r="I321" s="7"/>
+      <c r="J321" s="4"/>
+      <c r="K321" s="2"/>
+      <c r="L321" s="2"/>
+    </row>
+    <row r="322" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A322" s="3"/>
+      <c r="B322" s="3"/>
+      <c r="C322" s="3"/>
+      <c r="D322" s="3"/>
+      <c r="E322" s="3"/>
+      <c r="F322" s="2"/>
+      <c r="G322" s="2"/>
+      <c r="H322" s="2"/>
+      <c r="I322" s="7"/>
+      <c r="J322" s="4"/>
+      <c r="K322" s="2"/>
+      <c r="L322" s="2"/>
+    </row>
+    <row r="323" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A323" s="3"/>
+      <c r="B323" s="3"/>
+      <c r="C323" s="3"/>
+      <c r="D323" s="3"/>
+      <c r="E323" s="3"/>
+      <c r="F323" s="2"/>
+      <c r="G323" s="2"/>
+      <c r="H323" s="2"/>
+      <c r="I323" s="7"/>
+      <c r="J323" s="4"/>
+      <c r="K323" s="2"/>
+      <c r="L323" s="2"/>
+    </row>
+    <row r="324" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A324" s="3"/>
+      <c r="B324" s="3"/>
+      <c r="C324" s="3"/>
+      <c r="D324" s="3"/>
+      <c r="E324" s="3"/>
+      <c r="F324" s="2"/>
+      <c r="G324" s="2"/>
+      <c r="H324" s="2"/>
+      <c r="I324" s="7"/>
+      <c r="J324" s="4"/>
+      <c r="K324" s="2"/>
+      <c r="L324" s="2"/>
+    </row>
+    <row r="325" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A325" s="3"/>
+      <c r="B325" s="3"/>
+      <c r="C325" s="3"/>
+      <c r="D325" s="3"/>
+      <c r="E325" s="3"/>
+      <c r="F325" s="2"/>
+      <c r="G325" s="2"/>
+      <c r="H325" s="2"/>
+      <c r="I325" s="7"/>
+      <c r="J325" s="4"/>
+      <c r="K325" s="2"/>
+      <c r="L325" s="2"/>
+    </row>
+    <row r="326" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A326" s="3"/>
+      <c r="B326" s="3"/>
+      <c r="C326" s="3"/>
+      <c r="D326" s="3"/>
+      <c r="E326" s="3"/>
+      <c r="F326" s="2"/>
+      <c r="G326" s="2"/>
+      <c r="H326" s="2"/>
+      <c r="I326" s="7"/>
+      <c r="J326" s="4"/>
+      <c r="K326" s="2"/>
+      <c r="L326" s="2"/>
+    </row>
+    <row r="327" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A327" s="3"/>
+      <c r="B327" s="3"/>
+      <c r="C327" s="3"/>
+      <c r="D327" s="3"/>
+      <c r="E327" s="3"/>
+      <c r="F327" s="2"/>
+      <c r="G327" s="2"/>
+      <c r="H327" s="2"/>
+      <c r="I327" s="7"/>
+      <c r="J327" s="4"/>
+      <c r="K327" s="2"/>
+      <c r="L327" s="2"/>
+    </row>
+    <row r="328" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A328" s="3"/>
+      <c r="B328" s="3"/>
+      <c r="C328" s="3"/>
+      <c r="D328" s="3"/>
+      <c r="E328" s="3"/>
+      <c r="F328" s="2"/>
+      <c r="G328" s="2"/>
+      <c r="H328" s="2"/>
+      <c r="I328" s="7"/>
+      <c r="J328" s="4"/>
+      <c r="K328" s="2"/>
+      <c r="L328" s="2"/>
+    </row>
+    <row r="329" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A329" s="3"/>
+      <c r="B329" s="3"/>
+      <c r="C329" s="3"/>
+      <c r="D329" s="3"/>
+      <c r="E329" s="3"/>
+      <c r="F329" s="2"/>
+      <c r="G329" s="2"/>
+      <c r="H329" s="2"/>
+      <c r="I329" s="7"/>
+      <c r="J329" s="4"/>
+      <c r="K329" s="2"/>
+      <c r="L329" s="2"/>
+    </row>
+    <row r="330" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A330" s="3"/>
+      <c r="B330" s="3"/>
+      <c r="C330" s="3"/>
+      <c r="D330" s="3"/>
+      <c r="E330" s="3"/>
+      <c r="F330" s="2"/>
+      <c r="G330" s="2"/>
+      <c r="H330" s="2"/>
+      <c r="I330" s="7"/>
+      <c r="J330" s="4"/>
+      <c r="K330" s="2"/>
+      <c r="L330" s="2"/>
+    </row>
+    <row r="331" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A331" s="3"/>
+      <c r="B331" s="3"/>
+      <c r="C331" s="3"/>
+      <c r="D331" s="3"/>
+      <c r="E331" s="3"/>
+      <c r="F331" s="2"/>
+      <c r="G331" s="2"/>
+      <c r="H331" s="2"/>
+      <c r="I331" s="7"/>
+      <c r="J331" s="4"/>
+      <c r="K331" s="2"/>
+      <c r="L331" s="2"/>
+    </row>
+    <row r="332" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A332" s="3"/>
+      <c r="B332" s="3"/>
+      <c r="C332" s="3"/>
+      <c r="D332" s="3"/>
+      <c r="E332" s="3"/>
+      <c r="F332" s="2"/>
+      <c r="G332" s="2"/>
+      <c r="H332" s="2"/>
+      <c r="I332" s="7"/>
+      <c r="J332" s="4"/>
+      <c r="K332" s="2"/>
+      <c r="L332" s="2"/>
+    </row>
+    <row r="333" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A333" s="3"/>
+      <c r="B333" s="3"/>
+      <c r="C333" s="3"/>
+      <c r="D333" s="3"/>
+      <c r="E333" s="3"/>
+      <c r="F333" s="2"/>
+      <c r="G333" s="2"/>
+      <c r="H333" s="2"/>
+      <c r="I333" s="7"/>
+      <c r="J333" s="4"/>
+      <c r="K333" s="2"/>
+      <c r="L333" s="2"/>
+    </row>
+    <row r="334" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A334" s="3"/>
+      <c r="B334" s="3"/>
+      <c r="C334" s="3"/>
+      <c r="D334" s="3"/>
+      <c r="E334" s="3"/>
+      <c r="F334" s="2"/>
+      <c r="G334" s="2"/>
+      <c r="H334" s="2"/>
+      <c r="I334" s="7"/>
+      <c r="J334" s="4"/>
+      <c r="K334" s="2"/>
+      <c r="L334" s="2"/>
+    </row>
+    <row r="335" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A335" s="3"/>
+      <c r="B335" s="3"/>
+      <c r="C335" s="3"/>
+      <c r="D335" s="3"/>
+      <c r="E335" s="3"/>
+      <c r="F335" s="2"/>
+      <c r="G335" s="2"/>
+      <c r="H335" s="2"/>
+      <c r="I335" s="7"/>
+      <c r="J335" s="4"/>
+      <c r="K335" s="2"/>
+      <c r="L335" s="2"/>
+    </row>
+    <row r="336" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A336" s="3"/>
+      <c r="B336" s="3"/>
+      <c r="C336" s="3"/>
+      <c r="D336" s="3"/>
+      <c r="E336" s="3"/>
+      <c r="F336" s="2"/>
+      <c r="G336" s="2"/>
+      <c r="H336" s="2"/>
+      <c r="I336" s="7"/>
+      <c r="J336" s="4"/>
+      <c r="K336" s="2"/>
+      <c r="L336" s="2"/>
+    </row>
+    <row r="337" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A337" s="3"/>
+      <c r="B337" s="3"/>
+      <c r="C337" s="3"/>
+      <c r="D337" s="3"/>
+      <c r="E337" s="3"/>
+      <c r="F337" s="2"/>
+      <c r="G337" s="2"/>
+      <c r="H337" s="2"/>
+      <c r="I337" s="7"/>
+      <c r="J337" s="4"/>
+      <c r="K337" s="2"/>
+      <c r="L337" s="2"/>
+    </row>
+    <row r="338" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A338" s="3"/>
+      <c r="B338" s="3"/>
+      <c r="C338" s="3"/>
+      <c r="D338" s="3"/>
+      <c r="E338" s="3"/>
+      <c r="F338" s="2"/>
+      <c r="G338" s="2"/>
+      <c r="H338" s="2"/>
+      <c r="I338" s="7"/>
+      <c r="J338" s="4"/>
+      <c r="K338" s="2"/>
+      <c r="L338" s="2"/>
+    </row>
+    <row r="339" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A339" s="3"/>
+      <c r="B339" s="3"/>
+      <c r="C339" s="3"/>
+      <c r="D339" s="3"/>
+      <c r="E339" s="3"/>
+      <c r="F339" s="2"/>
+      <c r="G339" s="2"/>
+      <c r="H339" s="2"/>
+      <c r="I339" s="7"/>
+      <c r="J339" s="4"/>
+      <c r="K339" s="2"/>
+      <c r="L339" s="2"/>
+    </row>
+    <row r="340" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A340" s="3"/>
+      <c r="B340" s="3"/>
+      <c r="C340" s="3"/>
+      <c r="D340" s="3"/>
+      <c r="E340" s="3"/>
+      <c r="F340" s="2"/>
+      <c r="G340" s="2"/>
+      <c r="H340" s="2"/>
+      <c r="I340" s="7"/>
+      <c r="J340" s="4"/>
+      <c r="K340" s="2"/>
+      <c r="L340" s="2"/>
+    </row>
+    <row r="341" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A341" s="3"/>
+      <c r="B341" s="3"/>
+      <c r="C341" s="3"/>
+      <c r="D341" s="3"/>
+      <c r="E341" s="3"/>
+      <c r="F341" s="2"/>
+      <c r="G341" s="2"/>
+      <c r="H341" s="2"/>
+      <c r="I341" s="7"/>
+      <c r="J341" s="4"/>
+      <c r="K341" s="2"/>
+      <c r="L341" s="2"/>
+    </row>
+    <row r="342" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A342" s="3"/>
+      <c r="B342" s="3"/>
+      <c r="C342" s="3"/>
+      <c r="D342" s="3"/>
+      <c r="E342" s="3"/>
+      <c r="F342" s="2"/>
+      <c r="G342" s="2"/>
+      <c r="H342" s="2"/>
+      <c r="I342" s="7"/>
+      <c r="J342" s="4"/>
+      <c r="K342" s="2"/>
+      <c r="L342" s="2"/>
+    </row>
+    <row r="343" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A343" s="3"/>
+      <c r="B343" s="3"/>
+      <c r="C343" s="3"/>
+      <c r="D343" s="3"/>
+      <c r="E343" s="3"/>
+      <c r="F343" s="2"/>
+      <c r="G343" s="2"/>
+      <c r="H343" s="2"/>
+      <c r="I343" s="7"/>
+      <c r="J343" s="4"/>
+      <c r="K343" s="2"/>
+      <c r="L343" s="2"/>
+    </row>
+    <row r="344" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A344" s="3"/>
+      <c r="B344" s="3"/>
+      <c r="C344" s="3"/>
+      <c r="D344" s="3"/>
+      <c r="E344" s="3"/>
+      <c r="F344" s="2"/>
+      <c r="G344" s="2"/>
+      <c r="H344" s="2"/>
+      <c r="I344" s="7"/>
+      <c r="J344" s="4"/>
+      <c r="K344" s="2"/>
+      <c r="L344" s="2"/>
+    </row>
+    <row r="345" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A345" s="3"/>
+      <c r="B345" s="3"/>
+      <c r="C345" s="3"/>
+      <c r="D345" s="3"/>
+      <c r="E345" s="3"/>
+      <c r="F345" s="2"/>
+      <c r="G345" s="2"/>
+      <c r="H345" s="2"/>
+      <c r="I345" s="7"/>
+      <c r="J345" s="4"/>
+      <c r="K345" s="2"/>
+      <c r="L345" s="2"/>
+    </row>
+    <row r="346" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A346" s="3"/>
+      <c r="B346" s="3"/>
+      <c r="C346" s="3"/>
+      <c r="D346" s="3"/>
+      <c r="E346" s="3"/>
+      <c r="F346" s="2"/>
+      <c r="G346" s="2"/>
+      <c r="H346" s="2"/>
+      <c r="I346" s="7"/>
+      <c r="J346" s="4"/>
+      <c r="K346" s="2"/>
+      <c r="L346" s="2"/>
+    </row>
+    <row r="347" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A347" s="3"/>
+      <c r="B347" s="3"/>
+      <c r="C347" s="3"/>
+      <c r="D347" s="3"/>
+      <c r="E347" s="3"/>
+      <c r="F347" s="2"/>
+      <c r="G347" s="2"/>
+      <c r="H347" s="2"/>
+      <c r="I347" s="7"/>
+      <c r="J347" s="4"/>
+      <c r="K347" s="2"/>
+      <c r="L347" s="2"/>
+    </row>
+    <row r="348" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A348" s="3"/>
+      <c r="B348" s="3"/>
+      <c r="C348" s="3"/>
+      <c r="D348" s="3"/>
+      <c r="E348" s="3"/>
+      <c r="F348" s="2"/>
+      <c r="G348" s="2"/>
+      <c r="H348" s="2"/>
+      <c r="I348" s="7"/>
+      <c r="J348" s="4"/>
+      <c r="K348" s="2"/>
+      <c r="L348" s="2"/>
+    </row>
+    <row r="349" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A349" s="3"/>
+      <c r="B349" s="3"/>
+      <c r="C349" s="3"/>
+      <c r="D349" s="3"/>
+      <c r="E349" s="3"/>
+      <c r="F349" s="2"/>
+      <c r="G349" s="2"/>
+      <c r="H349" s="2"/>
+      <c r="I349" s="7"/>
+      <c r="J349" s="4"/>
+      <c r="K349" s="2"/>
+      <c r="L349" s="2"/>
+    </row>
+    <row r="350" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A350" s="3"/>
+      <c r="B350" s="3"/>
+      <c r="C350" s="3"/>
+      <c r="D350" s="3"/>
+      <c r="E350" s="3"/>
+      <c r="F350" s="2"/>
+      <c r="G350" s="2"/>
+      <c r="H350" s="2"/>
+      <c r="I350" s="7"/>
+      <c r="J350" s="4"/>
+      <c r="K350" s="2"/>
+      <c r="L350" s="2"/>
+    </row>
+    <row r="351" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A351" s="3"/>
+      <c r="B351" s="3"/>
+      <c r="C351" s="3"/>
+      <c r="D351" s="3"/>
+      <c r="E351" s="3"/>
+      <c r="F351" s="2"/>
+      <c r="G351" s="2"/>
+      <c r="H351" s="2"/>
+      <c r="I351" s="7"/>
+      <c r="J351" s="4"/>
+      <c r="K351" s="2"/>
+      <c r="L351" s="2"/>
+    </row>
+    <row r="352" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A352" s="3"/>
+      <c r="B352" s="3"/>
+      <c r="C352" s="3"/>
+      <c r="D352" s="3"/>
+      <c r="E352" s="3"/>
+      <c r="F352" s="2"/>
+      <c r="G352" s="2"/>
+      <c r="H352" s="2"/>
+      <c r="I352" s="7"/>
+      <c r="J352" s="4"/>
+      <c r="K352" s="2"/>
+      <c r="L352" s="2"/>
+    </row>
+    <row r="353" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A353" s="3"/>
+      <c r="B353" s="3"/>
+      <c r="C353" s="3"/>
+      <c r="D353" s="3"/>
+      <c r="E353" s="3"/>
+      <c r="F353" s="2"/>
+      <c r="G353" s="2"/>
+      <c r="H353" s="2"/>
+      <c r="I353" s="7"/>
+      <c r="J353" s="4"/>
+      <c r="K353" s="2"/>
+      <c r="L353" s="2"/>
+    </row>
+    <row r="354" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A354" s="3"/>
+      <c r="B354" s="3"/>
+      <c r="C354" s="3"/>
+      <c r="D354" s="3"/>
+      <c r="E354" s="3"/>
+      <c r="F354" s="2"/>
+      <c r="G354" s="2"/>
+      <c r="H354" s="2"/>
+      <c r="I354" s="7"/>
+      <c r="J354" s="4"/>
+      <c r="K354" s="2"/>
+      <c r="L354" s="2"/>
+    </row>
+    <row r="355" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A355" s="3"/>
+      <c r="B355" s="3"/>
+      <c r="C355" s="3"/>
+      <c r="D355" s="3"/>
+      <c r="E355" s="3"/>
+      <c r="F355" s="2"/>
+      <c r="G355" s="2"/>
+      <c r="H355" s="2"/>
+      <c r="I355" s="7"/>
+      <c r="J355" s="4"/>
+      <c r="K355" s="2"/>
+      <c r="L355" s="2"/>
+    </row>
+    <row r="356" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A356" s="3"/>
+      <c r="B356" s="3"/>
+      <c r="C356" s="3"/>
+      <c r="D356" s="3"/>
+      <c r="E356" s="3"/>
+      <c r="F356" s="2"/>
+      <c r="G356" s="2"/>
+      <c r="H356" s="2"/>
+      <c r="I356" s="7"/>
+      <c r="J356" s="4"/>
+      <c r="K356" s="2"/>
+      <c r="L356" s="2"/>
+    </row>
+    <row r="357" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A357" s="3"/>
+      <c r="B357" s="3"/>
+      <c r="C357" s="3"/>
+      <c r="D357" s="3"/>
+      <c r="E357" s="3"/>
+      <c r="F357" s="2"/>
+      <c r="G357" s="2"/>
+      <c r="H357" s="2"/>
+      <c r="I357" s="7"/>
+      <c r="J357" s="4"/>
+      <c r="K357" s="2"/>
+      <c r="L357" s="2"/>
+    </row>
+    <row r="358" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A358" s="3"/>
+      <c r="B358" s="3"/>
+      <c r="C358" s="3"/>
+      <c r="D358" s="3"/>
+      <c r="E358" s="3"/>
+      <c r="F358" s="2"/>
+      <c r="G358" s="2"/>
+      <c r="H358" s="2"/>
+      <c r="I358" s="7"/>
+      <c r="J358" s="4"/>
+      <c r="K358" s="2"/>
+      <c r="L358" s="2"/>
+    </row>
+    <row r="359" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A359" s="3"/>
+      <c r="B359" s="3"/>
+      <c r="C359" s="3"/>
+      <c r="D359" s="3"/>
+      <c r="E359" s="3"/>
+      <c r="F359" s="2"/>
+      <c r="G359" s="2"/>
+      <c r="H359" s="2"/>
+      <c r="I359" s="7"/>
+      <c r="J359" s="4"/>
+      <c r="K359" s="2"/>
+      <c r="L359" s="2"/>
+    </row>
+    <row r="360" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A360" s="3"/>
+      <c r="B360" s="3"/>
+      <c r="C360" s="3"/>
+      <c r="D360" s="3"/>
+      <c r="E360" s="3"/>
+      <c r="F360" s="2"/>
+      <c r="G360" s="2"/>
+      <c r="H360" s="2"/>
+      <c r="I360" s="7"/>
+      <c r="J360" s="4"/>
+      <c r="K360" s="2"/>
+      <c r="L360" s="2"/>
+    </row>
+    <row r="361" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A361" s="3"/>
+      <c r="B361" s="3"/>
+      <c r="C361" s="3"/>
+      <c r="D361" s="3"/>
+      <c r="E361" s="3"/>
+      <c r="F361" s="2"/>
+      <c r="G361" s="2"/>
+      <c r="H361" s="2"/>
+      <c r="I361" s="7"/>
+      <c r="J361" s="4"/>
+      <c r="K361" s="2"/>
+      <c r="L361" s="2"/>
+    </row>
+    <row r="362" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A362" s="3"/>
+      <c r="B362" s="3"/>
+      <c r="C362" s="3"/>
+      <c r="D362" s="3"/>
+      <c r="E362" s="3"/>
+      <c r="F362" s="2"/>
+      <c r="G362" s="2"/>
+      <c r="H362" s="2"/>
+      <c r="I362" s="7"/>
+      <c r="J362" s="4"/>
+      <c r="K362" s="2"/>
+      <c r="L362" s="2"/>
+    </row>
+    <row r="363" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A363" s="3"/>
+      <c r="B363" s="3"/>
+      <c r="C363" s="3"/>
+      <c r="D363" s="3"/>
+      <c r="E363" s="3"/>
+      <c r="F363" s="2"/>
+      <c r="G363" s="2"/>
+      <c r="H363" s="2"/>
+      <c r="I363" s="7"/>
+      <c r="J363" s="4"/>
+      <c r="K363" s="2"/>
+      <c r="L363" s="2"/>
+    </row>
+    <row r="364" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A364" s="3"/>
+      <c r="B364" s="3"/>
+      <c r="C364" s="3"/>
+      <c r="D364" s="3"/>
+      <c r="E364" s="3"/>
+      <c r="F364" s="2"/>
+      <c r="G364" s="2"/>
+      <c r="H364" s="2"/>
+      <c r="I364" s="7"/>
+      <c r="J364" s="4"/>
+      <c r="K364" s="2"/>
+      <c r="L364" s="2"/>
+    </row>
+    <row r="365" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A365" s="3"/>
+      <c r="B365" s="3"/>
+      <c r="C365" s="3"/>
+      <c r="D365" s="3"/>
+      <c r="E365" s="3"/>
+      <c r="F365" s="2"/>
+      <c r="G365" s="2"/>
+      <c r="H365" s="2"/>
+      <c r="I365" s="7"/>
+      <c r="J365" s="4"/>
+      <c r="K365" s="2"/>
+      <c r="L365" s="2"/>
+    </row>
+    <row r="366" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A366" s="3"/>
+      <c r="B366" s="3"/>
+      <c r="C366" s="3"/>
+      <c r="D366" s="3"/>
+      <c r="E366" s="3"/>
+      <c r="F366" s="2"/>
+      <c r="G366" s="2"/>
+      <c r="H366" s="2"/>
+      <c r="I366" s="7"/>
+      <c r="J366" s="4"/>
+      <c r="K366" s="2"/>
+      <c r="L366" s="2"/>
+    </row>
+    <row r="367" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A367" s="3"/>
+      <c r="B367" s="3"/>
+      <c r="C367" s="3"/>
+      <c r="D367" s="3"/>
+      <c r="E367" s="3"/>
+      <c r="F367" s="2"/>
+      <c r="G367" s="2"/>
+      <c r="H367" s="2"/>
+      <c r="I367" s="7"/>
+      <c r="J367" s="4"/>
+      <c r="K367" s="2"/>
+      <c r="L367" s="2"/>
+    </row>
+    <row r="368" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A368" s="3"/>
+      <c r="B368" s="3"/>
+      <c r="C368" s="3"/>
+      <c r="D368" s="3"/>
+      <c r="E368" s="3"/>
+      <c r="F368" s="2"/>
+      <c r="G368" s="2"/>
+      <c r="H368" s="2"/>
+      <c r="I368" s="7"/>
+      <c r="J368" s="4"/>
+      <c r="K368" s="2"/>
+      <c r="L368" s="2"/>
+    </row>
+    <row r="369" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A369" s="3"/>
+      <c r="B369" s="3"/>
+      <c r="C369" s="3"/>
+      <c r="D369" s="3"/>
+      <c r="E369" s="3"/>
+      <c r="F369" s="2"/>
+      <c r="G369" s="2"/>
+      <c r="H369" s="2"/>
+      <c r="I369" s="7"/>
+      <c r="J369" s="4"/>
+      <c r="K369" s="2"/>
+      <c r="L369" s="2"/>
+    </row>
+    <row r="370" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A370" s="3"/>
+      <c r="B370" s="3"/>
+      <c r="C370" s="3"/>
+      <c r="D370" s="3"/>
+      <c r="E370" s="3"/>
+      <c r="F370" s="2"/>
+      <c r="G370" s="2"/>
+      <c r="H370" s="2"/>
+      <c r="I370" s="7"/>
+      <c r="J370" s="4"/>
+      <c r="K370" s="2"/>
+      <c r="L370" s="2"/>
+    </row>
+    <row r="371" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A371" s="3"/>
+      <c r="B371" s="3"/>
+      <c r="C371" s="3"/>
+      <c r="D371" s="3"/>
+      <c r="E371" s="3"/>
+      <c r="F371" s="2"/>
+      <c r="G371" s="2"/>
+      <c r="H371" s="2"/>
+      <c r="I371" s="7"/>
+      <c r="J371" s="4"/>
+      <c r="K371" s="2"/>
+      <c r="L371" s="2"/>
+    </row>
+    <row r="372" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A372" s="3"/>
+      <c r="B372" s="3"/>
+      <c r="C372" s="3"/>
+      <c r="D372" s="3"/>
+      <c r="E372" s="3"/>
+      <c r="F372" s="2"/>
+      <c r="G372" s="2"/>
+      <c r="H372" s="2"/>
+      <c r="I372" s="7"/>
+      <c r="J372" s="4"/>
+      <c r="K372" s="2"/>
+      <c r="L372" s="2"/>
+    </row>
+    <row r="373" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A373" s="3"/>
+      <c r="B373" s="3"/>
+      <c r="C373" s="3"/>
+      <c r="D373" s="3"/>
+      <c r="E373" s="3"/>
+      <c r="F373" s="2"/>
+      <c r="G373" s="2"/>
+      <c r="H373" s="2"/>
+      <c r="I373" s="7"/>
+      <c r="J373" s="4"/>
+      <c r="K373" s="2"/>
+      <c r="L373" s="2"/>
+    </row>
+    <row r="374" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A374" s="3"/>
+      <c r="B374" s="3"/>
+      <c r="C374" s="3"/>
+      <c r="D374" s="3"/>
+      <c r="E374" s="3"/>
+      <c r="F374" s="2"/>
+      <c r="G374" s="2"/>
+      <c r="H374" s="2"/>
+      <c r="I374" s="7"/>
+      <c r="J374" s="4"/>
+      <c r="K374" s="2"/>
+      <c r="L374" s="2"/>
+    </row>
+    <row r="375" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A375" s="3"/>
+      <c r="B375" s="3"/>
+      <c r="C375" s="3"/>
+      <c r="D375" s="3"/>
+      <c r="E375" s="3"/>
+      <c r="F375" s="2"/>
+      <c r="G375" s="2"/>
+      <c r="H375" s="2"/>
+      <c r="I375" s="7"/>
+      <c r="J375" s="4"/>
+      <c r="K375" s="2"/>
+      <c r="L375" s="2"/>
+    </row>
+    <row r="376" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A376" s="3"/>
+      <c r="B376" s="3"/>
+      <c r="C376" s="3"/>
+      <c r="D376" s="3"/>
+      <c r="E376" s="3"/>
+      <c r="F376" s="2"/>
+      <c r="G376" s="2"/>
+      <c r="H376" s="2"/>
+      <c r="I376" s="7"/>
+      <c r="J376" s="4"/>
+      <c r="K376" s="2"/>
+      <c r="L376" s="2"/>
+    </row>
+    <row r="377" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A377" s="3"/>
+      <c r="B377" s="3"/>
+      <c r="C377" s="3"/>
+      <c r="D377" s="3"/>
+      <c r="E377" s="3"/>
+      <c r="F377" s="2"/>
+      <c r="G377" s="2"/>
+      <c r="H377" s="2"/>
+      <c r="I377" s="7"/>
+      <c r="J377" s="4"/>
+      <c r="K377" s="2"/>
+      <c r="L377" s="2"/>
+    </row>
+    <row r="378" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A378" s="3"/>
+      <c r="B378" s="3"/>
+      <c r="C378" s="3"/>
+      <c r="D378" s="3"/>
+      <c r="E378" s="3"/>
+      <c r="F378" s="2"/>
+      <c r="G378" s="2"/>
+      <c r="H378" s="2"/>
+      <c r="I378" s="7"/>
+      <c r="J378" s="4"/>
+      <c r="K378" s="2"/>
+      <c r="L378" s="2"/>
+    </row>
+    <row r="379" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A379" s="3"/>
+      <c r="B379" s="3"/>
+      <c r="C379" s="3"/>
+      <c r="D379" s="3"/>
+      <c r="E379" s="3"/>
+      <c r="F379" s="2"/>
+      <c r="G379" s="2"/>
+      <c r="H379" s="2"/>
+      <c r="I379" s="7"/>
+      <c r="J379" s="4"/>
+      <c r="K379" s="2"/>
+      <c r="L379" s="2"/>
+    </row>
+    <row r="380" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A380" s="3"/>
+      <c r="B380" s="3"/>
+      <c r="C380" s="3"/>
+      <c r="D380" s="3"/>
+      <c r="E380" s="3"/>
+      <c r="F380" s="2"/>
+      <c r="G380" s="2"/>
+      <c r="H380" s="2"/>
+      <c r="I380" s="7"/>
+      <c r="J380" s="4"/>
+      <c r="K380" s="2"/>
+      <c r="L380" s="2"/>
+    </row>
+    <row r="381" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A381" s="3"/>
+      <c r="B381" s="3"/>
+      <c r="C381" s="3"/>
+      <c r="D381" s="3"/>
+      <c r="E381" s="3"/>
+      <c r="F381" s="2"/>
+      <c r="G381" s="2"/>
+      <c r="H381" s="2"/>
+      <c r="I381" s="7"/>
+      <c r="J381" s="4"/>
+      <c r="K381" s="2"/>
+      <c r="L381" s="2"/>
+    </row>
+    <row r="382" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A382" s="3"/>
+      <c r="B382" s="3"/>
+      <c r="C382" s="3"/>
+      <c r="D382" s="3"/>
+      <c r="E382" s="3"/>
+      <c r="F382" s="2"/>
+      <c r="G382" s="2"/>
+      <c r="H382" s="2"/>
+      <c r="I382" s="7"/>
+      <c r="J382" s="4"/>
+      <c r="K382" s="2"/>
+      <c r="L382" s="2"/>
+    </row>
+    <row r="383" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A383" s="3"/>
+      <c r="B383" s="3"/>
+      <c r="C383" s="3"/>
+      <c r="D383" s="3"/>
+      <c r="E383" s="3"/>
+      <c r="F383" s="2"/>
+      <c r="G383" s="2"/>
+      <c r="H383" s="2"/>
+      <c r="I383" s="7"/>
+      <c r="J383" s="4"/>
+      <c r="K383" s="2"/>
+      <c r="L383" s="2"/>
+    </row>
+    <row r="384" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A384" s="3"/>
+      <c r="B384" s="3"/>
+      <c r="C384" s="3"/>
+      <c r="D384" s="3"/>
+      <c r="E384" s="3"/>
+      <c r="F384" s="2"/>
+      <c r="G384" s="2"/>
+      <c r="H384" s="2"/>
+      <c r="I384" s="7"/>
+      <c r="J384" s="4"/>
+      <c r="K384" s="2"/>
+      <c r="L384" s="2"/>
+    </row>
+    <row r="385" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A385" s="3"/>
+      <c r="B385" s="3"/>
+      <c r="C385" s="3"/>
+      <c r="D385" s="3"/>
+      <c r="E385" s="3"/>
+      <c r="F385" s="2"/>
+      <c r="G385" s="2"/>
+      <c r="H385" s="2"/>
+      <c r="I385" s="7"/>
+      <c r="J385" s="4"/>
+      <c r="K385" s="2"/>
+      <c r="L385" s="2"/>
+    </row>
+    <row r="386" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A386" s="3"/>
+      <c r="B386" s="3"/>
+      <c r="C386" s="3"/>
+      <c r="D386" s="3"/>
+      <c r="E386" s="3"/>
+      <c r="F386" s="2"/>
+      <c r="G386" s="2"/>
+      <c r="H386" s="2"/>
+      <c r="I386" s="7"/>
+      <c r="J386" s="4"/>
+      <c r="K386" s="2"/>
+      <c r="L386" s="2"/>
+    </row>
+    <row r="387" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A387" s="3"/>
+      <c r="B387" s="3"/>
+      <c r="C387" s="3"/>
+      <c r="D387" s="3"/>
+      <c r="E387" s="3"/>
+      <c r="F387" s="2"/>
+      <c r="G387" s="2"/>
+      <c r="H387" s="2"/>
+      <c r="I387" s="7"/>
+      <c r="J387" s="4"/>
+      <c r="K387" s="2"/>
+      <c r="L387" s="2"/>
+    </row>
+    <row r="388" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A388" s="3"/>
+      <c r="B388" s="3"/>
+      <c r="C388" s="3"/>
+      <c r="D388" s="3"/>
+      <c r="E388" s="3"/>
+      <c r="F388" s="2"/>
+      <c r="G388" s="2"/>
+      <c r="H388" s="2"/>
+      <c r="I388" s="7"/>
+      <c r="J388" s="4"/>
+      <c r="K388" s="2"/>
+      <c r="L388" s="2"/>
+    </row>
+    <row r="389" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A389" s="3"/>
+      <c r="B389" s="3"/>
+      <c r="C389" s="3"/>
+      <c r="D389" s="3"/>
+      <c r="E389" s="3"/>
+      <c r="F389" s="2"/>
+      <c r="G389" s="2"/>
+      <c r="H389" s="2"/>
+      <c r="I389" s="7"/>
+      <c r="J389" s="4"/>
+      <c r="K389" s="2"/>
+      <c r="L389" s="2"/>
+    </row>
+    <row r="390" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A390" s="3"/>
+      <c r="B390" s="3"/>
+      <c r="C390" s="3"/>
+      <c r="D390" s="3"/>
+      <c r="E390" s="3"/>
+      <c r="F390" s="2"/>
+      <c r="G390" s="2"/>
+      <c r="H390" s="2"/>
+      <c r="I390" s="7"/>
+      <c r="J390" s="4"/>
+      <c r="K390" s="2"/>
+      <c r="L390" s="2"/>
+    </row>
+    <row r="391" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A391" s="3"/>
+      <c r="B391" s="3"/>
+      <c r="C391" s="3"/>
+      <c r="D391" s="3"/>
+      <c r="E391" s="3"/>
+      <c r="F391" s="2"/>
+      <c r="G391" s="2"/>
+      <c r="H391" s="2"/>
+      <c r="I391" s="7"/>
+      <c r="J391" s="4"/>
+      <c r="K391" s="2"/>
+      <c r="L391" s="2"/>
+    </row>
+    <row r="392" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A392" s="3"/>
+      <c r="B392" s="3"/>
+      <c r="C392" s="3"/>
+      <c r="D392" s="3"/>
+      <c r="E392" s="3"/>
+      <c r="F392" s="2"/>
+      <c r="G392" s="2"/>
+      <c r="H392" s="2"/>
+      <c r="I392" s="7"/>
+      <c r="J392" s="4"/>
+      <c r="K392" s="2"/>
+      <c r="L392" s="2"/>
+    </row>
+    <row r="393" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A393" s="3"/>
+      <c r="B393" s="3"/>
+      <c r="C393" s="3"/>
+      <c r="D393" s="3"/>
+      <c r="E393" s="3"/>
+      <c r="F393" s="2"/>
+      <c r="G393" s="2"/>
+      <c r="H393" s="2"/>
+      <c r="I393" s="7"/>
+      <c r="J393" s="4"/>
+      <c r="K393" s="2"/>
+      <c r="L393" s="2"/>
+    </row>
+    <row r="394" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A394" s="3"/>
+      <c r="B394" s="3"/>
+      <c r="C394" s="3"/>
+      <c r="D394" s="3"/>
+      <c r="E394" s="3"/>
+      <c r="F394" s="2"/>
+      <c r="G394" s="2"/>
+      <c r="H394" s="2"/>
+      <c r="I394" s="7"/>
+      <c r="J394" s="4"/>
+      <c r="K394" s="2"/>
+      <c r="L394" s="2"/>
+    </row>
+    <row r="395" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A395" s="3"/>
+      <c r="B395" s="3"/>
+      <c r="C395" s="3"/>
+      <c r="D395" s="3"/>
+      <c r="E395" s="3"/>
+      <c r="F395" s="2"/>
+      <c r="G395" s="2"/>
+      <c r="H395" s="2"/>
+      <c r="I395" s="7"/>
+      <c r="J395" s="4"/>
+      <c r="K395" s="2"/>
+      <c r="L395" s="2"/>
+    </row>
+    <row r="396" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A396" s="3"/>
+      <c r="B396" s="3"/>
+      <c r="C396" s="3"/>
+      <c r="D396" s="3"/>
+      <c r="E396" s="3"/>
+      <c r="F396" s="2"/>
+      <c r="G396" s="2"/>
+      <c r="H396" s="2"/>
+      <c r="I396" s="7"/>
+      <c r="J396" s="4"/>
+      <c r="K396" s="2"/>
+      <c r="L396" s="2"/>
+    </row>
+    <row r="397" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A397" s="3"/>
+      <c r="B397" s="3"/>
+      <c r="C397" s="3"/>
+      <c r="D397" s="3"/>
+      <c r="E397" s="3"/>
+      <c r="F397" s="2"/>
+      <c r="G397" s="2"/>
+      <c r="H397" s="2"/>
+      <c r="I397" s="7"/>
+      <c r="J397" s="4"/>
+      <c r="K397" s="2"/>
+      <c r="L397" s="2"/>
+    </row>
+    <row r="398" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A398" s="3"/>
+      <c r="B398" s="3"/>
+      <c r="C398" s="3"/>
+      <c r="D398" s="3"/>
+      <c r="E398" s="3"/>
+      <c r="F398" s="2"/>
+      <c r="G398" s="2"/>
+      <c r="H398" s="2"/>
+      <c r="I398" s="7"/>
+      <c r="J398" s="4"/>
+      <c r="K398" s="2"/>
+      <c r="L398" s="2"/>
+    </row>
+    <row r="399" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A399" s="3"/>
+      <c r="B399" s="3"/>
+      <c r="C399" s="3"/>
+      <c r="D399" s="3"/>
+      <c r="E399" s="3"/>
+      <c r="F399" s="2"/>
+      <c r="G399" s="2"/>
+      <c r="H399" s="2"/>
+      <c r="I399" s="7"/>
+      <c r="J399" s="4"/>
+      <c r="K399" s="2"/>
+      <c r="L399" s="2"/>
+    </row>
+    <row r="400" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A400" s="3"/>
+      <c r="B400" s="3"/>
+      <c r="C400" s="3"/>
+      <c r="D400" s="3"/>
+      <c r="E400" s="3"/>
+      <c r="F400" s="2"/>
+      <c r="G400" s="2"/>
+      <c r="H400" s="2"/>
+      <c r="I400" s="7"/>
+      <c r="J400" s="4"/>
+      <c r="K400" s="2"/>
+      <c r="L400" s="2"/>
+    </row>
+    <row r="401" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A401" s="3"/>
+      <c r="B401" s="3"/>
+      <c r="C401" s="3"/>
+      <c r="D401" s="3"/>
+      <c r="E401" s="3"/>
+      <c r="F401" s="2"/>
+      <c r="G401" s="2"/>
+      <c r="H401" s="2"/>
+      <c r="I401" s="7"/>
+      <c r="J401" s="4"/>
+      <c r="K401" s="2"/>
+      <c r="L401" s="2"/>
+    </row>
+    <row r="402" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A402" s="3"/>
+      <c r="B402" s="3"/>
+      <c r="C402" s="3"/>
+      <c r="D402" s="3"/>
+      <c r="E402" s="3"/>
+      <c r="F402" s="2"/>
+      <c r="G402" s="2"/>
+      <c r="H402" s="2"/>
+      <c r="I402" s="7"/>
+      <c r="J402" s="4"/>
+      <c r="K402" s="2"/>
+      <c r="L402" s="2"/>
+    </row>
+    <row r="403" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A403" s="3"/>
+      <c r="B403" s="3"/>
+      <c r="C403" s="3"/>
+      <c r="D403" s="3"/>
+      <c r="E403" s="3"/>
+      <c r="F403" s="2"/>
+      <c r="G403" s="2"/>
+      <c r="H403" s="2"/>
+      <c r="I403" s="7"/>
+      <c r="J403" s="4"/>
+      <c r="K403" s="2"/>
+      <c r="L403" s="2"/>
+    </row>
+    <row r="404" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A404" s="3"/>
+      <c r="B404" s="3"/>
+      <c r="C404" s="3"/>
+      <c r="D404" s="3"/>
+      <c r="E404" s="3"/>
+      <c r="F404" s="2"/>
+      <c r="G404" s="2"/>
+      <c r="H404" s="2"/>
+      <c r="I404" s="7"/>
+      <c r="J404" s="4"/>
+      <c r="K404" s="2"/>
+      <c r="L404" s="2"/>
+    </row>
+    <row r="405" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A405" s="3"/>
+      <c r="B405" s="3"/>
+      <c r="C405" s="3"/>
+      <c r="D405" s="3"/>
+      <c r="E405" s="3"/>
+      <c r="F405" s="2"/>
+      <c r="G405" s="2"/>
+      <c r="H405" s="2"/>
+      <c r="I405" s="7"/>
+      <c r="J405" s="4"/>
+      <c r="K405" s="2"/>
+      <c r="L405" s="2"/>
+    </row>
+    <row r="406" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A406" s="3"/>
+      <c r="B406" s="3"/>
+      <c r="C406" s="3"/>
+      <c r="D406" s="3"/>
+      <c r="E406" s="3"/>
+      <c r="F406" s="2"/>
+      <c r="G406" s="2"/>
+      <c r="H406" s="2"/>
+      <c r="I406" s="7"/>
+      <c r="J406" s="4"/>
+      <c r="K406" s="2"/>
+      <c r="L406" s="2"/>
+    </row>
+    <row r="407" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A407" s="3"/>
+      <c r="B407" s="3"/>
+      <c r="C407" s="3"/>
+      <c r="D407" s="3"/>
+      <c r="E407" s="3"/>
+      <c r="F407" s="2"/>
+      <c r="G407" s="2"/>
+      <c r="H407" s="2"/>
+      <c r="I407" s="7"/>
+      <c r="J407" s="4"/>
+      <c r="K407" s="2"/>
+      <c r="L407" s="2"/>
+    </row>
+    <row r="408" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A408" s="3"/>
+      <c r="B408" s="3"/>
+      <c r="C408" s="3"/>
+      <c r="D408" s="3"/>
+      <c r="E408" s="3"/>
+      <c r="F408" s="2"/>
+      <c r="G408" s="2"/>
+      <c r="H408" s="2"/>
+      <c r="I408" s="7"/>
+      <c r="J408" s="4"/>
+      <c r="K408" s="2"/>
+      <c r="L408" s="2"/>
+    </row>
+    <row r="409" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A409" s="3"/>
+      <c r="B409" s="3"/>
+      <c r="C409" s="3"/>
+      <c r="D409" s="3"/>
+      <c r="E409" s="3"/>
+      <c r="F409" s="2"/>
+      <c r="G409" s="2"/>
+      <c r="H409" s="2"/>
+      <c r="I409" s="7"/>
+      <c r="J409" s="4"/>
+      <c r="K409" s="2"/>
+      <c r="L409" s="2"/>
+    </row>
+    <row r="410" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A410" s="3"/>
+      <c r="B410" s="3"/>
+      <c r="C410" s="3"/>
+      <c r="D410" s="3"/>
+      <c r="E410" s="3"/>
+      <c r="F410" s="2"/>
+      <c r="G410" s="2"/>
+      <c r="H410" s="2"/>
+      <c r="I410" s="7"/>
+      <c r="J410" s="4"/>
+      <c r="K410" s="2"/>
+      <c r="L410" s="2"/>
+    </row>
+    <row r="411" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A411" s="3"/>
+      <c r="B411" s="3"/>
+      <c r="C411" s="3"/>
+      <c r="D411" s="3"/>
+      <c r="E411" s="3"/>
+      <c r="F411" s="2"/>
+      <c r="G411" s="2"/>
+      <c r="H411" s="2"/>
+      <c r="I411" s="7"/>
+      <c r="J411" s="4"/>
+      <c r="K411" s="2"/>
+      <c r="L411" s="2"/>
+    </row>
+    <row r="412" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A412" s="3"/>
+      <c r="B412" s="3"/>
+      <c r="C412" s="3"/>
+      <c r="D412" s="3"/>
+      <c r="E412" s="3"/>
+      <c r="F412" s="2"/>
+      <c r="G412" s="2"/>
+      <c r="H412" s="2"/>
+      <c r="I412" s="7"/>
+      <c r="J412" s="4"/>
+      <c r="K412" s="2"/>
+      <c r="L412" s="2"/>
+    </row>
+    <row r="413" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A413" s="3"/>
+      <c r="B413" s="3"/>
+      <c r="C413" s="3"/>
+      <c r="D413" s="3"/>
+      <c r="E413" s="3"/>
+      <c r="F413" s="2"/>
+      <c r="G413" s="2"/>
+      <c r="H413" s="2"/>
+      <c r="I413" s="7"/>
+      <c r="J413" s="4"/>
+      <c r="K413" s="2"/>
+      <c r="L413" s="2"/>
+    </row>
+    <row r="414" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A414" s="3"/>
+      <c r="B414" s="3"/>
+      <c r="C414" s="3"/>
+      <c r="D414" s="3"/>
+      <c r="E414" s="3"/>
+      <c r="F414" s="2"/>
+      <c r="G414" s="2"/>
+      <c r="H414" s="2"/>
+      <c r="I414" s="7"/>
+      <c r="J414" s="4"/>
+      <c r="K414" s="2"/>
+      <c r="L414" s="2"/>
+    </row>
+    <row r="415" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A415" s="3"/>
+      <c r="B415" s="3"/>
+      <c r="C415" s="3"/>
+      <c r="D415" s="3"/>
+      <c r="E415" s="3"/>
+      <c r="F415" s="2"/>
+      <c r="G415" s="2"/>
+      <c r="H415" s="2"/>
+      <c r="I415" s="7"/>
+      <c r="J415" s="4"/>
+      <c r="K415" s="2"/>
+      <c r="L415" s="2"/>
+    </row>
+    <row r="416" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A416" s="3"/>
+      <c r="B416" s="3"/>
+      <c r="C416" s="3"/>
+      <c r="D416" s="3"/>
+      <c r="E416" s="3"/>
+      <c r="F416" s="2"/>
+      <c r="G416" s="2"/>
+      <c r="H416" s="2"/>
+      <c r="I416" s="7"/>
+      <c r="J416" s="4"/>
+      <c r="K416" s="2"/>
+      <c r="L416" s="2"/>
+    </row>
+    <row r="417" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A417" s="3"/>
+      <c r="B417" s="3"/>
+      <c r="C417" s="3"/>
+      <c r="D417" s="3"/>
+      <c r="E417" s="3"/>
+      <c r="F417" s="2"/>
+      <c r="G417" s="2"/>
+      <c r="H417" s="2"/>
+      <c r="I417" s="7"/>
+      <c r="J417" s="4"/>
+      <c r="K417" s="2"/>
+      <c r="L417" s="2"/>
+    </row>
+    <row r="418" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A418" s="3"/>
+      <c r="B418" s="3"/>
+      <c r="C418" s="3"/>
+      <c r="D418" s="3"/>
+      <c r="E418" s="3"/>
+      <c r="F418" s="2"/>
+      <c r="G418" s="2"/>
+      <c r="H418" s="2"/>
+      <c r="I418" s="7"/>
+      <c r="J418" s="4"/>
+      <c r="K418" s="2"/>
+      <c r="L418" s="2"/>
+    </row>
+    <row r="419" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A419" s="3"/>
+      <c r="B419" s="3"/>
+      <c r="C419" s="3"/>
+      <c r="D419" s="3"/>
+      <c r="E419" s="3"/>
+      <c r="F419" s="2"/>
+      <c r="G419" s="2"/>
+      <c r="H419" s="2"/>
+      <c r="I419" s="7"/>
+      <c r="J419" s="4"/>
+      <c r="K419" s="2"/>
+      <c r="L419" s="2"/>
+    </row>
+    <row r="420" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A420" s="3"/>
+      <c r="B420" s="3"/>
+      <c r="C420" s="3"/>
+      <c r="D420" s="3"/>
+      <c r="E420" s="3"/>
+      <c r="F420" s="2"/>
+      <c r="G420" s="2"/>
+      <c r="H420" s="2"/>
+      <c r="I420" s="7"/>
+      <c r="J420" s="4"/>
+      <c r="K420" s="2"/>
+      <c r="L420" s="2"/>
+    </row>
+    <row r="421" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A421" s="3"/>
+      <c r="B421" s="3"/>
+      <c r="C421" s="3"/>
+      <c r="D421" s="3"/>
+      <c r="E421" s="3"/>
+      <c r="F421" s="2"/>
+      <c r="G421" s="2"/>
+      <c r="H421" s="2"/>
+      <c r="I421" s="7"/>
+      <c r="J421" s="4"/>
+      <c r="K421" s="2"/>
+      <c r="L421" s="2"/>
+    </row>
+    <row r="422" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A422" s="3"/>
+      <c r="B422" s="3"/>
+      <c r="C422" s="3"/>
+      <c r="D422" s="3"/>
+      <c r="E422" s="3"/>
+      <c r="F422" s="2"/>
+      <c r="G422" s="2"/>
+      <c r="H422" s="2"/>
+      <c r="I422" s="7"/>
+      <c r="J422" s="4"/>
+      <c r="K422" s="2"/>
+      <c r="L422" s="2"/>
+    </row>
+    <row r="423" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A423" s="3"/>
+      <c r="B423" s="3"/>
+      <c r="C423" s="3"/>
+      <c r="D423" s="3"/>
+      <c r="E423" s="3"/>
+      <c r="F423" s="2"/>
+      <c r="G423" s="2"/>
+      <c r="H423" s="2"/>
+      <c r="I423" s="7"/>
+      <c r="J423" s="4"/>
+      <c r="K423" s="2"/>
+      <c r="L423" s="2"/>
+    </row>
+    <row r="424" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A424" s="3"/>
+      <c r="B424" s="3"/>
+      <c r="C424" s="3"/>
+      <c r="D424" s="3"/>
+      <c r="E424" s="3"/>
+      <c r="F424" s="2"/>
+      <c r="G424" s="2"/>
+      <c r="H424" s="2"/>
+      <c r="I424" s="7"/>
+      <c r="J424" s="4"/>
+      <c r="K424" s="2"/>
+      <c r="L424" s="2"/>
+    </row>
+    <row r="425" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A425" s="3"/>
+      <c r="B425" s="3"/>
+      <c r="C425" s="3"/>
+      <c r="D425" s="3"/>
+      <c r="E425" s="3"/>
+      <c r="F425" s="2"/>
+      <c r="G425" s="2"/>
+      <c r="H425" s="2"/>
+      <c r="I425" s="7"/>
+      <c r="J425" s="4"/>
+      <c r="K425" s="2"/>
+      <c r="L425" s="2"/>
+    </row>
+    <row r="426" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A426" s="3"/>
+      <c r="B426" s="3"/>
+      <c r="C426" s="3"/>
+      <c r="D426" s="3"/>
+      <c r="E426" s="3"/>
+      <c r="F426" s="2"/>
+      <c r="G426" s="2"/>
+      <c r="H426" s="2"/>
+      <c r="I426" s="7"/>
+      <c r="J426" s="4"/>
+      <c r="K426" s="2"/>
+      <c r="L426" s="2"/>
+    </row>
+    <row r="427" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A427" s="3"/>
+      <c r="B427" s="3"/>
+      <c r="C427" s="3"/>
+      <c r="D427" s="3"/>
+      <c r="E427" s="3"/>
+      <c r="F427" s="2"/>
+      <c r="G427" s="2"/>
+      <c r="H427" s="2"/>
+      <c r="I427" s="7"/>
+      <c r="J427" s="4"/>
+      <c r="K427" s="2"/>
+      <c r="L427" s="2"/>
+    </row>
+    <row r="428" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A428" s="3"/>
+      <c r="B428" s="3"/>
+      <c r="C428" s="3"/>
+      <c r="D428" s="3"/>
+      <c r="E428" s="3"/>
+      <c r="F428" s="2"/>
+      <c r="G428" s="2"/>
+      <c r="H428" s="2"/>
+      <c r="I428" s="7"/>
+      <c r="J428" s="4"/>
+      <c r="K428" s="2"/>
+      <c r="L428" s="2"/>
+    </row>
+    <row r="429" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A429" s="3"/>
+      <c r="B429" s="3"/>
+      <c r="C429" s="3"/>
+      <c r="D429" s="3"/>
+      <c r="E429" s="3"/>
+      <c r="F429" s="2"/>
+      <c r="G429" s="2"/>
+      <c r="H429" s="2"/>
+      <c r="I429" s="7"/>
+      <c r="J429" s="4"/>
+      <c r="K429" s="2"/>
+      <c r="L429" s="2"/>
+    </row>
+    <row r="430" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A430" s="3"/>
+      <c r="B430" s="3"/>
+      <c r="C430" s="3"/>
+      <c r="D430" s="3"/>
+      <c r="E430" s="3"/>
+      <c r="F430" s="2"/>
+      <c r="G430" s="2"/>
+      <c r="H430" s="2"/>
+      <c r="I430" s="7"/>
+      <c r="J430" s="4"/>
+      <c r="K430" s="2"/>
+      <c r="L430" s="2"/>
+    </row>
+    <row r="431" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A431" s="3"/>
+      <c r="B431" s="3"/>
+      <c r="C431" s="3"/>
+      <c r="D431" s="3"/>
+      <c r="E431" s="3"/>
+      <c r="F431" s="2"/>
+      <c r="G431" s="2"/>
+      <c r="H431" s="2"/>
+      <c r="I431" s="7"/>
+      <c r="J431" s="4"/>
+      <c r="K431" s="2"/>
+      <c r="L431" s="2"/>
+    </row>
+    <row r="432" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A432" s="3"/>
+      <c r="B432" s="3"/>
+      <c r="C432" s="3"/>
+      <c r="D432" s="3"/>
+      <c r="E432" s="3"/>
+      <c r="F432" s="2"/>
+      <c r="G432" s="2"/>
+      <c r="H432" s="2"/>
+      <c r="I432" s="7"/>
+      <c r="J432" s="4"/>
+      <c r="K432" s="2"/>
+      <c r="L432" s="2"/>
+    </row>
+    <row r="433" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A433" s="3"/>
+      <c r="B433" s="3"/>
+      <c r="C433" s="3"/>
+      <c r="D433" s="3"/>
+      <c r="E433" s="3"/>
+      <c r="F433" s="2"/>
+      <c r="G433" s="2"/>
+      <c r="H433" s="2"/>
+      <c r="I433" s="7"/>
+      <c r="J433" s="4"/>
+      <c r="K433" s="2"/>
+      <c r="L433" s="2"/>
+    </row>
+    <row r="434" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A434" s="3"/>
+      <c r="B434" s="3"/>
+      <c r="C434" s="3"/>
+      <c r="D434" s="3"/>
+      <c r="E434" s="3"/>
+      <c r="F434" s="2"/>
+      <c r="G434" s="2"/>
+      <c r="H434" s="2"/>
+      <c r="I434" s="7"/>
+      <c r="J434" s="4"/>
+      <c r="K434" s="2"/>
+      <c r="L434" s="2"/>
+    </row>
+    <row r="435" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A435" s="3"/>
+      <c r="B435" s="3"/>
+      <c r="C435" s="3"/>
+      <c r="D435" s="3"/>
+      <c r="E435" s="3"/>
+      <c r="F435" s="2"/>
+      <c r="G435" s="2"/>
+      <c r="H435" s="2"/>
+      <c r="I435" s="7"/>
+      <c r="J435" s="4"/>
+      <c r="K435" s="2"/>
+      <c r="L435" s="2"/>
+    </row>
+    <row r="436" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A436" s="3"/>
+      <c r="B436" s="3"/>
+      <c r="C436" s="3"/>
+      <c r="D436" s="3"/>
+      <c r="E436" s="3"/>
+      <c r="F436" s="2"/>
+      <c r="G436" s="2"/>
+      <c r="H436" s="2"/>
+      <c r="I436" s="7"/>
+      <c r="J436" s="4"/>
+      <c r="K436" s="2"/>
+      <c r="L436" s="2"/>
+    </row>
+    <row r="437" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A437" s="3"/>
+      <c r="B437" s="3"/>
+      <c r="C437" s="3"/>
+      <c r="D437" s="3"/>
+      <c r="E437" s="3"/>
+      <c r="F437" s="2"/>
+      <c r="G437" s="2"/>
+      <c r="H437" s="2"/>
+      <c r="I437" s="7"/>
+      <c r="J437" s="4"/>
+      <c r="K437" s="2"/>
+      <c r="L437" s="2"/>
+    </row>
+    <row r="438" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A438" s="3"/>
+      <c r="B438" s="3"/>
+      <c r="C438" s="3"/>
+      <c r="D438" s="3"/>
+      <c r="E438" s="3"/>
+      <c r="F438" s="2"/>
+      <c r="G438" s="2"/>
+      <c r="H438" s="2"/>
+      <c r="I438" s="7"/>
+      <c r="J438" s="4"/>
+      <c r="K438" s="2"/>
+      <c r="L438" s="2"/>
+    </row>
+    <row r="439" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A439" s="3"/>
+      <c r="B439" s="3"/>
+      <c r="C439" s="3"/>
+      <c r="D439" s="3"/>
+      <c r="E439" s="3"/>
+      <c r="F439" s="2"/>
+      <c r="G439" s="2"/>
+      <c r="H439" s="2"/>
+      <c r="I439" s="7"/>
+      <c r="J439" s="4"/>
+      <c r="K439" s="2"/>
+      <c r="L439" s="2"/>
+    </row>
+    <row r="440" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A440" s="3"/>
+      <c r="B440" s="3"/>
+      <c r="C440" s="3"/>
+      <c r="D440" s="3"/>
+      <c r="E440" s="3"/>
+      <c r="F440" s="2"/>
+      <c r="G440" s="2"/>
+      <c r="H440" s="2"/>
+      <c r="I440" s="7"/>
+      <c r="J440" s="4"/>
+      <c r="K440" s="2"/>
+      <c r="L440" s="2"/>
+    </row>
+    <row r="441" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A441" s="3"/>
+      <c r="B441" s="3"/>
+      <c r="C441" s="3"/>
+      <c r="D441" s="3"/>
+      <c r="E441" s="3"/>
+      <c r="F441" s="2"/>
+      <c r="G441" s="2"/>
+      <c r="H441" s="2"/>
+      <c r="I441" s="7"/>
+      <c r="J441" s="4"/>
+      <c r="K441" s="2"/>
+      <c r="L441" s="2"/>
+    </row>
+    <row r="442" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A442" s="3"/>
+      <c r="B442" s="3"/>
+      <c r="C442" s="3"/>
+      <c r="D442" s="3"/>
+      <c r="E442" s="3"/>
+      <c r="F442" s="2"/>
+      <c r="G442" s="2"/>
+      <c r="H442" s="2"/>
+      <c r="I442" s="7"/>
+      <c r="J442" s="4"/>
+      <c r="K442" s="2"/>
+      <c r="L442" s="2"/>
+    </row>
+    <row r="443" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A443" s="3"/>
+      <c r="B443" s="3"/>
+      <c r="C443" s="3"/>
+      <c r="D443" s="3"/>
+      <c r="E443" s="3"/>
+      <c r="F443" s="2"/>
+      <c r="G443" s="2"/>
+      <c r="H443" s="2"/>
+      <c r="I443" s="7"/>
+      <c r="J443" s="4"/>
+      <c r="K443" s="2"/>
+      <c r="L443" s="2"/>
+    </row>
+    <row r="444" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A444" s="3"/>
+      <c r="B444" s="3"/>
+      <c r="C444" s="3"/>
+      <c r="D444" s="3"/>
+      <c r="E444" s="3"/>
+      <c r="F444" s="2"/>
+      <c r="G444" s="2"/>
+      <c r="H444" s="2"/>
+      <c r="I444" s="7"/>
+      <c r="J444" s="4"/>
+      <c r="K444" s="2"/>
+      <c r="L444" s="2"/>
+    </row>
+    <row r="445" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A445" s="3"/>
+      <c r="B445" s="3"/>
+      <c r="C445" s="3"/>
+      <c r="D445" s="3"/>
+      <c r="E445" s="3"/>
+      <c r="F445" s="2"/>
+      <c r="G445" s="2"/>
+      <c r="H445" s="2"/>
+      <c r="I445" s="7"/>
+      <c r="J445" s="4"/>
+      <c r="K445" s="2"/>
+      <c r="L445" s="2"/>
+    </row>
+    <row r="446" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A446" s="3"/>
+      <c r="B446" s="3"/>
+      <c r="C446" s="3"/>
+      <c r="D446" s="3"/>
+      <c r="E446" s="3"/>
+      <c r="F446" s="2"/>
+      <c r="G446" s="2"/>
+      <c r="H446" s="2"/>
+      <c r="I446" s="7"/>
+      <c r="J446" s="4"/>
+      <c r="K446" s="2"/>
+      <c r="L446" s="2"/>
+    </row>
+    <row r="447" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A447" s="3"/>
+      <c r="B447" s="3"/>
+      <c r="C447" s="3"/>
+      <c r="D447" s="3"/>
+      <c r="E447" s="3"/>
+      <c r="F447" s="2"/>
+      <c r="G447" s="2"/>
+      <c r="H447" s="2"/>
+      <c r="I447" s="7"/>
+      <c r="J447" s="4"/>
+      <c r="K447" s="2"/>
+      <c r="L447" s="2"/>
+    </row>
+    <row r="448" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A448" s="3"/>
+      <c r="B448" s="3"/>
+      <c r="C448" s="3"/>
+      <c r="D448" s="3"/>
+      <c r="E448" s="3"/>
+      <c r="F448" s="2"/>
+      <c r="G448" s="2"/>
+      <c r="H448" s="2"/>
+      <c r="I448" s="7"/>
+      <c r="J448" s="4"/>
+      <c r="K448" s="2"/>
+      <c r="L448" s="2"/>
+    </row>
+    <row r="449" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A449" s="3"/>
+      <c r="B449" s="3"/>
+      <c r="C449" s="3"/>
+      <c r="D449" s="3"/>
+      <c r="E449" s="3"/>
+      <c r="F449" s="2"/>
+      <c r="G449" s="2"/>
+      <c r="H449" s="2"/>
+      <c r="I449" s="7"/>
+      <c r="J449" s="4"/>
+      <c r="K449" s="2"/>
+      <c r="L449" s="2"/>
+    </row>
+    <row r="450" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A450" s="3"/>
+      <c r="B450" s="3"/>
+      <c r="C450" s="3"/>
+      <c r="D450" s="3"/>
+      <c r="E450" s="3"/>
+      <c r="F450" s="2"/>
+      <c r="G450" s="2"/>
+      <c r="H450" s="2"/>
+      <c r="I450" s="7"/>
+      <c r="J450" s="4"/>
+      <c r="K450" s="2"/>
+      <c r="L450" s="2"/>
+    </row>
+    <row r="451" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A451" s="3"/>
+      <c r="B451" s="3"/>
+      <c r="C451" s="3"/>
+      <c r="D451" s="3"/>
+      <c r="E451" s="3"/>
+      <c r="F451" s="2"/>
+      <c r="G451" s="2"/>
+      <c r="H451" s="2"/>
+      <c r="I451" s="7"/>
+      <c r="J451" s="4"/>
+      <c r="K451" s="2"/>
+      <c r="L451" s="2"/>
+    </row>
+    <row r="452" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A452" s="3"/>
+      <c r="B452" s="3"/>
+      <c r="C452" s="3"/>
+      <c r="D452" s="3"/>
+      <c r="E452" s="3"/>
+      <c r="F452" s="2"/>
+      <c r="G452" s="2"/>
+      <c r="H452" s="2"/>
+      <c r="I452" s="7"/>
+      <c r="J452" s="4"/>
+      <c r="K452" s="2"/>
+      <c r="L452" s="2"/>
+    </row>
+    <row r="453" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A453" s="3"/>
+      <c r="B453" s="3"/>
+      <c r="C453" s="3"/>
+      <c r="D453" s="3"/>
+      <c r="E453" s="3"/>
+      <c r="F453" s="2"/>
+      <c r="G453" s="2"/>
+      <c r="H453" s="2"/>
+      <c r="I453" s="7"/>
+      <c r="J453" s="4"/>
+      <c r="K453" s="2"/>
+      <c r="L453" s="2"/>
+    </row>
+    <row r="454" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A454" s="3"/>
+      <c r="B454" s="3"/>
+      <c r="C454" s="3"/>
+      <c r="D454" s="3"/>
+      <c r="E454" s="3"/>
+      <c r="F454" s="2"/>
+      <c r="G454" s="2"/>
+      <c r="H454" s="2"/>
+      <c r="I454" s="7"/>
+      <c r="J454" s="4"/>
+      <c r="K454" s="2"/>
+      <c r="L454" s="2"/>
+    </row>
+    <row r="455" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A455" s="3"/>
+      <c r="B455" s="3"/>
+      <c r="C455" s="3"/>
+      <c r="D455" s="3"/>
+      <c r="E455" s="3"/>
+      <c r="F455" s="2"/>
+      <c r="G455" s="2"/>
+      <c r="H455" s="2"/>
+      <c r="I455" s="7"/>
+      <c r="J455" s="4"/>
+      <c r="K455" s="2"/>
+      <c r="L455" s="2"/>
+    </row>
+    <row r="456" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A456" s="3"/>
+      <c r="B456" s="3"/>
+      <c r="C456" s="3"/>
+      <c r="D456" s="3"/>
+      <c r="E456" s="3"/>
+      <c r="F456" s="2"/>
+      <c r="G456" s="2"/>
+      <c r="H456" s="2"/>
+      <c r="I456" s="7"/>
+      <c r="J456" s="4"/>
+      <c r="K456" s="2"/>
+      <c r="L456" s="2"/>
+    </row>
+    <row r="457" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A457" s="3"/>
+      <c r="B457" s="3"/>
+      <c r="C457" s="3"/>
+      <c r="D457" s="3"/>
+      <c r="E457" s="3"/>
+      <c r="F457" s="2"/>
+      <c r="G457" s="2"/>
+      <c r="H457" s="2"/>
+      <c r="I457" s="7"/>
+      <c r="J457" s="4"/>
+      <c r="K457" s="2"/>
+      <c r="L457" s="2"/>
+    </row>
+    <row r="458" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A458" s="3"/>
+      <c r="B458" s="3"/>
+      <c r="C458" s="3"/>
+      <c r="D458" s="3"/>
+      <c r="E458" s="3"/>
+      <c r="F458" s="2"/>
+      <c r="G458" s="2"/>
+      <c r="H458" s="2"/>
+      <c r="I458" s="7"/>
+      <c r="J458" s="4"/>
+      <c r="K458" s="2"/>
+      <c r="L458" s="2"/>
+    </row>
+    <row r="459" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A459" s="3"/>
+      <c r="B459" s="3"/>
+      <c r="C459" s="3"/>
+      <c r="D459" s="3"/>
+      <c r="E459" s="3"/>
+      <c r="F459" s="2"/>
+      <c r="G459" s="2"/>
+      <c r="H459" s="2"/>
+      <c r="I459" s="7"/>
+      <c r="J459" s="4"/>
+      <c r="K459" s="2"/>
+      <c r="L459" s="2"/>
+    </row>
+    <row r="460" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A460" s="3"/>
+      <c r="B460" s="3"/>
+      <c r="C460" s="3"/>
+      <c r="D460" s="3"/>
+      <c r="E460" s="3"/>
+      <c r="F460" s="2"/>
+      <c r="G460" s="2"/>
+      <c r="H460" s="2"/>
+      <c r="I460" s="7"/>
+      <c r="J460" s="4"/>
+      <c r="K460" s="2"/>
+      <c r="L460" s="2"/>
+    </row>
+    <row r="461" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A461" s="3"/>
+      <c r="B461" s="3"/>
+      <c r="C461" s="3"/>
+      <c r="D461" s="3"/>
+      <c r="E461" s="3"/>
+      <c r="F461" s="2"/>
+      <c r="G461" s="2"/>
+      <c r="H461" s="2"/>
+      <c r="I461" s="7"/>
+      <c r="J461" s="4"/>
+      <c r="K461" s="2"/>
+      <c r="L461" s="2"/>
+    </row>
+    <row r="462" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A462" s="3"/>
+      <c r="B462" s="3"/>
+      <c r="C462" s="3"/>
+      <c r="D462" s="3"/>
+      <c r="E462" s="3"/>
+      <c r="F462" s="2"/>
+      <c r="G462" s="2"/>
+      <c r="H462" s="2"/>
+      <c r="I462" s="7"/>
+      <c r="J462" s="4"/>
+      <c r="K462" s="2"/>
+      <c r="L462" s="2"/>
+    </row>
+    <row r="463" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A463" s="3"/>
+      <c r="B463" s="3"/>
+      <c r="C463" s="3"/>
+      <c r="D463" s="3"/>
+      <c r="E463" s="3"/>
+      <c r="F463" s="2"/>
+      <c r="G463" s="2"/>
+      <c r="H463" s="2"/>
+      <c r="I463" s="7"/>
+      <c r="J463" s="4"/>
+      <c r="K463" s="2"/>
+      <c r="L463" s="2"/>
+    </row>
+    <row r="464" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A464" s="3"/>
+      <c r="B464" s="3"/>
+      <c r="C464" s="3"/>
+      <c r="D464" s="3"/>
+      <c r="E464" s="3"/>
+      <c r="F464" s="2"/>
+      <c r="G464" s="2"/>
+      <c r="H464" s="2"/>
+      <c r="I464" s="7"/>
+      <c r="J464" s="4"/>
+      <c r="K464" s="2"/>
+      <c r="L464" s="2"/>
+    </row>
+    <row r="465" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A465" s="3"/>
+      <c r="B465" s="3"/>
+      <c r="C465" s="3"/>
+      <c r="D465" s="3"/>
+      <c r="E465" s="3"/>
+      <c r="F465" s="2"/>
+      <c r="G465" s="2"/>
+      <c r="H465" s="2"/>
+      <c r="I465" s="7"/>
+      <c r="J465" s="4"/>
+      <c r="K465" s="2"/>
+      <c r="L465" s="2"/>
+    </row>
+    <row r="466" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A466" s="3"/>
+      <c r="B466" s="3"/>
+      <c r="C466" s="3"/>
+      <c r="D466" s="3"/>
+      <c r="E466" s="3"/>
+      <c r="F466" s="2"/>
+      <c r="G466" s="2"/>
+      <c r="H466" s="2"/>
+      <c r="I466" s="7"/>
+      <c r="J466" s="4"/>
+      <c r="K466" s="2"/>
+      <c r="L466" s="2"/>
+    </row>
+    <row r="467" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A467" s="3"/>
+      <c r="B467" s="3"/>
+      <c r="C467" s="3"/>
+      <c r="D467" s="3"/>
+      <c r="E467" s="3"/>
+      <c r="F467" s="2"/>
+      <c r="G467" s="2"/>
+      <c r="H467" s="2"/>
+      <c r="I467" s="7"/>
+      <c r="J467" s="4"/>
+      <c r="K467" s="2"/>
+      <c r="L467" s="2"/>
+    </row>
+    <row r="468" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A468" s="3"/>
+      <c r="B468" s="3"/>
+      <c r="C468" s="3"/>
+      <c r="D468" s="3"/>
+      <c r="E468" s="3"/>
+      <c r="F468" s="2"/>
+      <c r="G468" s="2"/>
+      <c r="H468" s="2"/>
+      <c r="I468" s="7"/>
+      <c r="J468" s="4"/>
+      <c r="K468" s="2"/>
+      <c r="L468" s="2"/>
+    </row>
+    <row r="469" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A469" s="3"/>
+      <c r="B469" s="3"/>
+      <c r="C469" s="3"/>
+      <c r="D469" s="3"/>
+      <c r="E469" s="3"/>
+      <c r="F469" s="2"/>
+      <c r="G469" s="2"/>
+      <c r="H469" s="2"/>
+      <c r="I469" s="7"/>
+      <c r="J469" s="4"/>
+      <c r="K469" s="2"/>
+      <c r="L469" s="2"/>
+    </row>
+    <row r="470" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A470" s="3"/>
+      <c r="B470" s="3"/>
+      <c r="C470" s="3"/>
+      <c r="D470" s="3"/>
+      <c r="E470" s="3"/>
+      <c r="F470" s="2"/>
+      <c r="G470" s="2"/>
+      <c r="H470" s="2"/>
+      <c r="I470" s="7"/>
+      <c r="J470" s="4"/>
+      <c r="K470" s="2"/>
+      <c r="L470" s="2"/>
+    </row>
+    <row r="471" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A471" s="3"/>
+      <c r="B471" s="3"/>
+      <c r="C471" s="3"/>
+      <c r="D471" s="3"/>
+      <c r="E471" s="3"/>
+      <c r="F471" s="2"/>
+      <c r="G471" s="2"/>
+      <c r="H471" s="2"/>
+      <c r="I471" s="7"/>
+      <c r="J471" s="4"/>
+      <c r="K471" s="2"/>
+      <c r="L471" s="2"/>
+    </row>
+    <row r="472" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A472" s="3"/>
+      <c r="B472" s="3"/>
+      <c r="C472" s="3"/>
+      <c r="D472" s="3"/>
+      <c r="E472" s="3"/>
+      <c r="F472" s="2"/>
+      <c r="G472" s="2"/>
+      <c r="H472" s="2"/>
+      <c r="I472" s="7"/>
+      <c r="J472" s="4"/>
+      <c r="K472" s="2"/>
+      <c r="L472" s="2"/>
+    </row>
+    <row r="473" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A473" s="3"/>
+      <c r="B473" s="3"/>
+      <c r="C473" s="3"/>
+      <c r="D473" s="3"/>
+      <c r="E473" s="3"/>
+      <c r="F473" s="2"/>
+      <c r="G473" s="2"/>
+      <c r="H473" s="2"/>
+      <c r="I473" s="7"/>
+      <c r="J473" s="4"/>
+      <c r="K473" s="2"/>
+      <c r="L473" s="2"/>
+    </row>
+    <row r="474" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A474" s="3"/>
+      <c r="B474" s="3"/>
+      <c r="C474" s="3"/>
+      <c r="D474" s="3"/>
+      <c r="E474" s="3"/>
+      <c r="F474" s="2"/>
+      <c r="G474" s="2"/>
+      <c r="H474" s="2"/>
+      <c r="I474" s="7"/>
+      <c r="J474" s="4"/>
+      <c r="K474" s="2"/>
+      <c r="L474" s="2"/>
+    </row>
+    <row r="475" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A475" s="3"/>
+      <c r="B475" s="3"/>
+      <c r="C475" s="3"/>
+      <c r="D475" s="3"/>
+      <c r="E475" s="3"/>
+      <c r="F475" s="2"/>
+      <c r="G475" s="2"/>
+      <c r="H475" s="2"/>
+      <c r="I475" s="7"/>
+      <c r="J475" s="4"/>
+      <c r="K475" s="2"/>
+      <c r="L475" s="2"/>
+    </row>
+    <row r="476" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A476" s="3"/>
+      <c r="B476" s="3"/>
+      <c r="C476" s="3"/>
+      <c r="D476" s="3"/>
+      <c r="E476" s="3"/>
+      <c r="F476" s="2"/>
+      <c r="G476" s="2"/>
+      <c r="H476" s="2"/>
+      <c r="I476" s="7"/>
+      <c r="J476" s="4"/>
+      <c r="K476" s="2"/>
+      <c r="L476" s="2"/>
+    </row>
+    <row r="477" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A477" s="3"/>
+      <c r="B477" s="3"/>
+      <c r="C477" s="3"/>
+      <c r="D477" s="3"/>
+      <c r="E477" s="3"/>
+      <c r="F477" s="2"/>
+      <c r="G477" s="2"/>
+      <c r="H477" s="2"/>
+      <c r="I477" s="7"/>
+      <c r="J477" s="4"/>
+      <c r="K477" s="2"/>
+      <c r="L477" s="2"/>
+    </row>
+    <row r="478" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A478" s="3"/>
+      <c r="B478" s="3"/>
+      <c r="C478" s="3"/>
+      <c r="D478" s="3"/>
+      <c r="E478" s="3"/>
+      <c r="F478" s="2"/>
+      <c r="G478" s="2"/>
+      <c r="H478" s="2"/>
+      <c r="I478" s="7"/>
+      <c r="J478" s="4"/>
+      <c r="K478" s="2"/>
+      <c r="L478" s="2"/>
+    </row>
+    <row r="479" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A479" s="3"/>
+      <c r="B479" s="3"/>
+      <c r="C479" s="3"/>
+      <c r="D479" s="3"/>
+      <c r="E479" s="3"/>
+      <c r="F479" s="2"/>
+      <c r="G479" s="2"/>
+      <c r="H479" s="2"/>
+      <c r="I479" s="7"/>
+      <c r="J479" s="4"/>
+      <c r="K479" s="2"/>
+      <c r="L479" s="2"/>
+    </row>
+    <row r="480" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A480" s="3"/>
+      <c r="B480" s="3"/>
+      <c r="C480" s="3"/>
+      <c r="D480" s="3"/>
+      <c r="E480" s="3"/>
+      <c r="F480" s="2"/>
+      <c r="G480" s="2"/>
+      <c r="H480" s="2"/>
+      <c r="I480" s="7"/>
+      <c r="J480" s="4"/>
+      <c r="K480" s="2"/>
+      <c r="L480" s="2"/>
+    </row>
+    <row r="481" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A481" s="3"/>
+      <c r="B481" s="3"/>
+      <c r="C481" s="3"/>
+      <c r="D481" s="3"/>
+      <c r="E481" s="3"/>
+      <c r="F481" s="2"/>
+      <c r="G481" s="2"/>
+      <c r="H481" s="2"/>
+      <c r="I481" s="7"/>
+      <c r="J481" s="4"/>
+      <c r="K481" s="2"/>
+      <c r="L481" s="2"/>
+    </row>
+    <row r="482" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A482" s="3"/>
+      <c r="B482" s="3"/>
+      <c r="C482" s="3"/>
+      <c r="D482" s="3"/>
+      <c r="E482" s="3"/>
+      <c r="F482" s="2"/>
+      <c r="G482" s="2"/>
+      <c r="H482" s="2"/>
+      <c r="I482" s="7"/>
+      <c r="J482" s="4"/>
+      <c r="K482" s="2"/>
+      <c r="L482" s="2"/>
+    </row>
+    <row r="483" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A483" s="3"/>
+      <c r="B483" s="3"/>
+      <c r="C483" s="3"/>
+      <c r="D483" s="3"/>
+      <c r="E483" s="3"/>
+      <c r="F483" s="2"/>
+      <c r="G483" s="2"/>
+      <c r="H483" s="2"/>
+      <c r="I483" s="7"/>
+      <c r="J483" s="4"/>
+      <c r="K483" s="2"/>
+      <c r="L483" s="2"/>
+    </row>
+    <row r="484" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A484" s="3"/>
+      <c r="B484" s="3"/>
+      <c r="C484" s="3"/>
+      <c r="D484" s="3"/>
+      <c r="E484" s="3"/>
+      <c r="F484" s="2"/>
+      <c r="G484" s="2"/>
+      <c r="H484" s="2"/>
+      <c r="I484" s="7"/>
+      <c r="J484" s="4"/>
+      <c r="K484" s="2"/>
+      <c r="L484" s="2"/>
+    </row>
+    <row r="485" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A485" s="3"/>
+      <c r="B485" s="3"/>
+      <c r="C485" s="3"/>
+      <c r="D485" s="3"/>
+      <c r="E485" s="3"/>
+      <c r="F485" s="2"/>
+      <c r="G485" s="2"/>
+      <c r="H485" s="2"/>
+      <c r="I485" s="7"/>
+      <c r="J485" s="4"/>
+      <c r="K485" s="2"/>
+      <c r="L485" s="2"/>
+    </row>
+    <row r="486" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A486" s="3"/>
+      <c r="B486" s="3"/>
+      <c r="C486" s="3"/>
+      <c r="D486" s="3"/>
+      <c r="E486" s="3"/>
+      <c r="F486" s="2"/>
+      <c r="G486" s="2"/>
+      <c r="H486" s="2"/>
+      <c r="I486" s="7"/>
+      <c r="J486" s="4"/>
+      <c r="K486" s="2"/>
+      <c r="L486" s="2"/>
+    </row>
+    <row r="487" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A487" s="3"/>
+      <c r="B487" s="3"/>
+      <c r="C487" s="3"/>
+      <c r="D487" s="3"/>
+      <c r="E487" s="3"/>
+      <c r="F487" s="2"/>
+      <c r="G487" s="2"/>
+      <c r="H487" s="2"/>
+      <c r="I487" s="7"/>
+      <c r="J487" s="4"/>
+      <c r="K487" s="2"/>
+      <c r="L487" s="2"/>
+    </row>
+    <row r="488" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A488" s="3"/>
+      <c r="B488" s="3"/>
+      <c r="C488" s="3"/>
+      <c r="D488" s="3"/>
+      <c r="E488" s="3"/>
+      <c r="F488" s="2"/>
+      <c r="G488" s="2"/>
+      <c r="H488" s="2"/>
+      <c r="I488" s="7"/>
+      <c r="J488" s="4"/>
+      <c r="K488" s="2"/>
+      <c r="L488" s="2"/>
+    </row>
+    <row r="489" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A489" s="3"/>
+      <c r="B489" s="3"/>
+      <c r="C489" s="3"/>
+      <c r="D489" s="3"/>
+      <c r="E489" s="3"/>
+      <c r="F489" s="2"/>
+      <c r="G489" s="2"/>
+      <c r="H489" s="2"/>
+      <c r="I489" s="7"/>
+      <c r="J489" s="4"/>
+      <c r="K489" s="2"/>
+      <c r="L489" s="2"/>
+    </row>
+    <row r="490" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A490" s="3"/>
+      <c r="B490" s="3"/>
+      <c r="C490" s="3"/>
+      <c r="D490" s="3"/>
+      <c r="E490" s="3"/>
+      <c r="F490" s="2"/>
+      <c r="G490" s="2"/>
+      <c r="H490" s="2"/>
+      <c r="I490" s="7"/>
+      <c r="J490" s="4"/>
+      <c r="K490" s="2"/>
+      <c r="L490" s="2"/>
+    </row>
+    <row r="491" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A491" s="3"/>
+      <c r="B491" s="3"/>
+      <c r="C491" s="3"/>
+      <c r="D491" s="3"/>
+      <c r="E491" s="3"/>
+      <c r="F491" s="2"/>
+      <c r="G491" s="2"/>
+      <c r="H491" s="2"/>
+      <c r="I491" s="7"/>
+      <c r="J491" s="4"/>
+      <c r="K491" s="2"/>
+      <c r="L491" s="2"/>
+    </row>
+    <row r="492" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A492" s="3"/>
+      <c r="B492" s="3"/>
+      <c r="C492" s="3"/>
+      <c r="D492" s="3"/>
+      <c r="E492" s="3"/>
+      <c r="F492" s="2"/>
+      <c r="G492" s="2"/>
+      <c r="H492" s="2"/>
+      <c r="I492" s="7"/>
+      <c r="J492" s="4"/>
+      <c r="K492" s="2"/>
+      <c r="L492" s="2"/>
+    </row>
+    <row r="493" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A493" s="3"/>
+      <c r="B493" s="3"/>
+      <c r="C493" s="3"/>
+      <c r="D493" s="3"/>
+      <c r="E493" s="3"/>
+      <c r="F493" s="2"/>
+      <c r="G493" s="2"/>
+      <c r="H493" s="2"/>
+      <c r="I493" s="7"/>
+      <c r="J493" s="4"/>
+      <c r="K493" s="2"/>
+      <c r="L493" s="2"/>
+    </row>
+    <row r="494" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A494" s="3"/>
+      <c r="B494" s="3"/>
+      <c r="C494" s="3"/>
+      <c r="D494" s="3"/>
+      <c r="E494" s="3"/>
+      <c r="F494" s="2"/>
+      <c r="G494" s="2"/>
+      <c r="H494" s="2"/>
+      <c r="I494" s="7"/>
+      <c r="J494" s="4"/>
+      <c r="K494" s="2"/>
+      <c r="L494" s="2"/>
+    </row>
+    <row r="495" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A495" s="3"/>
+      <c r="B495" s="3"/>
+      <c r="C495" s="3"/>
+      <c r="D495" s="3"/>
+      <c r="E495" s="3"/>
+      <c r="F495" s="2"/>
+      <c r="G495" s="2"/>
+      <c r="H495" s="2"/>
+      <c r="I495" s="7"/>
+      <c r="J495" s="4"/>
+      <c r="K495" s="2"/>
+      <c r="L495" s="2"/>
+    </row>
+    <row r="496" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A496" s="3"/>
+      <c r="B496" s="3"/>
+      <c r="C496" s="3"/>
+      <c r="D496" s="3"/>
+      <c r="E496" s="3"/>
+      <c r="F496" s="2"/>
+      <c r="G496" s="2"/>
+      <c r="H496" s="2"/>
+      <c r="I496" s="7"/>
+      <c r="J496" s="4"/>
+      <c r="K496" s="2"/>
+      <c r="L496" s="2"/>
+    </row>
+    <row r="497" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A497" s="3"/>
+      <c r="B497" s="3"/>
+      <c r="C497" s="3"/>
+      <c r="D497" s="3"/>
+      <c r="E497" s="3"/>
+      <c r="F497" s="2"/>
+      <c r="G497" s="2"/>
+      <c r="H497" s="2"/>
+      <c r="I497" s="7"/>
+      <c r="J497" s="4"/>
+      <c r="K497" s="2"/>
+      <c r="L497" s="2"/>
+    </row>
+    <row r="498" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A498" s="3"/>
+      <c r="B498" s="3"/>
+      <c r="C498" s="3"/>
+      <c r="D498" s="3"/>
+      <c r="E498" s="3"/>
+      <c r="F498" s="2"/>
+      <c r="G498" s="2"/>
+      <c r="H498" s="2"/>
+      <c r="I498" s="7"/>
+      <c r="J498" s="4"/>
+      <c r="K498" s="2"/>
+      <c r="L498" s="2"/>
+    </row>
+    <row r="499" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A499" s="3"/>
+      <c r="B499" s="3"/>
+      <c r="C499" s="3"/>
+      <c r="D499" s="3"/>
+      <c r="E499" s="3"/>
+      <c r="F499" s="2"/>
+      <c r="G499" s="2"/>
+      <c r="H499" s="2"/>
+      <c r="I499" s="7"/>
+      <c r="J499" s="4"/>
+      <c r="K499" s="2"/>
+      <c r="L499" s="2"/>
+    </row>
+    <row r="500" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A500" s="3"/>
+      <c r="B500" s="3"/>
+      <c r="C500" s="3"/>
+      <c r="D500" s="3"/>
+      <c r="E500" s="3"/>
+      <c r="F500" s="2"/>
+      <c r="G500" s="2"/>
+      <c r="H500" s="2"/>
+      <c r="I500" s="7"/>
+      <c r="J500" s="4"/>
+      <c r="K500" s="2"/>
+      <c r="L500" s="2"/>
+    </row>
+    <row r="501" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A501" s="3"/>
+      <c r="B501" s="3"/>
+      <c r="C501" s="3"/>
+      <c r="D501" s="3"/>
+      <c r="E501" s="3"/>
+      <c r="F501" s="2"/>
+      <c r="G501" s="2"/>
+      <c r="H501" s="2"/>
+      <c r="I501" s="7"/>
+      <c r="J501" s="4"/>
+      <c r="K501" s="2"/>
+      <c r="L501" s="2"/>
+    </row>
+    <row r="502" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A502" s="3"/>
+      <c r="B502" s="3"/>
+      <c r="C502" s="3"/>
+      <c r="D502" s="3"/>
+      <c r="E502" s="3"/>
+      <c r="F502" s="2"/>
+      <c r="G502" s="2"/>
+      <c r="H502" s="2"/>
+      <c r="I502" s="7"/>
+      <c r="J502" s="4"/>
+      <c r="K502" s="2"/>
+      <c r="L502" s="2"/>
+    </row>
+    <row r="503" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A503" s="3"/>
+      <c r="B503" s="3"/>
+      <c r="C503" s="3"/>
+      <c r="D503" s="3"/>
+      <c r="E503" s="3"/>
+      <c r="F503" s="2"/>
+      <c r="G503" s="2"/>
+      <c r="H503" s="2"/>
+      <c r="I503" s="7"/>
+      <c r="J503" s="4"/>
+      <c r="K503" s="2"/>
+      <c r="L503" s="2"/>
+    </row>
+    <row r="504" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A504" s="3"/>
+      <c r="B504" s="3"/>
+      <c r="C504" s="3"/>
+      <c r="D504" s="3"/>
+      <c r="E504" s="3"/>
+      <c r="F504" s="2"/>
+      <c r="G504" s="2"/>
+      <c r="H504" s="2"/>
+      <c r="I504" s="7"/>
+      <c r="J504" s="4"/>
+      <c r="K504" s="2"/>
+      <c r="L504" s="2"/>
+    </row>
+    <row r="505" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A505" s="3"/>
+      <c r="B505" s="3"/>
+      <c r="C505" s="3"/>
+      <c r="D505" s="3"/>
+      <c r="E505" s="3"/>
+      <c r="F505" s="2"/>
+      <c r="G505" s="2"/>
+      <c r="H505" s="2"/>
+      <c r="I505" s="7"/>
+      <c r="J505" s="4"/>
+      <c r="K505" s="2"/>
+      <c r="L505" s="2"/>
+    </row>
+    <row r="506" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A506" s="3"/>
+      <c r="B506" s="3"/>
+      <c r="C506" s="3"/>
+      <c r="D506" s="3"/>
+      <c r="E506" s="3"/>
+      <c r="F506" s="2"/>
+      <c r="G506" s="2"/>
+      <c r="H506" s="2"/>
+      <c r="I506" s="7"/>
+      <c r="J506" s="4"/>
+      <c r="K506" s="2"/>
+      <c r="L506" s="2"/>
+    </row>
+    <row r="507" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A507" s="3"/>
+      <c r="B507" s="3"/>
+      <c r="C507" s="3"/>
+      <c r="D507" s="3"/>
+      <c r="E507" s="3"/>
+      <c r="F507" s="2"/>
+      <c r="G507" s="2"/>
+      <c r="H507" s="2"/>
+      <c r="I507" s="7"/>
+      <c r="J507" s="4"/>
+      <c r="K507" s="2"/>
+      <c r="L507" s="2"/>
+    </row>
+    <row r="508" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A508" s="3"/>
+      <c r="B508" s="3"/>
+      <c r="C508" s="3"/>
+      <c r="D508" s="3"/>
+      <c r="E508" s="3"/>
+      <c r="F508" s="2"/>
+      <c r="G508" s="2"/>
+      <c r="H508" s="2"/>
+      <c r="I508" s="7"/>
+      <c r="J508" s="4"/>
+      <c r="K508" s="2"/>
+      <c r="L508" s="2"/>
+    </row>
+    <row r="509" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A509" s="3"/>
+      <c r="B509" s="3"/>
+      <c r="C509" s="3"/>
+      <c r="D509" s="3"/>
+      <c r="E509" s="3"/>
+      <c r="F509" s="2"/>
+      <c r="G509" s="2"/>
+      <c r="H509" s="2"/>
+      <c r="I509" s="7"/>
+      <c r="J509" s="4"/>
+      <c r="K509" s="2"/>
+      <c r="L509" s="2"/>
+    </row>
+    <row r="510" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A510" s="3"/>
+      <c r="B510" s="3"/>
+      <c r="C510" s="3"/>
+      <c r="D510" s="3"/>
+      <c r="E510" s="3"/>
+      <c r="F510" s="2"/>
+      <c r="G510" s="2"/>
+      <c r="H510" s="2"/>
+      <c r="I510" s="7"/>
+      <c r="J510" s="4"/>
+      <c r="K510" s="2"/>
+      <c r="L510" s="2"/>
+    </row>
+    <row r="511" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A511" s="3"/>
+      <c r="B511" s="3"/>
+      <c r="C511" s="3"/>
+      <c r="D511" s="3"/>
+      <c r="E511" s="3"/>
+      <c r="F511" s="2"/>
+      <c r="G511" s="2"/>
+      <c r="H511" s="2"/>
+      <c r="I511" s="7"/>
+      <c r="J511" s="4"/>
+      <c r="K511" s="2"/>
+      <c r="L511" s="2"/>
+    </row>
+    <row r="512" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A512" s="3"/>
+      <c r="B512" s="3"/>
+      <c r="C512" s="3"/>
+      <c r="D512" s="3"/>
+      <c r="E512" s="3"/>
+      <c r="F512" s="2"/>
+      <c r="G512" s="2"/>
+      <c r="H512" s="2"/>
+      <c r="I512" s="7"/>
+      <c r="J512" s="4"/>
+      <c r="K512" s="2"/>
+      <c r="L512" s="2"/>
+    </row>
+    <row r="513" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A513" s="3"/>
+      <c r="B513" s="3"/>
+      <c r="C513" s="3"/>
+      <c r="D513" s="3"/>
+      <c r="E513" s="3"/>
+      <c r="F513" s="2"/>
+      <c r="G513" s="2"/>
+      <c r="H513" s="2"/>
+      <c r="I513" s="7"/>
+      <c r="J513" s="4"/>
+      <c r="K513" s="2"/>
+      <c r="L513" s="2"/>
+    </row>
+    <row r="514" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A514" s="3"/>
+      <c r="B514" s="3"/>
+      <c r="C514" s="3"/>
+      <c r="D514" s="3"/>
+      <c r="E514" s="3"/>
+      <c r="F514" s="2"/>
+      <c r="G514" s="2"/>
+      <c r="H514" s="2"/>
+      <c r="I514" s="7"/>
+      <c r="J514" s="4"/>
+      <c r="K514" s="2"/>
+      <c r="L514" s="2"/>
+    </row>
+    <row r="515" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A515" s="3"/>
+      <c r="B515" s="3"/>
+      <c r="C515" s="3"/>
+      <c r="D515" s="3"/>
+      <c r="E515" s="3"/>
+      <c r="F515" s="2"/>
+      <c r="G515" s="2"/>
+      <c r="H515" s="2"/>
+      <c r="I515" s="7"/>
+      <c r="J515" s="4"/>
+      <c r="K515" s="2"/>
+      <c r="L515" s="2"/>
+    </row>
+    <row r="516" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A516" s="3"/>
+      <c r="B516" s="3"/>
+      <c r="C516" s="3"/>
+      <c r="D516" s="3"/>
+      <c r="E516" s="3"/>
+      <c r="F516" s="2"/>
+      <c r="G516" s="2"/>
+      <c r="H516" s="2"/>
+      <c r="I516" s="7"/>
+      <c r="J516" s="4"/>
+      <c r="K516" s="2"/>
+      <c r="L516" s="2"/>
+    </row>
+    <row r="517" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A517" s="3"/>
+      <c r="B517" s="3"/>
+      <c r="C517" s="3"/>
+      <c r="D517" s="3"/>
+      <c r="E517" s="3"/>
+      <c r="F517" s="2"/>
+      <c r="G517" s="2"/>
+      <c r="H517" s="2"/>
+      <c r="I517" s="7"/>
+      <c r="J517" s="4"/>
+      <c r="K517" s="2"/>
+      <c r="L517" s="2"/>
+    </row>
+    <row r="518" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A518" s="3"/>
+      <c r="B518" s="3"/>
+      <c r="C518" s="3"/>
+      <c r="D518" s="3"/>
+      <c r="E518" s="3"/>
+      <c r="F518" s="2"/>
+      <c r="G518" s="2"/>
+      <c r="H518" s="2"/>
+      <c r="I518" s="7"/>
+      <c r="J518" s="4"/>
+      <c r="K518" s="2"/>
+      <c r="L518" s="2"/>
+    </row>
+    <row r="519" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A519" s="3"/>
+      <c r="B519" s="3"/>
+      <c r="C519" s="3"/>
+      <c r="D519" s="3"/>
+      <c r="E519" s="3"/>
+      <c r="F519" s="2"/>
+      <c r="G519" s="2"/>
+      <c r="H519" s="2"/>
+      <c r="I519" s="7"/>
+      <c r="J519" s="4"/>
+      <c r="K519" s="2"/>
+      <c r="L519" s="2"/>
+    </row>
+    <row r="520" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A520" s="3"/>
+      <c r="B520" s="3"/>
+      <c r="C520" s="3"/>
+      <c r="D520" s="3"/>
+      <c r="E520" s="3"/>
+      <c r="F520" s="2"/>
+      <c r="G520" s="2"/>
+      <c r="H520" s="2"/>
+      <c r="I520" s="7"/>
+      <c r="J520" s="4"/>
+      <c r="K520" s="2"/>
+      <c r="L520" s="2"/>
     </row>
   </sheetData>
   <dataConsolidate/>
-  <conditionalFormatting sqref="K2:L12">
-    <cfRule type="notContainsBlanks" priority="7" stopIfTrue="1">
+  <conditionalFormatting sqref="H2:H520">
+    <cfRule type="expression" priority="1" stopIfTrue="1">
+      <formula>H2&gt;0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="2" priority="2" stopIfTrue="1">
+      <formula>B2=1</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="1" priority="3" stopIfTrue="1">
+      <formula>E2=9</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K2:L520">
+    <cfRule type="notContainsBlanks" priority="4" stopIfTrue="1">
       <formula>LEN(TRIM(K2))&gt;0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="0" priority="8" stopIfTrue="1">
+    <cfRule type="expression" dxfId="0" priority="5" stopIfTrue="1">
       <formula>E2=2</formula>
     </cfRule>
   </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G61" xr:uid="{00000000-0002-0000-0000-000000000000}">
+      <formula1>"x"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.70833333333333304" right="0.70833333333333304" top="0.74791666666666701" bottom="0.74791666666666701" header="0" footer="0"/>
   <pageSetup scale="75" orientation="portrait" r:id="rId1"/>
   <headerFooter>
     <oddFooter>&amp;C&amp;P</oddFooter>
   </headerFooter>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="7">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000004000000}">
+          <x14:formula1>
+            <xm:f>DADOS!$F$14:$F$363</xm:f>
+          </x14:formula1>
+          <xm:sqref>H62</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000001000000}">
+          <x14:formula1>
+            <xm:f>DADOS!$A$2:$A$82</xm:f>
+          </x14:formula1>
+          <xm:sqref>A3:A61</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000002000000}">
+          <x14:formula1>
+            <xm:f>DADOS!$B$2:$B$3</xm:f>
+          </x14:formula1>
+          <xm:sqref>C3:C61</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000003000000}">
+          <x14:formula1>
+            <xm:f>DADOS!$E$2:$E$5</xm:f>
+          </x14:formula1>
+          <xm:sqref>B3:B61</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000005000000}">
+          <x14:formula1>
+            <xm:f>DADOS!$F$2:$F$353</xm:f>
+          </x14:formula1>
+          <xm:sqref>H3:H61</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000006000000}">
+          <x14:formula1>
+            <xm:f>DADOS!$D$2:$D$5</xm:f>
+          </x14:formula1>
+          <xm:sqref>E3:E61</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000007000000}">
+          <x14:formula1>
+            <xm:f>DADOS!$C$2:$C$32</xm:f>
+          </x14:formula1>
+          <xm:sqref>D3:D61</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
 </worksheet>
 </file>
 
@@ -1187,33 +8240,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="5" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A2" s="4">
+      <c r="A2" s="6">
         <v>1071</v>
       </c>
       <c r="B2">
         <v>0</v>
       </c>
-      <c r="C2" s="4">
+      <c r="C2" s="6">
         <v>10</v>
       </c>
       <c r="D2">
@@ -1222,18 +8275,18 @@
       <c r="E2">
         <v>1</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="F2" s="9" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A3" s="4">
+      <c r="A3" s="6">
         <v>1081</v>
       </c>
       <c r="B3">
         <v>1</v>
       </c>
-      <c r="C3" s="4">
+      <c r="C3" s="6">
         <v>13</v>
       </c>
       <c r="D3">
@@ -1242,15 +8295,15 @@
       <c r="E3">
         <v>3</v>
       </c>
-      <c r="F3" s="5" t="s">
+      <c r="F3" s="9" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A4" s="4">
+      <c r="A4" s="6">
         <v>1101</v>
       </c>
-      <c r="C4" s="4">
+      <c r="C4" s="6">
         <v>15</v>
       </c>
       <c r="D4">
@@ -1259,15 +8312,15 @@
       <c r="E4">
         <v>4</v>
       </c>
-      <c r="F4" s="5" t="s">
+      <c r="F4" s="9" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A5" s="4">
+      <c r="A5" s="6">
         <v>1191</v>
       </c>
-      <c r="C5" s="4">
+      <c r="C5" s="6">
         <v>21</v>
       </c>
       <c r="D5">
@@ -1276,103 +8329,103 @@
       <c r="E5">
         <v>5</v>
       </c>
-      <c r="F5" s="5" t="s">
+      <c r="F5" s="9" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A6" s="4">
+      <c r="A6" s="6">
         <v>1221</v>
       </c>
-      <c r="C6" s="4">
+      <c r="C6" s="6">
         <v>25</v>
       </c>
-      <c r="F6" s="5" t="s">
+      <c r="F6" s="9" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A7" s="4">
+      <c r="A7" s="6">
         <v>1231</v>
       </c>
-      <c r="C7" s="4">
+      <c r="C7" s="6">
         <v>26</v>
       </c>
-      <c r="F7" s="5" t="s">
+      <c r="F7" s="9" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A8" s="4">
+      <c r="A8" s="6">
         <v>1251</v>
       </c>
-      <c r="C8" s="4">
+      <c r="C8" s="6">
         <v>27</v>
       </c>
-      <c r="F8" s="5" t="s">
+      <c r="F8" s="9" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A9" s="4">
+      <c r="A9" s="6">
         <v>1261</v>
       </c>
-      <c r="C9" s="4">
+      <c r="C9" s="6">
         <v>29</v>
       </c>
-      <c r="F9" s="5" t="s">
+      <c r="F9" s="9" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A10" s="4">
+      <c r="A10" s="6">
         <v>1271</v>
       </c>
-      <c r="C10" s="4">
+      <c r="C10" s="6">
         <v>31</v>
       </c>
-      <c r="F10" s="5" t="s">
+      <c r="F10" s="9" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A11" s="4">
+      <c r="A11" s="6">
         <v>1301</v>
       </c>
-      <c r="C11" s="4">
+      <c r="C11" s="6">
         <v>32</v>
       </c>
-      <c r="F11" s="5" t="s">
+      <c r="F11" s="9" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A12" s="4">
+      <c r="A12" s="6">
         <v>1371</v>
       </c>
-      <c r="C12" s="4">
+      <c r="C12" s="6">
         <v>33</v>
       </c>
-      <c r="F12" s="5" t="s">
+      <c r="F12" s="9" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A13" s="4">
+      <c r="A13" s="6">
         <v>1401</v>
       </c>
-      <c r="C13" s="4">
+      <c r="C13" s="6">
         <v>39</v>
       </c>
-      <c r="F13" s="5" t="s">
+      <c r="F13" s="9" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A14" s="4">
+      <c r="A14" s="6">
         <v>1451</v>
       </c>
-      <c r="C14" s="4">
+      <c r="C14" s="6">
         <v>45</v>
       </c>
       <c r="F14">
@@ -1380,10 +8433,10 @@
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A15" s="4">
+      <c r="A15" s="6">
         <v>1481</v>
       </c>
-      <c r="C15" s="4">
+      <c r="C15" s="6">
         <v>47</v>
       </c>
       <c r="F15">
@@ -1391,10 +8444,10 @@
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A16" s="4">
+      <c r="A16" s="6">
         <v>1491</v>
       </c>
-      <c r="C16" s="4">
+      <c r="C16" s="6">
         <v>48</v>
       </c>
       <c r="F16">
@@ -1402,10 +8455,10 @@
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A17" s="4">
+      <c r="A17" s="6">
         <v>1501</v>
       </c>
-      <c r="C17" s="4">
+      <c r="C17" s="6">
         <v>49</v>
       </c>
       <c r="F17">
@@ -1413,10 +8466,10 @@
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A18" s="4">
+      <c r="A18" s="6">
         <v>1511</v>
       </c>
-      <c r="C18" s="4">
+      <c r="C18" s="6">
         <v>50</v>
       </c>
       <c r="F18">
@@ -1424,10 +8477,10 @@
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A19" s="4">
+      <c r="A19" s="6">
         <v>1521</v>
       </c>
-      <c r="C19" s="4">
+      <c r="C19" s="6">
         <v>52</v>
       </c>
       <c r="F19">
@@ -1435,10 +8488,10 @@
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A20" s="4">
+      <c r="A20" s="6">
         <v>1541</v>
       </c>
-      <c r="C20" s="4">
+      <c r="C20" s="6">
         <v>54</v>
       </c>
       <c r="F20">
@@ -1446,10 +8499,10 @@
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A21" s="4">
+      <c r="A21" s="6">
         <v>1631</v>
       </c>
-      <c r="C21" s="4">
+      <c r="C21" s="6">
         <v>59</v>
       </c>
       <c r="F21">
@@ -1457,10 +8510,10 @@
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A22" s="4">
+      <c r="A22" s="6">
         <v>1711</v>
       </c>
-      <c r="C22" s="4">
+      <c r="C22" s="6">
         <v>60</v>
       </c>
       <c r="F22">
@@ -1468,10 +8521,10 @@
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A23" s="4">
+      <c r="A23" s="6">
         <v>1721</v>
       </c>
-      <c r="C23" s="4">
+      <c r="C23" s="6">
         <v>61</v>
       </c>
       <c r="F23">
@@ -1479,10 +8532,10 @@
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A24" s="4">
+      <c r="A24" s="6">
         <v>1911</v>
       </c>
-      <c r="C24" s="4">
+      <c r="C24" s="6">
         <v>71</v>
       </c>
       <c r="F24">
@@ -1490,10 +8543,10 @@
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A25" s="4">
+      <c r="A25" s="6">
         <v>1915</v>
       </c>
-      <c r="C25" s="4">
+      <c r="C25" s="6">
         <v>72</v>
       </c>
       <c r="F25">
@@ -1501,10 +8554,10 @@
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A26" s="4">
+      <c r="A26" s="6">
         <v>1941</v>
       </c>
-      <c r="C26" s="4">
+      <c r="C26" s="6">
         <v>80</v>
       </c>
       <c r="F26">
@@ -1512,10 +8565,10 @@
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A27" s="4">
+      <c r="A27" s="6">
         <v>2011</v>
       </c>
-      <c r="C27" s="4">
+      <c r="C27" s="6">
         <v>82</v>
       </c>
       <c r="F27">
@@ -1523,10 +8576,10 @@
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A28" s="4">
+      <c r="A28" s="6">
         <v>2041</v>
       </c>
-      <c r="C28" s="4">
+      <c r="C28" s="6">
         <v>83</v>
       </c>
       <c r="F28">
@@ -1534,10 +8587,10 @@
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A29" s="4">
+      <c r="A29" s="6">
         <v>2061</v>
       </c>
-      <c r="C29" s="4">
+      <c r="C29" s="6">
         <v>89</v>
       </c>
       <c r="F29">
@@ -1545,10 +8598,10 @@
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A30" s="4">
+      <c r="A30" s="6">
         <v>2071</v>
       </c>
-      <c r="C30" s="4">
+      <c r="C30" s="6">
         <v>91</v>
       </c>
       <c r="F30">
@@ -1556,10 +8609,10 @@
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A31" s="4">
+      <c r="A31" s="6">
         <v>2091</v>
       </c>
-      <c r="C31" s="4">
+      <c r="C31" s="6">
         <v>94</v>
       </c>
       <c r="F31">
@@ -1567,10 +8620,10 @@
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A32" s="4">
+      <c r="A32" s="6">
         <v>2101</v>
       </c>
-      <c r="C32" s="4">
+      <c r="C32" s="6">
         <v>95</v>
       </c>
       <c r="F32">
@@ -1578,7 +8631,7 @@
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A33" s="4">
+      <c r="A33" s="6">
         <v>2121</v>
       </c>
       <c r="F33">
@@ -1586,7 +8639,7 @@
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A34" s="4">
+      <c r="A34" s="6">
         <v>2151</v>
       </c>
       <c r="F34">
@@ -1594,7 +8647,7 @@
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A35" s="4">
+      <c r="A35" s="6">
         <v>2161</v>
       </c>
       <c r="F35">
@@ -1602,7 +8655,7 @@
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A36" s="4">
+      <c r="A36" s="6">
         <v>2171</v>
       </c>
       <c r="F36">
@@ -1610,7 +8663,7 @@
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A37" s="4">
+      <c r="A37" s="6">
         <v>2181</v>
       </c>
       <c r="F37">
@@ -1618,7 +8671,7 @@
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A38" s="4">
+      <c r="A38" s="6">
         <v>2201</v>
       </c>
       <c r="F38">
@@ -1626,7 +8679,7 @@
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A39" s="4">
+      <c r="A39" s="6">
         <v>2211</v>
       </c>
       <c r="F39">
@@ -1634,7 +8687,7 @@
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A40" s="4">
+      <c r="A40" s="6">
         <v>2241</v>
       </c>
       <c r="F40">
@@ -1642,7 +8695,7 @@
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A41" s="4">
+      <c r="A41" s="6">
         <v>2251</v>
       </c>
       <c r="F41">
@@ -1650,7 +8703,7 @@
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A42" s="4">
+      <c r="A42" s="6">
         <v>2261</v>
       </c>
       <c r="F42">
@@ -1658,7 +8711,7 @@
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A43" s="4">
+      <c r="A43" s="6">
         <v>2271</v>
       </c>
       <c r="F43">
@@ -1666,7 +8719,7 @@
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A44" s="4">
+      <c r="A44" s="6">
         <v>2281</v>
       </c>
       <c r="F44">
@@ -1674,7 +8727,7 @@
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A45" s="4">
+      <c r="A45" s="6">
         <v>2301</v>
       </c>
       <c r="F45">
@@ -1682,7 +8735,7 @@
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A46" s="4">
+      <c r="A46" s="6">
         <v>2311</v>
       </c>
       <c r="F46">
@@ -1690,7 +8743,7 @@
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A47" s="4">
+      <c r="A47" s="6">
         <v>2321</v>
       </c>
       <c r="F47">
@@ -1698,7 +8751,7 @@
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A48" s="4">
+      <c r="A48" s="6">
         <v>2351</v>
       </c>
       <c r="F48">
@@ -1706,7 +8759,7 @@
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A49" s="4">
+      <c r="A49" s="6">
         <v>2371</v>
       </c>
       <c r="F49">
@@ -1714,7 +8767,7 @@
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A50" s="4">
+      <c r="A50" s="6">
         <v>2421</v>
       </c>
       <c r="F50">
@@ -1722,7 +8775,7 @@
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A51" s="4">
+      <c r="A51" s="6">
         <v>2431</v>
       </c>
       <c r="F51">
@@ -1730,7 +8783,7 @@
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A52" s="4">
+      <c r="A52" s="6">
         <v>2441</v>
       </c>
       <c r="F52">
@@ -1738,7 +8791,7 @@
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A53" s="4">
+      <c r="A53" s="6">
         <v>2461</v>
       </c>
       <c r="F53">
@@ -1746,7 +8799,7 @@
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A54" s="4">
+      <c r="A54" s="6">
         <v>3041</v>
       </c>
       <c r="F54">
@@ -1754,7 +8807,7 @@
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A55" s="4">
+      <c r="A55" s="6">
         <v>3051</v>
       </c>
       <c r="F55">
@@ -1762,7 +8815,7 @@
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A56" s="4">
+      <c r="A56" s="6">
         <v>3151</v>
       </c>
       <c r="F56">
@@ -1770,7 +8823,7 @@
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A57" s="4">
+      <c r="A57" s="6">
         <v>4091</v>
       </c>
       <c r="F57">
@@ -1778,7 +8831,7 @@
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A58" s="4">
+      <c r="A58" s="6">
         <v>4101</v>
       </c>
       <c r="F58">
@@ -1786,7 +8839,7 @@
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A59" s="4">
+      <c r="A59" s="6">
         <v>4111</v>
       </c>
       <c r="F59">
@@ -1794,7 +8847,7 @@
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A60" s="4">
+      <c r="A60" s="6">
         <v>4141</v>
       </c>
       <c r="F60">
@@ -1802,7 +8855,7 @@
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A61" s="4">
+      <c r="A61" s="6">
         <v>4151</v>
       </c>
       <c r="F61">
@@ -1810,7 +8863,7 @@
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A62" s="4">
+      <c r="A62" s="6">
         <v>4171</v>
       </c>
       <c r="F62">
@@ -1818,7 +8871,7 @@
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A63" s="4">
+      <c r="A63" s="6">
         <v>4251</v>
       </c>
       <c r="F63">
@@ -1826,7 +8879,7 @@
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A64" s="4">
+      <c r="A64" s="6">
         <v>4291</v>
       </c>
       <c r="F64">
@@ -1834,7 +8887,7 @@
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A65" s="4">
+      <c r="A65" s="6">
         <v>4321</v>
       </c>
       <c r="F65">
@@ -1842,7 +8895,7 @@
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A66" s="4">
+      <c r="A66" s="6">
         <v>4331</v>
       </c>
       <c r="F66">
@@ -1850,7 +8903,7 @@
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A67" s="4">
+      <c r="A67" s="6">
         <v>4341</v>
       </c>
       <c r="F67">
@@ -1858,7 +8911,7 @@
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A68" s="4">
+      <c r="A68" s="6">
         <v>4381</v>
       </c>
       <c r="F68">
@@ -1866,7 +8919,7 @@
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A69" s="4">
+      <c r="A69" s="6">
         <v>4421</v>
       </c>
       <c r="F69">
@@ -1874,7 +8927,7 @@
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A70" s="4">
+      <c r="A70" s="6">
         <v>4491</v>
       </c>
       <c r="F70">
@@ -1882,7 +8935,7 @@
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A71" s="4">
+      <c r="A71" s="6">
         <v>4541</v>
       </c>
       <c r="F71">
@@ -1890,7 +8943,7 @@
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A72" s="4">
+      <c r="A72" s="6">
         <v>4551</v>
       </c>
       <c r="F72">
@@ -1898,7 +8951,7 @@
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A73" s="4">
+      <c r="A73" s="6">
         <v>4601</v>
       </c>
       <c r="F73">
@@ -1906,7 +8959,7 @@
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A74" s="4">
+      <c r="A74" s="6">
         <v>4621</v>
       </c>
       <c r="F74">
@@ -1914,7 +8967,7 @@
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A75" s="4">
+      <c r="A75" s="6">
         <v>4631</v>
       </c>
       <c r="F75">
@@ -1922,7 +8975,7 @@
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A76" s="4">
+      <c r="A76" s="6">
         <v>4641</v>
       </c>
       <c r="F76">
@@ -1930,7 +8983,7 @@
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A77" s="4">
+      <c r="A77" s="6">
         <v>4651</v>
       </c>
       <c r="F77">
@@ -1938,7 +8991,7 @@
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A78" s="4">
+      <c r="A78" s="6">
         <v>4661</v>
       </c>
       <c r="F78">
@@ -1946,7 +8999,7 @@
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A79" s="4">
+      <c r="A79" s="6">
         <v>4671</v>
       </c>
       <c r="F79">
@@ -1954,7 +9007,7 @@
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A80" s="4">
+      <c r="A80" s="6">
         <v>4701</v>
       </c>
       <c r="F80">
@@ -1962,7 +9015,7 @@
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A81" s="4">
+      <c r="A81" s="6">
         <v>4711</v>
       </c>
       <c r="F81">
@@ -1970,7 +9023,7 @@
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A82" s="4">
+      <c r="A82" s="6">
         <v>4721</v>
       </c>
       <c r="F82">

--- a/data/remanejamento.xlsx
+++ b/data/remanejamento.xlsx
@@ -1,24 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\guilhermemelof\code\splor-mg\siafi-automacao-cota\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34E0ED5D-E8DD-4DD3-B23B-73A4BB4F7D9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B4C85F4-DE41-4A33-B9A0-48623C19BC30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CombinedSheet" sheetId="2" r:id="rId1"/>
-    <sheet name="DADOS" sheetId="3" state="hidden" r:id="rId2"/>
+    <sheet name="Planilha1" sheetId="4" r:id="rId2"/>
+    <sheet name="DADOS" sheetId="3" state="hidden" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">CombinedSheet!$A$1:$Q$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">DADOS!$A$1:$F$352</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">DADOS!$A$1:$F$352</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
@@ -30,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="29">
   <si>
     <t>UO_COD</t>
   </si>
@@ -238,7 +239,7 @@
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -261,6 +262,12 @@
       <patternFill patternType="solid">
         <fgColor theme="0"/>
         <bgColor theme="0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
   </fills>
@@ -388,7 +395,7 @@
     <xf numFmtId="43" fontId="6" fillId="0" borderId="1" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="1" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -437,6 +444,15 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="43" fontId="10" fillId="0" borderId="3" xfId="26" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -788,74 +804,90 @@
     </row>
     <row r="2" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3">
-        <v>1231</v>
+        <v>1081</v>
       </c>
       <c r="B2" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C2" s="3">
         <v>0</v>
       </c>
       <c r="D2" s="3">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E2" s="3">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="F2" s="15">
-        <v>4419</v>
-      </c>
-      <c r="G2" s="15" t="s">
-        <v>28</v>
-      </c>
-      <c r="H2" s="15"/>
-      <c r="I2" s="16"/>
-      <c r="J2" s="17">
-        <v>18380103.300000001</v>
-      </c>
+        <v>7803</v>
+      </c>
+      <c r="G2" s="15"/>
+      <c r="H2" s="15">
+        <v>9116</v>
+      </c>
+      <c r="I2" s="16">
+        <v>7000000</v>
+      </c>
+      <c r="J2" s="17"/>
       <c r="K2" s="2"/>
       <c r="L2" s="2"/>
     </row>
     <row r="3" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="11">
-        <v>1231</v>
+        <v>1081</v>
       </c>
       <c r="B3" s="11">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C3" s="11">
         <v>0</v>
       </c>
       <c r="D3" s="11">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E3" s="11">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="F3" s="12">
-        <v>4420</v>
-      </c>
-      <c r="G3" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="H3" s="12"/>
-      <c r="I3" s="13"/>
-      <c r="J3" s="14">
-        <v>888800.80999999994</v>
-      </c>
+        <v>7803</v>
+      </c>
+      <c r="G3" s="12"/>
+      <c r="H3" s="12">
+        <v>9103</v>
+      </c>
+      <c r="I3" s="13">
+        <v>10000000</v>
+      </c>
+      <c r="J3" s="14"/>
       <c r="K3" s="2"/>
       <c r="L3" s="2"/>
     </row>
     <row r="4" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="3"/>
-      <c r="B4" s="3"/>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3"/>
-      <c r="E4" s="3"/>
-      <c r="F4" s="2"/>
+      <c r="A4" s="3">
+        <v>1081</v>
+      </c>
+      <c r="B4" s="3">
+        <v>3</v>
+      </c>
+      <c r="C4" s="3">
+        <v>0</v>
+      </c>
+      <c r="D4" s="3">
+        <v>10</v>
+      </c>
+      <c r="E4" s="3">
+        <v>9</v>
+      </c>
+      <c r="F4" s="2">
+        <v>7803</v>
+      </c>
       <c r="G4" s="2"/>
-      <c r="H4" s="2"/>
-      <c r="I4" s="7"/>
+      <c r="H4" s="2">
+        <v>1310</v>
+      </c>
+      <c r="I4" s="7">
+        <v>3000000</v>
+      </c>
       <c r="J4" s="4"/>
       <c r="K4" s="2"/>
       <c r="L4" s="2"/>
@@ -866,15 +898,31 @@
       <c r="Q4" s="8"/>
     </row>
     <row r="5" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="3"/>
-      <c r="B5" s="3"/>
-      <c r="C5" s="3"/>
-      <c r="D5" s="3"/>
-      <c r="E5" s="3"/>
-      <c r="F5" s="2"/>
+      <c r="A5" s="3">
+        <v>1081</v>
+      </c>
+      <c r="B5" s="3">
+        <v>1</v>
+      </c>
+      <c r="C5" s="3">
+        <v>0</v>
+      </c>
+      <c r="D5" s="3">
+        <v>10</v>
+      </c>
+      <c r="E5" s="3">
+        <v>9</v>
+      </c>
+      <c r="F5" s="2">
+        <v>7803</v>
+      </c>
       <c r="G5" s="2"/>
-      <c r="H5" s="2"/>
-      <c r="I5" s="7"/>
+      <c r="H5" s="2">
+        <v>9103</v>
+      </c>
+      <c r="I5" s="7">
+        <v>10000000</v>
+      </c>
       <c r="J5" s="4"/>
       <c r="K5" s="2"/>
       <c r="L5" s="2"/>
@@ -8232,6 +8280,43 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{905606C8-2DA6-4405-B9A4-3DDB09CD6E91}">
+  <dimension ref="A1:I1"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:9" ht="15" x14ac:dyDescent="0.25">
+      <c r="A1" s="18">
+        <v>1261</v>
+      </c>
+      <c r="B1" s="18">
+        <v>3</v>
+      </c>
+      <c r="C1" s="18">
+        <v>0</v>
+      </c>
+      <c r="D1" s="18">
+        <v>10</v>
+      </c>
+      <c r="E1" s="18">
+        <v>1</v>
+      </c>
+      <c r="F1" s="19">
+        <v>2122</v>
+      </c>
+      <c r="G1" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="H1" s="19"/>
+      <c r="I1" s="20">
+        <v>3571806.82</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:F353"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
@@ -10398,6 +10483,17 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="b91e7f20-fe0a-487d-91a9-605ac1c64acf" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="6f4338ef-addb-4c87-aefe-1895241b335f">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100B08D58FADB61F04EBBB4F355C06EFBED" ma:contentTypeVersion="19" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="b1e0f6055e0e9a4b9e75d6c71ee7de91">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="6f4338ef-addb-4c87-aefe-1895241b335f" xmlns:ns3="b91e7f20-fe0a-487d-91a9-605ac1c64acf" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="b43930f3490e4d4da1ab3f8da7df6f51" ns2:_="" ns3:_="">
     <xsd:import namespace="6f4338ef-addb-4c87-aefe-1895241b335f"/>
@@ -10658,7 +10754,7 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -10667,18 +10763,18 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="b91e7f20-fe0a-487d-91a9-605ac1c64acf" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="6f4338ef-addb-4c87-aefe-1895241b335f">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{78AD39BD-2F37-414E-8652-4DCF45E4F24B}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="b91e7f20-fe0a-487d-91a9-605ac1c64acf"/>
+    <ds:schemaRef ds:uri="6f4338ef-addb-4c87-aefe-1895241b335f"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9E3F47A8-3F3E-4CD4-856C-EFC2EF6F2BBF}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -10697,21 +10793,10 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A11A0DA3-0444-476A-A216-870D1067E696}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{78AD39BD-2F37-414E-8652-4DCF45E4F24B}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="b91e7f20-fe0a-487d-91a9-605ac1c64acf"/>
-    <ds:schemaRef ds:uri="6f4338ef-addb-4c87-aefe-1895241b335f"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/data/remanejamento.xlsx
+++ b/data/remanejamento.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\guilhermemelof\code\splor-mg\siafi-automacao-cota\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\brunohorosa\code\splor-mg\siafi-automacao-cota\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B4C85F4-DE41-4A33-B9A0-48623C19BC30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCC5A4A7-CD64-403F-A0EB-C7F6C0A33E69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CombinedSheet" sheetId="2" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="29">
   <si>
     <t>UO_COD</t>
   </si>
@@ -129,7 +129,7 @@
     <numFmt numFmtId="164" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* \-??_);_(@_)"/>
     <numFmt numFmtId="165" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@"/>
   </numFmts>
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="17" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -219,11 +219,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -239,7 +234,7 @@
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -256,12 +251,6 @@
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.39997558519241921"/>
         <bgColor rgb="FF953734"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0"/>
-        <bgColor theme="0"/>
       </patternFill>
     </fill>
     <fill>
@@ -395,7 +384,7 @@
     <xf numFmtId="43" fontId="6" fillId="0" borderId="1" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="1" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -425,16 +414,13 @@
     <xf numFmtId="10" fontId="12" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="14" fillId="4" borderId="4" xfId="34" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="34" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="34" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="15" fillId="0" borderId="5" xfId="34" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="165" fontId="16" fillId="0" borderId="5" xfId="34" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="17" fillId="0" borderId="5" xfId="34" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="33" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -446,7 +432,7 @@
     <xf numFmtId="43" fontId="10" fillId="0" borderId="3" xfId="26" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -804,7 +790,7 @@
     </row>
     <row r="2" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3">
-        <v>1081</v>
+        <v>1261</v>
       </c>
       <c r="B2" s="3">
         <v>3</v>
@@ -816,78 +802,62 @@
         <v>10</v>
       </c>
       <c r="E2" s="3">
-        <v>9</v>
-      </c>
-      <c r="F2" s="15">
-        <v>7803</v>
-      </c>
-      <c r="G2" s="15"/>
-      <c r="H2" s="15">
-        <v>9116</v>
-      </c>
-      <c r="I2" s="16">
-        <v>7000000</v>
-      </c>
-      <c r="J2" s="17"/>
+        <v>1</v>
+      </c>
+      <c r="F2" s="14">
+        <v>4547</v>
+      </c>
+      <c r="G2" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="H2" s="14"/>
+      <c r="I2" s="15">
+        <v>1</v>
+      </c>
+      <c r="J2" s="16"/>
       <c r="K2" s="2"/>
       <c r="L2" s="2"/>
     </row>
     <row r="3" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="11">
-        <v>1081</v>
-      </c>
-      <c r="B3" s="11">
+      <c r="A3" s="3">
+        <v>1261</v>
+      </c>
+      <c r="B3" s="3">
         <v>3</v>
       </c>
-      <c r="C3" s="11">
+      <c r="C3" s="3">
         <v>0</v>
       </c>
-      <c r="D3" s="11">
+      <c r="D3" s="3">
         <v>10</v>
       </c>
-      <c r="E3" s="11">
-        <v>9</v>
-      </c>
-      <c r="F3" s="12">
-        <v>7803</v>
-      </c>
-      <c r="G3" s="12"/>
-      <c r="H3" s="12">
-        <v>9103</v>
-      </c>
-      <c r="I3" s="13">
-        <v>10000000</v>
-      </c>
-      <c r="J3" s="14"/>
+      <c r="E3" s="3">
+        <v>1</v>
+      </c>
+      <c r="F3" s="14">
+        <v>4547</v>
+      </c>
+      <c r="G3" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="H3" s="11"/>
+      <c r="I3" s="12"/>
+      <c r="J3" s="13">
+        <v>1</v>
+      </c>
       <c r="K3" s="2"/>
       <c r="L3" s="2"/>
     </row>
     <row r="4" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="3">
-        <v>1081</v>
-      </c>
-      <c r="B4" s="3">
-        <v>3</v>
-      </c>
-      <c r="C4" s="3">
-        <v>0</v>
-      </c>
-      <c r="D4" s="3">
-        <v>10</v>
-      </c>
-      <c r="E4" s="3">
-        <v>9</v>
-      </c>
-      <c r="F4" s="2">
-        <v>7803</v>
-      </c>
+      <c r="A4" s="3"/>
+      <c r="B4" s="3"/>
+      <c r="C4" s="3"/>
+      <c r="D4" s="3"/>
+      <c r="E4" s="3"/>
+      <c r="F4" s="2"/>
       <c r="G4" s="2"/>
-      <c r="H4" s="2">
-        <v>1310</v>
-      </c>
-      <c r="I4" s="7">
-        <v>3000000</v>
-      </c>
+      <c r="H4" s="2"/>
+      <c r="I4" s="7"/>
       <c r="J4" s="4"/>
       <c r="K4" s="2"/>
       <c r="L4" s="2"/>
@@ -898,31 +868,15 @@
       <c r="Q4" s="8"/>
     </row>
     <row r="5" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="3">
-        <v>1081</v>
-      </c>
-      <c r="B5" s="3">
-        <v>1</v>
-      </c>
-      <c r="C5" s="3">
-        <v>0</v>
-      </c>
-      <c r="D5" s="3">
-        <v>10</v>
-      </c>
-      <c r="E5" s="3">
-        <v>9</v>
-      </c>
-      <c r="F5" s="2">
-        <v>7803</v>
-      </c>
+      <c r="A5" s="3"/>
+      <c r="B5" s="3"/>
+      <c r="C5" s="3"/>
+      <c r="D5" s="3"/>
+      <c r="E5" s="3"/>
+      <c r="F5" s="2"/>
       <c r="G5" s="2"/>
-      <c r="H5" s="2">
-        <v>9103</v>
-      </c>
-      <c r="I5" s="7">
-        <v>10000000</v>
-      </c>
+      <c r="H5" s="2"/>
+      <c r="I5" s="7"/>
       <c r="J5" s="4"/>
       <c r="K5" s="2"/>
       <c r="L5" s="2"/>
@@ -8241,19 +8195,19 @@
           <x14:formula1>
             <xm:f>DADOS!$A$2:$A$82</xm:f>
           </x14:formula1>
-          <xm:sqref>A3:A61</xm:sqref>
+          <xm:sqref>A4:A61</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000002000000}">
           <x14:formula1>
             <xm:f>DADOS!$B$2:$B$3</xm:f>
           </x14:formula1>
-          <xm:sqref>C3:C61</xm:sqref>
+          <xm:sqref>C4:C61</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000003000000}">
           <x14:formula1>
             <xm:f>DADOS!$E$2:$E$5</xm:f>
           </x14:formula1>
-          <xm:sqref>B3:B61</xm:sqref>
+          <xm:sqref>B4:B61</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000005000000}">
           <x14:formula1>
@@ -8265,13 +8219,13 @@
           <x14:formula1>
             <xm:f>DADOS!$D$2:$D$5</xm:f>
           </x14:formula1>
-          <xm:sqref>E3:E61</xm:sqref>
+          <xm:sqref>E4:E61</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000007000000}">
           <x14:formula1>
             <xm:f>DADOS!$C$2:$C$32</xm:f>
           </x14:formula1>
-          <xm:sqref>D3:D61</xm:sqref>
+          <xm:sqref>D4:D61</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -8285,29 +8239,29 @@
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="A1" s="18">
+      <c r="A1" s="17">
         <v>1261</v>
       </c>
-      <c r="B1" s="18">
+      <c r="B1" s="17">
         <v>3</v>
       </c>
-      <c r="C1" s="18">
+      <c r="C1" s="17">
         <v>0</v>
       </c>
-      <c r="D1" s="18">
+      <c r="D1" s="17">
         <v>10</v>
       </c>
-      <c r="E1" s="18">
+      <c r="E1" s="17">
         <v>1</v>
       </c>
-      <c r="F1" s="19">
+      <c r="F1" s="18">
         <v>2122</v>
       </c>
-      <c r="G1" s="19" t="s">
+      <c r="G1" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="H1" s="19"/>
-      <c r="I1" s="20">
+      <c r="H1" s="18"/>
+      <c r="I1" s="19">
         <v>3571806.82</v>
       </c>
     </row>
@@ -10483,17 +10437,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="b91e7f20-fe0a-487d-91a9-605ac1c64acf" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="6f4338ef-addb-4c87-aefe-1895241b335f">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100B08D58FADB61F04EBBB4F355C06EFBED" ma:contentTypeVersion="19" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="b1e0f6055e0e9a4b9e75d6c71ee7de91">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="6f4338ef-addb-4c87-aefe-1895241b335f" xmlns:ns3="b91e7f20-fe0a-487d-91a9-605ac1c64acf" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="b43930f3490e4d4da1ab3f8da7df6f51" ns2:_="" ns3:_="">
     <xsd:import namespace="6f4338ef-addb-4c87-aefe-1895241b335f"/>
@@ -10754,6 +10697,17 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="b91e7f20-fe0a-487d-91a9-605ac1c64acf" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="6f4338ef-addb-4c87-aefe-1895241b335f">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -10764,17 +10718,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{78AD39BD-2F37-414E-8652-4DCF45E4F24B}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="b91e7f20-fe0a-487d-91a9-605ac1c64acf"/>
-    <ds:schemaRef ds:uri="6f4338ef-addb-4c87-aefe-1895241b335f"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9E3F47A8-3F3E-4CD4-856C-EFC2EF6F2BBF}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -10793,6 +10736,17 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{78AD39BD-2F37-414E-8652-4DCF45E4F24B}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="b91e7f20-fe0a-487d-91a9-605ac1c64acf"/>
+    <ds:schemaRef ds:uri="6f4338ef-addb-4c87-aefe-1895241b335f"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A11A0DA3-0444-476A-A216-870D1067E696}">
   <ds:schemaRefs>

--- a/data/remanejamento.xlsx
+++ b/data/remanejamento.xlsx
@@ -595,21 +595,7 @@
     <cellStyle name="Vírgula 4 2" xfId="66"/>
     <cellStyle name="Vírgula 5" xfId="67"/>
   </cellStyles>
-  <dxfs count="7">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF95B3D7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="00FFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="6">
     <dxf>
       <font>
         <name val="Arial"/>
@@ -617,7 +603,6 @@
         <family val="0"/>
         <color rgb="FF000000"/>
       </font>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </dxf>
     <dxf>
       <fill>
@@ -638,6 +623,13 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFAE5252"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00FFFFFF"/>
         </patternFill>
       </fill>
     </dxf>
@@ -728,7 +720,7 @@
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="12.57"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="1" width="11.99"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="1" width="8.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="15.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="15.87"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="8.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="11.42"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="9" style="1" width="16.57"/>
@@ -824,16 +816,16 @@
         <v>1</v>
       </c>
       <c r="F3" s="9" t="n">
-        <v>4420</v>
+        <v>4419</v>
       </c>
       <c r="G3" s="9" t="s">
         <v>12</v>
       </c>
       <c r="H3" s="9"/>
-      <c r="I3" s="10"/>
-      <c r="J3" s="11" t="n">
+      <c r="I3" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="J3" s="11"/>
       <c r="K3" s="7"/>
       <c r="L3" s="7"/>
     </row>
@@ -8142,21 +8134,21 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="H2:H520">
-    <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
+    <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>H2&gt;0</formula>
     </cfRule>
-    <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
+    <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
       <formula>B2=1</formula>
     </cfRule>
-    <cfRule type="expression" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="4">
+    <cfRule type="expression" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
       <formula>E2=9</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K2:L520">
-    <cfRule type="expression" priority="5" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
+    <cfRule type="expression" priority="5" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>LEN(TRIM(K2))&gt;0</formula>
     </cfRule>
-    <cfRule type="expression" priority="6" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="5">
+    <cfRule type="expression" priority="6" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
       <formula>E2=2</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8210,7 +8202,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:F353"/>
-  <sheetFormatPr defaultColWidth="8.6875" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6953125" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="13.14"/>
   </cols>

--- a/data/remanejamento.xlsx
+++ b/data/remanejamento.xlsx
@@ -127,7 +127,7 @@
     <numFmt numFmtId="170" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* \-??_-;_-@"/>
     <numFmt numFmtId="171" formatCode="@"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="13">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -196,13 +196,6 @@
       <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
@@ -465,7 +458,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="17">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -498,19 +491,15 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="11" fillId="3" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="170" fontId="13" fillId="0" borderId="2" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="170" fontId="12" fillId="0" borderId="2" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="170" fontId="11" fillId="0" borderId="2" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -720,7 +709,7 @@
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="12.57"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="1" width="11.99"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="1" width="8.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="15.87"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="15.88"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="8.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="11.42"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="9" style="1" width="16.57"/>
@@ -771,22 +760,22 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="n">
-        <v>1231</v>
+        <v>1511</v>
       </c>
       <c r="B2" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>0</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E2" s="3" t="n">
         <v>1</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>4419</v>
+        <v>2500</v>
       </c>
       <c r="G2" s="4" t="s">
         <v>12</v>
@@ -800,32 +789,32 @@
       <c r="L2" s="7"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="8" t="n">
-        <v>1231</v>
-      </c>
-      <c r="B3" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="C3" s="8" t="n">
+      <c r="A3" s="3" t="n">
+        <v>1511</v>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D3" s="8" t="n">
-        <v>15</v>
-      </c>
-      <c r="E3" s="8" t="n">
+      <c r="D3" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="E3" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="F3" s="9" t="n">
-        <v>4419</v>
-      </c>
-      <c r="G3" s="9" t="s">
+      <c r="F3" s="4" t="n">
+        <v>2500</v>
+      </c>
+      <c r="G3" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="H3" s="9"/>
-      <c r="I3" s="10" t="n">
+      <c r="H3" s="8"/>
+      <c r="I3" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="J3" s="11"/>
+      <c r="J3" s="10"/>
       <c r="K3" s="7"/>
       <c r="L3" s="7"/>
     </row>
@@ -838,15 +827,15 @@
       <c r="F4" s="7"/>
       <c r="G4" s="7"/>
       <c r="H4" s="7"/>
-      <c r="I4" s="12"/>
-      <c r="J4" s="13"/>
+      <c r="I4" s="11"/>
+      <c r="J4" s="12"/>
       <c r="K4" s="7"/>
       <c r="L4" s="7"/>
-      <c r="M4" s="14"/>
-      <c r="N4" s="14"/>
-      <c r="O4" s="14"/>
-      <c r="P4" s="14"/>
-      <c r="Q4" s="14"/>
+      <c r="M4" s="13"/>
+      <c r="N4" s="13"/>
+      <c r="O4" s="13"/>
+      <c r="P4" s="13"/>
+      <c r="Q4" s="13"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="3"/>
@@ -857,15 +846,15 @@
       <c r="F5" s="7"/>
       <c r="G5" s="7"/>
       <c r="H5" s="7"/>
-      <c r="I5" s="12"/>
-      <c r="J5" s="13"/>
+      <c r="I5" s="11"/>
+      <c r="J5" s="12"/>
       <c r="K5" s="7"/>
       <c r="L5" s="7"/>
-      <c r="M5" s="14"/>
-      <c r="N5" s="14"/>
-      <c r="O5" s="14"/>
-      <c r="P5" s="14"/>
-      <c r="Q5" s="14"/>
+      <c r="M5" s="13"/>
+      <c r="N5" s="13"/>
+      <c r="O5" s="13"/>
+      <c r="P5" s="13"/>
+      <c r="Q5" s="13"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="3"/>
@@ -876,15 +865,15 @@
       <c r="F6" s="7"/>
       <c r="G6" s="7"/>
       <c r="H6" s="7"/>
-      <c r="I6" s="12"/>
-      <c r="J6" s="13"/>
+      <c r="I6" s="11"/>
+      <c r="J6" s="12"/>
       <c r="K6" s="7"/>
       <c r="L6" s="7"/>
-      <c r="M6" s="14"/>
-      <c r="N6" s="14"/>
-      <c r="O6" s="14"/>
-      <c r="P6" s="14"/>
-      <c r="Q6" s="14"/>
+      <c r="M6" s="13"/>
+      <c r="N6" s="13"/>
+      <c r="O6" s="13"/>
+      <c r="P6" s="13"/>
+      <c r="Q6" s="13"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="3"/>
@@ -895,15 +884,15 @@
       <c r="F7" s="7"/>
       <c r="G7" s="7"/>
       <c r="H7" s="7"/>
-      <c r="I7" s="12"/>
-      <c r="J7" s="13"/>
+      <c r="I7" s="11"/>
+      <c r="J7" s="12"/>
       <c r="K7" s="7"/>
       <c r="L7" s="7"/>
-      <c r="M7" s="14"/>
-      <c r="N7" s="14"/>
-      <c r="O7" s="14"/>
-      <c r="P7" s="14"/>
-      <c r="Q7" s="14"/>
+      <c r="M7" s="13"/>
+      <c r="N7" s="13"/>
+      <c r="O7" s="13"/>
+      <c r="P7" s="13"/>
+      <c r="Q7" s="13"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="3"/>
@@ -914,15 +903,15 @@
       <c r="F8" s="7"/>
       <c r="G8" s="7"/>
       <c r="H8" s="7"/>
-      <c r="I8" s="12"/>
-      <c r="J8" s="13"/>
+      <c r="I8" s="11"/>
+      <c r="J8" s="12"/>
       <c r="K8" s="7"/>
       <c r="L8" s="7"/>
-      <c r="M8" s="14"/>
-      <c r="N8" s="14"/>
-      <c r="O8" s="14"/>
-      <c r="P8" s="14"/>
-      <c r="Q8" s="14"/>
+      <c r="M8" s="13"/>
+      <c r="N8" s="13"/>
+      <c r="O8" s="13"/>
+      <c r="P8" s="13"/>
+      <c r="Q8" s="13"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="3"/>
@@ -933,15 +922,15 @@
       <c r="F9" s="7"/>
       <c r="G9" s="7"/>
       <c r="H9" s="7"/>
-      <c r="I9" s="12"/>
-      <c r="J9" s="13"/>
+      <c r="I9" s="11"/>
+      <c r="J9" s="12"/>
       <c r="K9" s="7"/>
       <c r="L9" s="7"/>
-      <c r="M9" s="14"/>
-      <c r="N9" s="14"/>
-      <c r="O9" s="14"/>
-      <c r="P9" s="14"/>
-      <c r="Q9" s="14"/>
+      <c r="M9" s="13"/>
+      <c r="N9" s="13"/>
+      <c r="O9" s="13"/>
+      <c r="P9" s="13"/>
+      <c r="Q9" s="13"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="3"/>
@@ -952,15 +941,15 @@
       <c r="F10" s="7"/>
       <c r="G10" s="7"/>
       <c r="H10" s="7"/>
-      <c r="I10" s="12"/>
-      <c r="J10" s="13"/>
+      <c r="I10" s="11"/>
+      <c r="J10" s="12"/>
       <c r="K10" s="7"/>
       <c r="L10" s="7"/>
-      <c r="M10" s="14"/>
-      <c r="N10" s="14"/>
-      <c r="O10" s="14"/>
-      <c r="P10" s="14"/>
-      <c r="Q10" s="14"/>
+      <c r="M10" s="13"/>
+      <c r="N10" s="13"/>
+      <c r="O10" s="13"/>
+      <c r="P10" s="13"/>
+      <c r="Q10" s="13"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="3"/>
@@ -971,15 +960,15 @@
       <c r="F11" s="7"/>
       <c r="G11" s="7"/>
       <c r="H11" s="7"/>
-      <c r="I11" s="12"/>
-      <c r="J11" s="13"/>
+      <c r="I11" s="11"/>
+      <c r="J11" s="12"/>
       <c r="K11" s="7"/>
       <c r="L11" s="7"/>
-      <c r="M11" s="14"/>
-      <c r="N11" s="14"/>
-      <c r="O11" s="14"/>
-      <c r="P11" s="14"/>
-      <c r="Q11" s="14"/>
+      <c r="M11" s="13"/>
+      <c r="N11" s="13"/>
+      <c r="O11" s="13"/>
+      <c r="P11" s="13"/>
+      <c r="Q11" s="13"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="3"/>
@@ -990,15 +979,15 @@
       <c r="F12" s="7"/>
       <c r="G12" s="7"/>
       <c r="H12" s="7"/>
-      <c r="I12" s="12"/>
-      <c r="J12" s="13"/>
+      <c r="I12" s="11"/>
+      <c r="J12" s="12"/>
       <c r="K12" s="7"/>
       <c r="L12" s="7"/>
-      <c r="M12" s="14"/>
-      <c r="N12" s="14"/>
-      <c r="O12" s="14"/>
-      <c r="P12" s="14"/>
-      <c r="Q12" s="14"/>
+      <c r="M12" s="13"/>
+      <c r="N12" s="13"/>
+      <c r="O12" s="13"/>
+      <c r="P12" s="13"/>
+      <c r="Q12" s="13"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="3"/>
@@ -1009,15 +998,15 @@
       <c r="F13" s="7"/>
       <c r="G13" s="7"/>
       <c r="H13" s="7"/>
-      <c r="I13" s="12"/>
-      <c r="J13" s="13"/>
+      <c r="I13" s="11"/>
+      <c r="J13" s="12"/>
       <c r="K13" s="7"/>
       <c r="L13" s="7"/>
-      <c r="M13" s="14"/>
-      <c r="N13" s="14"/>
-      <c r="O13" s="14"/>
-      <c r="P13" s="14"/>
-      <c r="Q13" s="14"/>
+      <c r="M13" s="13"/>
+      <c r="N13" s="13"/>
+      <c r="O13" s="13"/>
+      <c r="P13" s="13"/>
+      <c r="Q13" s="13"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="3"/>
@@ -1028,15 +1017,15 @@
       <c r="F14" s="7"/>
       <c r="G14" s="7"/>
       <c r="H14" s="7"/>
-      <c r="I14" s="12"/>
-      <c r="J14" s="13"/>
+      <c r="I14" s="11"/>
+      <c r="J14" s="12"/>
       <c r="K14" s="7"/>
       <c r="L14" s="7"/>
-      <c r="M14" s="14"/>
-      <c r="N14" s="14"/>
-      <c r="O14" s="14"/>
-      <c r="P14" s="14"/>
-      <c r="Q14" s="14"/>
+      <c r="M14" s="13"/>
+      <c r="N14" s="13"/>
+      <c r="O14" s="13"/>
+      <c r="P14" s="13"/>
+      <c r="Q14" s="13"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="3"/>
@@ -1047,15 +1036,15 @@
       <c r="F15" s="7"/>
       <c r="G15" s="7"/>
       <c r="H15" s="7"/>
-      <c r="I15" s="12"/>
-      <c r="J15" s="13"/>
+      <c r="I15" s="11"/>
+      <c r="J15" s="12"/>
       <c r="K15" s="7"/>
       <c r="L15" s="7"/>
-      <c r="M15" s="14"/>
-      <c r="N15" s="14"/>
-      <c r="O15" s="14"/>
-      <c r="P15" s="14"/>
-      <c r="Q15" s="14"/>
+      <c r="M15" s="13"/>
+      <c r="N15" s="13"/>
+      <c r="O15" s="13"/>
+      <c r="P15" s="13"/>
+      <c r="Q15" s="13"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="3"/>
@@ -1066,15 +1055,15 @@
       <c r="F16" s="7"/>
       <c r="G16" s="7"/>
       <c r="H16" s="7"/>
-      <c r="I16" s="12"/>
-      <c r="J16" s="13"/>
+      <c r="I16" s="11"/>
+      <c r="J16" s="12"/>
       <c r="K16" s="7"/>
       <c r="L16" s="7"/>
-      <c r="M16" s="14"/>
-      <c r="N16" s="14"/>
-      <c r="O16" s="14"/>
-      <c r="P16" s="14"/>
-      <c r="Q16" s="14"/>
+      <c r="M16" s="13"/>
+      <c r="N16" s="13"/>
+      <c r="O16" s="13"/>
+      <c r="P16" s="13"/>
+      <c r="Q16" s="13"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="3"/>
@@ -1085,8 +1074,8 @@
       <c r="F17" s="7"/>
       <c r="G17" s="7"/>
       <c r="H17" s="7"/>
-      <c r="I17" s="12"/>
-      <c r="J17" s="13"/>
+      <c r="I17" s="11"/>
+      <c r="J17" s="12"/>
       <c r="K17" s="7"/>
       <c r="L17" s="7"/>
     </row>
@@ -1099,8 +1088,8 @@
       <c r="F18" s="7"/>
       <c r="G18" s="7"/>
       <c r="H18" s="7"/>
-      <c r="I18" s="12"/>
-      <c r="J18" s="13"/>
+      <c r="I18" s="11"/>
+      <c r="J18" s="12"/>
       <c r="K18" s="7"/>
       <c r="L18" s="7"/>
     </row>
@@ -1113,8 +1102,8 @@
       <c r="F19" s="7"/>
       <c r="G19" s="7"/>
       <c r="H19" s="7"/>
-      <c r="I19" s="12"/>
-      <c r="J19" s="13"/>
+      <c r="I19" s="11"/>
+      <c r="J19" s="12"/>
       <c r="K19" s="7"/>
       <c r="L19" s="7"/>
     </row>
@@ -1127,8 +1116,8 @@
       <c r="F20" s="7"/>
       <c r="G20" s="7"/>
       <c r="H20" s="7"/>
-      <c r="I20" s="12"/>
-      <c r="J20" s="13"/>
+      <c r="I20" s="11"/>
+      <c r="J20" s="12"/>
       <c r="K20" s="7"/>
       <c r="L20" s="7"/>
     </row>
@@ -1141,8 +1130,8 @@
       <c r="F21" s="7"/>
       <c r="G21" s="7"/>
       <c r="H21" s="7"/>
-      <c r="I21" s="12"/>
-      <c r="J21" s="13"/>
+      <c r="I21" s="11"/>
+      <c r="J21" s="12"/>
       <c r="K21" s="7"/>
       <c r="L21" s="7"/>
     </row>
@@ -1155,8 +1144,8 @@
       <c r="F22" s="7"/>
       <c r="G22" s="7"/>
       <c r="H22" s="7"/>
-      <c r="I22" s="12"/>
-      <c r="J22" s="13"/>
+      <c r="I22" s="11"/>
+      <c r="J22" s="12"/>
       <c r="K22" s="7"/>
       <c r="L22" s="7"/>
     </row>
@@ -1169,8 +1158,8 @@
       <c r="F23" s="7"/>
       <c r="G23" s="7"/>
       <c r="H23" s="7"/>
-      <c r="I23" s="12"/>
-      <c r="J23" s="13"/>
+      <c r="I23" s="11"/>
+      <c r="J23" s="12"/>
       <c r="K23" s="7"/>
       <c r="L23" s="7"/>
     </row>
@@ -1183,8 +1172,8 @@
       <c r="F24" s="7"/>
       <c r="G24" s="7"/>
       <c r="H24" s="7"/>
-      <c r="I24" s="12"/>
-      <c r="J24" s="13"/>
+      <c r="I24" s="11"/>
+      <c r="J24" s="12"/>
       <c r="K24" s="7"/>
       <c r="L24" s="7"/>
     </row>
@@ -1197,8 +1186,8 @@
       <c r="F25" s="7"/>
       <c r="G25" s="7"/>
       <c r="H25" s="7"/>
-      <c r="I25" s="12"/>
-      <c r="J25" s="13"/>
+      <c r="I25" s="11"/>
+      <c r="J25" s="12"/>
       <c r="K25" s="7"/>
       <c r="L25" s="7"/>
     </row>
@@ -1211,8 +1200,8 @@
       <c r="F26" s="7"/>
       <c r="G26" s="7"/>
       <c r="H26" s="7"/>
-      <c r="I26" s="12"/>
-      <c r="J26" s="13"/>
+      <c r="I26" s="11"/>
+      <c r="J26" s="12"/>
       <c r="K26" s="7"/>
       <c r="L26" s="7"/>
     </row>
@@ -1225,8 +1214,8 @@
       <c r="F27" s="7"/>
       <c r="G27" s="7"/>
       <c r="H27" s="7"/>
-      <c r="I27" s="12"/>
-      <c r="J27" s="13"/>
+      <c r="I27" s="11"/>
+      <c r="J27" s="12"/>
       <c r="K27" s="7"/>
       <c r="L27" s="7"/>
     </row>
@@ -1239,8 +1228,8 @@
       <c r="F28" s="7"/>
       <c r="G28" s="7"/>
       <c r="H28" s="7"/>
-      <c r="I28" s="12"/>
-      <c r="J28" s="13"/>
+      <c r="I28" s="11"/>
+      <c r="J28" s="12"/>
       <c r="K28" s="7"/>
       <c r="L28" s="7"/>
     </row>
@@ -1253,8 +1242,8 @@
       <c r="F29" s="7"/>
       <c r="G29" s="7"/>
       <c r="H29" s="7"/>
-      <c r="I29" s="12"/>
-      <c r="J29" s="13"/>
+      <c r="I29" s="11"/>
+      <c r="J29" s="12"/>
       <c r="K29" s="7"/>
       <c r="L29" s="7"/>
     </row>
@@ -1267,8 +1256,8 @@
       <c r="F30" s="7"/>
       <c r="G30" s="7"/>
       <c r="H30" s="7"/>
-      <c r="I30" s="12"/>
-      <c r="J30" s="13"/>
+      <c r="I30" s="11"/>
+      <c r="J30" s="12"/>
       <c r="K30" s="7"/>
       <c r="L30" s="7"/>
     </row>
@@ -1281,8 +1270,8 @@
       <c r="F31" s="7"/>
       <c r="G31" s="7"/>
       <c r="H31" s="7"/>
-      <c r="I31" s="12"/>
-      <c r="J31" s="13"/>
+      <c r="I31" s="11"/>
+      <c r="J31" s="12"/>
       <c r="K31" s="7"/>
       <c r="L31" s="7"/>
     </row>
@@ -1295,8 +1284,8 @@
       <c r="F32" s="7"/>
       <c r="G32" s="7"/>
       <c r="H32" s="7"/>
-      <c r="I32" s="12"/>
-      <c r="J32" s="13"/>
+      <c r="I32" s="11"/>
+      <c r="J32" s="12"/>
       <c r="K32" s="7"/>
       <c r="L32" s="7"/>
     </row>
@@ -1309,8 +1298,8 @@
       <c r="F33" s="7"/>
       <c r="G33" s="7"/>
       <c r="H33" s="7"/>
-      <c r="I33" s="12"/>
-      <c r="J33" s="13"/>
+      <c r="I33" s="11"/>
+      <c r="J33" s="12"/>
       <c r="K33" s="7"/>
       <c r="L33" s="7"/>
     </row>
@@ -1323,8 +1312,8 @@
       <c r="F34" s="7"/>
       <c r="G34" s="7"/>
       <c r="H34" s="7"/>
-      <c r="I34" s="12"/>
-      <c r="J34" s="13"/>
+      <c r="I34" s="11"/>
+      <c r="J34" s="12"/>
       <c r="K34" s="7"/>
       <c r="L34" s="7"/>
     </row>
@@ -1337,8 +1326,8 @@
       <c r="F35" s="7"/>
       <c r="G35" s="7"/>
       <c r="H35" s="7"/>
-      <c r="I35" s="12"/>
-      <c r="J35" s="13"/>
+      <c r="I35" s="11"/>
+      <c r="J35" s="12"/>
       <c r="K35" s="7"/>
       <c r="L35" s="7"/>
     </row>
@@ -1351,8 +1340,8 @@
       <c r="F36" s="7"/>
       <c r="G36" s="7"/>
       <c r="H36" s="7"/>
-      <c r="I36" s="12"/>
-      <c r="J36" s="13"/>
+      <c r="I36" s="11"/>
+      <c r="J36" s="12"/>
       <c r="K36" s="7"/>
       <c r="L36" s="7"/>
     </row>
@@ -1365,8 +1354,8 @@
       <c r="F37" s="7"/>
       <c r="G37" s="7"/>
       <c r="H37" s="7"/>
-      <c r="I37" s="12"/>
-      <c r="J37" s="13"/>
+      <c r="I37" s="11"/>
+      <c r="J37" s="12"/>
       <c r="K37" s="7"/>
       <c r="L37" s="7"/>
     </row>
@@ -1379,8 +1368,8 @@
       <c r="F38" s="7"/>
       <c r="G38" s="7"/>
       <c r="H38" s="7"/>
-      <c r="I38" s="12"/>
-      <c r="J38" s="13"/>
+      <c r="I38" s="11"/>
+      <c r="J38" s="12"/>
       <c r="K38" s="7"/>
       <c r="L38" s="7"/>
     </row>
@@ -1393,8 +1382,8 @@
       <c r="F39" s="7"/>
       <c r="G39" s="7"/>
       <c r="H39" s="7"/>
-      <c r="I39" s="12"/>
-      <c r="J39" s="13"/>
+      <c r="I39" s="11"/>
+      <c r="J39" s="12"/>
       <c r="K39" s="7"/>
       <c r="L39" s="7"/>
     </row>
@@ -1407,8 +1396,8 @@
       <c r="F40" s="7"/>
       <c r="G40" s="7"/>
       <c r="H40" s="7"/>
-      <c r="I40" s="12"/>
-      <c r="J40" s="13"/>
+      <c r="I40" s="11"/>
+      <c r="J40" s="12"/>
       <c r="K40" s="7"/>
       <c r="L40" s="7"/>
     </row>
@@ -1421,8 +1410,8 @@
       <c r="F41" s="7"/>
       <c r="G41" s="7"/>
       <c r="H41" s="7"/>
-      <c r="I41" s="12"/>
-      <c r="J41" s="13"/>
+      <c r="I41" s="11"/>
+      <c r="J41" s="12"/>
       <c r="K41" s="7"/>
       <c r="L41" s="7"/>
     </row>
@@ -1435,8 +1424,8 @@
       <c r="F42" s="7"/>
       <c r="G42" s="7"/>
       <c r="H42" s="7"/>
-      <c r="I42" s="12"/>
-      <c r="J42" s="13"/>
+      <c r="I42" s="11"/>
+      <c r="J42" s="12"/>
       <c r="K42" s="7"/>
       <c r="L42" s="7"/>
     </row>
@@ -1449,8 +1438,8 @@
       <c r="F43" s="7"/>
       <c r="G43" s="7"/>
       <c r="H43" s="7"/>
-      <c r="I43" s="12"/>
-      <c r="J43" s="13"/>
+      <c r="I43" s="11"/>
+      <c r="J43" s="12"/>
       <c r="K43" s="7"/>
       <c r="L43" s="7"/>
     </row>
@@ -1463,8 +1452,8 @@
       <c r="F44" s="7"/>
       <c r="G44" s="7"/>
       <c r="H44" s="7"/>
-      <c r="I44" s="12"/>
-      <c r="J44" s="13"/>
+      <c r="I44" s="11"/>
+      <c r="J44" s="12"/>
       <c r="K44" s="7"/>
       <c r="L44" s="7"/>
     </row>
@@ -1477,8 +1466,8 @@
       <c r="F45" s="7"/>
       <c r="G45" s="7"/>
       <c r="H45" s="7"/>
-      <c r="I45" s="12"/>
-      <c r="J45" s="13"/>
+      <c r="I45" s="11"/>
+      <c r="J45" s="12"/>
       <c r="K45" s="7"/>
       <c r="L45" s="7"/>
     </row>
@@ -1491,8 +1480,8 @@
       <c r="F46" s="7"/>
       <c r="G46" s="7"/>
       <c r="H46" s="7"/>
-      <c r="I46" s="12"/>
-      <c r="J46" s="13"/>
+      <c r="I46" s="11"/>
+      <c r="J46" s="12"/>
       <c r="K46" s="7"/>
       <c r="L46" s="7"/>
     </row>
@@ -1505,8 +1494,8 @@
       <c r="F47" s="7"/>
       <c r="G47" s="7"/>
       <c r="H47" s="7"/>
-      <c r="I47" s="12"/>
-      <c r="J47" s="13"/>
+      <c r="I47" s="11"/>
+      <c r="J47" s="12"/>
       <c r="K47" s="7"/>
       <c r="L47" s="7"/>
     </row>
@@ -1519,8 +1508,8 @@
       <c r="F48" s="7"/>
       <c r="G48" s="7"/>
       <c r="H48" s="7"/>
-      <c r="I48" s="12"/>
-      <c r="J48" s="13"/>
+      <c r="I48" s="11"/>
+      <c r="J48" s="12"/>
       <c r="K48" s="7"/>
       <c r="L48" s="7"/>
     </row>
@@ -1533,8 +1522,8 @@
       <c r="F49" s="7"/>
       <c r="G49" s="7"/>
       <c r="H49" s="7"/>
-      <c r="I49" s="12"/>
-      <c r="J49" s="13"/>
+      <c r="I49" s="11"/>
+      <c r="J49" s="12"/>
       <c r="K49" s="7"/>
       <c r="L49" s="7"/>
     </row>
@@ -1547,8 +1536,8 @@
       <c r="F50" s="7"/>
       <c r="G50" s="7"/>
       <c r="H50" s="7"/>
-      <c r="I50" s="12"/>
-      <c r="J50" s="13"/>
+      <c r="I50" s="11"/>
+      <c r="J50" s="12"/>
       <c r="K50" s="7"/>
       <c r="L50" s="7"/>
     </row>
@@ -1561,8 +1550,8 @@
       <c r="F51" s="7"/>
       <c r="G51" s="7"/>
       <c r="H51" s="7"/>
-      <c r="I51" s="12"/>
-      <c r="J51" s="13"/>
+      <c r="I51" s="11"/>
+      <c r="J51" s="12"/>
       <c r="K51" s="7"/>
       <c r="L51" s="7"/>
     </row>
@@ -1575,8 +1564,8 @@
       <c r="F52" s="7"/>
       <c r="G52" s="7"/>
       <c r="H52" s="7"/>
-      <c r="I52" s="12"/>
-      <c r="J52" s="13"/>
+      <c r="I52" s="11"/>
+      <c r="J52" s="12"/>
       <c r="K52" s="7"/>
       <c r="L52" s="7"/>
     </row>
@@ -1589,8 +1578,8 @@
       <c r="F53" s="7"/>
       <c r="G53" s="7"/>
       <c r="H53" s="7"/>
-      <c r="I53" s="12"/>
-      <c r="J53" s="13"/>
+      <c r="I53" s="11"/>
+      <c r="J53" s="12"/>
       <c r="K53" s="7"/>
       <c r="L53" s="7"/>
     </row>
@@ -1603,8 +1592,8 @@
       <c r="F54" s="7"/>
       <c r="G54" s="7"/>
       <c r="H54" s="7"/>
-      <c r="I54" s="12"/>
-      <c r="J54" s="13"/>
+      <c r="I54" s="11"/>
+      <c r="J54" s="12"/>
       <c r="K54" s="7"/>
       <c r="L54" s="7"/>
     </row>
@@ -1617,8 +1606,8 @@
       <c r="F55" s="7"/>
       <c r="G55" s="7"/>
       <c r="H55" s="7"/>
-      <c r="I55" s="12"/>
-      <c r="J55" s="13"/>
+      <c r="I55" s="11"/>
+      <c r="J55" s="12"/>
       <c r="K55" s="7"/>
       <c r="L55" s="7"/>
     </row>
@@ -1631,8 +1620,8 @@
       <c r="F56" s="7"/>
       <c r="G56" s="7"/>
       <c r="H56" s="7"/>
-      <c r="I56" s="12"/>
-      <c r="J56" s="13"/>
+      <c r="I56" s="11"/>
+      <c r="J56" s="12"/>
       <c r="K56" s="7"/>
       <c r="L56" s="7"/>
     </row>
@@ -1645,8 +1634,8 @@
       <c r="F57" s="7"/>
       <c r="G57" s="7"/>
       <c r="H57" s="7"/>
-      <c r="I57" s="12"/>
-      <c r="J57" s="13"/>
+      <c r="I57" s="11"/>
+      <c r="J57" s="12"/>
       <c r="K57" s="7"/>
       <c r="L57" s="7"/>
     </row>
@@ -1659,8 +1648,8 @@
       <c r="F58" s="7"/>
       <c r="G58" s="7"/>
       <c r="H58" s="7"/>
-      <c r="I58" s="12"/>
-      <c r="J58" s="13"/>
+      <c r="I58" s="11"/>
+      <c r="J58" s="12"/>
       <c r="K58" s="7"/>
       <c r="L58" s="7"/>
     </row>
@@ -1673,8 +1662,8 @@
       <c r="F59" s="7"/>
       <c r="G59" s="7"/>
       <c r="H59" s="7"/>
-      <c r="I59" s="12"/>
-      <c r="J59" s="13"/>
+      <c r="I59" s="11"/>
+      <c r="J59" s="12"/>
       <c r="K59" s="7"/>
       <c r="L59" s="7"/>
     </row>
@@ -1687,8 +1676,8 @@
       <c r="F60" s="7"/>
       <c r="G60" s="7"/>
       <c r="H60" s="7"/>
-      <c r="I60" s="12"/>
-      <c r="J60" s="13"/>
+      <c r="I60" s="11"/>
+      <c r="J60" s="12"/>
       <c r="K60" s="7"/>
       <c r="L60" s="7"/>
     </row>
@@ -1701,8 +1690,8 @@
       <c r="F61" s="7"/>
       <c r="G61" s="7"/>
       <c r="H61" s="7"/>
-      <c r="I61" s="12"/>
-      <c r="J61" s="13"/>
+      <c r="I61" s="11"/>
+      <c r="J61" s="12"/>
       <c r="K61" s="7"/>
       <c r="L61" s="7"/>
     </row>
@@ -1715,8 +1704,8 @@
       <c r="F62" s="7"/>
       <c r="G62" s="7"/>
       <c r="H62" s="7"/>
-      <c r="I62" s="12"/>
-      <c r="J62" s="13"/>
+      <c r="I62" s="11"/>
+      <c r="J62" s="12"/>
       <c r="K62" s="7"/>
       <c r="L62" s="7"/>
     </row>
@@ -1729,8 +1718,8 @@
       <c r="F63" s="7"/>
       <c r="G63" s="7"/>
       <c r="H63" s="7"/>
-      <c r="I63" s="12"/>
-      <c r="J63" s="13"/>
+      <c r="I63" s="11"/>
+      <c r="J63" s="12"/>
       <c r="K63" s="7"/>
       <c r="L63" s="7"/>
     </row>
@@ -1743,8 +1732,8 @@
       <c r="F64" s="7"/>
       <c r="G64" s="7"/>
       <c r="H64" s="7"/>
-      <c r="I64" s="12"/>
-      <c r="J64" s="13"/>
+      <c r="I64" s="11"/>
+      <c r="J64" s="12"/>
       <c r="K64" s="7"/>
       <c r="L64" s="7"/>
     </row>
@@ -1757,8 +1746,8 @@
       <c r="F65" s="7"/>
       <c r="G65" s="7"/>
       <c r="H65" s="7"/>
-      <c r="I65" s="12"/>
-      <c r="J65" s="13"/>
+      <c r="I65" s="11"/>
+      <c r="J65" s="12"/>
       <c r="K65" s="7"/>
       <c r="L65" s="7"/>
     </row>
@@ -1771,8 +1760,8 @@
       <c r="F66" s="7"/>
       <c r="G66" s="7"/>
       <c r="H66" s="7"/>
-      <c r="I66" s="12"/>
-      <c r="J66" s="13"/>
+      <c r="I66" s="11"/>
+      <c r="J66" s="12"/>
       <c r="K66" s="7"/>
       <c r="L66" s="7"/>
     </row>
@@ -1785,8 +1774,8 @@
       <c r="F67" s="7"/>
       <c r="G67" s="7"/>
       <c r="H67" s="7"/>
-      <c r="I67" s="12"/>
-      <c r="J67" s="13"/>
+      <c r="I67" s="11"/>
+      <c r="J67" s="12"/>
       <c r="K67" s="7"/>
       <c r="L67" s="7"/>
     </row>
@@ -1799,8 +1788,8 @@
       <c r="F68" s="7"/>
       <c r="G68" s="7"/>
       <c r="H68" s="7"/>
-      <c r="I68" s="12"/>
-      <c r="J68" s="13"/>
+      <c r="I68" s="11"/>
+      <c r="J68" s="12"/>
       <c r="K68" s="7"/>
       <c r="L68" s="7"/>
     </row>
@@ -1813,8 +1802,8 @@
       <c r="F69" s="7"/>
       <c r="G69" s="7"/>
       <c r="H69" s="7"/>
-      <c r="I69" s="12"/>
-      <c r="J69" s="13"/>
+      <c r="I69" s="11"/>
+      <c r="J69" s="12"/>
       <c r="K69" s="7"/>
       <c r="L69" s="7"/>
     </row>
@@ -1827,8 +1816,8 @@
       <c r="F70" s="7"/>
       <c r="G70" s="7"/>
       <c r="H70" s="7"/>
-      <c r="I70" s="12"/>
-      <c r="J70" s="13"/>
+      <c r="I70" s="11"/>
+      <c r="J70" s="12"/>
       <c r="K70" s="7"/>
       <c r="L70" s="7"/>
     </row>
@@ -1841,8 +1830,8 @@
       <c r="F71" s="7"/>
       <c r="G71" s="7"/>
       <c r="H71" s="7"/>
-      <c r="I71" s="12"/>
-      <c r="J71" s="13"/>
+      <c r="I71" s="11"/>
+      <c r="J71" s="12"/>
       <c r="K71" s="7"/>
       <c r="L71" s="7"/>
     </row>
@@ -1855,8 +1844,8 @@
       <c r="F72" s="7"/>
       <c r="G72" s="7"/>
       <c r="H72" s="7"/>
-      <c r="I72" s="12"/>
-      <c r="J72" s="13"/>
+      <c r="I72" s="11"/>
+      <c r="J72" s="12"/>
       <c r="K72" s="7"/>
       <c r="L72" s="7"/>
     </row>
@@ -1869,8 +1858,8 @@
       <c r="F73" s="7"/>
       <c r="G73" s="7"/>
       <c r="H73" s="7"/>
-      <c r="I73" s="12"/>
-      <c r="J73" s="13"/>
+      <c r="I73" s="11"/>
+      <c r="J73" s="12"/>
       <c r="K73" s="7"/>
       <c r="L73" s="7"/>
     </row>
@@ -1883,8 +1872,8 @@
       <c r="F74" s="7"/>
       <c r="G74" s="7"/>
       <c r="H74" s="7"/>
-      <c r="I74" s="12"/>
-      <c r="J74" s="13"/>
+      <c r="I74" s="11"/>
+      <c r="J74" s="12"/>
       <c r="K74" s="7"/>
       <c r="L74" s="7"/>
     </row>
@@ -1897,8 +1886,8 @@
       <c r="F75" s="7"/>
       <c r="G75" s="7"/>
       <c r="H75" s="7"/>
-      <c r="I75" s="12"/>
-      <c r="J75" s="13"/>
+      <c r="I75" s="11"/>
+      <c r="J75" s="12"/>
       <c r="K75" s="7"/>
       <c r="L75" s="7"/>
     </row>
@@ -1911,8 +1900,8 @@
       <c r="F76" s="7"/>
       <c r="G76" s="7"/>
       <c r="H76" s="7"/>
-      <c r="I76" s="12"/>
-      <c r="J76" s="13"/>
+      <c r="I76" s="11"/>
+      <c r="J76" s="12"/>
       <c r="K76" s="7"/>
       <c r="L76" s="7"/>
     </row>
@@ -1925,8 +1914,8 @@
       <c r="F77" s="7"/>
       <c r="G77" s="7"/>
       <c r="H77" s="7"/>
-      <c r="I77" s="12"/>
-      <c r="J77" s="13"/>
+      <c r="I77" s="11"/>
+      <c r="J77" s="12"/>
       <c r="K77" s="7"/>
       <c r="L77" s="7"/>
     </row>
@@ -1939,8 +1928,8 @@
       <c r="F78" s="7"/>
       <c r="G78" s="7"/>
       <c r="H78" s="7"/>
-      <c r="I78" s="12"/>
-      <c r="J78" s="13"/>
+      <c r="I78" s="11"/>
+      <c r="J78" s="12"/>
       <c r="K78" s="7"/>
       <c r="L78" s="7"/>
     </row>
@@ -1953,8 +1942,8 @@
       <c r="F79" s="7"/>
       <c r="G79" s="7"/>
       <c r="H79" s="7"/>
-      <c r="I79" s="12"/>
-      <c r="J79" s="13"/>
+      <c r="I79" s="11"/>
+      <c r="J79" s="12"/>
       <c r="K79" s="7"/>
       <c r="L79" s="7"/>
     </row>
@@ -1967,8 +1956,8 @@
       <c r="F80" s="7"/>
       <c r="G80" s="7"/>
       <c r="H80" s="7"/>
-      <c r="I80" s="12"/>
-      <c r="J80" s="13"/>
+      <c r="I80" s="11"/>
+      <c r="J80" s="12"/>
       <c r="K80" s="7"/>
       <c r="L80" s="7"/>
     </row>
@@ -1981,8 +1970,8 @@
       <c r="F81" s="7"/>
       <c r="G81" s="7"/>
       <c r="H81" s="7"/>
-      <c r="I81" s="12"/>
-      <c r="J81" s="13"/>
+      <c r="I81" s="11"/>
+      <c r="J81" s="12"/>
       <c r="K81" s="7"/>
       <c r="L81" s="7"/>
     </row>
@@ -1995,8 +1984,8 @@
       <c r="F82" s="7"/>
       <c r="G82" s="7"/>
       <c r="H82" s="7"/>
-      <c r="I82" s="12"/>
-      <c r="J82" s="13"/>
+      <c r="I82" s="11"/>
+      <c r="J82" s="12"/>
       <c r="K82" s="7"/>
       <c r="L82" s="7"/>
     </row>
@@ -2009,8 +1998,8 @@
       <c r="F83" s="7"/>
       <c r="G83" s="7"/>
       <c r="H83" s="7"/>
-      <c r="I83" s="12"/>
-      <c r="J83" s="13"/>
+      <c r="I83" s="11"/>
+      <c r="J83" s="12"/>
       <c r="K83" s="7"/>
       <c r="L83" s="7"/>
     </row>
@@ -2023,8 +2012,8 @@
       <c r="F84" s="7"/>
       <c r="G84" s="7"/>
       <c r="H84" s="7"/>
-      <c r="I84" s="12"/>
-      <c r="J84" s="13"/>
+      <c r="I84" s="11"/>
+      <c r="J84" s="12"/>
       <c r="K84" s="7"/>
       <c r="L84" s="7"/>
     </row>
@@ -2037,8 +2026,8 @@
       <c r="F85" s="7"/>
       <c r="G85" s="7"/>
       <c r="H85" s="7"/>
-      <c r="I85" s="12"/>
-      <c r="J85" s="13"/>
+      <c r="I85" s="11"/>
+      <c r="J85" s="12"/>
       <c r="K85" s="7"/>
       <c r="L85" s="7"/>
     </row>
@@ -2051,8 +2040,8 @@
       <c r="F86" s="7"/>
       <c r="G86" s="7"/>
       <c r="H86" s="7"/>
-      <c r="I86" s="12"/>
-      <c r="J86" s="13"/>
+      <c r="I86" s="11"/>
+      <c r="J86" s="12"/>
       <c r="K86" s="7"/>
       <c r="L86" s="7"/>
     </row>
@@ -2065,8 +2054,8 @@
       <c r="F87" s="7"/>
       <c r="G87" s="7"/>
       <c r="H87" s="7"/>
-      <c r="I87" s="12"/>
-      <c r="J87" s="13"/>
+      <c r="I87" s="11"/>
+      <c r="J87" s="12"/>
       <c r="K87" s="7"/>
       <c r="L87" s="7"/>
     </row>
@@ -2079,8 +2068,8 @@
       <c r="F88" s="7"/>
       <c r="G88" s="7"/>
       <c r="H88" s="7"/>
-      <c r="I88" s="12"/>
-      <c r="J88" s="13"/>
+      <c r="I88" s="11"/>
+      <c r="J88" s="12"/>
       <c r="K88" s="7"/>
       <c r="L88" s="7"/>
     </row>
@@ -2093,8 +2082,8 @@
       <c r="F89" s="7"/>
       <c r="G89" s="7"/>
       <c r="H89" s="7"/>
-      <c r="I89" s="12"/>
-      <c r="J89" s="13"/>
+      <c r="I89" s="11"/>
+      <c r="J89" s="12"/>
       <c r="K89" s="7"/>
       <c r="L89" s="7"/>
     </row>
@@ -2107,8 +2096,8 @@
       <c r="F90" s="7"/>
       <c r="G90" s="7"/>
       <c r="H90" s="7"/>
-      <c r="I90" s="12"/>
-      <c r="J90" s="13"/>
+      <c r="I90" s="11"/>
+      <c r="J90" s="12"/>
       <c r="K90" s="7"/>
       <c r="L90" s="7"/>
     </row>
@@ -2121,8 +2110,8 @@
       <c r="F91" s="7"/>
       <c r="G91" s="7"/>
       <c r="H91" s="7"/>
-      <c r="I91" s="12"/>
-      <c r="J91" s="13"/>
+      <c r="I91" s="11"/>
+      <c r="J91" s="12"/>
       <c r="K91" s="7"/>
       <c r="L91" s="7"/>
     </row>
@@ -2135,8 +2124,8 @@
       <c r="F92" s="7"/>
       <c r="G92" s="7"/>
       <c r="H92" s="7"/>
-      <c r="I92" s="12"/>
-      <c r="J92" s="13"/>
+      <c r="I92" s="11"/>
+      <c r="J92" s="12"/>
       <c r="K92" s="7"/>
       <c r="L92" s="7"/>
     </row>
@@ -2149,8 +2138,8 @@
       <c r="F93" s="7"/>
       <c r="G93" s="7"/>
       <c r="H93" s="7"/>
-      <c r="I93" s="12"/>
-      <c r="J93" s="13"/>
+      <c r="I93" s="11"/>
+      <c r="J93" s="12"/>
       <c r="K93" s="7"/>
       <c r="L93" s="7"/>
     </row>
@@ -2163,8 +2152,8 @@
       <c r="F94" s="7"/>
       <c r="G94" s="7"/>
       <c r="H94" s="7"/>
-      <c r="I94" s="12"/>
-      <c r="J94" s="13"/>
+      <c r="I94" s="11"/>
+      <c r="J94" s="12"/>
       <c r="K94" s="7"/>
       <c r="L94" s="7"/>
     </row>
@@ -2177,8 +2166,8 @@
       <c r="F95" s="7"/>
       <c r="G95" s="7"/>
       <c r="H95" s="7"/>
-      <c r="I95" s="12"/>
-      <c r="J95" s="13"/>
+      <c r="I95" s="11"/>
+      <c r="J95" s="12"/>
       <c r="K95" s="7"/>
       <c r="L95" s="7"/>
     </row>
@@ -2191,8 +2180,8 @@
       <c r="F96" s="7"/>
       <c r="G96" s="7"/>
       <c r="H96" s="7"/>
-      <c r="I96" s="12"/>
-      <c r="J96" s="13"/>
+      <c r="I96" s="11"/>
+      <c r="J96" s="12"/>
       <c r="K96" s="7"/>
       <c r="L96" s="7"/>
     </row>
@@ -2205,8 +2194,8 @@
       <c r="F97" s="7"/>
       <c r="G97" s="7"/>
       <c r="H97" s="7"/>
-      <c r="I97" s="12"/>
-      <c r="J97" s="13"/>
+      <c r="I97" s="11"/>
+      <c r="J97" s="12"/>
       <c r="K97" s="7"/>
       <c r="L97" s="7"/>
     </row>
@@ -2219,8 +2208,8 @@
       <c r="F98" s="7"/>
       <c r="G98" s="7"/>
       <c r="H98" s="7"/>
-      <c r="I98" s="12"/>
-      <c r="J98" s="13"/>
+      <c r="I98" s="11"/>
+      <c r="J98" s="12"/>
       <c r="K98" s="7"/>
       <c r="L98" s="7"/>
     </row>
@@ -2233,8 +2222,8 @@
       <c r="F99" s="7"/>
       <c r="G99" s="7"/>
       <c r="H99" s="7"/>
-      <c r="I99" s="12"/>
-      <c r="J99" s="13"/>
+      <c r="I99" s="11"/>
+      <c r="J99" s="12"/>
       <c r="K99" s="7"/>
       <c r="L99" s="7"/>
     </row>
@@ -2247,8 +2236,8 @@
       <c r="F100" s="7"/>
       <c r="G100" s="7"/>
       <c r="H100" s="7"/>
-      <c r="I100" s="12"/>
-      <c r="J100" s="13"/>
+      <c r="I100" s="11"/>
+      <c r="J100" s="12"/>
       <c r="K100" s="7"/>
       <c r="L100" s="7"/>
     </row>
@@ -2261,8 +2250,8 @@
       <c r="F101" s="7"/>
       <c r="G101" s="7"/>
       <c r="H101" s="7"/>
-      <c r="I101" s="12"/>
-      <c r="J101" s="13"/>
+      <c r="I101" s="11"/>
+      <c r="J101" s="12"/>
       <c r="K101" s="7"/>
       <c r="L101" s="7"/>
     </row>
@@ -2275,8 +2264,8 @@
       <c r="F102" s="7"/>
       <c r="G102" s="7"/>
       <c r="H102" s="7"/>
-      <c r="I102" s="12"/>
-      <c r="J102" s="13"/>
+      <c r="I102" s="11"/>
+      <c r="J102" s="12"/>
       <c r="K102" s="7"/>
       <c r="L102" s="7"/>
     </row>
@@ -2289,8 +2278,8 @@
       <c r="F103" s="7"/>
       <c r="G103" s="7"/>
       <c r="H103" s="7"/>
-      <c r="I103" s="12"/>
-      <c r="J103" s="13"/>
+      <c r="I103" s="11"/>
+      <c r="J103" s="12"/>
       <c r="K103" s="7"/>
       <c r="L103" s="7"/>
     </row>
@@ -2303,8 +2292,8 @@
       <c r="F104" s="7"/>
       <c r="G104" s="7"/>
       <c r="H104" s="7"/>
-      <c r="I104" s="12"/>
-      <c r="J104" s="13"/>
+      <c r="I104" s="11"/>
+      <c r="J104" s="12"/>
       <c r="K104" s="7"/>
       <c r="L104" s="7"/>
     </row>
@@ -2317,8 +2306,8 @@
       <c r="F105" s="7"/>
       <c r="G105" s="7"/>
       <c r="H105" s="7"/>
-      <c r="I105" s="12"/>
-      <c r="J105" s="13"/>
+      <c r="I105" s="11"/>
+      <c r="J105" s="12"/>
       <c r="K105" s="7"/>
       <c r="L105" s="7"/>
     </row>
@@ -2331,8 +2320,8 @@
       <c r="F106" s="7"/>
       <c r="G106" s="7"/>
       <c r="H106" s="7"/>
-      <c r="I106" s="12"/>
-      <c r="J106" s="13"/>
+      <c r="I106" s="11"/>
+      <c r="J106" s="12"/>
       <c r="K106" s="7"/>
       <c r="L106" s="7"/>
     </row>
@@ -2345,8 +2334,8 @@
       <c r="F107" s="7"/>
       <c r="G107" s="7"/>
       <c r="H107" s="7"/>
-      <c r="I107" s="12"/>
-      <c r="J107" s="13"/>
+      <c r="I107" s="11"/>
+      <c r="J107" s="12"/>
       <c r="K107" s="7"/>
       <c r="L107" s="7"/>
     </row>
@@ -2359,8 +2348,8 @@
       <c r="F108" s="7"/>
       <c r="G108" s="7"/>
       <c r="H108" s="7"/>
-      <c r="I108" s="12"/>
-      <c r="J108" s="13"/>
+      <c r="I108" s="11"/>
+      <c r="J108" s="12"/>
       <c r="K108" s="7"/>
       <c r="L108" s="7"/>
     </row>
@@ -2373,8 +2362,8 @@
       <c r="F109" s="7"/>
       <c r="G109" s="7"/>
       <c r="H109" s="7"/>
-      <c r="I109" s="12"/>
-      <c r="J109" s="13"/>
+      <c r="I109" s="11"/>
+      <c r="J109" s="12"/>
       <c r="K109" s="7"/>
       <c r="L109" s="7"/>
     </row>
@@ -2387,8 +2376,8 @@
       <c r="F110" s="7"/>
       <c r="G110" s="7"/>
       <c r="H110" s="7"/>
-      <c r="I110" s="12"/>
-      <c r="J110" s="13"/>
+      <c r="I110" s="11"/>
+      <c r="J110" s="12"/>
       <c r="K110" s="7"/>
       <c r="L110" s="7"/>
     </row>
@@ -2401,8 +2390,8 @@
       <c r="F111" s="7"/>
       <c r="G111" s="7"/>
       <c r="H111" s="7"/>
-      <c r="I111" s="12"/>
-      <c r="J111" s="13"/>
+      <c r="I111" s="11"/>
+      <c r="J111" s="12"/>
       <c r="K111" s="7"/>
       <c r="L111" s="7"/>
     </row>
@@ -2415,8 +2404,8 @@
       <c r="F112" s="7"/>
       <c r="G112" s="7"/>
       <c r="H112" s="7"/>
-      <c r="I112" s="12"/>
-      <c r="J112" s="13"/>
+      <c r="I112" s="11"/>
+      <c r="J112" s="12"/>
       <c r="K112" s="7"/>
       <c r="L112" s="7"/>
     </row>
@@ -2429,8 +2418,8 @@
       <c r="F113" s="7"/>
       <c r="G113" s="7"/>
       <c r="H113" s="7"/>
-      <c r="I113" s="12"/>
-      <c r="J113" s="13"/>
+      <c r="I113" s="11"/>
+      <c r="J113" s="12"/>
       <c r="K113" s="7"/>
       <c r="L113" s="7"/>
     </row>
@@ -2443,8 +2432,8 @@
       <c r="F114" s="7"/>
       <c r="G114" s="7"/>
       <c r="H114" s="7"/>
-      <c r="I114" s="12"/>
-      <c r="J114" s="13"/>
+      <c r="I114" s="11"/>
+      <c r="J114" s="12"/>
       <c r="K114" s="7"/>
       <c r="L114" s="7"/>
     </row>
@@ -2457,8 +2446,8 @@
       <c r="F115" s="7"/>
       <c r="G115" s="7"/>
       <c r="H115" s="7"/>
-      <c r="I115" s="12"/>
-      <c r="J115" s="13"/>
+      <c r="I115" s="11"/>
+      <c r="J115" s="12"/>
       <c r="K115" s="7"/>
       <c r="L115" s="7"/>
     </row>
@@ -2471,8 +2460,8 @@
       <c r="F116" s="7"/>
       <c r="G116" s="7"/>
       <c r="H116" s="7"/>
-      <c r="I116" s="12"/>
-      <c r="J116" s="13"/>
+      <c r="I116" s="11"/>
+      <c r="J116" s="12"/>
       <c r="K116" s="7"/>
       <c r="L116" s="7"/>
     </row>
@@ -2485,8 +2474,8 @@
       <c r="F117" s="7"/>
       <c r="G117" s="7"/>
       <c r="H117" s="7"/>
-      <c r="I117" s="12"/>
-      <c r="J117" s="13"/>
+      <c r="I117" s="11"/>
+      <c r="J117" s="12"/>
       <c r="K117" s="7"/>
       <c r="L117" s="7"/>
     </row>
@@ -2499,8 +2488,8 @@
       <c r="F118" s="7"/>
       <c r="G118" s="7"/>
       <c r="H118" s="7"/>
-      <c r="I118" s="12"/>
-      <c r="J118" s="13"/>
+      <c r="I118" s="11"/>
+      <c r="J118" s="12"/>
       <c r="K118" s="7"/>
       <c r="L118" s="7"/>
     </row>
@@ -2513,8 +2502,8 @@
       <c r="F119" s="7"/>
       <c r="G119" s="7"/>
       <c r="H119" s="7"/>
-      <c r="I119" s="12"/>
-      <c r="J119" s="13"/>
+      <c r="I119" s="11"/>
+      <c r="J119" s="12"/>
       <c r="K119" s="7"/>
       <c r="L119" s="7"/>
     </row>
@@ -2527,8 +2516,8 @@
       <c r="F120" s="7"/>
       <c r="G120" s="7"/>
       <c r="H120" s="7"/>
-      <c r="I120" s="12"/>
-      <c r="J120" s="13"/>
+      <c r="I120" s="11"/>
+      <c r="J120" s="12"/>
       <c r="K120" s="7"/>
       <c r="L120" s="7"/>
     </row>
@@ -2541,8 +2530,8 @@
       <c r="F121" s="7"/>
       <c r="G121" s="7"/>
       <c r="H121" s="7"/>
-      <c r="I121" s="12"/>
-      <c r="J121" s="13"/>
+      <c r="I121" s="11"/>
+      <c r="J121" s="12"/>
       <c r="K121" s="7"/>
       <c r="L121" s="7"/>
     </row>
@@ -2555,8 +2544,8 @@
       <c r="F122" s="7"/>
       <c r="G122" s="7"/>
       <c r="H122" s="7"/>
-      <c r="I122" s="12"/>
-      <c r="J122" s="13"/>
+      <c r="I122" s="11"/>
+      <c r="J122" s="12"/>
       <c r="K122" s="7"/>
       <c r="L122" s="7"/>
     </row>
@@ -2569,8 +2558,8 @@
       <c r="F123" s="7"/>
       <c r="G123" s="7"/>
       <c r="H123" s="7"/>
-      <c r="I123" s="12"/>
-      <c r="J123" s="13"/>
+      <c r="I123" s="11"/>
+      <c r="J123" s="12"/>
       <c r="K123" s="7"/>
       <c r="L123" s="7"/>
     </row>
@@ -2583,8 +2572,8 @@
       <c r="F124" s="7"/>
       <c r="G124" s="7"/>
       <c r="H124" s="7"/>
-      <c r="I124" s="12"/>
-      <c r="J124" s="13"/>
+      <c r="I124" s="11"/>
+      <c r="J124" s="12"/>
       <c r="K124" s="7"/>
       <c r="L124" s="7"/>
     </row>
@@ -2597,8 +2586,8 @@
       <c r="F125" s="7"/>
       <c r="G125" s="7"/>
       <c r="H125" s="7"/>
-      <c r="I125" s="12"/>
-      <c r="J125" s="13"/>
+      <c r="I125" s="11"/>
+      <c r="J125" s="12"/>
       <c r="K125" s="7"/>
       <c r="L125" s="7"/>
     </row>
@@ -2611,8 +2600,8 @@
       <c r="F126" s="7"/>
       <c r="G126" s="7"/>
       <c r="H126" s="7"/>
-      <c r="I126" s="12"/>
-      <c r="J126" s="13"/>
+      <c r="I126" s="11"/>
+      <c r="J126" s="12"/>
       <c r="K126" s="7"/>
       <c r="L126" s="7"/>
     </row>
@@ -2625,8 +2614,8 @@
       <c r="F127" s="7"/>
       <c r="G127" s="7"/>
       <c r="H127" s="7"/>
-      <c r="I127" s="12"/>
-      <c r="J127" s="13"/>
+      <c r="I127" s="11"/>
+      <c r="J127" s="12"/>
       <c r="K127" s="7"/>
       <c r="L127" s="7"/>
     </row>
@@ -2639,8 +2628,8 @@
       <c r="F128" s="7"/>
       <c r="G128" s="7"/>
       <c r="H128" s="7"/>
-      <c r="I128" s="12"/>
-      <c r="J128" s="13"/>
+      <c r="I128" s="11"/>
+      <c r="J128" s="12"/>
       <c r="K128" s="7"/>
       <c r="L128" s="7"/>
     </row>
@@ -2653,8 +2642,8 @@
       <c r="F129" s="7"/>
       <c r="G129" s="7"/>
       <c r="H129" s="7"/>
-      <c r="I129" s="12"/>
-      <c r="J129" s="13"/>
+      <c r="I129" s="11"/>
+      <c r="J129" s="12"/>
       <c r="K129" s="7"/>
       <c r="L129" s="7"/>
     </row>
@@ -2667,8 +2656,8 @@
       <c r="F130" s="7"/>
       <c r="G130" s="7"/>
       <c r="H130" s="7"/>
-      <c r="I130" s="12"/>
-      <c r="J130" s="13"/>
+      <c r="I130" s="11"/>
+      <c r="J130" s="12"/>
       <c r="K130" s="7"/>
       <c r="L130" s="7"/>
     </row>
@@ -2681,8 +2670,8 @@
       <c r="F131" s="7"/>
       <c r="G131" s="7"/>
       <c r="H131" s="7"/>
-      <c r="I131" s="12"/>
-      <c r="J131" s="13"/>
+      <c r="I131" s="11"/>
+      <c r="J131" s="12"/>
       <c r="K131" s="7"/>
       <c r="L131" s="7"/>
     </row>
@@ -2695,8 +2684,8 @@
       <c r="F132" s="7"/>
       <c r="G132" s="7"/>
       <c r="H132" s="7"/>
-      <c r="I132" s="12"/>
-      <c r="J132" s="13"/>
+      <c r="I132" s="11"/>
+      <c r="J132" s="12"/>
       <c r="K132" s="7"/>
       <c r="L132" s="7"/>
     </row>
@@ -2709,8 +2698,8 @@
       <c r="F133" s="7"/>
       <c r="G133" s="7"/>
       <c r="H133" s="7"/>
-      <c r="I133" s="12"/>
-      <c r="J133" s="13"/>
+      <c r="I133" s="11"/>
+      <c r="J133" s="12"/>
       <c r="K133" s="7"/>
       <c r="L133" s="7"/>
     </row>
@@ -2723,8 +2712,8 @@
       <c r="F134" s="7"/>
       <c r="G134" s="7"/>
       <c r="H134" s="7"/>
-      <c r="I134" s="12"/>
-      <c r="J134" s="13"/>
+      <c r="I134" s="11"/>
+      <c r="J134" s="12"/>
       <c r="K134" s="7"/>
       <c r="L134" s="7"/>
     </row>
@@ -2737,8 +2726,8 @@
       <c r="F135" s="7"/>
       <c r="G135" s="7"/>
       <c r="H135" s="7"/>
-      <c r="I135" s="12"/>
-      <c r="J135" s="13"/>
+      <c r="I135" s="11"/>
+      <c r="J135" s="12"/>
       <c r="K135" s="7"/>
       <c r="L135" s="7"/>
     </row>
@@ -2751,8 +2740,8 @@
       <c r="F136" s="7"/>
       <c r="G136" s="7"/>
       <c r="H136" s="7"/>
-      <c r="I136" s="12"/>
-      <c r="J136" s="13"/>
+      <c r="I136" s="11"/>
+      <c r="J136" s="12"/>
       <c r="K136" s="7"/>
       <c r="L136" s="7"/>
     </row>
@@ -2765,8 +2754,8 @@
       <c r="F137" s="7"/>
       <c r="G137" s="7"/>
       <c r="H137" s="7"/>
-      <c r="I137" s="12"/>
-      <c r="J137" s="13"/>
+      <c r="I137" s="11"/>
+      <c r="J137" s="12"/>
       <c r="K137" s="7"/>
       <c r="L137" s="7"/>
     </row>
@@ -2779,8 +2768,8 @@
       <c r="F138" s="7"/>
       <c r="G138" s="7"/>
       <c r="H138" s="7"/>
-      <c r="I138" s="12"/>
-      <c r="J138" s="13"/>
+      <c r="I138" s="11"/>
+      <c r="J138" s="12"/>
       <c r="K138" s="7"/>
       <c r="L138" s="7"/>
     </row>
@@ -2793,8 +2782,8 @@
       <c r="F139" s="7"/>
       <c r="G139" s="7"/>
       <c r="H139" s="7"/>
-      <c r="I139" s="12"/>
-      <c r="J139" s="13"/>
+      <c r="I139" s="11"/>
+      <c r="J139" s="12"/>
       <c r="K139" s="7"/>
       <c r="L139" s="7"/>
     </row>
@@ -2807,8 +2796,8 @@
       <c r="F140" s="7"/>
       <c r="G140" s="7"/>
       <c r="H140" s="7"/>
-      <c r="I140" s="12"/>
-      <c r="J140" s="13"/>
+      <c r="I140" s="11"/>
+      <c r="J140" s="12"/>
       <c r="K140" s="7"/>
       <c r="L140" s="7"/>
     </row>
@@ -2821,8 +2810,8 @@
       <c r="F141" s="7"/>
       <c r="G141" s="7"/>
       <c r="H141" s="7"/>
-      <c r="I141" s="12"/>
-      <c r="J141" s="13"/>
+      <c r="I141" s="11"/>
+      <c r="J141" s="12"/>
       <c r="K141" s="7"/>
       <c r="L141" s="7"/>
     </row>
@@ -2835,8 +2824,8 @@
       <c r="F142" s="7"/>
       <c r="G142" s="7"/>
       <c r="H142" s="7"/>
-      <c r="I142" s="12"/>
-      <c r="J142" s="13"/>
+      <c r="I142" s="11"/>
+      <c r="J142" s="12"/>
       <c r="K142" s="7"/>
       <c r="L142" s="7"/>
     </row>
@@ -2849,8 +2838,8 @@
       <c r="F143" s="7"/>
       <c r="G143" s="7"/>
       <c r="H143" s="7"/>
-      <c r="I143" s="12"/>
-      <c r="J143" s="13"/>
+      <c r="I143" s="11"/>
+      <c r="J143" s="12"/>
       <c r="K143" s="7"/>
       <c r="L143" s="7"/>
     </row>
@@ -2863,8 +2852,8 @@
       <c r="F144" s="7"/>
       <c r="G144" s="7"/>
       <c r="H144" s="7"/>
-      <c r="I144" s="12"/>
-      <c r="J144" s="13"/>
+      <c r="I144" s="11"/>
+      <c r="J144" s="12"/>
       <c r="K144" s="7"/>
       <c r="L144" s="7"/>
     </row>
@@ -2877,8 +2866,8 @@
       <c r="F145" s="7"/>
       <c r="G145" s="7"/>
       <c r="H145" s="7"/>
-      <c r="I145" s="12"/>
-      <c r="J145" s="13"/>
+      <c r="I145" s="11"/>
+      <c r="J145" s="12"/>
       <c r="K145" s="7"/>
       <c r="L145" s="7"/>
     </row>
@@ -2891,8 +2880,8 @@
       <c r="F146" s="7"/>
       <c r="G146" s="7"/>
       <c r="H146" s="7"/>
-      <c r="I146" s="12"/>
-      <c r="J146" s="13"/>
+      <c r="I146" s="11"/>
+      <c r="J146" s="12"/>
       <c r="K146" s="7"/>
       <c r="L146" s="7"/>
     </row>
@@ -2905,8 +2894,8 @@
       <c r="F147" s="7"/>
       <c r="G147" s="7"/>
       <c r="H147" s="7"/>
-      <c r="I147" s="12"/>
-      <c r="J147" s="13"/>
+      <c r="I147" s="11"/>
+      <c r="J147" s="12"/>
       <c r="K147" s="7"/>
       <c r="L147" s="7"/>
     </row>
@@ -2919,8 +2908,8 @@
       <c r="F148" s="7"/>
       <c r="G148" s="7"/>
       <c r="H148" s="7"/>
-      <c r="I148" s="12"/>
-      <c r="J148" s="13"/>
+      <c r="I148" s="11"/>
+      <c r="J148" s="12"/>
       <c r="K148" s="7"/>
       <c r="L148" s="7"/>
     </row>
@@ -2933,8 +2922,8 @@
       <c r="F149" s="7"/>
       <c r="G149" s="7"/>
       <c r="H149" s="7"/>
-      <c r="I149" s="12"/>
-      <c r="J149" s="13"/>
+      <c r="I149" s="11"/>
+      <c r="J149" s="12"/>
       <c r="K149" s="7"/>
       <c r="L149" s="7"/>
     </row>
@@ -2947,8 +2936,8 @@
       <c r="F150" s="7"/>
       <c r="G150" s="7"/>
       <c r="H150" s="7"/>
-      <c r="I150" s="12"/>
-      <c r="J150" s="13"/>
+      <c r="I150" s="11"/>
+      <c r="J150" s="12"/>
       <c r="K150" s="7"/>
       <c r="L150" s="7"/>
     </row>
@@ -2961,8 +2950,8 @@
       <c r="F151" s="7"/>
       <c r="G151" s="7"/>
       <c r="H151" s="7"/>
-      <c r="I151" s="12"/>
-      <c r="J151" s="13"/>
+      <c r="I151" s="11"/>
+      <c r="J151" s="12"/>
       <c r="K151" s="7"/>
       <c r="L151" s="7"/>
     </row>
@@ -2975,8 +2964,8 @@
       <c r="F152" s="7"/>
       <c r="G152" s="7"/>
       <c r="H152" s="7"/>
-      <c r="I152" s="12"/>
-      <c r="J152" s="13"/>
+      <c r="I152" s="11"/>
+      <c r="J152" s="12"/>
       <c r="K152" s="7"/>
       <c r="L152" s="7"/>
     </row>
@@ -2989,8 +2978,8 @@
       <c r="F153" s="7"/>
       <c r="G153" s="7"/>
       <c r="H153" s="7"/>
-      <c r="I153" s="12"/>
-      <c r="J153" s="13"/>
+      <c r="I153" s="11"/>
+      <c r="J153" s="12"/>
       <c r="K153" s="7"/>
       <c r="L153" s="7"/>
     </row>
@@ -3003,8 +2992,8 @@
       <c r="F154" s="7"/>
       <c r="G154" s="7"/>
       <c r="H154" s="7"/>
-      <c r="I154" s="12"/>
-      <c r="J154" s="13"/>
+      <c r="I154" s="11"/>
+      <c r="J154" s="12"/>
       <c r="K154" s="7"/>
       <c r="L154" s="7"/>
     </row>
@@ -3017,8 +3006,8 @@
       <c r="F155" s="7"/>
       <c r="G155" s="7"/>
       <c r="H155" s="7"/>
-      <c r="I155" s="12"/>
-      <c r="J155" s="13"/>
+      <c r="I155" s="11"/>
+      <c r="J155" s="12"/>
       <c r="K155" s="7"/>
       <c r="L155" s="7"/>
     </row>
@@ -3031,8 +3020,8 @@
       <c r="F156" s="7"/>
       <c r="G156" s="7"/>
       <c r="H156" s="7"/>
-      <c r="I156" s="12"/>
-      <c r="J156" s="13"/>
+      <c r="I156" s="11"/>
+      <c r="J156" s="12"/>
       <c r="K156" s="7"/>
       <c r="L156" s="7"/>
     </row>
@@ -3045,8 +3034,8 @@
       <c r="F157" s="7"/>
       <c r="G157" s="7"/>
       <c r="H157" s="7"/>
-      <c r="I157" s="12"/>
-      <c r="J157" s="13"/>
+      <c r="I157" s="11"/>
+      <c r="J157" s="12"/>
       <c r="K157" s="7"/>
       <c r="L157" s="7"/>
     </row>
@@ -3059,8 +3048,8 @@
       <c r="F158" s="7"/>
       <c r="G158" s="7"/>
       <c r="H158" s="7"/>
-      <c r="I158" s="12"/>
-      <c r="J158" s="13"/>
+      <c r="I158" s="11"/>
+      <c r="J158" s="12"/>
       <c r="K158" s="7"/>
       <c r="L158" s="7"/>
     </row>
@@ -3073,8 +3062,8 @@
       <c r="F159" s="7"/>
       <c r="G159" s="7"/>
       <c r="H159" s="7"/>
-      <c r="I159" s="12"/>
-      <c r="J159" s="13"/>
+      <c r="I159" s="11"/>
+      <c r="J159" s="12"/>
       <c r="K159" s="7"/>
       <c r="L159" s="7"/>
     </row>
@@ -3087,8 +3076,8 @@
       <c r="F160" s="7"/>
       <c r="G160" s="7"/>
       <c r="H160" s="7"/>
-      <c r="I160" s="12"/>
-      <c r="J160" s="13"/>
+      <c r="I160" s="11"/>
+      <c r="J160" s="12"/>
       <c r="K160" s="7"/>
       <c r="L160" s="7"/>
     </row>
@@ -3101,8 +3090,8 @@
       <c r="F161" s="7"/>
       <c r="G161" s="7"/>
       <c r="H161" s="7"/>
-      <c r="I161" s="12"/>
-      <c r="J161" s="13"/>
+      <c r="I161" s="11"/>
+      <c r="J161" s="12"/>
       <c r="K161" s="7"/>
       <c r="L161" s="7"/>
     </row>
@@ -3115,8 +3104,8 @@
       <c r="F162" s="7"/>
       <c r="G162" s="7"/>
       <c r="H162" s="7"/>
-      <c r="I162" s="12"/>
-      <c r="J162" s="13"/>
+      <c r="I162" s="11"/>
+      <c r="J162" s="12"/>
       <c r="K162" s="7"/>
       <c r="L162" s="7"/>
     </row>
@@ -3129,8 +3118,8 @@
       <c r="F163" s="7"/>
       <c r="G163" s="7"/>
       <c r="H163" s="7"/>
-      <c r="I163" s="12"/>
-      <c r="J163" s="13"/>
+      <c r="I163" s="11"/>
+      <c r="J163" s="12"/>
       <c r="K163" s="7"/>
       <c r="L163" s="7"/>
     </row>
@@ -3143,8 +3132,8 @@
       <c r="F164" s="7"/>
       <c r="G164" s="7"/>
       <c r="H164" s="7"/>
-      <c r="I164" s="12"/>
-      <c r="J164" s="13"/>
+      <c r="I164" s="11"/>
+      <c r="J164" s="12"/>
       <c r="K164" s="7"/>
       <c r="L164" s="7"/>
     </row>
@@ -3157,8 +3146,8 @@
       <c r="F165" s="7"/>
       <c r="G165" s="7"/>
       <c r="H165" s="7"/>
-      <c r="I165" s="12"/>
-      <c r="J165" s="13"/>
+      <c r="I165" s="11"/>
+      <c r="J165" s="12"/>
       <c r="K165" s="7"/>
       <c r="L165" s="7"/>
     </row>
@@ -3171,8 +3160,8 @@
       <c r="F166" s="7"/>
       <c r="G166" s="7"/>
       <c r="H166" s="7"/>
-      <c r="I166" s="12"/>
-      <c r="J166" s="13"/>
+      <c r="I166" s="11"/>
+      <c r="J166" s="12"/>
       <c r="K166" s="7"/>
       <c r="L166" s="7"/>
     </row>
@@ -3185,8 +3174,8 @@
       <c r="F167" s="7"/>
       <c r="G167" s="7"/>
       <c r="H167" s="7"/>
-      <c r="I167" s="12"/>
-      <c r="J167" s="13"/>
+      <c r="I167" s="11"/>
+      <c r="J167" s="12"/>
       <c r="K167" s="7"/>
       <c r="L167" s="7"/>
     </row>
@@ -3199,8 +3188,8 @@
       <c r="F168" s="7"/>
       <c r="G168" s="7"/>
       <c r="H168" s="7"/>
-      <c r="I168" s="12"/>
-      <c r="J168" s="13"/>
+      <c r="I168" s="11"/>
+      <c r="J168" s="12"/>
       <c r="K168" s="7"/>
       <c r="L168" s="7"/>
     </row>
@@ -3213,8 +3202,8 @@
       <c r="F169" s="7"/>
       <c r="G169" s="7"/>
       <c r="H169" s="7"/>
-      <c r="I169" s="12"/>
-      <c r="J169" s="13"/>
+      <c r="I169" s="11"/>
+      <c r="J169" s="12"/>
       <c r="K169" s="7"/>
       <c r="L169" s="7"/>
     </row>
@@ -3227,8 +3216,8 @@
       <c r="F170" s="7"/>
       <c r="G170" s="7"/>
       <c r="H170" s="7"/>
-      <c r="I170" s="12"/>
-      <c r="J170" s="13"/>
+      <c r="I170" s="11"/>
+      <c r="J170" s="12"/>
       <c r="K170" s="7"/>
       <c r="L170" s="7"/>
     </row>
@@ -3241,8 +3230,8 @@
       <c r="F171" s="7"/>
       <c r="G171" s="7"/>
       <c r="H171" s="7"/>
-      <c r="I171" s="12"/>
-      <c r="J171" s="13"/>
+      <c r="I171" s="11"/>
+      <c r="J171" s="12"/>
       <c r="K171" s="7"/>
       <c r="L171" s="7"/>
     </row>
@@ -3255,8 +3244,8 @@
       <c r="F172" s="7"/>
       <c r="G172" s="7"/>
       <c r="H172" s="7"/>
-      <c r="I172" s="12"/>
-      <c r="J172" s="13"/>
+      <c r="I172" s="11"/>
+      <c r="J172" s="12"/>
       <c r="K172" s="7"/>
       <c r="L172" s="7"/>
     </row>
@@ -3269,8 +3258,8 @@
       <c r="F173" s="7"/>
       <c r="G173" s="7"/>
       <c r="H173" s="7"/>
-      <c r="I173" s="12"/>
-      <c r="J173" s="13"/>
+      <c r="I173" s="11"/>
+      <c r="J173" s="12"/>
       <c r="K173" s="7"/>
       <c r="L173" s="7"/>
     </row>
@@ -3283,8 +3272,8 @@
       <c r="F174" s="7"/>
       <c r="G174" s="7"/>
       <c r="H174" s="7"/>
-      <c r="I174" s="12"/>
-      <c r="J174" s="13"/>
+      <c r="I174" s="11"/>
+      <c r="J174" s="12"/>
       <c r="K174" s="7"/>
       <c r="L174" s="7"/>
     </row>
@@ -3297,8 +3286,8 @@
       <c r="F175" s="7"/>
       <c r="G175" s="7"/>
       <c r="H175" s="7"/>
-      <c r="I175" s="12"/>
-      <c r="J175" s="13"/>
+      <c r="I175" s="11"/>
+      <c r="J175" s="12"/>
       <c r="K175" s="7"/>
       <c r="L175" s="7"/>
     </row>
@@ -3311,8 +3300,8 @@
       <c r="F176" s="7"/>
       <c r="G176" s="7"/>
       <c r="H176" s="7"/>
-      <c r="I176" s="12"/>
-      <c r="J176" s="13"/>
+      <c r="I176" s="11"/>
+      <c r="J176" s="12"/>
       <c r="K176" s="7"/>
       <c r="L176" s="7"/>
     </row>
@@ -3325,8 +3314,8 @@
       <c r="F177" s="7"/>
       <c r="G177" s="7"/>
       <c r="H177" s="7"/>
-      <c r="I177" s="12"/>
-      <c r="J177" s="13"/>
+      <c r="I177" s="11"/>
+      <c r="J177" s="12"/>
       <c r="K177" s="7"/>
       <c r="L177" s="7"/>
     </row>
@@ -3339,8 +3328,8 @@
       <c r="F178" s="7"/>
       <c r="G178" s="7"/>
       <c r="H178" s="7"/>
-      <c r="I178" s="12"/>
-      <c r="J178" s="13"/>
+      <c r="I178" s="11"/>
+      <c r="J178" s="12"/>
       <c r="K178" s="7"/>
       <c r="L178" s="7"/>
     </row>
@@ -3353,8 +3342,8 @@
       <c r="F179" s="7"/>
       <c r="G179" s="7"/>
       <c r="H179" s="7"/>
-      <c r="I179" s="12"/>
-      <c r="J179" s="13"/>
+      <c r="I179" s="11"/>
+      <c r="J179" s="12"/>
       <c r="K179" s="7"/>
       <c r="L179" s="7"/>
     </row>
@@ -3367,8 +3356,8 @@
       <c r="F180" s="7"/>
       <c r="G180" s="7"/>
       <c r="H180" s="7"/>
-      <c r="I180" s="12"/>
-      <c r="J180" s="13"/>
+      <c r="I180" s="11"/>
+      <c r="J180" s="12"/>
       <c r="K180" s="7"/>
       <c r="L180" s="7"/>
     </row>
@@ -3381,8 +3370,8 @@
       <c r="F181" s="7"/>
       <c r="G181" s="7"/>
       <c r="H181" s="7"/>
-      <c r="I181" s="12"/>
-      <c r="J181" s="13"/>
+      <c r="I181" s="11"/>
+      <c r="J181" s="12"/>
       <c r="K181" s="7"/>
       <c r="L181" s="7"/>
     </row>
@@ -3395,8 +3384,8 @@
       <c r="F182" s="7"/>
       <c r="G182" s="7"/>
       <c r="H182" s="7"/>
-      <c r="I182" s="12"/>
-      <c r="J182" s="13"/>
+      <c r="I182" s="11"/>
+      <c r="J182" s="12"/>
       <c r="K182" s="7"/>
       <c r="L182" s="7"/>
     </row>
@@ -3409,8 +3398,8 @@
       <c r="F183" s="7"/>
       <c r="G183" s="7"/>
       <c r="H183" s="7"/>
-      <c r="I183" s="12"/>
-      <c r="J183" s="13"/>
+      <c r="I183" s="11"/>
+      <c r="J183" s="12"/>
       <c r="K183" s="7"/>
       <c r="L183" s="7"/>
     </row>
@@ -3423,8 +3412,8 @@
       <c r="F184" s="7"/>
       <c r="G184" s="7"/>
       <c r="H184" s="7"/>
-      <c r="I184" s="12"/>
-      <c r="J184" s="13"/>
+      <c r="I184" s="11"/>
+      <c r="J184" s="12"/>
       <c r="K184" s="7"/>
       <c r="L184" s="7"/>
     </row>
@@ -3437,8 +3426,8 @@
       <c r="F185" s="7"/>
       <c r="G185" s="7"/>
       <c r="H185" s="7"/>
-      <c r="I185" s="12"/>
-      <c r="J185" s="13"/>
+      <c r="I185" s="11"/>
+      <c r="J185" s="12"/>
       <c r="K185" s="7"/>
       <c r="L185" s="7"/>
     </row>
@@ -3451,8 +3440,8 @@
       <c r="F186" s="7"/>
       <c r="G186" s="7"/>
       <c r="H186" s="7"/>
-      <c r="I186" s="12"/>
-      <c r="J186" s="13"/>
+      <c r="I186" s="11"/>
+      <c r="J186" s="12"/>
       <c r="K186" s="7"/>
       <c r="L186" s="7"/>
     </row>
@@ -3465,8 +3454,8 @@
       <c r="F187" s="7"/>
       <c r="G187" s="7"/>
       <c r="H187" s="7"/>
-      <c r="I187" s="12"/>
-      <c r="J187" s="13"/>
+      <c r="I187" s="11"/>
+      <c r="J187" s="12"/>
       <c r="K187" s="7"/>
       <c r="L187" s="7"/>
     </row>
@@ -3479,8 +3468,8 @@
       <c r="F188" s="7"/>
       <c r="G188" s="7"/>
       <c r="H188" s="7"/>
-      <c r="I188" s="12"/>
-      <c r="J188" s="13"/>
+      <c r="I188" s="11"/>
+      <c r="J188" s="12"/>
       <c r="K188" s="7"/>
       <c r="L188" s="7"/>
     </row>
@@ -3493,8 +3482,8 @@
       <c r="F189" s="7"/>
       <c r="G189" s="7"/>
       <c r="H189" s="7"/>
-      <c r="I189" s="12"/>
-      <c r="J189" s="13"/>
+      <c r="I189" s="11"/>
+      <c r="J189" s="12"/>
       <c r="K189" s="7"/>
       <c r="L189" s="7"/>
     </row>
@@ -3507,8 +3496,8 @@
       <c r="F190" s="7"/>
       <c r="G190" s="7"/>
       <c r="H190" s="7"/>
-      <c r="I190" s="12"/>
-      <c r="J190" s="13"/>
+      <c r="I190" s="11"/>
+      <c r="J190" s="12"/>
       <c r="K190" s="7"/>
       <c r="L190" s="7"/>
     </row>
@@ -3521,8 +3510,8 @@
       <c r="F191" s="7"/>
       <c r="G191" s="7"/>
       <c r="H191" s="7"/>
-      <c r="I191" s="12"/>
-      <c r="J191" s="13"/>
+      <c r="I191" s="11"/>
+      <c r="J191" s="12"/>
       <c r="K191" s="7"/>
       <c r="L191" s="7"/>
     </row>
@@ -3535,8 +3524,8 @@
       <c r="F192" s="7"/>
       <c r="G192" s="7"/>
       <c r="H192" s="7"/>
-      <c r="I192" s="12"/>
-      <c r="J192" s="13"/>
+      <c r="I192" s="11"/>
+      <c r="J192" s="12"/>
       <c r="K192" s="7"/>
       <c r="L192" s="7"/>
     </row>
@@ -3549,8 +3538,8 @@
       <c r="F193" s="7"/>
       <c r="G193" s="7"/>
       <c r="H193" s="7"/>
-      <c r="I193" s="12"/>
-      <c r="J193" s="13"/>
+      <c r="I193" s="11"/>
+      <c r="J193" s="12"/>
       <c r="K193" s="7"/>
       <c r="L193" s="7"/>
     </row>
@@ -3563,8 +3552,8 @@
       <c r="F194" s="7"/>
       <c r="G194" s="7"/>
       <c r="H194" s="7"/>
-      <c r="I194" s="12"/>
-      <c r="J194" s="13"/>
+      <c r="I194" s="11"/>
+      <c r="J194" s="12"/>
       <c r="K194" s="7"/>
       <c r="L194" s="7"/>
     </row>
@@ -3577,8 +3566,8 @@
       <c r="F195" s="7"/>
       <c r="G195" s="7"/>
       <c r="H195" s="7"/>
-      <c r="I195" s="12"/>
-      <c r="J195" s="13"/>
+      <c r="I195" s="11"/>
+      <c r="J195" s="12"/>
       <c r="K195" s="7"/>
       <c r="L195" s="7"/>
     </row>
@@ -3591,8 +3580,8 @@
       <c r="F196" s="7"/>
       <c r="G196" s="7"/>
       <c r="H196" s="7"/>
-      <c r="I196" s="12"/>
-      <c r="J196" s="13"/>
+      <c r="I196" s="11"/>
+      <c r="J196" s="12"/>
       <c r="K196" s="7"/>
       <c r="L196" s="7"/>
     </row>
@@ -3605,8 +3594,8 @@
       <c r="F197" s="7"/>
       <c r="G197" s="7"/>
       <c r="H197" s="7"/>
-      <c r="I197" s="12"/>
-      <c r="J197" s="13"/>
+      <c r="I197" s="11"/>
+      <c r="J197" s="12"/>
       <c r="K197" s="7"/>
       <c r="L197" s="7"/>
     </row>
@@ -3619,8 +3608,8 @@
       <c r="F198" s="7"/>
       <c r="G198" s="7"/>
       <c r="H198" s="7"/>
-      <c r="I198" s="12"/>
-      <c r="J198" s="13"/>
+      <c r="I198" s="11"/>
+      <c r="J198" s="12"/>
       <c r="K198" s="7"/>
       <c r="L198" s="7"/>
     </row>
@@ -3633,8 +3622,8 @@
       <c r="F199" s="7"/>
       <c r="G199" s="7"/>
       <c r="H199" s="7"/>
-      <c r="I199" s="12"/>
-      <c r="J199" s="13"/>
+      <c r="I199" s="11"/>
+      <c r="J199" s="12"/>
       <c r="K199" s="7"/>
       <c r="L199" s="7"/>
     </row>
@@ -3647,8 +3636,8 @@
       <c r="F200" s="7"/>
       <c r="G200" s="7"/>
       <c r="H200" s="7"/>
-      <c r="I200" s="12"/>
-      <c r="J200" s="13"/>
+      <c r="I200" s="11"/>
+      <c r="J200" s="12"/>
       <c r="K200" s="7"/>
       <c r="L200" s="7"/>
     </row>
@@ -3661,8 +3650,8 @@
       <c r="F201" s="7"/>
       <c r="G201" s="7"/>
       <c r="H201" s="7"/>
-      <c r="I201" s="12"/>
-      <c r="J201" s="13"/>
+      <c r="I201" s="11"/>
+      <c r="J201" s="12"/>
       <c r="K201" s="7"/>
       <c r="L201" s="7"/>
     </row>
@@ -3675,8 +3664,8 @@
       <c r="F202" s="7"/>
       <c r="G202" s="7"/>
       <c r="H202" s="7"/>
-      <c r="I202" s="12"/>
-      <c r="J202" s="13"/>
+      <c r="I202" s="11"/>
+      <c r="J202" s="12"/>
       <c r="K202" s="7"/>
       <c r="L202" s="7"/>
     </row>
@@ -3689,8 +3678,8 @@
       <c r="F203" s="7"/>
       <c r="G203" s="7"/>
       <c r="H203" s="7"/>
-      <c r="I203" s="12"/>
-      <c r="J203" s="13"/>
+      <c r="I203" s="11"/>
+      <c r="J203" s="12"/>
       <c r="K203" s="7"/>
       <c r="L203" s="7"/>
     </row>
@@ -3703,8 +3692,8 @@
       <c r="F204" s="7"/>
       <c r="G204" s="7"/>
       <c r="H204" s="7"/>
-      <c r="I204" s="12"/>
-      <c r="J204" s="13"/>
+      <c r="I204" s="11"/>
+      <c r="J204" s="12"/>
       <c r="K204" s="7"/>
       <c r="L204" s="7"/>
     </row>
@@ -3717,8 +3706,8 @@
       <c r="F205" s="7"/>
       <c r="G205" s="7"/>
       <c r="H205" s="7"/>
-      <c r="I205" s="12"/>
-      <c r="J205" s="13"/>
+      <c r="I205" s="11"/>
+      <c r="J205" s="12"/>
       <c r="K205" s="7"/>
       <c r="L205" s="7"/>
     </row>
@@ -3731,8 +3720,8 @@
       <c r="F206" s="7"/>
       <c r="G206" s="7"/>
       <c r="H206" s="7"/>
-      <c r="I206" s="12"/>
-      <c r="J206" s="13"/>
+      <c r="I206" s="11"/>
+      <c r="J206" s="12"/>
       <c r="K206" s="7"/>
       <c r="L206" s="7"/>
     </row>
@@ -3745,8 +3734,8 @@
       <c r="F207" s="7"/>
       <c r="G207" s="7"/>
       <c r="H207" s="7"/>
-      <c r="I207" s="12"/>
-      <c r="J207" s="13"/>
+      <c r="I207" s="11"/>
+      <c r="J207" s="12"/>
       <c r="K207" s="7"/>
       <c r="L207" s="7"/>
     </row>
@@ -3759,8 +3748,8 @@
       <c r="F208" s="7"/>
       <c r="G208" s="7"/>
       <c r="H208" s="7"/>
-      <c r="I208" s="12"/>
-      <c r="J208" s="13"/>
+      <c r="I208" s="11"/>
+      <c r="J208" s="12"/>
       <c r="K208" s="7"/>
       <c r="L208" s="7"/>
     </row>
@@ -3773,8 +3762,8 @@
       <c r="F209" s="7"/>
       <c r="G209" s="7"/>
       <c r="H209" s="7"/>
-      <c r="I209" s="12"/>
-      <c r="J209" s="13"/>
+      <c r="I209" s="11"/>
+      <c r="J209" s="12"/>
       <c r="K209" s="7"/>
       <c r="L209" s="7"/>
     </row>
@@ -3787,8 +3776,8 @@
       <c r="F210" s="7"/>
       <c r="G210" s="7"/>
       <c r="H210" s="7"/>
-      <c r="I210" s="12"/>
-      <c r="J210" s="13"/>
+      <c r="I210" s="11"/>
+      <c r="J210" s="12"/>
       <c r="K210" s="7"/>
       <c r="L210" s="7"/>
     </row>
@@ -3801,8 +3790,8 @@
       <c r="F211" s="7"/>
       <c r="G211" s="7"/>
       <c r="H211" s="7"/>
-      <c r="I211" s="12"/>
-      <c r="J211" s="13"/>
+      <c r="I211" s="11"/>
+      <c r="J211" s="12"/>
       <c r="K211" s="7"/>
       <c r="L211" s="7"/>
     </row>
@@ -3815,8 +3804,8 @@
       <c r="F212" s="7"/>
       <c r="G212" s="7"/>
       <c r="H212" s="7"/>
-      <c r="I212" s="12"/>
-      <c r="J212" s="13"/>
+      <c r="I212" s="11"/>
+      <c r="J212" s="12"/>
       <c r="K212" s="7"/>
       <c r="L212" s="7"/>
     </row>
@@ -3829,8 +3818,8 @@
       <c r="F213" s="7"/>
       <c r="G213" s="7"/>
       <c r="H213" s="7"/>
-      <c r="I213" s="12"/>
-      <c r="J213" s="13"/>
+      <c r="I213" s="11"/>
+      <c r="J213" s="12"/>
       <c r="K213" s="7"/>
       <c r="L213" s="7"/>
     </row>
@@ -3843,8 +3832,8 @@
       <c r="F214" s="7"/>
       <c r="G214" s="7"/>
       <c r="H214" s="7"/>
-      <c r="I214" s="12"/>
-      <c r="J214" s="13"/>
+      <c r="I214" s="11"/>
+      <c r="J214" s="12"/>
       <c r="K214" s="7"/>
       <c r="L214" s="7"/>
     </row>
@@ -3857,8 +3846,8 @@
       <c r="F215" s="7"/>
       <c r="G215" s="7"/>
       <c r="H215" s="7"/>
-      <c r="I215" s="12"/>
-      <c r="J215" s="13"/>
+      <c r="I215" s="11"/>
+      <c r="J215" s="12"/>
       <c r="K215" s="7"/>
       <c r="L215" s="7"/>
     </row>
@@ -3871,8 +3860,8 @@
       <c r="F216" s="7"/>
       <c r="G216" s="7"/>
       <c r="H216" s="7"/>
-      <c r="I216" s="12"/>
-      <c r="J216" s="13"/>
+      <c r="I216" s="11"/>
+      <c r="J216" s="12"/>
       <c r="K216" s="7"/>
       <c r="L216" s="7"/>
     </row>
@@ -3885,8 +3874,8 @@
       <c r="F217" s="7"/>
       <c r="G217" s="7"/>
       <c r="H217" s="7"/>
-      <c r="I217" s="12"/>
-      <c r="J217" s="13"/>
+      <c r="I217" s="11"/>
+      <c r="J217" s="12"/>
       <c r="K217" s="7"/>
       <c r="L217" s="7"/>
     </row>
@@ -3899,8 +3888,8 @@
       <c r="F218" s="7"/>
       <c r="G218" s="7"/>
       <c r="H218" s="7"/>
-      <c r="I218" s="12"/>
-      <c r="J218" s="13"/>
+      <c r="I218" s="11"/>
+      <c r="J218" s="12"/>
       <c r="K218" s="7"/>
       <c r="L218" s="7"/>
     </row>
@@ -3913,8 +3902,8 @@
       <c r="F219" s="7"/>
       <c r="G219" s="7"/>
       <c r="H219" s="7"/>
-      <c r="I219" s="12"/>
-      <c r="J219" s="13"/>
+      <c r="I219" s="11"/>
+      <c r="J219" s="12"/>
       <c r="K219" s="7"/>
       <c r="L219" s="7"/>
     </row>
@@ -3927,8 +3916,8 @@
       <c r="F220" s="7"/>
       <c r="G220" s="7"/>
       <c r="H220" s="7"/>
-      <c r="I220" s="12"/>
-      <c r="J220" s="13"/>
+      <c r="I220" s="11"/>
+      <c r="J220" s="12"/>
       <c r="K220" s="7"/>
       <c r="L220" s="7"/>
     </row>
@@ -3941,8 +3930,8 @@
       <c r="F221" s="7"/>
       <c r="G221" s="7"/>
       <c r="H221" s="7"/>
-      <c r="I221" s="12"/>
-      <c r="J221" s="13"/>
+      <c r="I221" s="11"/>
+      <c r="J221" s="12"/>
       <c r="K221" s="7"/>
       <c r="L221" s="7"/>
     </row>
@@ -3955,8 +3944,8 @@
       <c r="F222" s="7"/>
       <c r="G222" s="7"/>
       <c r="H222" s="7"/>
-      <c r="I222" s="12"/>
-      <c r="J222" s="13"/>
+      <c r="I222" s="11"/>
+      <c r="J222" s="12"/>
       <c r="K222" s="7"/>
       <c r="L222" s="7"/>
     </row>
@@ -3969,8 +3958,8 @@
       <c r="F223" s="7"/>
       <c r="G223" s="7"/>
       <c r="H223" s="7"/>
-      <c r="I223" s="12"/>
-      <c r="J223" s="13"/>
+      <c r="I223" s="11"/>
+      <c r="J223" s="12"/>
       <c r="K223" s="7"/>
       <c r="L223" s="7"/>
     </row>
@@ -3983,8 +3972,8 @@
       <c r="F224" s="7"/>
       <c r="G224" s="7"/>
       <c r="H224" s="7"/>
-      <c r="I224" s="12"/>
-      <c r="J224" s="13"/>
+      <c r="I224" s="11"/>
+      <c r="J224" s="12"/>
       <c r="K224" s="7"/>
       <c r="L224" s="7"/>
     </row>
@@ -3997,8 +3986,8 @@
       <c r="F225" s="7"/>
       <c r="G225" s="7"/>
       <c r="H225" s="7"/>
-      <c r="I225" s="12"/>
-      <c r="J225" s="13"/>
+      <c r="I225" s="11"/>
+      <c r="J225" s="12"/>
       <c r="K225" s="7"/>
       <c r="L225" s="7"/>
     </row>
@@ -4011,8 +4000,8 @@
       <c r="F226" s="7"/>
       <c r="G226" s="7"/>
       <c r="H226" s="7"/>
-      <c r="I226" s="12"/>
-      <c r="J226" s="13"/>
+      <c r="I226" s="11"/>
+      <c r="J226" s="12"/>
       <c r="K226" s="7"/>
       <c r="L226" s="7"/>
     </row>
@@ -4025,8 +4014,8 @@
       <c r="F227" s="7"/>
       <c r="G227" s="7"/>
       <c r="H227" s="7"/>
-      <c r="I227" s="12"/>
-      <c r="J227" s="13"/>
+      <c r="I227" s="11"/>
+      <c r="J227" s="12"/>
       <c r="K227" s="7"/>
       <c r="L227" s="7"/>
     </row>
@@ -4039,8 +4028,8 @@
       <c r="F228" s="7"/>
       <c r="G228" s="7"/>
       <c r="H228" s="7"/>
-      <c r="I228" s="12"/>
-      <c r="J228" s="13"/>
+      <c r="I228" s="11"/>
+      <c r="J228" s="12"/>
       <c r="K228" s="7"/>
       <c r="L228" s="7"/>
     </row>
@@ -4053,8 +4042,8 @@
       <c r="F229" s="7"/>
       <c r="G229" s="7"/>
       <c r="H229" s="7"/>
-      <c r="I229" s="12"/>
-      <c r="J229" s="13"/>
+      <c r="I229" s="11"/>
+      <c r="J229" s="12"/>
       <c r="K229" s="7"/>
       <c r="L229" s="7"/>
     </row>
@@ -4067,8 +4056,8 @@
       <c r="F230" s="7"/>
       <c r="G230" s="7"/>
       <c r="H230" s="7"/>
-      <c r="I230" s="12"/>
-      <c r="J230" s="13"/>
+      <c r="I230" s="11"/>
+      <c r="J230" s="12"/>
       <c r="K230" s="7"/>
       <c r="L230" s="7"/>
     </row>
@@ -4081,8 +4070,8 @@
       <c r="F231" s="7"/>
       <c r="G231" s="7"/>
       <c r="H231" s="7"/>
-      <c r="I231" s="12"/>
-      <c r="J231" s="13"/>
+      <c r="I231" s="11"/>
+      <c r="J231" s="12"/>
       <c r="K231" s="7"/>
       <c r="L231" s="7"/>
     </row>
@@ -4095,8 +4084,8 @@
       <c r="F232" s="7"/>
       <c r="G232" s="7"/>
       <c r="H232" s="7"/>
-      <c r="I232" s="12"/>
-      <c r="J232" s="13"/>
+      <c r="I232" s="11"/>
+      <c r="J232" s="12"/>
       <c r="K232" s="7"/>
       <c r="L232" s="7"/>
     </row>
@@ -4109,8 +4098,8 @@
       <c r="F233" s="7"/>
       <c r="G233" s="7"/>
       <c r="H233" s="7"/>
-      <c r="I233" s="12"/>
-      <c r="J233" s="13"/>
+      <c r="I233" s="11"/>
+      <c r="J233" s="12"/>
       <c r="K233" s="7"/>
       <c r="L233" s="7"/>
     </row>
@@ -4123,8 +4112,8 @@
       <c r="F234" s="7"/>
       <c r="G234" s="7"/>
       <c r="H234" s="7"/>
-      <c r="I234" s="12"/>
-      <c r="J234" s="13"/>
+      <c r="I234" s="11"/>
+      <c r="J234" s="12"/>
       <c r="K234" s="7"/>
       <c r="L234" s="7"/>
     </row>
@@ -4137,8 +4126,8 @@
       <c r="F235" s="7"/>
       <c r="G235" s="7"/>
       <c r="H235" s="7"/>
-      <c r="I235" s="12"/>
-      <c r="J235" s="13"/>
+      <c r="I235" s="11"/>
+      <c r="J235" s="12"/>
       <c r="K235" s="7"/>
       <c r="L235" s="7"/>
     </row>
@@ -4151,8 +4140,8 @@
       <c r="F236" s="7"/>
       <c r="G236" s="7"/>
       <c r="H236" s="7"/>
-      <c r="I236" s="12"/>
-      <c r="J236" s="13"/>
+      <c r="I236" s="11"/>
+      <c r="J236" s="12"/>
       <c r="K236" s="7"/>
       <c r="L236" s="7"/>
     </row>
@@ -4165,8 +4154,8 @@
       <c r="F237" s="7"/>
       <c r="G237" s="7"/>
       <c r="H237" s="7"/>
-      <c r="I237" s="12"/>
-      <c r="J237" s="13"/>
+      <c r="I237" s="11"/>
+      <c r="J237" s="12"/>
       <c r="K237" s="7"/>
       <c r="L237" s="7"/>
     </row>
@@ -4179,8 +4168,8 @@
       <c r="F238" s="7"/>
       <c r="G238" s="7"/>
       <c r="H238" s="7"/>
-      <c r="I238" s="12"/>
-      <c r="J238" s="13"/>
+      <c r="I238" s="11"/>
+      <c r="J238" s="12"/>
       <c r="K238" s="7"/>
       <c r="L238" s="7"/>
     </row>
@@ -4193,8 +4182,8 @@
       <c r="F239" s="7"/>
       <c r="G239" s="7"/>
       <c r="H239" s="7"/>
-      <c r="I239" s="12"/>
-      <c r="J239" s="13"/>
+      <c r="I239" s="11"/>
+      <c r="J239" s="12"/>
       <c r="K239" s="7"/>
       <c r="L239" s="7"/>
     </row>
@@ -4207,8 +4196,8 @@
       <c r="F240" s="7"/>
       <c r="G240" s="7"/>
       <c r="H240" s="7"/>
-      <c r="I240" s="12"/>
-      <c r="J240" s="13"/>
+      <c r="I240" s="11"/>
+      <c r="J240" s="12"/>
       <c r="K240" s="7"/>
       <c r="L240" s="7"/>
     </row>
@@ -4221,8 +4210,8 @@
       <c r="F241" s="7"/>
       <c r="G241" s="7"/>
       <c r="H241" s="7"/>
-      <c r="I241" s="12"/>
-      <c r="J241" s="13"/>
+      <c r="I241" s="11"/>
+      <c r="J241" s="12"/>
       <c r="K241" s="7"/>
       <c r="L241" s="7"/>
     </row>
@@ -4235,8 +4224,8 @@
       <c r="F242" s="7"/>
       <c r="G242" s="7"/>
       <c r="H242" s="7"/>
-      <c r="I242" s="12"/>
-      <c r="J242" s="13"/>
+      <c r="I242" s="11"/>
+      <c r="J242" s="12"/>
       <c r="K242" s="7"/>
       <c r="L242" s="7"/>
     </row>
@@ -4249,8 +4238,8 @@
       <c r="F243" s="7"/>
       <c r="G243" s="7"/>
       <c r="H243" s="7"/>
-      <c r="I243" s="12"/>
-      <c r="J243" s="13"/>
+      <c r="I243" s="11"/>
+      <c r="J243" s="12"/>
       <c r="K243" s="7"/>
       <c r="L243" s="7"/>
     </row>
@@ -4263,8 +4252,8 @@
       <c r="F244" s="7"/>
       <c r="G244" s="7"/>
       <c r="H244" s="7"/>
-      <c r="I244" s="12"/>
-      <c r="J244" s="13"/>
+      <c r="I244" s="11"/>
+      <c r="J244" s="12"/>
       <c r="K244" s="7"/>
       <c r="L244" s="7"/>
     </row>
@@ -4277,8 +4266,8 @@
       <c r="F245" s="7"/>
       <c r="G245" s="7"/>
       <c r="H245" s="7"/>
-      <c r="I245" s="12"/>
-      <c r="J245" s="13"/>
+      <c r="I245" s="11"/>
+      <c r="J245" s="12"/>
       <c r="K245" s="7"/>
       <c r="L245" s="7"/>
     </row>
@@ -4291,8 +4280,8 @@
       <c r="F246" s="7"/>
       <c r="G246" s="7"/>
       <c r="H246" s="7"/>
-      <c r="I246" s="12"/>
-      <c r="J246" s="13"/>
+      <c r="I246" s="11"/>
+      <c r="J246" s="12"/>
       <c r="K246" s="7"/>
       <c r="L246" s="7"/>
     </row>
@@ -4305,8 +4294,8 @@
       <c r="F247" s="7"/>
       <c r="G247" s="7"/>
       <c r="H247" s="7"/>
-      <c r="I247" s="12"/>
-      <c r="J247" s="13"/>
+      <c r="I247" s="11"/>
+      <c r="J247" s="12"/>
       <c r="K247" s="7"/>
       <c r="L247" s="7"/>
     </row>
@@ -4319,8 +4308,8 @@
       <c r="F248" s="7"/>
       <c r="G248" s="7"/>
       <c r="H248" s="7"/>
-      <c r="I248" s="12"/>
-      <c r="J248" s="13"/>
+      <c r="I248" s="11"/>
+      <c r="J248" s="12"/>
       <c r="K248" s="7"/>
       <c r="L248" s="7"/>
     </row>
@@ -4333,8 +4322,8 @@
       <c r="F249" s="7"/>
       <c r="G249" s="7"/>
       <c r="H249" s="7"/>
-      <c r="I249" s="12"/>
-      <c r="J249" s="13"/>
+      <c r="I249" s="11"/>
+      <c r="J249" s="12"/>
       <c r="K249" s="7"/>
       <c r="L249" s="7"/>
     </row>
@@ -4347,8 +4336,8 @@
       <c r="F250" s="7"/>
       <c r="G250" s="7"/>
       <c r="H250" s="7"/>
-      <c r="I250" s="12"/>
-      <c r="J250" s="13"/>
+      <c r="I250" s="11"/>
+      <c r="J250" s="12"/>
       <c r="K250" s="7"/>
       <c r="L250" s="7"/>
     </row>
@@ -4361,8 +4350,8 @@
       <c r="F251" s="7"/>
       <c r="G251" s="7"/>
       <c r="H251" s="7"/>
-      <c r="I251" s="12"/>
-      <c r="J251" s="13"/>
+      <c r="I251" s="11"/>
+      <c r="J251" s="12"/>
       <c r="K251" s="7"/>
       <c r="L251" s="7"/>
     </row>
@@ -4375,8 +4364,8 @@
       <c r="F252" s="7"/>
       <c r="G252" s="7"/>
       <c r="H252" s="7"/>
-      <c r="I252" s="12"/>
-      <c r="J252" s="13"/>
+      <c r="I252" s="11"/>
+      <c r="J252" s="12"/>
       <c r="K252" s="7"/>
       <c r="L252" s="7"/>
     </row>
@@ -4389,8 +4378,8 @@
       <c r="F253" s="7"/>
       <c r="G253" s="7"/>
       <c r="H253" s="7"/>
-      <c r="I253" s="12"/>
-      <c r="J253" s="13"/>
+      <c r="I253" s="11"/>
+      <c r="J253" s="12"/>
       <c r="K253" s="7"/>
       <c r="L253" s="7"/>
     </row>
@@ -4403,8 +4392,8 @@
       <c r="F254" s="7"/>
       <c r="G254" s="7"/>
       <c r="H254" s="7"/>
-      <c r="I254" s="12"/>
-      <c r="J254" s="13"/>
+      <c r="I254" s="11"/>
+      <c r="J254" s="12"/>
       <c r="K254" s="7"/>
       <c r="L254" s="7"/>
     </row>
@@ -4417,8 +4406,8 @@
       <c r="F255" s="7"/>
       <c r="G255" s="7"/>
       <c r="H255" s="7"/>
-      <c r="I255" s="12"/>
-      <c r="J255" s="13"/>
+      <c r="I255" s="11"/>
+      <c r="J255" s="12"/>
       <c r="K255" s="7"/>
       <c r="L255" s="7"/>
     </row>
@@ -4431,8 +4420,8 @@
       <c r="F256" s="7"/>
       <c r="G256" s="7"/>
       <c r="H256" s="7"/>
-      <c r="I256" s="12"/>
-      <c r="J256" s="13"/>
+      <c r="I256" s="11"/>
+      <c r="J256" s="12"/>
       <c r="K256" s="7"/>
       <c r="L256" s="7"/>
     </row>
@@ -4445,8 +4434,8 @@
       <c r="F257" s="7"/>
       <c r="G257" s="7"/>
       <c r="H257" s="7"/>
-      <c r="I257" s="12"/>
-      <c r="J257" s="13"/>
+      <c r="I257" s="11"/>
+      <c r="J257" s="12"/>
       <c r="K257" s="7"/>
       <c r="L257" s="7"/>
     </row>
@@ -4459,8 +4448,8 @@
       <c r="F258" s="7"/>
       <c r="G258" s="7"/>
       <c r="H258" s="7"/>
-      <c r="I258" s="12"/>
-      <c r="J258" s="13"/>
+      <c r="I258" s="11"/>
+      <c r="J258" s="12"/>
       <c r="K258" s="7"/>
       <c r="L258" s="7"/>
     </row>
@@ -4473,8 +4462,8 @@
       <c r="F259" s="7"/>
       <c r="G259" s="7"/>
       <c r="H259" s="7"/>
-      <c r="I259" s="12"/>
-      <c r="J259" s="13"/>
+      <c r="I259" s="11"/>
+      <c r="J259" s="12"/>
       <c r="K259" s="7"/>
       <c r="L259" s="7"/>
     </row>
@@ -4487,8 +4476,8 @@
       <c r="F260" s="7"/>
       <c r="G260" s="7"/>
       <c r="H260" s="7"/>
-      <c r="I260" s="12"/>
-      <c r="J260" s="13"/>
+      <c r="I260" s="11"/>
+      <c r="J260" s="12"/>
       <c r="K260" s="7"/>
       <c r="L260" s="7"/>
     </row>
@@ -4501,8 +4490,8 @@
       <c r="F261" s="7"/>
       <c r="G261" s="7"/>
       <c r="H261" s="7"/>
-      <c r="I261" s="12"/>
-      <c r="J261" s="13"/>
+      <c r="I261" s="11"/>
+      <c r="J261" s="12"/>
       <c r="K261" s="7"/>
       <c r="L261" s="7"/>
     </row>
@@ -4515,8 +4504,8 @@
       <c r="F262" s="7"/>
       <c r="G262" s="7"/>
       <c r="H262" s="7"/>
-      <c r="I262" s="12"/>
-      <c r="J262" s="13"/>
+      <c r="I262" s="11"/>
+      <c r="J262" s="12"/>
       <c r="K262" s="7"/>
       <c r="L262" s="7"/>
     </row>
@@ -4529,8 +4518,8 @@
       <c r="F263" s="7"/>
       <c r="G263" s="7"/>
       <c r="H263" s="7"/>
-      <c r="I263" s="12"/>
-      <c r="J263" s="13"/>
+      <c r="I263" s="11"/>
+      <c r="J263" s="12"/>
       <c r="K263" s="7"/>
       <c r="L263" s="7"/>
     </row>
@@ -4543,8 +4532,8 @@
       <c r="F264" s="7"/>
       <c r="G264" s="7"/>
       <c r="H264" s="7"/>
-      <c r="I264" s="12"/>
-      <c r="J264" s="13"/>
+      <c r="I264" s="11"/>
+      <c r="J264" s="12"/>
       <c r="K264" s="7"/>
       <c r="L264" s="7"/>
     </row>
@@ -4557,8 +4546,8 @@
       <c r="F265" s="7"/>
       <c r="G265" s="7"/>
       <c r="H265" s="7"/>
-      <c r="I265" s="12"/>
-      <c r="J265" s="13"/>
+      <c r="I265" s="11"/>
+      <c r="J265" s="12"/>
       <c r="K265" s="7"/>
       <c r="L265" s="7"/>
     </row>
@@ -4571,8 +4560,8 @@
       <c r="F266" s="7"/>
       <c r="G266" s="7"/>
       <c r="H266" s="7"/>
-      <c r="I266" s="12"/>
-      <c r="J266" s="13"/>
+      <c r="I266" s="11"/>
+      <c r="J266" s="12"/>
       <c r="K266" s="7"/>
       <c r="L266" s="7"/>
     </row>
@@ -4585,8 +4574,8 @@
       <c r="F267" s="7"/>
       <c r="G267" s="7"/>
       <c r="H267" s="7"/>
-      <c r="I267" s="12"/>
-      <c r="J267" s="13"/>
+      <c r="I267" s="11"/>
+      <c r="J267" s="12"/>
       <c r="K267" s="7"/>
       <c r="L267" s="7"/>
     </row>
@@ -4599,8 +4588,8 @@
       <c r="F268" s="7"/>
       <c r="G268" s="7"/>
       <c r="H268" s="7"/>
-      <c r="I268" s="12"/>
-      <c r="J268" s="13"/>
+      <c r="I268" s="11"/>
+      <c r="J268" s="12"/>
       <c r="K268" s="7"/>
       <c r="L268" s="7"/>
     </row>
@@ -4613,8 +4602,8 @@
       <c r="F269" s="7"/>
       <c r="G269" s="7"/>
       <c r="H269" s="7"/>
-      <c r="I269" s="12"/>
-      <c r="J269" s="13"/>
+      <c r="I269" s="11"/>
+      <c r="J269" s="12"/>
       <c r="K269" s="7"/>
       <c r="L269" s="7"/>
     </row>
@@ -4627,8 +4616,8 @@
       <c r="F270" s="7"/>
       <c r="G270" s="7"/>
       <c r="H270" s="7"/>
-      <c r="I270" s="12"/>
-      <c r="J270" s="13"/>
+      <c r="I270" s="11"/>
+      <c r="J270" s="12"/>
       <c r="K270" s="7"/>
       <c r="L270" s="7"/>
     </row>
@@ -4641,8 +4630,8 @@
       <c r="F271" s="7"/>
       <c r="G271" s="7"/>
       <c r="H271" s="7"/>
-      <c r="I271" s="12"/>
-      <c r="J271" s="13"/>
+      <c r="I271" s="11"/>
+      <c r="J271" s="12"/>
       <c r="K271" s="7"/>
       <c r="L271" s="7"/>
     </row>
@@ -4655,8 +4644,8 @@
       <c r="F272" s="7"/>
       <c r="G272" s="7"/>
       <c r="H272" s="7"/>
-      <c r="I272" s="12"/>
-      <c r="J272" s="13"/>
+      <c r="I272" s="11"/>
+      <c r="J272" s="12"/>
       <c r="K272" s="7"/>
       <c r="L272" s="7"/>
     </row>
@@ -4669,8 +4658,8 @@
       <c r="F273" s="7"/>
       <c r="G273" s="7"/>
       <c r="H273" s="7"/>
-      <c r="I273" s="12"/>
-      <c r="J273" s="13"/>
+      <c r="I273" s="11"/>
+      <c r="J273" s="12"/>
       <c r="K273" s="7"/>
       <c r="L273" s="7"/>
     </row>
@@ -4683,8 +4672,8 @@
       <c r="F274" s="7"/>
       <c r="G274" s="7"/>
       <c r="H274" s="7"/>
-      <c r="I274" s="12"/>
-      <c r="J274" s="13"/>
+      <c r="I274" s="11"/>
+      <c r="J274" s="12"/>
       <c r="K274" s="7"/>
       <c r="L274" s="7"/>
     </row>
@@ -4697,8 +4686,8 @@
       <c r="F275" s="7"/>
       <c r="G275" s="7"/>
       <c r="H275" s="7"/>
-      <c r="I275" s="12"/>
-      <c r="J275" s="13"/>
+      <c r="I275" s="11"/>
+      <c r="J275" s="12"/>
       <c r="K275" s="7"/>
       <c r="L275" s="7"/>
     </row>
@@ -4711,8 +4700,8 @@
       <c r="F276" s="7"/>
       <c r="G276" s="7"/>
       <c r="H276" s="7"/>
-      <c r="I276" s="12"/>
-      <c r="J276" s="13"/>
+      <c r="I276" s="11"/>
+      <c r="J276" s="12"/>
       <c r="K276" s="7"/>
       <c r="L276" s="7"/>
     </row>
@@ -4725,8 +4714,8 @@
       <c r="F277" s="7"/>
       <c r="G277" s="7"/>
       <c r="H277" s="7"/>
-      <c r="I277" s="12"/>
-      <c r="J277" s="13"/>
+      <c r="I277" s="11"/>
+      <c r="J277" s="12"/>
       <c r="K277" s="7"/>
       <c r="L277" s="7"/>
     </row>
@@ -4739,8 +4728,8 @@
       <c r="F278" s="7"/>
       <c r="G278" s="7"/>
       <c r="H278" s="7"/>
-      <c r="I278" s="12"/>
-      <c r="J278" s="13"/>
+      <c r="I278" s="11"/>
+      <c r="J278" s="12"/>
       <c r="K278" s="7"/>
       <c r="L278" s="7"/>
     </row>
@@ -4753,8 +4742,8 @@
       <c r="F279" s="7"/>
       <c r="G279" s="7"/>
       <c r="H279" s="7"/>
-      <c r="I279" s="12"/>
-      <c r="J279" s="13"/>
+      <c r="I279" s="11"/>
+      <c r="J279" s="12"/>
       <c r="K279" s="7"/>
       <c r="L279" s="7"/>
     </row>
@@ -4767,8 +4756,8 @@
       <c r="F280" s="7"/>
       <c r="G280" s="7"/>
       <c r="H280" s="7"/>
-      <c r="I280" s="12"/>
-      <c r="J280" s="13"/>
+      <c r="I280" s="11"/>
+      <c r="J280" s="12"/>
       <c r="K280" s="7"/>
       <c r="L280" s="7"/>
     </row>
@@ -4781,8 +4770,8 @@
       <c r="F281" s="7"/>
       <c r="G281" s="7"/>
       <c r="H281" s="7"/>
-      <c r="I281" s="12"/>
-      <c r="J281" s="13"/>
+      <c r="I281" s="11"/>
+      <c r="J281" s="12"/>
       <c r="K281" s="7"/>
       <c r="L281" s="7"/>
     </row>
@@ -4795,8 +4784,8 @@
       <c r="F282" s="7"/>
       <c r="G282" s="7"/>
       <c r="H282" s="7"/>
-      <c r="I282" s="12"/>
-      <c r="J282" s="13"/>
+      <c r="I282" s="11"/>
+      <c r="J282" s="12"/>
       <c r="K282" s="7"/>
       <c r="L282" s="7"/>
     </row>
@@ -4809,8 +4798,8 @@
       <c r="F283" s="7"/>
       <c r="G283" s="7"/>
       <c r="H283" s="7"/>
-      <c r="I283" s="12"/>
-      <c r="J283" s="13"/>
+      <c r="I283" s="11"/>
+      <c r="J283" s="12"/>
       <c r="K283" s="7"/>
       <c r="L283" s="7"/>
     </row>
@@ -4823,8 +4812,8 @@
       <c r="F284" s="7"/>
       <c r="G284" s="7"/>
       <c r="H284" s="7"/>
-      <c r="I284" s="12"/>
-      <c r="J284" s="13"/>
+      <c r="I284" s="11"/>
+      <c r="J284" s="12"/>
       <c r="K284" s="7"/>
       <c r="L284" s="7"/>
     </row>
@@ -4837,8 +4826,8 @@
       <c r="F285" s="7"/>
       <c r="G285" s="7"/>
       <c r="H285" s="7"/>
-      <c r="I285" s="12"/>
-      <c r="J285" s="13"/>
+      <c r="I285" s="11"/>
+      <c r="J285" s="12"/>
       <c r="K285" s="7"/>
       <c r="L285" s="7"/>
     </row>
@@ -4851,8 +4840,8 @@
       <c r="F286" s="7"/>
       <c r="G286" s="7"/>
       <c r="H286" s="7"/>
-      <c r="I286" s="12"/>
-      <c r="J286" s="13"/>
+      <c r="I286" s="11"/>
+      <c r="J286" s="12"/>
       <c r="K286" s="7"/>
       <c r="L286" s="7"/>
     </row>
@@ -4865,8 +4854,8 @@
       <c r="F287" s="7"/>
       <c r="G287" s="7"/>
       <c r="H287" s="7"/>
-      <c r="I287" s="12"/>
-      <c r="J287" s="13"/>
+      <c r="I287" s="11"/>
+      <c r="J287" s="12"/>
       <c r="K287" s="7"/>
       <c r="L287" s="7"/>
     </row>
@@ -4879,8 +4868,8 @@
       <c r="F288" s="7"/>
       <c r="G288" s="7"/>
       <c r="H288" s="7"/>
-      <c r="I288" s="12"/>
-      <c r="J288" s="13"/>
+      <c r="I288" s="11"/>
+      <c r="J288" s="12"/>
       <c r="K288" s="7"/>
       <c r="L288" s="7"/>
     </row>
@@ -4893,8 +4882,8 @@
       <c r="F289" s="7"/>
       <c r="G289" s="7"/>
       <c r="H289" s="7"/>
-      <c r="I289" s="12"/>
-      <c r="J289" s="13"/>
+      <c r="I289" s="11"/>
+      <c r="J289" s="12"/>
       <c r="K289" s="7"/>
       <c r="L289" s="7"/>
     </row>
@@ -4907,8 +4896,8 @@
       <c r="F290" s="7"/>
       <c r="G290" s="7"/>
       <c r="H290" s="7"/>
-      <c r="I290" s="12"/>
-      <c r="J290" s="13"/>
+      <c r="I290" s="11"/>
+      <c r="J290" s="12"/>
       <c r="K290" s="7"/>
       <c r="L290" s="7"/>
     </row>
@@ -4921,8 +4910,8 @@
       <c r="F291" s="7"/>
       <c r="G291" s="7"/>
       <c r="H291" s="7"/>
-      <c r="I291" s="12"/>
-      <c r="J291" s="13"/>
+      <c r="I291" s="11"/>
+      <c r="J291" s="12"/>
       <c r="K291" s="7"/>
       <c r="L291" s="7"/>
     </row>
@@ -4935,8 +4924,8 @@
       <c r="F292" s="7"/>
       <c r="G292" s="7"/>
       <c r="H292" s="7"/>
-      <c r="I292" s="12"/>
-      <c r="J292" s="13"/>
+      <c r="I292" s="11"/>
+      <c r="J292" s="12"/>
       <c r="K292" s="7"/>
       <c r="L292" s="7"/>
     </row>
@@ -4949,8 +4938,8 @@
       <c r="F293" s="7"/>
       <c r="G293" s="7"/>
       <c r="H293" s="7"/>
-      <c r="I293" s="12"/>
-      <c r="J293" s="13"/>
+      <c r="I293" s="11"/>
+      <c r="J293" s="12"/>
       <c r="K293" s="7"/>
       <c r="L293" s="7"/>
     </row>
@@ -4963,8 +4952,8 @@
       <c r="F294" s="7"/>
       <c r="G294" s="7"/>
       <c r="H294" s="7"/>
-      <c r="I294" s="12"/>
-      <c r="J294" s="13"/>
+      <c r="I294" s="11"/>
+      <c r="J294" s="12"/>
       <c r="K294" s="7"/>
       <c r="L294" s="7"/>
     </row>
@@ -4977,8 +4966,8 @@
       <c r="F295" s="7"/>
       <c r="G295" s="7"/>
       <c r="H295" s="7"/>
-      <c r="I295" s="12"/>
-      <c r="J295" s="13"/>
+      <c r="I295" s="11"/>
+      <c r="J295" s="12"/>
       <c r="K295" s="7"/>
       <c r="L295" s="7"/>
     </row>
@@ -4991,8 +4980,8 @@
       <c r="F296" s="7"/>
       <c r="G296" s="7"/>
       <c r="H296" s="7"/>
-      <c r="I296" s="12"/>
-      <c r="J296" s="13"/>
+      <c r="I296" s="11"/>
+      <c r="J296" s="12"/>
       <c r="K296" s="7"/>
       <c r="L296" s="7"/>
     </row>
@@ -5005,8 +4994,8 @@
       <c r="F297" s="7"/>
       <c r="G297" s="7"/>
       <c r="H297" s="7"/>
-      <c r="I297" s="12"/>
-      <c r="J297" s="13"/>
+      <c r="I297" s="11"/>
+      <c r="J297" s="12"/>
       <c r="K297" s="7"/>
       <c r="L297" s="7"/>
     </row>
@@ -5019,8 +5008,8 @@
       <c r="F298" s="7"/>
       <c r="G298" s="7"/>
       <c r="H298" s="7"/>
-      <c r="I298" s="12"/>
-      <c r="J298" s="13"/>
+      <c r="I298" s="11"/>
+      <c r="J298" s="12"/>
       <c r="K298" s="7"/>
       <c r="L298" s="7"/>
     </row>
@@ -5033,8 +5022,8 @@
       <c r="F299" s="7"/>
       <c r="G299" s="7"/>
       <c r="H299" s="7"/>
-      <c r="I299" s="12"/>
-      <c r="J299" s="13"/>
+      <c r="I299" s="11"/>
+      <c r="J299" s="12"/>
       <c r="K299" s="7"/>
       <c r="L299" s="7"/>
     </row>
@@ -5047,8 +5036,8 @@
       <c r="F300" s="7"/>
       <c r="G300" s="7"/>
       <c r="H300" s="7"/>
-      <c r="I300" s="12"/>
-      <c r="J300" s="13"/>
+      <c r="I300" s="11"/>
+      <c r="J300" s="12"/>
       <c r="K300" s="7"/>
       <c r="L300" s="7"/>
     </row>
@@ -5061,8 +5050,8 @@
       <c r="F301" s="7"/>
       <c r="G301" s="7"/>
       <c r="H301" s="7"/>
-      <c r="I301" s="12"/>
-      <c r="J301" s="13"/>
+      <c r="I301" s="11"/>
+      <c r="J301" s="12"/>
       <c r="K301" s="7"/>
       <c r="L301" s="7"/>
     </row>
@@ -5075,8 +5064,8 @@
       <c r="F302" s="7"/>
       <c r="G302" s="7"/>
       <c r="H302" s="7"/>
-      <c r="I302" s="12"/>
-      <c r="J302" s="13"/>
+      <c r="I302" s="11"/>
+      <c r="J302" s="12"/>
       <c r="K302" s="7"/>
       <c r="L302" s="7"/>
     </row>
@@ -5089,8 +5078,8 @@
       <c r="F303" s="7"/>
       <c r="G303" s="7"/>
       <c r="H303" s="7"/>
-      <c r="I303" s="12"/>
-      <c r="J303" s="13"/>
+      <c r="I303" s="11"/>
+      <c r="J303" s="12"/>
       <c r="K303" s="7"/>
       <c r="L303" s="7"/>
     </row>
@@ -5103,8 +5092,8 @@
       <c r="F304" s="7"/>
       <c r="G304" s="7"/>
       <c r="H304" s="7"/>
-      <c r="I304" s="12"/>
-      <c r="J304" s="13"/>
+      <c r="I304" s="11"/>
+      <c r="J304" s="12"/>
       <c r="K304" s="7"/>
       <c r="L304" s="7"/>
     </row>
@@ -5117,8 +5106,8 @@
       <c r="F305" s="7"/>
       <c r="G305" s="7"/>
       <c r="H305" s="7"/>
-      <c r="I305" s="12"/>
-      <c r="J305" s="13"/>
+      <c r="I305" s="11"/>
+      <c r="J305" s="12"/>
       <c r="K305" s="7"/>
       <c r="L305" s="7"/>
     </row>
@@ -5131,8 +5120,8 @@
       <c r="F306" s="7"/>
       <c r="G306" s="7"/>
       <c r="H306" s="7"/>
-      <c r="I306" s="12"/>
-      <c r="J306" s="13"/>
+      <c r="I306" s="11"/>
+      <c r="J306" s="12"/>
       <c r="K306" s="7"/>
       <c r="L306" s="7"/>
     </row>
@@ -5145,8 +5134,8 @@
       <c r="F307" s="7"/>
       <c r="G307" s="7"/>
       <c r="H307" s="7"/>
-      <c r="I307" s="12"/>
-      <c r="J307" s="13"/>
+      <c r="I307" s="11"/>
+      <c r="J307" s="12"/>
       <c r="K307" s="7"/>
       <c r="L307" s="7"/>
     </row>
@@ -5159,8 +5148,8 @@
       <c r="F308" s="7"/>
       <c r="G308" s="7"/>
       <c r="H308" s="7"/>
-      <c r="I308" s="12"/>
-      <c r="J308" s="13"/>
+      <c r="I308" s="11"/>
+      <c r="J308" s="12"/>
       <c r="K308" s="7"/>
       <c r="L308" s="7"/>
     </row>
@@ -5173,8 +5162,8 @@
       <c r="F309" s="7"/>
       <c r="G309" s="7"/>
       <c r="H309" s="7"/>
-      <c r="I309" s="12"/>
-      <c r="J309" s="13"/>
+      <c r="I309" s="11"/>
+      <c r="J309" s="12"/>
       <c r="K309" s="7"/>
       <c r="L309" s="7"/>
     </row>
@@ -5187,8 +5176,8 @@
       <c r="F310" s="7"/>
       <c r="G310" s="7"/>
       <c r="H310" s="7"/>
-      <c r="I310" s="12"/>
-      <c r="J310" s="13"/>
+      <c r="I310" s="11"/>
+      <c r="J310" s="12"/>
       <c r="K310" s="7"/>
       <c r="L310" s="7"/>
     </row>
@@ -5201,8 +5190,8 @@
       <c r="F311" s="7"/>
       <c r="G311" s="7"/>
       <c r="H311" s="7"/>
-      <c r="I311" s="12"/>
-      <c r="J311" s="13"/>
+      <c r="I311" s="11"/>
+      <c r="J311" s="12"/>
       <c r="K311" s="7"/>
       <c r="L311" s="7"/>
     </row>
@@ -5215,8 +5204,8 @@
       <c r="F312" s="7"/>
       <c r="G312" s="7"/>
       <c r="H312" s="7"/>
-      <c r="I312" s="12"/>
-      <c r="J312" s="13"/>
+      <c r="I312" s="11"/>
+      <c r="J312" s="12"/>
       <c r="K312" s="7"/>
       <c r="L312" s="7"/>
     </row>
@@ -5229,8 +5218,8 @@
       <c r="F313" s="7"/>
       <c r="G313" s="7"/>
       <c r="H313" s="7"/>
-      <c r="I313" s="12"/>
-      <c r="J313" s="13"/>
+      <c r="I313" s="11"/>
+      <c r="J313" s="12"/>
       <c r="K313" s="7"/>
       <c r="L313" s="7"/>
     </row>
@@ -5243,8 +5232,8 @@
       <c r="F314" s="7"/>
       <c r="G314" s="7"/>
       <c r="H314" s="7"/>
-      <c r="I314" s="12"/>
-      <c r="J314" s="13"/>
+      <c r="I314" s="11"/>
+      <c r="J314" s="12"/>
       <c r="K314" s="7"/>
       <c r="L314" s="7"/>
     </row>
@@ -5257,8 +5246,8 @@
       <c r="F315" s="7"/>
       <c r="G315" s="7"/>
       <c r="H315" s="7"/>
-      <c r="I315" s="12"/>
-      <c r="J315" s="13"/>
+      <c r="I315" s="11"/>
+      <c r="J315" s="12"/>
       <c r="K315" s="7"/>
       <c r="L315" s="7"/>
     </row>
@@ -5271,8 +5260,8 @@
       <c r="F316" s="7"/>
       <c r="G316" s="7"/>
       <c r="H316" s="7"/>
-      <c r="I316" s="12"/>
-      <c r="J316" s="13"/>
+      <c r="I316" s="11"/>
+      <c r="J316" s="12"/>
       <c r="K316" s="7"/>
       <c r="L316" s="7"/>
     </row>
@@ -5285,8 +5274,8 @@
       <c r="F317" s="7"/>
       <c r="G317" s="7"/>
       <c r="H317" s="7"/>
-      <c r="I317" s="12"/>
-      <c r="J317" s="13"/>
+      <c r="I317" s="11"/>
+      <c r="J317" s="12"/>
       <c r="K317" s="7"/>
       <c r="L317" s="7"/>
     </row>
@@ -5299,8 +5288,8 @@
       <c r="F318" s="7"/>
       <c r="G318" s="7"/>
       <c r="H318" s="7"/>
-      <c r="I318" s="12"/>
-      <c r="J318" s="13"/>
+      <c r="I318" s="11"/>
+      <c r="J318" s="12"/>
       <c r="K318" s="7"/>
       <c r="L318" s="7"/>
     </row>
@@ -5313,8 +5302,8 @@
       <c r="F319" s="7"/>
       <c r="G319" s="7"/>
       <c r="H319" s="7"/>
-      <c r="I319" s="12"/>
-      <c r="J319" s="13"/>
+      <c r="I319" s="11"/>
+      <c r="J319" s="12"/>
       <c r="K319" s="7"/>
       <c r="L319" s="7"/>
     </row>
@@ -5327,8 +5316,8 @@
       <c r="F320" s="7"/>
       <c r="G320" s="7"/>
       <c r="H320" s="7"/>
-      <c r="I320" s="12"/>
-      <c r="J320" s="13"/>
+      <c r="I320" s="11"/>
+      <c r="J320" s="12"/>
       <c r="K320" s="7"/>
       <c r="L320" s="7"/>
     </row>
@@ -5341,8 +5330,8 @@
       <c r="F321" s="7"/>
       <c r="G321" s="7"/>
       <c r="H321" s="7"/>
-      <c r="I321" s="12"/>
-      <c r="J321" s="13"/>
+      <c r="I321" s="11"/>
+      <c r="J321" s="12"/>
       <c r="K321" s="7"/>
       <c r="L321" s="7"/>
     </row>
@@ -5355,8 +5344,8 @@
       <c r="F322" s="7"/>
       <c r="G322" s="7"/>
       <c r="H322" s="7"/>
-      <c r="I322" s="12"/>
-      <c r="J322" s="13"/>
+      <c r="I322" s="11"/>
+      <c r="J322" s="12"/>
       <c r="K322" s="7"/>
       <c r="L322" s="7"/>
     </row>
@@ -5369,8 +5358,8 @@
       <c r="F323" s="7"/>
       <c r="G323" s="7"/>
       <c r="H323" s="7"/>
-      <c r="I323" s="12"/>
-      <c r="J323" s="13"/>
+      <c r="I323" s="11"/>
+      <c r="J323" s="12"/>
       <c r="K323" s="7"/>
       <c r="L323" s="7"/>
     </row>
@@ -5383,8 +5372,8 @@
       <c r="F324" s="7"/>
       <c r="G324" s="7"/>
       <c r="H324" s="7"/>
-      <c r="I324" s="12"/>
-      <c r="J324" s="13"/>
+      <c r="I324" s="11"/>
+      <c r="J324" s="12"/>
       <c r="K324" s="7"/>
       <c r="L324" s="7"/>
     </row>
@@ -5397,8 +5386,8 @@
       <c r="F325" s="7"/>
       <c r="G325" s="7"/>
       <c r="H325" s="7"/>
-      <c r="I325" s="12"/>
-      <c r="J325" s="13"/>
+      <c r="I325" s="11"/>
+      <c r="J325" s="12"/>
       <c r="K325" s="7"/>
       <c r="L325" s="7"/>
     </row>
@@ -5411,8 +5400,8 @@
       <c r="F326" s="7"/>
       <c r="G326" s="7"/>
       <c r="H326" s="7"/>
-      <c r="I326" s="12"/>
-      <c r="J326" s="13"/>
+      <c r="I326" s="11"/>
+      <c r="J326" s="12"/>
       <c r="K326" s="7"/>
       <c r="L326" s="7"/>
     </row>
@@ -5425,8 +5414,8 @@
       <c r="F327" s="7"/>
       <c r="G327" s="7"/>
       <c r="H327" s="7"/>
-      <c r="I327" s="12"/>
-      <c r="J327" s="13"/>
+      <c r="I327" s="11"/>
+      <c r="J327" s="12"/>
       <c r="K327" s="7"/>
       <c r="L327" s="7"/>
     </row>
@@ -5439,8 +5428,8 @@
       <c r="F328" s="7"/>
       <c r="G328" s="7"/>
       <c r="H328" s="7"/>
-      <c r="I328" s="12"/>
-      <c r="J328" s="13"/>
+      <c r="I328" s="11"/>
+      <c r="J328" s="12"/>
       <c r="K328" s="7"/>
       <c r="L328" s="7"/>
     </row>
@@ -5453,8 +5442,8 @@
       <c r="F329" s="7"/>
       <c r="G329" s="7"/>
       <c r="H329" s="7"/>
-      <c r="I329" s="12"/>
-      <c r="J329" s="13"/>
+      <c r="I329" s="11"/>
+      <c r="J329" s="12"/>
       <c r="K329" s="7"/>
       <c r="L329" s="7"/>
     </row>
@@ -5467,8 +5456,8 @@
       <c r="F330" s="7"/>
       <c r="G330" s="7"/>
       <c r="H330" s="7"/>
-      <c r="I330" s="12"/>
-      <c r="J330" s="13"/>
+      <c r="I330" s="11"/>
+      <c r="J330" s="12"/>
       <c r="K330" s="7"/>
       <c r="L330" s="7"/>
     </row>
@@ -5481,8 +5470,8 @@
       <c r="F331" s="7"/>
       <c r="G331" s="7"/>
       <c r="H331" s="7"/>
-      <c r="I331" s="12"/>
-      <c r="J331" s="13"/>
+      <c r="I331" s="11"/>
+      <c r="J331" s="12"/>
       <c r="K331" s="7"/>
       <c r="L331" s="7"/>
     </row>
@@ -5495,8 +5484,8 @@
       <c r="F332" s="7"/>
       <c r="G332" s="7"/>
       <c r="H332" s="7"/>
-      <c r="I332" s="12"/>
-      <c r="J332" s="13"/>
+      <c r="I332" s="11"/>
+      <c r="J332" s="12"/>
       <c r="K332" s="7"/>
       <c r="L332" s="7"/>
     </row>
@@ -5509,8 +5498,8 @@
       <c r="F333" s="7"/>
       <c r="G333" s="7"/>
       <c r="H333" s="7"/>
-      <c r="I333" s="12"/>
-      <c r="J333" s="13"/>
+      <c r="I333" s="11"/>
+      <c r="J333" s="12"/>
       <c r="K333" s="7"/>
       <c r="L333" s="7"/>
     </row>
@@ -5523,8 +5512,8 @@
       <c r="F334" s="7"/>
       <c r="G334" s="7"/>
       <c r="H334" s="7"/>
-      <c r="I334" s="12"/>
-      <c r="J334" s="13"/>
+      <c r="I334" s="11"/>
+      <c r="J334" s="12"/>
       <c r="K334" s="7"/>
       <c r="L334" s="7"/>
     </row>
@@ -5537,8 +5526,8 @@
       <c r="F335" s="7"/>
       <c r="G335" s="7"/>
       <c r="H335" s="7"/>
-      <c r="I335" s="12"/>
-      <c r="J335" s="13"/>
+      <c r="I335" s="11"/>
+      <c r="J335" s="12"/>
       <c r="K335" s="7"/>
       <c r="L335" s="7"/>
     </row>
@@ -5551,8 +5540,8 @@
       <c r="F336" s="7"/>
       <c r="G336" s="7"/>
       <c r="H336" s="7"/>
-      <c r="I336" s="12"/>
-      <c r="J336" s="13"/>
+      <c r="I336" s="11"/>
+      <c r="J336" s="12"/>
       <c r="K336" s="7"/>
       <c r="L336" s="7"/>
     </row>
@@ -5565,8 +5554,8 @@
       <c r="F337" s="7"/>
       <c r="G337" s="7"/>
       <c r="H337" s="7"/>
-      <c r="I337" s="12"/>
-      <c r="J337" s="13"/>
+      <c r="I337" s="11"/>
+      <c r="J337" s="12"/>
       <c r="K337" s="7"/>
       <c r="L337" s="7"/>
     </row>
@@ -5579,8 +5568,8 @@
       <c r="F338" s="7"/>
       <c r="G338" s="7"/>
       <c r="H338" s="7"/>
-      <c r="I338" s="12"/>
-      <c r="J338" s="13"/>
+      <c r="I338" s="11"/>
+      <c r="J338" s="12"/>
       <c r="K338" s="7"/>
       <c r="L338" s="7"/>
     </row>
@@ -5593,8 +5582,8 @@
       <c r="F339" s="7"/>
       <c r="G339" s="7"/>
       <c r="H339" s="7"/>
-      <c r="I339" s="12"/>
-      <c r="J339" s="13"/>
+      <c r="I339" s="11"/>
+      <c r="J339" s="12"/>
       <c r="K339" s="7"/>
       <c r="L339" s="7"/>
     </row>
@@ -5607,8 +5596,8 @@
       <c r="F340" s="7"/>
       <c r="G340" s="7"/>
       <c r="H340" s="7"/>
-      <c r="I340" s="12"/>
-      <c r="J340" s="13"/>
+      <c r="I340" s="11"/>
+      <c r="J340" s="12"/>
       <c r="K340" s="7"/>
       <c r="L340" s="7"/>
     </row>
@@ -5621,8 +5610,8 @@
       <c r="F341" s="7"/>
       <c r="G341" s="7"/>
       <c r="H341" s="7"/>
-      <c r="I341" s="12"/>
-      <c r="J341" s="13"/>
+      <c r="I341" s="11"/>
+      <c r="J341" s="12"/>
       <c r="K341" s="7"/>
       <c r="L341" s="7"/>
     </row>
@@ -5635,8 +5624,8 @@
       <c r="F342" s="7"/>
       <c r="G342" s="7"/>
       <c r="H342" s="7"/>
-      <c r="I342" s="12"/>
-      <c r="J342" s="13"/>
+      <c r="I342" s="11"/>
+      <c r="J342" s="12"/>
       <c r="K342" s="7"/>
       <c r="L342" s="7"/>
     </row>
@@ -5649,8 +5638,8 @@
       <c r="F343" s="7"/>
       <c r="G343" s="7"/>
       <c r="H343" s="7"/>
-      <c r="I343" s="12"/>
-      <c r="J343" s="13"/>
+      <c r="I343" s="11"/>
+      <c r="J343" s="12"/>
       <c r="K343" s="7"/>
       <c r="L343" s="7"/>
     </row>
@@ -5663,8 +5652,8 @@
       <c r="F344" s="7"/>
       <c r="G344" s="7"/>
       <c r="H344" s="7"/>
-      <c r="I344" s="12"/>
-      <c r="J344" s="13"/>
+      <c r="I344" s="11"/>
+      <c r="J344" s="12"/>
       <c r="K344" s="7"/>
       <c r="L344" s="7"/>
     </row>
@@ -5677,8 +5666,8 @@
       <c r="F345" s="7"/>
       <c r="G345" s="7"/>
       <c r="H345" s="7"/>
-      <c r="I345" s="12"/>
-      <c r="J345" s="13"/>
+      <c r="I345" s="11"/>
+      <c r="J345" s="12"/>
       <c r="K345" s="7"/>
       <c r="L345" s="7"/>
     </row>
@@ -5691,8 +5680,8 @@
       <c r="F346" s="7"/>
       <c r="G346" s="7"/>
       <c r="H346" s="7"/>
-      <c r="I346" s="12"/>
-      <c r="J346" s="13"/>
+      <c r="I346" s="11"/>
+      <c r="J346" s="12"/>
       <c r="K346" s="7"/>
       <c r="L346" s="7"/>
     </row>
@@ -5705,8 +5694,8 @@
       <c r="F347" s="7"/>
       <c r="G347" s="7"/>
       <c r="H347" s="7"/>
-      <c r="I347" s="12"/>
-      <c r="J347" s="13"/>
+      <c r="I347" s="11"/>
+      <c r="J347" s="12"/>
       <c r="K347" s="7"/>
       <c r="L347" s="7"/>
     </row>
@@ -5719,8 +5708,8 @@
       <c r="F348" s="7"/>
       <c r="G348" s="7"/>
       <c r="H348" s="7"/>
-      <c r="I348" s="12"/>
-      <c r="J348" s="13"/>
+      <c r="I348" s="11"/>
+      <c r="J348" s="12"/>
       <c r="K348" s="7"/>
       <c r="L348" s="7"/>
     </row>
@@ -5733,8 +5722,8 @@
       <c r="F349" s="7"/>
       <c r="G349" s="7"/>
       <c r="H349" s="7"/>
-      <c r="I349" s="12"/>
-      <c r="J349" s="13"/>
+      <c r="I349" s="11"/>
+      <c r="J349" s="12"/>
       <c r="K349" s="7"/>
       <c r="L349" s="7"/>
     </row>
@@ -5747,8 +5736,8 @@
       <c r="F350" s="7"/>
       <c r="G350" s="7"/>
       <c r="H350" s="7"/>
-      <c r="I350" s="12"/>
-      <c r="J350" s="13"/>
+      <c r="I350" s="11"/>
+      <c r="J350" s="12"/>
       <c r="K350" s="7"/>
       <c r="L350" s="7"/>
     </row>
@@ -5761,8 +5750,8 @@
       <c r="F351" s="7"/>
       <c r="G351" s="7"/>
       <c r="H351" s="7"/>
-      <c r="I351" s="12"/>
-      <c r="J351" s="13"/>
+      <c r="I351" s="11"/>
+      <c r="J351" s="12"/>
       <c r="K351" s="7"/>
       <c r="L351" s="7"/>
     </row>
@@ -5775,8 +5764,8 @@
       <c r="F352" s="7"/>
       <c r="G352" s="7"/>
       <c r="H352" s="7"/>
-      <c r="I352" s="12"/>
-      <c r="J352" s="13"/>
+      <c r="I352" s="11"/>
+      <c r="J352" s="12"/>
       <c r="K352" s="7"/>
       <c r="L352" s="7"/>
     </row>
@@ -5789,8 +5778,8 @@
       <c r="F353" s="7"/>
       <c r="G353" s="7"/>
       <c r="H353" s="7"/>
-      <c r="I353" s="12"/>
-      <c r="J353" s="13"/>
+      <c r="I353" s="11"/>
+      <c r="J353" s="12"/>
       <c r="K353" s="7"/>
       <c r="L353" s="7"/>
     </row>
@@ -5803,8 +5792,8 @@
       <c r="F354" s="7"/>
       <c r="G354" s="7"/>
       <c r="H354" s="7"/>
-      <c r="I354" s="12"/>
-      <c r="J354" s="13"/>
+      <c r="I354" s="11"/>
+      <c r="J354" s="12"/>
       <c r="K354" s="7"/>
       <c r="L354" s="7"/>
     </row>
@@ -5817,8 +5806,8 @@
       <c r="F355" s="7"/>
       <c r="G355" s="7"/>
       <c r="H355" s="7"/>
-      <c r="I355" s="12"/>
-      <c r="J355" s="13"/>
+      <c r="I355" s="11"/>
+      <c r="J355" s="12"/>
       <c r="K355" s="7"/>
       <c r="L355" s="7"/>
     </row>
@@ -5831,8 +5820,8 @@
       <c r="F356" s="7"/>
       <c r="G356" s="7"/>
       <c r="H356" s="7"/>
-      <c r="I356" s="12"/>
-      <c r="J356" s="13"/>
+      <c r="I356" s="11"/>
+      <c r="J356" s="12"/>
       <c r="K356" s="7"/>
       <c r="L356" s="7"/>
     </row>
@@ -5845,8 +5834,8 @@
       <c r="F357" s="7"/>
       <c r="G357" s="7"/>
       <c r="H357" s="7"/>
-      <c r="I357" s="12"/>
-      <c r="J357" s="13"/>
+      <c r="I357" s="11"/>
+      <c r="J357" s="12"/>
       <c r="K357" s="7"/>
       <c r="L357" s="7"/>
     </row>
@@ -5859,8 +5848,8 @@
       <c r="F358" s="7"/>
       <c r="G358" s="7"/>
       <c r="H358" s="7"/>
-      <c r="I358" s="12"/>
-      <c r="J358" s="13"/>
+      <c r="I358" s="11"/>
+      <c r="J358" s="12"/>
       <c r="K358" s="7"/>
       <c r="L358" s="7"/>
     </row>
@@ -5873,8 +5862,8 @@
       <c r="F359" s="7"/>
       <c r="G359" s="7"/>
       <c r="H359" s="7"/>
-      <c r="I359" s="12"/>
-      <c r="J359" s="13"/>
+      <c r="I359" s="11"/>
+      <c r="J359" s="12"/>
       <c r="K359" s="7"/>
       <c r="L359" s="7"/>
     </row>
@@ -5887,8 +5876,8 @@
       <c r="F360" s="7"/>
       <c r="G360" s="7"/>
       <c r="H360" s="7"/>
-      <c r="I360" s="12"/>
-      <c r="J360" s="13"/>
+      <c r="I360" s="11"/>
+      <c r="J360" s="12"/>
       <c r="K360" s="7"/>
       <c r="L360" s="7"/>
     </row>
@@ -5901,8 +5890,8 @@
       <c r="F361" s="7"/>
       <c r="G361" s="7"/>
       <c r="H361" s="7"/>
-      <c r="I361" s="12"/>
-      <c r="J361" s="13"/>
+      <c r="I361" s="11"/>
+      <c r="J361" s="12"/>
       <c r="K361" s="7"/>
       <c r="L361" s="7"/>
     </row>
@@ -5915,8 +5904,8 @@
       <c r="F362" s="7"/>
       <c r="G362" s="7"/>
       <c r="H362" s="7"/>
-      <c r="I362" s="12"/>
-      <c r="J362" s="13"/>
+      <c r="I362" s="11"/>
+      <c r="J362" s="12"/>
       <c r="K362" s="7"/>
       <c r="L362" s="7"/>
     </row>
@@ -5929,8 +5918,8 @@
       <c r="F363" s="7"/>
       <c r="G363" s="7"/>
       <c r="H363" s="7"/>
-      <c r="I363" s="12"/>
-      <c r="J363" s="13"/>
+      <c r="I363" s="11"/>
+      <c r="J363" s="12"/>
       <c r="K363" s="7"/>
       <c r="L363" s="7"/>
     </row>
@@ -5943,8 +5932,8 @@
       <c r="F364" s="7"/>
       <c r="G364" s="7"/>
       <c r="H364" s="7"/>
-      <c r="I364" s="12"/>
-      <c r="J364" s="13"/>
+      <c r="I364" s="11"/>
+      <c r="J364" s="12"/>
       <c r="K364" s="7"/>
       <c r="L364" s="7"/>
     </row>
@@ -5957,8 +5946,8 @@
       <c r="F365" s="7"/>
       <c r="G365" s="7"/>
       <c r="H365" s="7"/>
-      <c r="I365" s="12"/>
-      <c r="J365" s="13"/>
+      <c r="I365" s="11"/>
+      <c r="J365" s="12"/>
       <c r="K365" s="7"/>
       <c r="L365" s="7"/>
     </row>
@@ -5971,8 +5960,8 @@
       <c r="F366" s="7"/>
       <c r="G366" s="7"/>
       <c r="H366" s="7"/>
-      <c r="I366" s="12"/>
-      <c r="J366" s="13"/>
+      <c r="I366" s="11"/>
+      <c r="J366" s="12"/>
       <c r="K366" s="7"/>
       <c r="L366" s="7"/>
     </row>
@@ -5985,8 +5974,8 @@
       <c r="F367" s="7"/>
       <c r="G367" s="7"/>
       <c r="H367" s="7"/>
-      <c r="I367" s="12"/>
-      <c r="J367" s="13"/>
+      <c r="I367" s="11"/>
+      <c r="J367" s="12"/>
       <c r="K367" s="7"/>
       <c r="L367" s="7"/>
     </row>
@@ -5999,8 +5988,8 @@
       <c r="F368" s="7"/>
       <c r="G368" s="7"/>
       <c r="H368" s="7"/>
-      <c r="I368" s="12"/>
-      <c r="J368" s="13"/>
+      <c r="I368" s="11"/>
+      <c r="J368" s="12"/>
       <c r="K368" s="7"/>
       <c r="L368" s="7"/>
     </row>
@@ -6013,8 +6002,8 @@
       <c r="F369" s="7"/>
       <c r="G369" s="7"/>
       <c r="H369" s="7"/>
-      <c r="I369" s="12"/>
-      <c r="J369" s="13"/>
+      <c r="I369" s="11"/>
+      <c r="J369" s="12"/>
       <c r="K369" s="7"/>
       <c r="L369" s="7"/>
     </row>
@@ -6027,8 +6016,8 @@
       <c r="F370" s="7"/>
       <c r="G370" s="7"/>
       <c r="H370" s="7"/>
-      <c r="I370" s="12"/>
-      <c r="J370" s="13"/>
+      <c r="I370" s="11"/>
+      <c r="J370" s="12"/>
       <c r="K370" s="7"/>
       <c r="L370" s="7"/>
     </row>
@@ -6041,8 +6030,8 @@
       <c r="F371" s="7"/>
       <c r="G371" s="7"/>
       <c r="H371" s="7"/>
-      <c r="I371" s="12"/>
-      <c r="J371" s="13"/>
+      <c r="I371" s="11"/>
+      <c r="J371" s="12"/>
       <c r="K371" s="7"/>
       <c r="L371" s="7"/>
     </row>
@@ -6055,8 +6044,8 @@
       <c r="F372" s="7"/>
       <c r="G372" s="7"/>
       <c r="H372" s="7"/>
-      <c r="I372" s="12"/>
-      <c r="J372" s="13"/>
+      <c r="I372" s="11"/>
+      <c r="J372" s="12"/>
       <c r="K372" s="7"/>
       <c r="L372" s="7"/>
     </row>
@@ -6069,8 +6058,8 @@
       <c r="F373" s="7"/>
       <c r="G373" s="7"/>
       <c r="H373" s="7"/>
-      <c r="I373" s="12"/>
-      <c r="J373" s="13"/>
+      <c r="I373" s="11"/>
+      <c r="J373" s="12"/>
       <c r="K373" s="7"/>
       <c r="L373" s="7"/>
     </row>
@@ -6083,8 +6072,8 @@
       <c r="F374" s="7"/>
       <c r="G374" s="7"/>
       <c r="H374" s="7"/>
-      <c r="I374" s="12"/>
-      <c r="J374" s="13"/>
+      <c r="I374" s="11"/>
+      <c r="J374" s="12"/>
       <c r="K374" s="7"/>
       <c r="L374" s="7"/>
     </row>
@@ -6097,8 +6086,8 @@
       <c r="F375" s="7"/>
       <c r="G375" s="7"/>
       <c r="H375" s="7"/>
-      <c r="I375" s="12"/>
-      <c r="J375" s="13"/>
+      <c r="I375" s="11"/>
+      <c r="J375" s="12"/>
       <c r="K375" s="7"/>
       <c r="L375" s="7"/>
     </row>
@@ -6111,8 +6100,8 @@
       <c r="F376" s="7"/>
       <c r="G376" s="7"/>
       <c r="H376" s="7"/>
-      <c r="I376" s="12"/>
-      <c r="J376" s="13"/>
+      <c r="I376" s="11"/>
+      <c r="J376" s="12"/>
       <c r="K376" s="7"/>
       <c r="L376" s="7"/>
     </row>
@@ -6125,8 +6114,8 @@
       <c r="F377" s="7"/>
       <c r="G377" s="7"/>
       <c r="H377" s="7"/>
-      <c r="I377" s="12"/>
-      <c r="J377" s="13"/>
+      <c r="I377" s="11"/>
+      <c r="J377" s="12"/>
       <c r="K377" s="7"/>
       <c r="L377" s="7"/>
     </row>
@@ -6139,8 +6128,8 @@
       <c r="F378" s="7"/>
       <c r="G378" s="7"/>
       <c r="H378" s="7"/>
-      <c r="I378" s="12"/>
-      <c r="J378" s="13"/>
+      <c r="I378" s="11"/>
+      <c r="J378" s="12"/>
       <c r="K378" s="7"/>
       <c r="L378" s="7"/>
     </row>
@@ -6153,8 +6142,8 @@
       <c r="F379" s="7"/>
       <c r="G379" s="7"/>
       <c r="H379" s="7"/>
-      <c r="I379" s="12"/>
-      <c r="J379" s="13"/>
+      <c r="I379" s="11"/>
+      <c r="J379" s="12"/>
       <c r="K379" s="7"/>
       <c r="L379" s="7"/>
     </row>
@@ -6167,8 +6156,8 @@
       <c r="F380" s="7"/>
       <c r="G380" s="7"/>
       <c r="H380" s="7"/>
-      <c r="I380" s="12"/>
-      <c r="J380" s="13"/>
+      <c r="I380" s="11"/>
+      <c r="J380" s="12"/>
       <c r="K380" s="7"/>
       <c r="L380" s="7"/>
     </row>
@@ -6181,8 +6170,8 @@
       <c r="F381" s="7"/>
       <c r="G381" s="7"/>
       <c r="H381" s="7"/>
-      <c r="I381" s="12"/>
-      <c r="J381" s="13"/>
+      <c r="I381" s="11"/>
+      <c r="J381" s="12"/>
       <c r="K381" s="7"/>
       <c r="L381" s="7"/>
     </row>
@@ -6195,8 +6184,8 @@
       <c r="F382" s="7"/>
       <c r="G382" s="7"/>
       <c r="H382" s="7"/>
-      <c r="I382" s="12"/>
-      <c r="J382" s="13"/>
+      <c r="I382" s="11"/>
+      <c r="J382" s="12"/>
       <c r="K382" s="7"/>
       <c r="L382" s="7"/>
     </row>
@@ -6209,8 +6198,8 @@
       <c r="F383" s="7"/>
       <c r="G383" s="7"/>
       <c r="H383" s="7"/>
-      <c r="I383" s="12"/>
-      <c r="J383" s="13"/>
+      <c r="I383" s="11"/>
+      <c r="J383" s="12"/>
       <c r="K383" s="7"/>
       <c r="L383" s="7"/>
     </row>
@@ -6223,8 +6212,8 @@
       <c r="F384" s="7"/>
       <c r="G384" s="7"/>
       <c r="H384" s="7"/>
-      <c r="I384" s="12"/>
-      <c r="J384" s="13"/>
+      <c r="I384" s="11"/>
+      <c r="J384" s="12"/>
       <c r="K384" s="7"/>
       <c r="L384" s="7"/>
     </row>
@@ -6237,8 +6226,8 @@
       <c r="F385" s="7"/>
       <c r="G385" s="7"/>
       <c r="H385" s="7"/>
-      <c r="I385" s="12"/>
-      <c r="J385" s="13"/>
+      <c r="I385" s="11"/>
+      <c r="J385" s="12"/>
       <c r="K385" s="7"/>
       <c r="L385" s="7"/>
     </row>
@@ -6251,8 +6240,8 @@
       <c r="F386" s="7"/>
       <c r="G386" s="7"/>
       <c r="H386" s="7"/>
-      <c r="I386" s="12"/>
-      <c r="J386" s="13"/>
+      <c r="I386" s="11"/>
+      <c r="J386" s="12"/>
       <c r="K386" s="7"/>
       <c r="L386" s="7"/>
     </row>
@@ -6265,8 +6254,8 @@
       <c r="F387" s="7"/>
       <c r="G387" s="7"/>
       <c r="H387" s="7"/>
-      <c r="I387" s="12"/>
-      <c r="J387" s="13"/>
+      <c r="I387" s="11"/>
+      <c r="J387" s="12"/>
       <c r="K387" s="7"/>
       <c r="L387" s="7"/>
     </row>
@@ -6279,8 +6268,8 @@
       <c r="F388" s="7"/>
       <c r="G388" s="7"/>
       <c r="H388" s="7"/>
-      <c r="I388" s="12"/>
-      <c r="J388" s="13"/>
+      <c r="I388" s="11"/>
+      <c r="J388" s="12"/>
       <c r="K388" s="7"/>
       <c r="L388" s="7"/>
     </row>
@@ -6293,8 +6282,8 @@
       <c r="F389" s="7"/>
       <c r="G389" s="7"/>
       <c r="H389" s="7"/>
-      <c r="I389" s="12"/>
-      <c r="J389" s="13"/>
+      <c r="I389" s="11"/>
+      <c r="J389" s="12"/>
       <c r="K389" s="7"/>
       <c r="L389" s="7"/>
     </row>
@@ -6307,8 +6296,8 @@
       <c r="F390" s="7"/>
       <c r="G390" s="7"/>
       <c r="H390" s="7"/>
-      <c r="I390" s="12"/>
-      <c r="J390" s="13"/>
+      <c r="I390" s="11"/>
+      <c r="J390" s="12"/>
       <c r="K390" s="7"/>
       <c r="L390" s="7"/>
     </row>
@@ -6321,8 +6310,8 @@
       <c r="F391" s="7"/>
       <c r="G391" s="7"/>
       <c r="H391" s="7"/>
-      <c r="I391" s="12"/>
-      <c r="J391" s="13"/>
+      <c r="I391" s="11"/>
+      <c r="J391" s="12"/>
       <c r="K391" s="7"/>
       <c r="L391" s="7"/>
     </row>
@@ -6335,8 +6324,8 @@
       <c r="F392" s="7"/>
       <c r="G392" s="7"/>
       <c r="H392" s="7"/>
-      <c r="I392" s="12"/>
-      <c r="J392" s="13"/>
+      <c r="I392" s="11"/>
+      <c r="J392" s="12"/>
       <c r="K392" s="7"/>
       <c r="L392" s="7"/>
     </row>
@@ -6349,8 +6338,8 @@
       <c r="F393" s="7"/>
       <c r="G393" s="7"/>
       <c r="H393" s="7"/>
-      <c r="I393" s="12"/>
-      <c r="J393" s="13"/>
+      <c r="I393" s="11"/>
+      <c r="J393" s="12"/>
       <c r="K393" s="7"/>
       <c r="L393" s="7"/>
     </row>
@@ -6363,8 +6352,8 @@
       <c r="F394" s="7"/>
       <c r="G394" s="7"/>
       <c r="H394" s="7"/>
-      <c r="I394" s="12"/>
-      <c r="J394" s="13"/>
+      <c r="I394" s="11"/>
+      <c r="J394" s="12"/>
       <c r="K394" s="7"/>
       <c r="L394" s="7"/>
     </row>
@@ -6377,8 +6366,8 @@
       <c r="F395" s="7"/>
       <c r="G395" s="7"/>
       <c r="H395" s="7"/>
-      <c r="I395" s="12"/>
-      <c r="J395" s="13"/>
+      <c r="I395" s="11"/>
+      <c r="J395" s="12"/>
       <c r="K395" s="7"/>
       <c r="L395" s="7"/>
     </row>
@@ -6391,8 +6380,8 @@
       <c r="F396" s="7"/>
       <c r="G396" s="7"/>
       <c r="H396" s="7"/>
-      <c r="I396" s="12"/>
-      <c r="J396" s="13"/>
+      <c r="I396" s="11"/>
+      <c r="J396" s="12"/>
       <c r="K396" s="7"/>
       <c r="L396" s="7"/>
     </row>
@@ -6405,8 +6394,8 @@
       <c r="F397" s="7"/>
       <c r="G397" s="7"/>
       <c r="H397" s="7"/>
-      <c r="I397" s="12"/>
-      <c r="J397" s="13"/>
+      <c r="I397" s="11"/>
+      <c r="J397" s="12"/>
       <c r="K397" s="7"/>
       <c r="L397" s="7"/>
     </row>
@@ -6419,8 +6408,8 @@
       <c r="F398" s="7"/>
       <c r="G398" s="7"/>
       <c r="H398" s="7"/>
-      <c r="I398" s="12"/>
-      <c r="J398" s="13"/>
+      <c r="I398" s="11"/>
+      <c r="J398" s="12"/>
       <c r="K398" s="7"/>
       <c r="L398" s="7"/>
     </row>
@@ -6433,8 +6422,8 @@
       <c r="F399" s="7"/>
       <c r="G399" s="7"/>
       <c r="H399" s="7"/>
-      <c r="I399" s="12"/>
-      <c r="J399" s="13"/>
+      <c r="I399" s="11"/>
+      <c r="J399" s="12"/>
       <c r="K399" s="7"/>
       <c r="L399" s="7"/>
     </row>
@@ -6447,8 +6436,8 @@
       <c r="F400" s="7"/>
       <c r="G400" s="7"/>
       <c r="H400" s="7"/>
-      <c r="I400" s="12"/>
-      <c r="J400" s="13"/>
+      <c r="I400" s="11"/>
+      <c r="J400" s="12"/>
       <c r="K400" s="7"/>
       <c r="L400" s="7"/>
     </row>
@@ -6461,8 +6450,8 @@
       <c r="F401" s="7"/>
       <c r="G401" s="7"/>
       <c r="H401" s="7"/>
-      <c r="I401" s="12"/>
-      <c r="J401" s="13"/>
+      <c r="I401" s="11"/>
+      <c r="J401" s="12"/>
       <c r="K401" s="7"/>
       <c r="L401" s="7"/>
     </row>
@@ -6475,8 +6464,8 @@
       <c r="F402" s="7"/>
       <c r="G402" s="7"/>
       <c r="H402" s="7"/>
-      <c r="I402" s="12"/>
-      <c r="J402" s="13"/>
+      <c r="I402" s="11"/>
+      <c r="J402" s="12"/>
       <c r="K402" s="7"/>
       <c r="L402" s="7"/>
     </row>
@@ -6489,8 +6478,8 @@
       <c r="F403" s="7"/>
       <c r="G403" s="7"/>
       <c r="H403" s="7"/>
-      <c r="I403" s="12"/>
-      <c r="J403" s="13"/>
+      <c r="I403" s="11"/>
+      <c r="J403" s="12"/>
       <c r="K403" s="7"/>
       <c r="L403" s="7"/>
     </row>
@@ -6503,8 +6492,8 @@
       <c r="F404" s="7"/>
       <c r="G404" s="7"/>
       <c r="H404" s="7"/>
-      <c r="I404" s="12"/>
-      <c r="J404" s="13"/>
+      <c r="I404" s="11"/>
+      <c r="J404" s="12"/>
       <c r="K404" s="7"/>
       <c r="L404" s="7"/>
     </row>
@@ -6517,8 +6506,8 @@
       <c r="F405" s="7"/>
       <c r="G405" s="7"/>
       <c r="H405" s="7"/>
-      <c r="I405" s="12"/>
-      <c r="J405" s="13"/>
+      <c r="I405" s="11"/>
+      <c r="J405" s="12"/>
       <c r="K405" s="7"/>
       <c r="L405" s="7"/>
     </row>
@@ -6531,8 +6520,8 @@
       <c r="F406" s="7"/>
       <c r="G406" s="7"/>
       <c r="H406" s="7"/>
-      <c r="I406" s="12"/>
-      <c r="J406" s="13"/>
+      <c r="I406" s="11"/>
+      <c r="J406" s="12"/>
       <c r="K406" s="7"/>
       <c r="L406" s="7"/>
     </row>
@@ -6545,8 +6534,8 @@
       <c r="F407" s="7"/>
       <c r="G407" s="7"/>
       <c r="H407" s="7"/>
-      <c r="I407" s="12"/>
-      <c r="J407" s="13"/>
+      <c r="I407" s="11"/>
+      <c r="J407" s="12"/>
       <c r="K407" s="7"/>
       <c r="L407" s="7"/>
     </row>
@@ -6559,8 +6548,8 @@
       <c r="F408" s="7"/>
       <c r="G408" s="7"/>
       <c r="H408" s="7"/>
-      <c r="I408" s="12"/>
-      <c r="J408" s="13"/>
+      <c r="I408" s="11"/>
+      <c r="J408" s="12"/>
       <c r="K408" s="7"/>
       <c r="L408" s="7"/>
     </row>
@@ -6573,8 +6562,8 @@
       <c r="F409" s="7"/>
       <c r="G409" s="7"/>
       <c r="H409" s="7"/>
-      <c r="I409" s="12"/>
-      <c r="J409" s="13"/>
+      <c r="I409" s="11"/>
+      <c r="J409" s="12"/>
       <c r="K409" s="7"/>
       <c r="L409" s="7"/>
     </row>
@@ -6587,8 +6576,8 @@
       <c r="F410" s="7"/>
       <c r="G410" s="7"/>
       <c r="H410" s="7"/>
-      <c r="I410" s="12"/>
-      <c r="J410" s="13"/>
+      <c r="I410" s="11"/>
+      <c r="J410" s="12"/>
       <c r="K410" s="7"/>
       <c r="L410" s="7"/>
     </row>
@@ -6601,8 +6590,8 @@
       <c r="F411" s="7"/>
       <c r="G411" s="7"/>
       <c r="H411" s="7"/>
-      <c r="I411" s="12"/>
-      <c r="J411" s="13"/>
+      <c r="I411" s="11"/>
+      <c r="J411" s="12"/>
       <c r="K411" s="7"/>
       <c r="L411" s="7"/>
     </row>
@@ -6615,8 +6604,8 @@
       <c r="F412" s="7"/>
       <c r="G412" s="7"/>
       <c r="H412" s="7"/>
-      <c r="I412" s="12"/>
-      <c r="J412" s="13"/>
+      <c r="I412" s="11"/>
+      <c r="J412" s="12"/>
       <c r="K412" s="7"/>
       <c r="L412" s="7"/>
     </row>
@@ -6629,8 +6618,8 @@
       <c r="F413" s="7"/>
       <c r="G413" s="7"/>
       <c r="H413" s="7"/>
-      <c r="I413" s="12"/>
-      <c r="J413" s="13"/>
+      <c r="I413" s="11"/>
+      <c r="J413" s="12"/>
       <c r="K413" s="7"/>
       <c r="L413" s="7"/>
     </row>
@@ -6643,8 +6632,8 @@
       <c r="F414" s="7"/>
       <c r="G414" s="7"/>
       <c r="H414" s="7"/>
-      <c r="I414" s="12"/>
-      <c r="J414" s="13"/>
+      <c r="I414" s="11"/>
+      <c r="J414" s="12"/>
       <c r="K414" s="7"/>
       <c r="L414" s="7"/>
     </row>
@@ -6657,8 +6646,8 @@
       <c r="F415" s="7"/>
       <c r="G415" s="7"/>
       <c r="H415" s="7"/>
-      <c r="I415" s="12"/>
-      <c r="J415" s="13"/>
+      <c r="I415" s="11"/>
+      <c r="J415" s="12"/>
       <c r="K415" s="7"/>
       <c r="L415" s="7"/>
     </row>
@@ -6671,8 +6660,8 @@
       <c r="F416" s="7"/>
       <c r="G416" s="7"/>
       <c r="H416" s="7"/>
-      <c r="I416" s="12"/>
-      <c r="J416" s="13"/>
+      <c r="I416" s="11"/>
+      <c r="J416" s="12"/>
       <c r="K416" s="7"/>
       <c r="L416" s="7"/>
     </row>
@@ -6685,8 +6674,8 @@
       <c r="F417" s="7"/>
       <c r="G417" s="7"/>
       <c r="H417" s="7"/>
-      <c r="I417" s="12"/>
-      <c r="J417" s="13"/>
+      <c r="I417" s="11"/>
+      <c r="J417" s="12"/>
       <c r="K417" s="7"/>
       <c r="L417" s="7"/>
     </row>
@@ -6699,8 +6688,8 @@
       <c r="F418" s="7"/>
       <c r="G418" s="7"/>
       <c r="H418" s="7"/>
-      <c r="I418" s="12"/>
-      <c r="J418" s="13"/>
+      <c r="I418" s="11"/>
+      <c r="J418" s="12"/>
       <c r="K418" s="7"/>
       <c r="L418" s="7"/>
     </row>
@@ -6713,8 +6702,8 @@
       <c r="F419" s="7"/>
       <c r="G419" s="7"/>
       <c r="H419" s="7"/>
-      <c r="I419" s="12"/>
-      <c r="J419" s="13"/>
+      <c r="I419" s="11"/>
+      <c r="J419" s="12"/>
       <c r="K419" s="7"/>
       <c r="L419" s="7"/>
     </row>
@@ -6727,8 +6716,8 @@
       <c r="F420" s="7"/>
       <c r="G420" s="7"/>
       <c r="H420" s="7"/>
-      <c r="I420" s="12"/>
-      <c r="J420" s="13"/>
+      <c r="I420" s="11"/>
+      <c r="J420" s="12"/>
       <c r="K420" s="7"/>
       <c r="L420" s="7"/>
     </row>
@@ -6741,8 +6730,8 @@
       <c r="F421" s="7"/>
       <c r="G421" s="7"/>
       <c r="H421" s="7"/>
-      <c r="I421" s="12"/>
-      <c r="J421" s="13"/>
+      <c r="I421" s="11"/>
+      <c r="J421" s="12"/>
       <c r="K421" s="7"/>
       <c r="L421" s="7"/>
     </row>
@@ -6755,8 +6744,8 @@
       <c r="F422" s="7"/>
       <c r="G422" s="7"/>
       <c r="H422" s="7"/>
-      <c r="I422" s="12"/>
-      <c r="J422" s="13"/>
+      <c r="I422" s="11"/>
+      <c r="J422" s="12"/>
       <c r="K422" s="7"/>
       <c r="L422" s="7"/>
     </row>
@@ -6769,8 +6758,8 @@
       <c r="F423" s="7"/>
       <c r="G423" s="7"/>
       <c r="H423" s="7"/>
-      <c r="I423" s="12"/>
-      <c r="J423" s="13"/>
+      <c r="I423" s="11"/>
+      <c r="J423" s="12"/>
       <c r="K423" s="7"/>
       <c r="L423" s="7"/>
     </row>
@@ -6783,8 +6772,8 @@
       <c r="F424" s="7"/>
       <c r="G424" s="7"/>
       <c r="H424" s="7"/>
-      <c r="I424" s="12"/>
-      <c r="J424" s="13"/>
+      <c r="I424" s="11"/>
+      <c r="J424" s="12"/>
       <c r="K424" s="7"/>
       <c r="L424" s="7"/>
     </row>
@@ -6797,8 +6786,8 @@
       <c r="F425" s="7"/>
       <c r="G425" s="7"/>
       <c r="H425" s="7"/>
-      <c r="I425" s="12"/>
-      <c r="J425" s="13"/>
+      <c r="I425" s="11"/>
+      <c r="J425" s="12"/>
       <c r="K425" s="7"/>
       <c r="L425" s="7"/>
     </row>
@@ -6811,8 +6800,8 @@
       <c r="F426" s="7"/>
       <c r="G426" s="7"/>
       <c r="H426" s="7"/>
-      <c r="I426" s="12"/>
-      <c r="J426" s="13"/>
+      <c r="I426" s="11"/>
+      <c r="J426" s="12"/>
       <c r="K426" s="7"/>
       <c r="L426" s="7"/>
     </row>
@@ -6825,8 +6814,8 @@
       <c r="F427" s="7"/>
       <c r="G427" s="7"/>
       <c r="H427" s="7"/>
-      <c r="I427" s="12"/>
-      <c r="J427" s="13"/>
+      <c r="I427" s="11"/>
+      <c r="J427" s="12"/>
       <c r="K427" s="7"/>
       <c r="L427" s="7"/>
     </row>
@@ -6839,8 +6828,8 @@
       <c r="F428" s="7"/>
       <c r="G428" s="7"/>
       <c r="H428" s="7"/>
-      <c r="I428" s="12"/>
-      <c r="J428" s="13"/>
+      <c r="I428" s="11"/>
+      <c r="J428" s="12"/>
       <c r="K428" s="7"/>
       <c r="L428" s="7"/>
     </row>
@@ -6853,8 +6842,8 @@
       <c r="F429" s="7"/>
       <c r="G429" s="7"/>
       <c r="H429" s="7"/>
-      <c r="I429" s="12"/>
-      <c r="J429" s="13"/>
+      <c r="I429" s="11"/>
+      <c r="J429" s="12"/>
       <c r="K429" s="7"/>
       <c r="L429" s="7"/>
     </row>
@@ -6867,8 +6856,8 @@
       <c r="F430" s="7"/>
       <c r="G430" s="7"/>
       <c r="H430" s="7"/>
-      <c r="I430" s="12"/>
-      <c r="J430" s="13"/>
+      <c r="I430" s="11"/>
+      <c r="J430" s="12"/>
       <c r="K430" s="7"/>
       <c r="L430" s="7"/>
     </row>
@@ -6881,8 +6870,8 @@
       <c r="F431" s="7"/>
       <c r="G431" s="7"/>
       <c r="H431" s="7"/>
-      <c r="I431" s="12"/>
-      <c r="J431" s="13"/>
+      <c r="I431" s="11"/>
+      <c r="J431" s="12"/>
       <c r="K431" s="7"/>
       <c r="L431" s="7"/>
     </row>
@@ -6895,8 +6884,8 @@
       <c r="F432" s="7"/>
       <c r="G432" s="7"/>
       <c r="H432" s="7"/>
-      <c r="I432" s="12"/>
-      <c r="J432" s="13"/>
+      <c r="I432" s="11"/>
+      <c r="J432" s="12"/>
       <c r="K432" s="7"/>
       <c r="L432" s="7"/>
     </row>
@@ -6909,8 +6898,8 @@
       <c r="F433" s="7"/>
       <c r="G433" s="7"/>
       <c r="H433" s="7"/>
-      <c r="I433" s="12"/>
-      <c r="J433" s="13"/>
+      <c r="I433" s="11"/>
+      <c r="J433" s="12"/>
       <c r="K433" s="7"/>
       <c r="L433" s="7"/>
     </row>
@@ -6923,8 +6912,8 @@
       <c r="F434" s="7"/>
       <c r="G434" s="7"/>
       <c r="H434" s="7"/>
-      <c r="I434" s="12"/>
-      <c r="J434" s="13"/>
+      <c r="I434" s="11"/>
+      <c r="J434" s="12"/>
       <c r="K434" s="7"/>
       <c r="L434" s="7"/>
     </row>
@@ -6937,8 +6926,8 @@
       <c r="F435" s="7"/>
       <c r="G435" s="7"/>
       <c r="H435" s="7"/>
-      <c r="I435" s="12"/>
-      <c r="J435" s="13"/>
+      <c r="I435" s="11"/>
+      <c r="J435" s="12"/>
       <c r="K435" s="7"/>
       <c r="L435" s="7"/>
     </row>
@@ -6951,8 +6940,8 @@
       <c r="F436" s="7"/>
       <c r="G436" s="7"/>
       <c r="H436" s="7"/>
-      <c r="I436" s="12"/>
-      <c r="J436" s="13"/>
+      <c r="I436" s="11"/>
+      <c r="J436" s="12"/>
       <c r="K436" s="7"/>
       <c r="L436" s="7"/>
     </row>
@@ -6965,8 +6954,8 @@
       <c r="F437" s="7"/>
       <c r="G437" s="7"/>
       <c r="H437" s="7"/>
-      <c r="I437" s="12"/>
-      <c r="J437" s="13"/>
+      <c r="I437" s="11"/>
+      <c r="J437" s="12"/>
       <c r="K437" s="7"/>
       <c r="L437" s="7"/>
     </row>
@@ -6979,8 +6968,8 @@
       <c r="F438" s="7"/>
       <c r="G438" s="7"/>
       <c r="H438" s="7"/>
-      <c r="I438" s="12"/>
-      <c r="J438" s="13"/>
+      <c r="I438" s="11"/>
+      <c r="J438" s="12"/>
       <c r="K438" s="7"/>
       <c r="L438" s="7"/>
     </row>
@@ -6993,8 +6982,8 @@
       <c r="F439" s="7"/>
       <c r="G439" s="7"/>
       <c r="H439" s="7"/>
-      <c r="I439" s="12"/>
-      <c r="J439" s="13"/>
+      <c r="I439" s="11"/>
+      <c r="J439" s="12"/>
       <c r="K439" s="7"/>
       <c r="L439" s="7"/>
     </row>
@@ -7007,8 +6996,8 @@
       <c r="F440" s="7"/>
       <c r="G440" s="7"/>
       <c r="H440" s="7"/>
-      <c r="I440" s="12"/>
-      <c r="J440" s="13"/>
+      <c r="I440" s="11"/>
+      <c r="J440" s="12"/>
       <c r="K440" s="7"/>
       <c r="L440" s="7"/>
     </row>
@@ -7021,8 +7010,8 @@
       <c r="F441" s="7"/>
       <c r="G441" s="7"/>
       <c r="H441" s="7"/>
-      <c r="I441" s="12"/>
-      <c r="J441" s="13"/>
+      <c r="I441" s="11"/>
+      <c r="J441" s="12"/>
       <c r="K441" s="7"/>
       <c r="L441" s="7"/>
     </row>
@@ -7035,8 +7024,8 @@
       <c r="F442" s="7"/>
       <c r="G442" s="7"/>
       <c r="H442" s="7"/>
-      <c r="I442" s="12"/>
-      <c r="J442" s="13"/>
+      <c r="I442" s="11"/>
+      <c r="J442" s="12"/>
       <c r="K442" s="7"/>
       <c r="L442" s="7"/>
     </row>
@@ -7049,8 +7038,8 @@
       <c r="F443" s="7"/>
       <c r="G443" s="7"/>
       <c r="H443" s="7"/>
-      <c r="I443" s="12"/>
-      <c r="J443" s="13"/>
+      <c r="I443" s="11"/>
+      <c r="J443" s="12"/>
       <c r="K443" s="7"/>
       <c r="L443" s="7"/>
     </row>
@@ -7063,8 +7052,8 @@
       <c r="F444" s="7"/>
       <c r="G444" s="7"/>
       <c r="H444" s="7"/>
-      <c r="I444" s="12"/>
-      <c r="J444" s="13"/>
+      <c r="I444" s="11"/>
+      <c r="J444" s="12"/>
       <c r="K444" s="7"/>
       <c r="L444" s="7"/>
     </row>
@@ -7077,8 +7066,8 @@
       <c r="F445" s="7"/>
       <c r="G445" s="7"/>
       <c r="H445" s="7"/>
-      <c r="I445" s="12"/>
-      <c r="J445" s="13"/>
+      <c r="I445" s="11"/>
+      <c r="J445" s="12"/>
       <c r="K445" s="7"/>
       <c r="L445" s="7"/>
     </row>
@@ -7091,8 +7080,8 @@
       <c r="F446" s="7"/>
       <c r="G446" s="7"/>
       <c r="H446" s="7"/>
-      <c r="I446" s="12"/>
-      <c r="J446" s="13"/>
+      <c r="I446" s="11"/>
+      <c r="J446" s="12"/>
       <c r="K446" s="7"/>
       <c r="L446" s="7"/>
     </row>
@@ -7105,8 +7094,8 @@
       <c r="F447" s="7"/>
       <c r="G447" s="7"/>
       <c r="H447" s="7"/>
-      <c r="I447" s="12"/>
-      <c r="J447" s="13"/>
+      <c r="I447" s="11"/>
+      <c r="J447" s="12"/>
       <c r="K447" s="7"/>
       <c r="L447" s="7"/>
     </row>
@@ -7119,8 +7108,8 @@
       <c r="F448" s="7"/>
       <c r="G448" s="7"/>
       <c r="H448" s="7"/>
-      <c r="I448" s="12"/>
-      <c r="J448" s="13"/>
+      <c r="I448" s="11"/>
+      <c r="J448" s="12"/>
       <c r="K448" s="7"/>
       <c r="L448" s="7"/>
     </row>
@@ -7133,8 +7122,8 @@
       <c r="F449" s="7"/>
       <c r="G449" s="7"/>
       <c r="H449" s="7"/>
-      <c r="I449" s="12"/>
-      <c r="J449" s="13"/>
+      <c r="I449" s="11"/>
+      <c r="J449" s="12"/>
       <c r="K449" s="7"/>
       <c r="L449" s="7"/>
     </row>
@@ -7147,8 +7136,8 @@
       <c r="F450" s="7"/>
       <c r="G450" s="7"/>
       <c r="H450" s="7"/>
-      <c r="I450" s="12"/>
-      <c r="J450" s="13"/>
+      <c r="I450" s="11"/>
+      <c r="J450" s="12"/>
       <c r="K450" s="7"/>
       <c r="L450" s="7"/>
     </row>
@@ -7161,8 +7150,8 @@
       <c r="F451" s="7"/>
       <c r="G451" s="7"/>
       <c r="H451" s="7"/>
-      <c r="I451" s="12"/>
-      <c r="J451" s="13"/>
+      <c r="I451" s="11"/>
+      <c r="J451" s="12"/>
       <c r="K451" s="7"/>
       <c r="L451" s="7"/>
     </row>
@@ -7175,8 +7164,8 @@
       <c r="F452" s="7"/>
       <c r="G452" s="7"/>
       <c r="H452" s="7"/>
-      <c r="I452" s="12"/>
-      <c r="J452" s="13"/>
+      <c r="I452" s="11"/>
+      <c r="J452" s="12"/>
       <c r="K452" s="7"/>
       <c r="L452" s="7"/>
     </row>
@@ -7189,8 +7178,8 @@
       <c r="F453" s="7"/>
       <c r="G453" s="7"/>
       <c r="H453" s="7"/>
-      <c r="I453" s="12"/>
-      <c r="J453" s="13"/>
+      <c r="I453" s="11"/>
+      <c r="J453" s="12"/>
       <c r="K453" s="7"/>
       <c r="L453" s="7"/>
     </row>
@@ -7203,8 +7192,8 @@
       <c r="F454" s="7"/>
       <c r="G454" s="7"/>
       <c r="H454" s="7"/>
-      <c r="I454" s="12"/>
-      <c r="J454" s="13"/>
+      <c r="I454" s="11"/>
+      <c r="J454" s="12"/>
       <c r="K454" s="7"/>
       <c r="L454" s="7"/>
     </row>
@@ -7217,8 +7206,8 @@
       <c r="F455" s="7"/>
       <c r="G455" s="7"/>
       <c r="H455" s="7"/>
-      <c r="I455" s="12"/>
-      <c r="J455" s="13"/>
+      <c r="I455" s="11"/>
+      <c r="J455" s="12"/>
       <c r="K455" s="7"/>
       <c r="L455" s="7"/>
     </row>
@@ -7231,8 +7220,8 @@
       <c r="F456" s="7"/>
       <c r="G456" s="7"/>
       <c r="H456" s="7"/>
-      <c r="I456" s="12"/>
-      <c r="J456" s="13"/>
+      <c r="I456" s="11"/>
+      <c r="J456" s="12"/>
       <c r="K456" s="7"/>
       <c r="L456" s="7"/>
     </row>
@@ -7245,8 +7234,8 @@
       <c r="F457" s="7"/>
       <c r="G457" s="7"/>
       <c r="H457" s="7"/>
-      <c r="I457" s="12"/>
-      <c r="J457" s="13"/>
+      <c r="I457" s="11"/>
+      <c r="J457" s="12"/>
       <c r="K457" s="7"/>
       <c r="L457" s="7"/>
     </row>
@@ -7259,8 +7248,8 @@
       <c r="F458" s="7"/>
       <c r="G458" s="7"/>
       <c r="H458" s="7"/>
-      <c r="I458" s="12"/>
-      <c r="J458" s="13"/>
+      <c r="I458" s="11"/>
+      <c r="J458" s="12"/>
       <c r="K458" s="7"/>
       <c r="L458" s="7"/>
     </row>
@@ -7273,8 +7262,8 @@
       <c r="F459" s="7"/>
       <c r="G459" s="7"/>
       <c r="H459" s="7"/>
-      <c r="I459" s="12"/>
-      <c r="J459" s="13"/>
+      <c r="I459" s="11"/>
+      <c r="J459" s="12"/>
       <c r="K459" s="7"/>
       <c r="L459" s="7"/>
     </row>
@@ -7287,8 +7276,8 @@
       <c r="F460" s="7"/>
       <c r="G460" s="7"/>
       <c r="H460" s="7"/>
-      <c r="I460" s="12"/>
-      <c r="J460" s="13"/>
+      <c r="I460" s="11"/>
+      <c r="J460" s="12"/>
       <c r="K460" s="7"/>
       <c r="L460" s="7"/>
     </row>
@@ -7301,8 +7290,8 @@
       <c r="F461" s="7"/>
       <c r="G461" s="7"/>
       <c r="H461" s="7"/>
-      <c r="I461" s="12"/>
-      <c r="J461" s="13"/>
+      <c r="I461" s="11"/>
+      <c r="J461" s="12"/>
       <c r="K461" s="7"/>
       <c r="L461" s="7"/>
     </row>
@@ -7315,8 +7304,8 @@
       <c r="F462" s="7"/>
       <c r="G462" s="7"/>
       <c r="H462" s="7"/>
-      <c r="I462" s="12"/>
-      <c r="J462" s="13"/>
+      <c r="I462" s="11"/>
+      <c r="J462" s="12"/>
       <c r="K462" s="7"/>
       <c r="L462" s="7"/>
     </row>
@@ -7329,8 +7318,8 @@
       <c r="F463" s="7"/>
       <c r="G463" s="7"/>
       <c r="H463" s="7"/>
-      <c r="I463" s="12"/>
-      <c r="J463" s="13"/>
+      <c r="I463" s="11"/>
+      <c r="J463" s="12"/>
       <c r="K463" s="7"/>
       <c r="L463" s="7"/>
     </row>
@@ -7343,8 +7332,8 @@
       <c r="F464" s="7"/>
       <c r="G464" s="7"/>
       <c r="H464" s="7"/>
-      <c r="I464" s="12"/>
-      <c r="J464" s="13"/>
+      <c r="I464" s="11"/>
+      <c r="J464" s="12"/>
       <c r="K464" s="7"/>
       <c r="L464" s="7"/>
     </row>
@@ -7357,8 +7346,8 @@
       <c r="F465" s="7"/>
       <c r="G465" s="7"/>
       <c r="H465" s="7"/>
-      <c r="I465" s="12"/>
-      <c r="J465" s="13"/>
+      <c r="I465" s="11"/>
+      <c r="J465" s="12"/>
       <c r="K465" s="7"/>
       <c r="L465" s="7"/>
     </row>
@@ -7371,8 +7360,8 @@
       <c r="F466" s="7"/>
       <c r="G466" s="7"/>
       <c r="H466" s="7"/>
-      <c r="I466" s="12"/>
-      <c r="J466" s="13"/>
+      <c r="I466" s="11"/>
+      <c r="J466" s="12"/>
       <c r="K466" s="7"/>
       <c r="L466" s="7"/>
     </row>
@@ -7385,8 +7374,8 @@
       <c r="F467" s="7"/>
       <c r="G467" s="7"/>
       <c r="H467" s="7"/>
-      <c r="I467" s="12"/>
-      <c r="J467" s="13"/>
+      <c r="I467" s="11"/>
+      <c r="J467" s="12"/>
       <c r="K467" s="7"/>
       <c r="L467" s="7"/>
     </row>
@@ -7399,8 +7388,8 @@
       <c r="F468" s="7"/>
       <c r="G468" s="7"/>
       <c r="H468" s="7"/>
-      <c r="I468" s="12"/>
-      <c r="J468" s="13"/>
+      <c r="I468" s="11"/>
+      <c r="J468" s="12"/>
       <c r="K468" s="7"/>
       <c r="L468" s="7"/>
     </row>
@@ -7413,8 +7402,8 @@
       <c r="F469" s="7"/>
       <c r="G469" s="7"/>
       <c r="H469" s="7"/>
-      <c r="I469" s="12"/>
-      <c r="J469" s="13"/>
+      <c r="I469" s="11"/>
+      <c r="J469" s="12"/>
       <c r="K469" s="7"/>
       <c r="L469" s="7"/>
     </row>
@@ -7427,8 +7416,8 @@
       <c r="F470" s="7"/>
       <c r="G470" s="7"/>
       <c r="H470" s="7"/>
-      <c r="I470" s="12"/>
-      <c r="J470" s="13"/>
+      <c r="I470" s="11"/>
+      <c r="J470" s="12"/>
       <c r="K470" s="7"/>
       <c r="L470" s="7"/>
     </row>
@@ -7441,8 +7430,8 @@
       <c r="F471" s="7"/>
       <c r="G471" s="7"/>
       <c r="H471" s="7"/>
-      <c r="I471" s="12"/>
-      <c r="J471" s="13"/>
+      <c r="I471" s="11"/>
+      <c r="J471" s="12"/>
       <c r="K471" s="7"/>
       <c r="L471" s="7"/>
     </row>
@@ -7455,8 +7444,8 @@
       <c r="F472" s="7"/>
       <c r="G472" s="7"/>
       <c r="H472" s="7"/>
-      <c r="I472" s="12"/>
-      <c r="J472" s="13"/>
+      <c r="I472" s="11"/>
+      <c r="J472" s="12"/>
       <c r="K472" s="7"/>
       <c r="L472" s="7"/>
     </row>
@@ -7469,8 +7458,8 @@
       <c r="F473" s="7"/>
       <c r="G473" s="7"/>
       <c r="H473" s="7"/>
-      <c r="I473" s="12"/>
-      <c r="J473" s="13"/>
+      <c r="I473" s="11"/>
+      <c r="J473" s="12"/>
       <c r="K473" s="7"/>
       <c r="L473" s="7"/>
     </row>
@@ -7483,8 +7472,8 @@
       <c r="F474" s="7"/>
       <c r="G474" s="7"/>
       <c r="H474" s="7"/>
-      <c r="I474" s="12"/>
-      <c r="J474" s="13"/>
+      <c r="I474" s="11"/>
+      <c r="J474" s="12"/>
       <c r="K474" s="7"/>
       <c r="L474" s="7"/>
     </row>
@@ -7497,8 +7486,8 @@
       <c r="F475" s="7"/>
       <c r="G475" s="7"/>
       <c r="H475" s="7"/>
-      <c r="I475" s="12"/>
-      <c r="J475" s="13"/>
+      <c r="I475" s="11"/>
+      <c r="J475" s="12"/>
       <c r="K475" s="7"/>
       <c r="L475" s="7"/>
     </row>
@@ -7511,8 +7500,8 @@
       <c r="F476" s="7"/>
       <c r="G476" s="7"/>
       <c r="H476" s="7"/>
-      <c r="I476" s="12"/>
-      <c r="J476" s="13"/>
+      <c r="I476" s="11"/>
+      <c r="J476" s="12"/>
       <c r="K476" s="7"/>
       <c r="L476" s="7"/>
     </row>
@@ -7525,8 +7514,8 @@
       <c r="F477" s="7"/>
       <c r="G477" s="7"/>
       <c r="H477" s="7"/>
-      <c r="I477" s="12"/>
-      <c r="J477" s="13"/>
+      <c r="I477" s="11"/>
+      <c r="J477" s="12"/>
       <c r="K477" s="7"/>
       <c r="L477" s="7"/>
     </row>
@@ -7539,8 +7528,8 @@
       <c r="F478" s="7"/>
       <c r="G478" s="7"/>
       <c r="H478" s="7"/>
-      <c r="I478" s="12"/>
-      <c r="J478" s="13"/>
+      <c r="I478" s="11"/>
+      <c r="J478" s="12"/>
       <c r="K478" s="7"/>
       <c r="L478" s="7"/>
     </row>
@@ -7553,8 +7542,8 @@
       <c r="F479" s="7"/>
       <c r="G479" s="7"/>
       <c r="H479" s="7"/>
-      <c r="I479" s="12"/>
-      <c r="J479" s="13"/>
+      <c r="I479" s="11"/>
+      <c r="J479" s="12"/>
       <c r="K479" s="7"/>
       <c r="L479" s="7"/>
     </row>
@@ -7567,8 +7556,8 @@
       <c r="F480" s="7"/>
       <c r="G480" s="7"/>
       <c r="H480" s="7"/>
-      <c r="I480" s="12"/>
-      <c r="J480" s="13"/>
+      <c r="I480" s="11"/>
+      <c r="J480" s="12"/>
       <c r="K480" s="7"/>
       <c r="L480" s="7"/>
     </row>
@@ -7581,8 +7570,8 @@
       <c r="F481" s="7"/>
       <c r="G481" s="7"/>
       <c r="H481" s="7"/>
-      <c r="I481" s="12"/>
-      <c r="J481" s="13"/>
+      <c r="I481" s="11"/>
+      <c r="J481" s="12"/>
       <c r="K481" s="7"/>
       <c r="L481" s="7"/>
     </row>
@@ -7595,8 +7584,8 @@
       <c r="F482" s="7"/>
       <c r="G482" s="7"/>
       <c r="H482" s="7"/>
-      <c r="I482" s="12"/>
-      <c r="J482" s="13"/>
+      <c r="I482" s="11"/>
+      <c r="J482" s="12"/>
       <c r="K482" s="7"/>
       <c r="L482" s="7"/>
     </row>
@@ -7609,8 +7598,8 @@
       <c r="F483" s="7"/>
       <c r="G483" s="7"/>
       <c r="H483" s="7"/>
-      <c r="I483" s="12"/>
-      <c r="J483" s="13"/>
+      <c r="I483" s="11"/>
+      <c r="J483" s="12"/>
       <c r="K483" s="7"/>
       <c r="L483" s="7"/>
     </row>
@@ -7623,8 +7612,8 @@
       <c r="F484" s="7"/>
       <c r="G484" s="7"/>
       <c r="H484" s="7"/>
-      <c r="I484" s="12"/>
-      <c r="J484" s="13"/>
+      <c r="I484" s="11"/>
+      <c r="J484" s="12"/>
       <c r="K484" s="7"/>
       <c r="L484" s="7"/>
     </row>
@@ -7637,8 +7626,8 @@
       <c r="F485" s="7"/>
       <c r="G485" s="7"/>
       <c r="H485" s="7"/>
-      <c r="I485" s="12"/>
-      <c r="J485" s="13"/>
+      <c r="I485" s="11"/>
+      <c r="J485" s="12"/>
       <c r="K485" s="7"/>
       <c r="L485" s="7"/>
     </row>
@@ -7651,8 +7640,8 @@
       <c r="F486" s="7"/>
       <c r="G486" s="7"/>
       <c r="H486" s="7"/>
-      <c r="I486" s="12"/>
-      <c r="J486" s="13"/>
+      <c r="I486" s="11"/>
+      <c r="J486" s="12"/>
       <c r="K486" s="7"/>
       <c r="L486" s="7"/>
     </row>
@@ -7665,8 +7654,8 @@
       <c r="F487" s="7"/>
       <c r="G487" s="7"/>
       <c r="H487" s="7"/>
-      <c r="I487" s="12"/>
-      <c r="J487" s="13"/>
+      <c r="I487" s="11"/>
+      <c r="J487" s="12"/>
       <c r="K487" s="7"/>
       <c r="L487" s="7"/>
     </row>
@@ -7679,8 +7668,8 @@
       <c r="F488" s="7"/>
       <c r="G488" s="7"/>
       <c r="H488" s="7"/>
-      <c r="I488" s="12"/>
-      <c r="J488" s="13"/>
+      <c r="I488" s="11"/>
+      <c r="J488" s="12"/>
       <c r="K488" s="7"/>
       <c r="L488" s="7"/>
     </row>
@@ -7693,8 +7682,8 @@
       <c r="F489" s="7"/>
       <c r="G489" s="7"/>
       <c r="H489" s="7"/>
-      <c r="I489" s="12"/>
-      <c r="J489" s="13"/>
+      <c r="I489" s="11"/>
+      <c r="J489" s="12"/>
       <c r="K489" s="7"/>
       <c r="L489" s="7"/>
     </row>
@@ -7707,8 +7696,8 @@
       <c r="F490" s="7"/>
       <c r="G490" s="7"/>
       <c r="H490" s="7"/>
-      <c r="I490" s="12"/>
-      <c r="J490" s="13"/>
+      <c r="I490" s="11"/>
+      <c r="J490" s="12"/>
       <c r="K490" s="7"/>
       <c r="L490" s="7"/>
     </row>
@@ -7721,8 +7710,8 @@
       <c r="F491" s="7"/>
       <c r="G491" s="7"/>
       <c r="H491" s="7"/>
-      <c r="I491" s="12"/>
-      <c r="J491" s="13"/>
+      <c r="I491" s="11"/>
+      <c r="J491" s="12"/>
       <c r="K491" s="7"/>
       <c r="L491" s="7"/>
     </row>
@@ -7735,8 +7724,8 @@
       <c r="F492" s="7"/>
       <c r="G492" s="7"/>
       <c r="H492" s="7"/>
-      <c r="I492" s="12"/>
-      <c r="J492" s="13"/>
+      <c r="I492" s="11"/>
+      <c r="J492" s="12"/>
       <c r="K492" s="7"/>
       <c r="L492" s="7"/>
     </row>
@@ -7749,8 +7738,8 @@
       <c r="F493" s="7"/>
       <c r="G493" s="7"/>
       <c r="H493" s="7"/>
-      <c r="I493" s="12"/>
-      <c r="J493" s="13"/>
+      <c r="I493" s="11"/>
+      <c r="J493" s="12"/>
       <c r="K493" s="7"/>
       <c r="L493" s="7"/>
     </row>
@@ -7763,8 +7752,8 @@
       <c r="F494" s="7"/>
       <c r="G494" s="7"/>
       <c r="H494" s="7"/>
-      <c r="I494" s="12"/>
-      <c r="J494" s="13"/>
+      <c r="I494" s="11"/>
+      <c r="J494" s="12"/>
       <c r="K494" s="7"/>
       <c r="L494" s="7"/>
     </row>
@@ -7777,8 +7766,8 @@
       <c r="F495" s="7"/>
       <c r="G495" s="7"/>
       <c r="H495" s="7"/>
-      <c r="I495" s="12"/>
-      <c r="J495" s="13"/>
+      <c r="I495" s="11"/>
+      <c r="J495" s="12"/>
       <c r="K495" s="7"/>
       <c r="L495" s="7"/>
     </row>
@@ -7791,8 +7780,8 @@
       <c r="F496" s="7"/>
       <c r="G496" s="7"/>
       <c r="H496" s="7"/>
-      <c r="I496" s="12"/>
-      <c r="J496" s="13"/>
+      <c r="I496" s="11"/>
+      <c r="J496" s="12"/>
       <c r="K496" s="7"/>
       <c r="L496" s="7"/>
     </row>
@@ -7805,8 +7794,8 @@
       <c r="F497" s="7"/>
       <c r="G497" s="7"/>
       <c r="H497" s="7"/>
-      <c r="I497" s="12"/>
-      <c r="J497" s="13"/>
+      <c r="I497" s="11"/>
+      <c r="J497" s="12"/>
       <c r="K497" s="7"/>
       <c r="L497" s="7"/>
     </row>
@@ -7819,8 +7808,8 @@
       <c r="F498" s="7"/>
       <c r="G498" s="7"/>
       <c r="H498" s="7"/>
-      <c r="I498" s="12"/>
-      <c r="J498" s="13"/>
+      <c r="I498" s="11"/>
+      <c r="J498" s="12"/>
       <c r="K498" s="7"/>
       <c r="L498" s="7"/>
     </row>
@@ -7833,8 +7822,8 @@
       <c r="F499" s="7"/>
       <c r="G499" s="7"/>
       <c r="H499" s="7"/>
-      <c r="I499" s="12"/>
-      <c r="J499" s="13"/>
+      <c r="I499" s="11"/>
+      <c r="J499" s="12"/>
       <c r="K499" s="7"/>
       <c r="L499" s="7"/>
     </row>
@@ -7847,8 +7836,8 @@
       <c r="F500" s="7"/>
       <c r="G500" s="7"/>
       <c r="H500" s="7"/>
-      <c r="I500" s="12"/>
-      <c r="J500" s="13"/>
+      <c r="I500" s="11"/>
+      <c r="J500" s="12"/>
       <c r="K500" s="7"/>
       <c r="L500" s="7"/>
     </row>
@@ -7861,8 +7850,8 @@
       <c r="F501" s="7"/>
       <c r="G501" s="7"/>
       <c r="H501" s="7"/>
-      <c r="I501" s="12"/>
-      <c r="J501" s="13"/>
+      <c r="I501" s="11"/>
+      <c r="J501" s="12"/>
       <c r="K501" s="7"/>
       <c r="L501" s="7"/>
     </row>
@@ -7875,8 +7864,8 @@
       <c r="F502" s="7"/>
       <c r="G502" s="7"/>
       <c r="H502" s="7"/>
-      <c r="I502" s="12"/>
-      <c r="J502" s="13"/>
+      <c r="I502" s="11"/>
+      <c r="J502" s="12"/>
       <c r="K502" s="7"/>
       <c r="L502" s="7"/>
     </row>
@@ -7889,8 +7878,8 @@
       <c r="F503" s="7"/>
       <c r="G503" s="7"/>
       <c r="H503" s="7"/>
-      <c r="I503" s="12"/>
-      <c r="J503" s="13"/>
+      <c r="I503" s="11"/>
+      <c r="J503" s="12"/>
       <c r="K503" s="7"/>
       <c r="L503" s="7"/>
     </row>
@@ -7903,8 +7892,8 @@
       <c r="F504" s="7"/>
       <c r="G504" s="7"/>
       <c r="H504" s="7"/>
-      <c r="I504" s="12"/>
-      <c r="J504" s="13"/>
+      <c r="I504" s="11"/>
+      <c r="J504" s="12"/>
       <c r="K504" s="7"/>
       <c r="L504" s="7"/>
     </row>
@@ -7917,8 +7906,8 @@
       <c r="F505" s="7"/>
       <c r="G505" s="7"/>
       <c r="H505" s="7"/>
-      <c r="I505" s="12"/>
-      <c r="J505" s="13"/>
+      <c r="I505" s="11"/>
+      <c r="J505" s="12"/>
       <c r="K505" s="7"/>
       <c r="L505" s="7"/>
     </row>
@@ -7931,8 +7920,8 @@
       <c r="F506" s="7"/>
       <c r="G506" s="7"/>
       <c r="H506" s="7"/>
-      <c r="I506" s="12"/>
-      <c r="J506" s="13"/>
+      <c r="I506" s="11"/>
+      <c r="J506" s="12"/>
       <c r="K506" s="7"/>
       <c r="L506" s="7"/>
     </row>
@@ -7945,8 +7934,8 @@
       <c r="F507" s="7"/>
       <c r="G507" s="7"/>
       <c r="H507" s="7"/>
-      <c r="I507" s="12"/>
-      <c r="J507" s="13"/>
+      <c r="I507" s="11"/>
+      <c r="J507" s="12"/>
       <c r="K507" s="7"/>
       <c r="L507" s="7"/>
     </row>
@@ -7959,8 +7948,8 @@
       <c r="F508" s="7"/>
       <c r="G508" s="7"/>
       <c r="H508" s="7"/>
-      <c r="I508" s="12"/>
-      <c r="J508" s="13"/>
+      <c r="I508" s="11"/>
+      <c r="J508" s="12"/>
       <c r="K508" s="7"/>
       <c r="L508" s="7"/>
     </row>
@@ -7973,8 +7962,8 @@
       <c r="F509" s="7"/>
       <c r="G509" s="7"/>
       <c r="H509" s="7"/>
-      <c r="I509" s="12"/>
-      <c r="J509" s="13"/>
+      <c r="I509" s="11"/>
+      <c r="J509" s="12"/>
       <c r="K509" s="7"/>
       <c r="L509" s="7"/>
     </row>
@@ -7987,8 +7976,8 @@
       <c r="F510" s="7"/>
       <c r="G510" s="7"/>
       <c r="H510" s="7"/>
-      <c r="I510" s="12"/>
-      <c r="J510" s="13"/>
+      <c r="I510" s="11"/>
+      <c r="J510" s="12"/>
       <c r="K510" s="7"/>
       <c r="L510" s="7"/>
     </row>
@@ -8001,8 +7990,8 @@
       <c r="F511" s="7"/>
       <c r="G511" s="7"/>
       <c r="H511" s="7"/>
-      <c r="I511" s="12"/>
-      <c r="J511" s="13"/>
+      <c r="I511" s="11"/>
+      <c r="J511" s="12"/>
       <c r="K511" s="7"/>
       <c r="L511" s="7"/>
     </row>
@@ -8015,8 +8004,8 @@
       <c r="F512" s="7"/>
       <c r="G512" s="7"/>
       <c r="H512" s="7"/>
-      <c r="I512" s="12"/>
-      <c r="J512" s="13"/>
+      <c r="I512" s="11"/>
+      <c r="J512" s="12"/>
       <c r="K512" s="7"/>
       <c r="L512" s="7"/>
     </row>
@@ -8029,8 +8018,8 @@
       <c r="F513" s="7"/>
       <c r="G513" s="7"/>
       <c r="H513" s="7"/>
-      <c r="I513" s="12"/>
-      <c r="J513" s="13"/>
+      <c r="I513" s="11"/>
+      <c r="J513" s="12"/>
       <c r="K513" s="7"/>
       <c r="L513" s="7"/>
     </row>
@@ -8043,8 +8032,8 @@
       <c r="F514" s="7"/>
       <c r="G514" s="7"/>
       <c r="H514" s="7"/>
-      <c r="I514" s="12"/>
-      <c r="J514" s="13"/>
+      <c r="I514" s="11"/>
+      <c r="J514" s="12"/>
       <c r="K514" s="7"/>
       <c r="L514" s="7"/>
     </row>
@@ -8057,8 +8046,8 @@
       <c r="F515" s="7"/>
       <c r="G515" s="7"/>
       <c r="H515" s="7"/>
-      <c r="I515" s="12"/>
-      <c r="J515" s="13"/>
+      <c r="I515" s="11"/>
+      <c r="J515" s="12"/>
       <c r="K515" s="7"/>
       <c r="L515" s="7"/>
     </row>
@@ -8071,8 +8060,8 @@
       <c r="F516" s="7"/>
       <c r="G516" s="7"/>
       <c r="H516" s="7"/>
-      <c r="I516" s="12"/>
-      <c r="J516" s="13"/>
+      <c r="I516" s="11"/>
+      <c r="J516" s="12"/>
       <c r="K516" s="7"/>
       <c r="L516" s="7"/>
     </row>
@@ -8085,8 +8074,8 @@
       <c r="F517" s="7"/>
       <c r="G517" s="7"/>
       <c r="H517" s="7"/>
-      <c r="I517" s="12"/>
-      <c r="J517" s="13"/>
+      <c r="I517" s="11"/>
+      <c r="J517" s="12"/>
       <c r="K517" s="7"/>
       <c r="L517" s="7"/>
     </row>
@@ -8099,8 +8088,8 @@
       <c r="F518" s="7"/>
       <c r="G518" s="7"/>
       <c r="H518" s="7"/>
-      <c r="I518" s="12"/>
-      <c r="J518" s="13"/>
+      <c r="I518" s="11"/>
+      <c r="J518" s="12"/>
       <c r="K518" s="7"/>
       <c r="L518" s="7"/>
     </row>
@@ -8113,8 +8102,8 @@
       <c r="F519" s="7"/>
       <c r="G519" s="7"/>
       <c r="H519" s="7"/>
-      <c r="I519" s="12"/>
-      <c r="J519" s="13"/>
+      <c r="I519" s="11"/>
+      <c r="J519" s="12"/>
       <c r="K519" s="7"/>
       <c r="L519" s="7"/>
     </row>
@@ -8127,8 +8116,8 @@
       <c r="F520" s="7"/>
       <c r="G520" s="7"/>
       <c r="H520" s="7"/>
-      <c r="I520" s="12"/>
-      <c r="J520" s="13"/>
+      <c r="I520" s="11"/>
+      <c r="J520" s="12"/>
       <c r="K520" s="7"/>
       <c r="L520" s="7"/>
     </row>
@@ -8161,15 +8150,15 @@
       <formula1>DADOS!$F$14:$F$363</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="A3:A61" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="A4:A61" type="list">
       <formula1>DADOS!$A$2:$A$82</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="C3:C61" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="C4:C61" type="list">
       <formula1>DADOS!$B$2:$B$3</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B3:B61" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B4:B61" type="list">
       <formula1>DADOS!$E$2:$E$5</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -8177,11 +8166,11 @@
       <formula1>DADOS!$F$2:$F$353</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="E3:E61" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="E4:E61" type="list">
       <formula1>DADOS!$D$2:$D$5</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="D3:D61" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="D4:D61" type="list">
       <formula1>DADOS!$C$2:$C$32</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -8202,39 +8191,39 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:F353"/>
-  <sheetFormatPr defaultColWidth="8.6953125" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.70703125" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="13.14"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="B1" s="15" t="s">
+      <c r="B1" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="15" t="s">
+      <c r="C1" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="D1" s="15" t="s">
+      <c r="D1" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="15" t="s">
+      <c r="E1" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="F1" s="15" t="s">
+      <c r="F1" s="14" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="16" t="n">
+      <c r="A2" s="15" t="n">
         <v>1071</v>
       </c>
       <c r="B2" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="C2" s="16" t="n">
+      <c r="C2" s="15" t="n">
         <v>10</v>
       </c>
       <c r="D2" s="0" t="n">
@@ -8243,18 +8232,18 @@
       <c r="E2" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="F2" s="17" t="s">
+      <c r="F2" s="16" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="16" t="n">
+      <c r="A3" s="15" t="n">
         <v>1081</v>
       </c>
       <c r="B3" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="C3" s="16" t="n">
+      <c r="C3" s="15" t="n">
         <v>13</v>
       </c>
       <c r="D3" s="0" t="n">
@@ -8263,15 +8252,15 @@
       <c r="E3" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="F3" s="17" t="s">
+      <c r="F3" s="16" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="16" t="n">
+      <c r="A4" s="15" t="n">
         <v>1101</v>
       </c>
-      <c r="C4" s="16" t="n">
+      <c r="C4" s="15" t="n">
         <v>15</v>
       </c>
       <c r="D4" s="0" t="n">
@@ -8280,15 +8269,15 @@
       <c r="E4" s="0" t="n">
         <v>4</v>
       </c>
-      <c r="F4" s="17" t="s">
+      <c r="F4" s="16" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="16" t="n">
+      <c r="A5" s="15" t="n">
         <v>1191</v>
       </c>
-      <c r="C5" s="16" t="n">
+      <c r="C5" s="15" t="n">
         <v>21</v>
       </c>
       <c r="D5" s="0" t="n">
@@ -8297,103 +8286,103 @@
       <c r="E5" s="0" t="n">
         <v>5</v>
       </c>
-      <c r="F5" s="17" t="s">
+      <c r="F5" s="16" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="16" t="n">
+      <c r="A6" s="15" t="n">
         <v>1221</v>
       </c>
-      <c r="C6" s="16" t="n">
+      <c r="C6" s="15" t="n">
         <v>25</v>
       </c>
-      <c r="F6" s="17" t="s">
+      <c r="F6" s="16" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="16" t="n">
+      <c r="A7" s="15" t="n">
         <v>1231</v>
       </c>
-      <c r="C7" s="16" t="n">
+      <c r="C7" s="15" t="n">
         <v>26</v>
       </c>
-      <c r="F7" s="17" t="s">
+      <c r="F7" s="16" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="16" t="n">
+      <c r="A8" s="15" t="n">
         <v>1251</v>
       </c>
-      <c r="C8" s="16" t="n">
+      <c r="C8" s="15" t="n">
         <v>27</v>
       </c>
-      <c r="F8" s="17" t="s">
+      <c r="F8" s="16" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="16" t="n">
+      <c r="A9" s="15" t="n">
         <v>1261</v>
       </c>
-      <c r="C9" s="16" t="n">
+      <c r="C9" s="15" t="n">
         <v>29</v>
       </c>
-      <c r="F9" s="17" t="s">
+      <c r="F9" s="16" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="16" t="n">
+      <c r="A10" s="15" t="n">
         <v>1271</v>
       </c>
-      <c r="C10" s="16" t="n">
+      <c r="C10" s="15" t="n">
         <v>31</v>
       </c>
-      <c r="F10" s="17" t="s">
+      <c r="F10" s="16" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="16" t="n">
+      <c r="A11" s="15" t="n">
         <v>1301</v>
       </c>
-      <c r="C11" s="16" t="n">
+      <c r="C11" s="15" t="n">
         <v>32</v>
       </c>
-      <c r="F11" s="17" t="s">
+      <c r="F11" s="16" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="16" t="n">
+      <c r="A12" s="15" t="n">
         <v>1371</v>
       </c>
-      <c r="C12" s="16" t="n">
+      <c r="C12" s="15" t="n">
         <v>33</v>
       </c>
-      <c r="F12" s="17" t="s">
+      <c r="F12" s="16" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="16" t="n">
+      <c r="A13" s="15" t="n">
         <v>1401</v>
       </c>
-      <c r="C13" s="16" t="n">
+      <c r="C13" s="15" t="n">
         <v>39</v>
       </c>
-      <c r="F13" s="17" t="s">
+      <c r="F13" s="16" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="16" t="n">
+      <c r="A14" s="15" t="n">
         <v>1451</v>
       </c>
-      <c r="C14" s="16" t="n">
+      <c r="C14" s="15" t="n">
         <v>45</v>
       </c>
       <c r="F14" s="0" t="n">
@@ -8401,10 +8390,10 @@
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="16" t="n">
+      <c r="A15" s="15" t="n">
         <v>1481</v>
       </c>
-      <c r="C15" s="16" t="n">
+      <c r="C15" s="15" t="n">
         <v>47</v>
       </c>
       <c r="F15" s="0" t="n">
@@ -8412,10 +8401,10 @@
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="16" t="n">
+      <c r="A16" s="15" t="n">
         <v>1491</v>
       </c>
-      <c r="C16" s="16" t="n">
+      <c r="C16" s="15" t="n">
         <v>48</v>
       </c>
       <c r="F16" s="0" t="n">
@@ -8423,10 +8412,10 @@
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="16" t="n">
+      <c r="A17" s="15" t="n">
         <v>1501</v>
       </c>
-      <c r="C17" s="16" t="n">
+      <c r="C17" s="15" t="n">
         <v>49</v>
       </c>
       <c r="F17" s="0" t="n">
@@ -8434,10 +8423,10 @@
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="16" t="n">
+      <c r="A18" s="15" t="n">
         <v>1511</v>
       </c>
-      <c r="C18" s="16" t="n">
+      <c r="C18" s="15" t="n">
         <v>50</v>
       </c>
       <c r="F18" s="0" t="n">
@@ -8445,10 +8434,10 @@
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="16" t="n">
+      <c r="A19" s="15" t="n">
         <v>1521</v>
       </c>
-      <c r="C19" s="16" t="n">
+      <c r="C19" s="15" t="n">
         <v>52</v>
       </c>
       <c r="F19" s="0" t="n">
@@ -8456,10 +8445,10 @@
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="16" t="n">
+      <c r="A20" s="15" t="n">
         <v>1541</v>
       </c>
-      <c r="C20" s="16" t="n">
+      <c r="C20" s="15" t="n">
         <v>54</v>
       </c>
       <c r="F20" s="0" t="n">
@@ -8467,10 +8456,10 @@
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="16" t="n">
+      <c r="A21" s="15" t="n">
         <v>1631</v>
       </c>
-      <c r="C21" s="16" t="n">
+      <c r="C21" s="15" t="n">
         <v>59</v>
       </c>
       <c r="F21" s="0" t="n">
@@ -8478,10 +8467,10 @@
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="16" t="n">
+      <c r="A22" s="15" t="n">
         <v>1711</v>
       </c>
-      <c r="C22" s="16" t="n">
+      <c r="C22" s="15" t="n">
         <v>60</v>
       </c>
       <c r="F22" s="0" t="n">
@@ -8489,10 +8478,10 @@
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="16" t="n">
+      <c r="A23" s="15" t="n">
         <v>1721</v>
       </c>
-      <c r="C23" s="16" t="n">
+      <c r="C23" s="15" t="n">
         <v>61</v>
       </c>
       <c r="F23" s="0" t="n">
@@ -8500,10 +8489,10 @@
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="16" t="n">
+      <c r="A24" s="15" t="n">
         <v>1911</v>
       </c>
-      <c r="C24" s="16" t="n">
+      <c r="C24" s="15" t="n">
         <v>71</v>
       </c>
       <c r="F24" s="0" t="n">
@@ -8511,10 +8500,10 @@
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="16" t="n">
+      <c r="A25" s="15" t="n">
         <v>1915</v>
       </c>
-      <c r="C25" s="16" t="n">
+      <c r="C25" s="15" t="n">
         <v>72</v>
       </c>
       <c r="F25" s="0" t="n">
@@ -8522,10 +8511,10 @@
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="16" t="n">
+      <c r="A26" s="15" t="n">
         <v>1941</v>
       </c>
-      <c r="C26" s="16" t="n">
+      <c r="C26" s="15" t="n">
         <v>80</v>
       </c>
       <c r="F26" s="0" t="n">
@@ -8533,10 +8522,10 @@
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="16" t="n">
+      <c r="A27" s="15" t="n">
         <v>2011</v>
       </c>
-      <c r="C27" s="16" t="n">
+      <c r="C27" s="15" t="n">
         <v>82</v>
       </c>
       <c r="F27" s="0" t="n">
@@ -8544,10 +8533,10 @@
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="16" t="n">
+      <c r="A28" s="15" t="n">
         <v>2041</v>
       </c>
-      <c r="C28" s="16" t="n">
+      <c r="C28" s="15" t="n">
         <v>83</v>
       </c>
       <c r="F28" s="0" t="n">
@@ -8555,10 +8544,10 @@
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="16" t="n">
+      <c r="A29" s="15" t="n">
         <v>2061</v>
       </c>
-      <c r="C29" s="16" t="n">
+      <c r="C29" s="15" t="n">
         <v>89</v>
       </c>
       <c r="F29" s="0" t="n">
@@ -8566,10 +8555,10 @@
       </c>
     </row>
     <row r="30" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="16" t="n">
+      <c r="A30" s="15" t="n">
         <v>2071</v>
       </c>
-      <c r="C30" s="16" t="n">
+      <c r="C30" s="15" t="n">
         <v>91</v>
       </c>
       <c r="F30" s="0" t="n">
@@ -8577,10 +8566,10 @@
       </c>
     </row>
     <row r="31" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="16" t="n">
+      <c r="A31" s="15" t="n">
         <v>2091</v>
       </c>
-      <c r="C31" s="16" t="n">
+      <c r="C31" s="15" t="n">
         <v>94</v>
       </c>
       <c r="F31" s="0" t="n">
@@ -8588,10 +8577,10 @@
       </c>
     </row>
     <row r="32" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="16" t="n">
+      <c r="A32" s="15" t="n">
         <v>2101</v>
       </c>
-      <c r="C32" s="16" t="n">
+      <c r="C32" s="15" t="n">
         <v>95</v>
       </c>
       <c r="F32" s="0" t="n">
@@ -8599,7 +8588,7 @@
       </c>
     </row>
     <row r="33" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="16" t="n">
+      <c r="A33" s="15" t="n">
         <v>2121</v>
       </c>
       <c r="F33" s="0" t="n">
@@ -8607,7 +8596,7 @@
       </c>
     </row>
     <row r="34" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="16" t="n">
+      <c r="A34" s="15" t="n">
         <v>2151</v>
       </c>
       <c r="F34" s="0" t="n">
@@ -8615,7 +8604,7 @@
       </c>
     </row>
     <row r="35" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="16" t="n">
+      <c r="A35" s="15" t="n">
         <v>2161</v>
       </c>
       <c r="F35" s="0" t="n">
@@ -8623,7 +8612,7 @@
       </c>
     </row>
     <row r="36" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="16" t="n">
+      <c r="A36" s="15" t="n">
         <v>2171</v>
       </c>
       <c r="F36" s="0" t="n">
@@ -8631,7 +8620,7 @@
       </c>
     </row>
     <row r="37" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="16" t="n">
+      <c r="A37" s="15" t="n">
         <v>2181</v>
       </c>
       <c r="F37" s="0" t="n">
@@ -8639,7 +8628,7 @@
       </c>
     </row>
     <row r="38" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="16" t="n">
+      <c r="A38" s="15" t="n">
         <v>2201</v>
       </c>
       <c r="F38" s="0" t="n">
@@ -8647,7 +8636,7 @@
       </c>
     </row>
     <row r="39" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="16" t="n">
+      <c r="A39" s="15" t="n">
         <v>2211</v>
       </c>
       <c r="F39" s="0" t="n">
@@ -8655,7 +8644,7 @@
       </c>
     </row>
     <row r="40" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="16" t="n">
+      <c r="A40" s="15" t="n">
         <v>2241</v>
       </c>
       <c r="F40" s="0" t="n">
@@ -8663,7 +8652,7 @@
       </c>
     </row>
     <row r="41" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="16" t="n">
+      <c r="A41" s="15" t="n">
         <v>2251</v>
       </c>
       <c r="F41" s="0" t="n">
@@ -8671,7 +8660,7 @@
       </c>
     </row>
     <row r="42" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="16" t="n">
+      <c r="A42" s="15" t="n">
         <v>2261</v>
       </c>
       <c r="F42" s="0" t="n">
@@ -8679,7 +8668,7 @@
       </c>
     </row>
     <row r="43" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="16" t="n">
+      <c r="A43" s="15" t="n">
         <v>2271</v>
       </c>
       <c r="F43" s="0" t="n">
@@ -8687,7 +8676,7 @@
       </c>
     </row>
     <row r="44" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="16" t="n">
+      <c r="A44" s="15" t="n">
         <v>2281</v>
       </c>
       <c r="F44" s="0" t="n">
@@ -8695,7 +8684,7 @@
       </c>
     </row>
     <row r="45" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="16" t="n">
+      <c r="A45" s="15" t="n">
         <v>2301</v>
       </c>
       <c r="F45" s="0" t="n">
@@ -8703,7 +8692,7 @@
       </c>
     </row>
     <row r="46" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="16" t="n">
+      <c r="A46" s="15" t="n">
         <v>2311</v>
       </c>
       <c r="F46" s="0" t="n">
@@ -8711,7 +8700,7 @@
       </c>
     </row>
     <row r="47" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="16" t="n">
+      <c r="A47" s="15" t="n">
         <v>2321</v>
       </c>
       <c r="F47" s="0" t="n">
@@ -8719,7 +8708,7 @@
       </c>
     </row>
     <row r="48" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="16" t="n">
+      <c r="A48" s="15" t="n">
         <v>2351</v>
       </c>
       <c r="F48" s="0" t="n">
@@ -8727,7 +8716,7 @@
       </c>
     </row>
     <row r="49" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="16" t="n">
+      <c r="A49" s="15" t="n">
         <v>2371</v>
       </c>
       <c r="F49" s="0" t="n">
@@ -8735,7 +8724,7 @@
       </c>
     </row>
     <row r="50" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="16" t="n">
+      <c r="A50" s="15" t="n">
         <v>2421</v>
       </c>
       <c r="F50" s="0" t="n">
@@ -8743,7 +8732,7 @@
       </c>
     </row>
     <row r="51" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="16" t="n">
+      <c r="A51" s="15" t="n">
         <v>2431</v>
       </c>
       <c r="F51" s="0" t="n">
@@ -8751,7 +8740,7 @@
       </c>
     </row>
     <row r="52" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="16" t="n">
+      <c r="A52" s="15" t="n">
         <v>2441</v>
       </c>
       <c r="F52" s="0" t="n">
@@ -8759,7 +8748,7 @@
       </c>
     </row>
     <row r="53" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="16" t="n">
+      <c r="A53" s="15" t="n">
         <v>2461</v>
       </c>
       <c r="F53" s="0" t="n">
@@ -8767,7 +8756,7 @@
       </c>
     </row>
     <row r="54" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="16" t="n">
+      <c r="A54" s="15" t="n">
         <v>3041</v>
       </c>
       <c r="F54" s="0" t="n">
@@ -8775,7 +8764,7 @@
       </c>
     </row>
     <row r="55" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="16" t="n">
+      <c r="A55" s="15" t="n">
         <v>3051</v>
       </c>
       <c r="F55" s="0" t="n">
@@ -8783,7 +8772,7 @@
       </c>
     </row>
     <row r="56" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="16" t="n">
+      <c r="A56" s="15" t="n">
         <v>3151</v>
       </c>
       <c r="F56" s="0" t="n">
@@ -8791,7 +8780,7 @@
       </c>
     </row>
     <row r="57" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="16" t="n">
+      <c r="A57" s="15" t="n">
         <v>4091</v>
       </c>
       <c r="F57" s="0" t="n">
@@ -8799,7 +8788,7 @@
       </c>
     </row>
     <row r="58" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="16" t="n">
+      <c r="A58" s="15" t="n">
         <v>4101</v>
       </c>
       <c r="F58" s="0" t="n">
@@ -8807,7 +8796,7 @@
       </c>
     </row>
     <row r="59" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="16" t="n">
+      <c r="A59" s="15" t="n">
         <v>4111</v>
       </c>
       <c r="F59" s="0" t="n">
@@ -8815,7 +8804,7 @@
       </c>
     </row>
     <row r="60" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="16" t="n">
+      <c r="A60" s="15" t="n">
         <v>4141</v>
       </c>
       <c r="F60" s="0" t="n">
@@ -8823,7 +8812,7 @@
       </c>
     </row>
     <row r="61" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="16" t="n">
+      <c r="A61" s="15" t="n">
         <v>4151</v>
       </c>
       <c r="F61" s="0" t="n">
@@ -8831,7 +8820,7 @@
       </c>
     </row>
     <row r="62" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="16" t="n">
+      <c r="A62" s="15" t="n">
         <v>4171</v>
       </c>
       <c r="F62" s="0" t="n">
@@ -8839,7 +8828,7 @@
       </c>
     </row>
     <row r="63" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="16" t="n">
+      <c r="A63" s="15" t="n">
         <v>4251</v>
       </c>
       <c r="F63" s="0" t="n">
@@ -8847,7 +8836,7 @@
       </c>
     </row>
     <row r="64" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="16" t="n">
+      <c r="A64" s="15" t="n">
         <v>4291</v>
       </c>
       <c r="F64" s="0" t="n">
@@ -8855,7 +8844,7 @@
       </c>
     </row>
     <row r="65" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="16" t="n">
+      <c r="A65" s="15" t="n">
         <v>4321</v>
       </c>
       <c r="F65" s="0" t="n">
@@ -8863,7 +8852,7 @@
       </c>
     </row>
     <row r="66" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="16" t="n">
+      <c r="A66" s="15" t="n">
         <v>4331</v>
       </c>
       <c r="F66" s="0" t="n">
@@ -8871,7 +8860,7 @@
       </c>
     </row>
     <row r="67" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="16" t="n">
+      <c r="A67" s="15" t="n">
         <v>4341</v>
       </c>
       <c r="F67" s="0" t="n">
@@ -8879,7 +8868,7 @@
       </c>
     </row>
     <row r="68" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="16" t="n">
+      <c r="A68" s="15" t="n">
         <v>4381</v>
       </c>
       <c r="F68" s="0" t="n">
@@ -8887,7 +8876,7 @@
       </c>
     </row>
     <row r="69" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="16" t="n">
+      <c r="A69" s="15" t="n">
         <v>4421</v>
       </c>
       <c r="F69" s="0" t="n">
@@ -8895,7 +8884,7 @@
       </c>
     </row>
     <row r="70" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="16" t="n">
+      <c r="A70" s="15" t="n">
         <v>4491</v>
       </c>
       <c r="F70" s="0" t="n">
@@ -8903,7 +8892,7 @@
       </c>
     </row>
     <row r="71" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="16" t="n">
+      <c r="A71" s="15" t="n">
         <v>4541</v>
       </c>
       <c r="F71" s="0" t="n">
@@ -8911,7 +8900,7 @@
       </c>
     </row>
     <row r="72" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="16" t="n">
+      <c r="A72" s="15" t="n">
         <v>4551</v>
       </c>
       <c r="F72" s="0" t="n">
@@ -8919,7 +8908,7 @@
       </c>
     </row>
     <row r="73" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="16" t="n">
+      <c r="A73" s="15" t="n">
         <v>4601</v>
       </c>
       <c r="F73" s="0" t="n">
@@ -8927,7 +8916,7 @@
       </c>
     </row>
     <row r="74" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="16" t="n">
+      <c r="A74" s="15" t="n">
         <v>4621</v>
       </c>
       <c r="F74" s="0" t="n">
@@ -8935,7 +8924,7 @@
       </c>
     </row>
     <row r="75" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="16" t="n">
+      <c r="A75" s="15" t="n">
         <v>4631</v>
       </c>
       <c r="F75" s="0" t="n">
@@ -8943,7 +8932,7 @@
       </c>
     </row>
     <row r="76" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="16" t="n">
+      <c r="A76" s="15" t="n">
         <v>4641</v>
       </c>
       <c r="F76" s="0" t="n">
@@ -8951,7 +8940,7 @@
       </c>
     </row>
     <row r="77" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="16" t="n">
+      <c r="A77" s="15" t="n">
         <v>4651</v>
       </c>
       <c r="F77" s="0" t="n">
@@ -8959,7 +8948,7 @@
       </c>
     </row>
     <row r="78" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="16" t="n">
+      <c r="A78" s="15" t="n">
         <v>4661</v>
       </c>
       <c r="F78" s="0" t="n">
@@ -8967,7 +8956,7 @@
       </c>
     </row>
     <row r="79" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="16" t="n">
+      <c r="A79" s="15" t="n">
         <v>4671</v>
       </c>
       <c r="F79" s="0" t="n">
@@ -8975,7 +8964,7 @@
       </c>
     </row>
     <row r="80" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="16" t="n">
+      <c r="A80" s="15" t="n">
         <v>4701</v>
       </c>
       <c r="F80" s="0" t="n">
@@ -8983,7 +8972,7 @@
       </c>
     </row>
     <row r="81" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A81" s="16" t="n">
+      <c r="A81" s="15" t="n">
         <v>4711</v>
       </c>
       <c r="F81" s="0" t="n">
@@ -8991,7 +8980,7 @@
       </c>
     </row>
     <row r="82" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A82" s="16" t="n">
+      <c r="A82" s="15" t="n">
         <v>4721</v>
       </c>
       <c r="F82" s="0" t="n">
